--- a/Cuadros_Prod_Gasto.xlsx
+++ b/Cuadros_Prod_Gasto.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\WTF IS PROGRAMMING 2.0\UR CLASES\7_SEMESTRE\ICE\Proyecciones\ICE_Proyecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B05A8F1-4C73-4C5A-8CE3-F14A6E4C444E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A9EE4B-3EB2-410A-B035-D0F488DDBC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{A3B4AD7B-0ED6-4521-BD6B-44541A0DC533}"/>
   </bookViews>
   <sheets>
     <sheet name="C1P" sheetId="2" r:id="rId1"/>
-    <sheet name="PIB oferta anual" sheetId="4" r:id="rId2"/>
+    <sheet name="PIB oferta anual NORMAL" sheetId="4" r:id="rId2"/>
     <sheet name="C1G" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -510,7 +510,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -690,6 +690,14 @@
       <b/>
       <u/>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -995,7 +1003,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1419,6 +1427,9 @@
     <xf numFmtId="168" fontId="0" fillId="9" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1463,6 +1474,12 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1667,7 +1684,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'PIB oferta anual'!$D$5:$W$5</c:f>
+              <c:f>'PIB oferta anual NORMAL'!$D$5:$W$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1736,7 +1753,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'PIB oferta anual'!$D$20:$W$20</c:f>
+              <c:f>'PIB oferta anual NORMAL'!$D$20:$W$20</c:f>
               <c:numCache>
                 <c:formatCode>0.000%</c:formatCode>
                 <c:ptCount val="20"/>
@@ -3184,31 +3201,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:87" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="177"/>
-      <c r="B1" s="177"/>
-      <c r="C1" s="177"/>
-      <c r="D1" s="177"/>
-      <c r="E1" s="177"/>
-      <c r="F1" s="177"/>
-      <c r="G1" s="177"/>
+      <c r="A1" s="178"/>
+      <c r="B1" s="178"/>
+      <c r="C1" s="178"/>
+      <c r="D1" s="178"/>
+      <c r="E1" s="178"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="178"/>
     </row>
     <row r="2" spans="1:87" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="177"/>
-      <c r="B2" s="177"/>
-      <c r="C2" s="177"/>
-      <c r="D2" s="177"/>
-      <c r="E2" s="177"/>
-      <c r="F2" s="177"/>
-      <c r="G2" s="177"/>
+      <c r="A2" s="178"/>
+      <c r="B2" s="178"/>
+      <c r="C2" s="178"/>
+      <c r="D2" s="178"/>
+      <c r="E2" s="178"/>
+      <c r="F2" s="178"/>
+      <c r="G2" s="178"/>
     </row>
     <row r="3" spans="1:87" s="3" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="177"/>
-      <c r="B3" s="177"/>
-      <c r="C3" s="177"/>
-      <c r="D3" s="177"/>
-      <c r="E3" s="177"/>
-      <c r="F3" s="177"/>
-      <c r="G3" s="177"/>
+      <c r="A3" s="178"/>
+      <c r="B3" s="178"/>
+      <c r="C3" s="178"/>
+      <c r="D3" s="178"/>
+      <c r="E3" s="178"/>
+      <c r="F3" s="178"/>
+      <c r="G3" s="178"/>
       <c r="H3" s="151">
         <f>SUM(D15:G15)</f>
         <v>37909</v>
@@ -3238,28 +3255,28 @@
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:87" s="4" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="178" t="s">
+      <c r="A5" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="178"/>
-      <c r="C5" s="178"/>
-      <c r="D5" s="178"/>
-      <c r="E5" s="178"/>
-      <c r="F5" s="178"/>
-      <c r="G5" s="178"/>
+      <c r="B5" s="179"/>
+      <c r="C5" s="179"/>
+      <c r="D5" s="179"/>
+      <c r="E5" s="179"/>
+      <c r="F5" s="179"/>
+      <c r="G5" s="179"/>
       <c r="CF5" s="152">
         <f>SUM(CF15:CI15)</f>
         <v>63888.120954066384</v>
       </c>
     </row>
     <row r="6" spans="1:87" s="4" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="178"/>
-      <c r="B6" s="178"/>
-      <c r="C6" s="178"/>
-      <c r="D6" s="178"/>
-      <c r="E6" s="178"/>
-      <c r="F6" s="178"/>
-      <c r="G6" s="178"/>
+      <c r="A6" s="179"/>
+      <c r="B6" s="179"/>
+      <c r="C6" s="179"/>
+      <c r="D6" s="179"/>
+      <c r="E6" s="179"/>
+      <c r="F6" s="179"/>
+      <c r="G6" s="179"/>
     </row>
     <row r="7" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -3320,154 +3337,158 @@
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
+      <c r="H11" s="45">
+        <f>SUM(D15:G15)</f>
+        <v>37909</v>
+      </c>
     </row>
     <row r="12" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="173" t="s">
+      <c r="A12" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="171" t="s">
+      <c r="B12" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="171" t="s">
+      <c r="C12" s="172" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="171">
+      <c r="D12" s="172">
         <v>2005</v>
       </c>
-      <c r="E12" s="171"/>
-      <c r="F12" s="171"/>
-      <c r="G12" s="171"/>
-      <c r="H12" s="171">
+      <c r="E12" s="172"/>
+      <c r="F12" s="172"/>
+      <c r="G12" s="172"/>
+      <c r="H12" s="172">
         <v>2006</v>
       </c>
-      <c r="I12" s="171"/>
-      <c r="J12" s="171"/>
-      <c r="K12" s="171"/>
-      <c r="L12" s="171">
+      <c r="I12" s="172"/>
+      <c r="J12" s="172"/>
+      <c r="K12" s="172"/>
+      <c r="L12" s="172">
         <v>2007</v>
       </c>
-      <c r="M12" s="171"/>
-      <c r="N12" s="171"/>
-      <c r="O12" s="171"/>
-      <c r="P12" s="171">
+      <c r="M12" s="172"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="172"/>
+      <c r="P12" s="172">
         <v>2008</v>
       </c>
-      <c r="Q12" s="171"/>
-      <c r="R12" s="171"/>
-      <c r="S12" s="171"/>
-      <c r="T12" s="171">
+      <c r="Q12" s="172"/>
+      <c r="R12" s="172"/>
+      <c r="S12" s="172"/>
+      <c r="T12" s="172">
         <v>2009</v>
       </c>
-      <c r="U12" s="171"/>
-      <c r="V12" s="171"/>
-      <c r="W12" s="171"/>
-      <c r="X12" s="171">
+      <c r="U12" s="172"/>
+      <c r="V12" s="172"/>
+      <c r="W12" s="172"/>
+      <c r="X12" s="172">
         <v>2010</v>
       </c>
-      <c r="Y12" s="171"/>
-      <c r="Z12" s="171"/>
-      <c r="AA12" s="171"/>
-      <c r="AB12" s="171">
+      <c r="Y12" s="172"/>
+      <c r="Z12" s="172"/>
+      <c r="AA12" s="172"/>
+      <c r="AB12" s="172">
         <v>2011</v>
       </c>
-      <c r="AC12" s="171"/>
-      <c r="AD12" s="171"/>
-      <c r="AE12" s="171"/>
-      <c r="AF12" s="171">
+      <c r="AC12" s="172"/>
+      <c r="AD12" s="172"/>
+      <c r="AE12" s="172"/>
+      <c r="AF12" s="172">
         <v>2012</v>
       </c>
-      <c r="AG12" s="171"/>
-      <c r="AH12" s="171"/>
-      <c r="AI12" s="171"/>
-      <c r="AJ12" s="171">
+      <c r="AG12" s="172"/>
+      <c r="AH12" s="172"/>
+      <c r="AI12" s="172"/>
+      <c r="AJ12" s="172">
         <v>2013</v>
       </c>
-      <c r="AK12" s="171"/>
-      <c r="AL12" s="171"/>
-      <c r="AM12" s="171"/>
-      <c r="AN12" s="171">
+      <c r="AK12" s="172"/>
+      <c r="AL12" s="172"/>
+      <c r="AM12" s="172"/>
+      <c r="AN12" s="172">
         <v>2014</v>
       </c>
-      <c r="AO12" s="171"/>
-      <c r="AP12" s="171"/>
-      <c r="AQ12" s="171"/>
-      <c r="AR12" s="171">
+      <c r="AO12" s="172"/>
+      <c r="AP12" s="172"/>
+      <c r="AQ12" s="172"/>
+      <c r="AR12" s="172">
         <v>2015</v>
       </c>
-      <c r="AS12" s="171"/>
-      <c r="AT12" s="171"/>
-      <c r="AU12" s="171"/>
-      <c r="AV12" s="171">
+      <c r="AS12" s="172"/>
+      <c r="AT12" s="172"/>
+      <c r="AU12" s="172"/>
+      <c r="AV12" s="172">
         <v>2016</v>
       </c>
-      <c r="AW12" s="171"/>
-      <c r="AX12" s="171"/>
-      <c r="AY12" s="171"/>
-      <c r="AZ12" s="171">
+      <c r="AW12" s="172"/>
+      <c r="AX12" s="172"/>
+      <c r="AY12" s="172"/>
+      <c r="AZ12" s="172">
         <v>2017</v>
       </c>
-      <c r="BA12" s="171"/>
-      <c r="BB12" s="171"/>
-      <c r="BC12" s="171"/>
-      <c r="BD12" s="171">
+      <c r="BA12" s="172"/>
+      <c r="BB12" s="172"/>
+      <c r="BC12" s="172"/>
+      <c r="BD12" s="172">
         <v>2018</v>
       </c>
-      <c r="BE12" s="171"/>
-      <c r="BF12" s="171"/>
-      <c r="BG12" s="171"/>
-      <c r="BH12" s="171">
+      <c r="BE12" s="172"/>
+      <c r="BF12" s="172"/>
+      <c r="BG12" s="172"/>
+      <c r="BH12" s="172">
         <v>2019</v>
       </c>
-      <c r="BI12" s="171"/>
-      <c r="BJ12" s="171"/>
-      <c r="BK12" s="171"/>
-      <c r="BL12" s="171">
+      <c r="BI12" s="172"/>
+      <c r="BJ12" s="172"/>
+      <c r="BK12" s="172"/>
+      <c r="BL12" s="172">
         <v>2020</v>
       </c>
-      <c r="BM12" s="171"/>
-      <c r="BN12" s="171"/>
-      <c r="BO12" s="171"/>
-      <c r="BP12" s="171">
+      <c r="BM12" s="172"/>
+      <c r="BN12" s="172"/>
+      <c r="BO12" s="172"/>
+      <c r="BP12" s="172">
         <v>2021</v>
       </c>
-      <c r="BQ12" s="171"/>
-      <c r="BR12" s="171"/>
-      <c r="BS12" s="171"/>
-      <c r="BT12" s="171">
+      <c r="BQ12" s="172"/>
+      <c r="BR12" s="172"/>
+      <c r="BS12" s="172"/>
+      <c r="BT12" s="172">
         <v>2022</v>
       </c>
-      <c r="BU12" s="171"/>
-      <c r="BV12" s="171"/>
-      <c r="BW12" s="171"/>
-      <c r="BX12" s="171">
+      <c r="BU12" s="172"/>
+      <c r="BV12" s="172"/>
+      <c r="BW12" s="172"/>
+      <c r="BX12" s="172">
         <v>2023</v>
       </c>
-      <c r="BY12" s="171" t="s">
+      <c r="BY12" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="BZ12" s="171"/>
-      <c r="CA12" s="171"/>
-      <c r="CB12" s="171" t="s">
+      <c r="BZ12" s="172"/>
+      <c r="CA12" s="172"/>
+      <c r="CB12" s="172" t="s">
         <v>12</v>
       </c>
-      <c r="CC12" s="171" t="s">
+      <c r="CC12" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="CD12" s="171"/>
-      <c r="CE12" s="171"/>
-      <c r="CF12" s="171" t="s">
+      <c r="CD12" s="172"/>
+      <c r="CE12" s="172"/>
+      <c r="CF12" s="172" t="s">
         <v>13</v>
       </c>
-      <c r="CG12" s="171" t="s">
+      <c r="CG12" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="CH12" s="171"/>
-      <c r="CI12" s="172"/>
+      <c r="CH12" s="172"/>
+      <c r="CI12" s="173"/>
     </row>
     <row r="13" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="174"/>
-      <c r="B13" s="175"/>
-      <c r="C13" s="175"/>
+      <c r="A13" s="175"/>
+      <c r="B13" s="176"/>
+      <c r="C13" s="176"/>
       <c r="D13" s="14" t="s">
         <v>14</v>
       </c>
@@ -7742,24 +7763,24 @@
       <c r="Q37" s="25"/>
     </row>
     <row r="39" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="176" t="s">
+      <c r="A39" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="176"/>
-      <c r="C39" s="176"/>
-      <c r="D39" s="176"/>
-      <c r="E39" s="176"/>
-      <c r="F39" s="176"/>
-      <c r="G39" s="176"/>
+      <c r="B39" s="177"/>
+      <c r="C39" s="177"/>
+      <c r="D39" s="177"/>
+      <c r="E39" s="177"/>
+      <c r="F39" s="177"/>
+      <c r="G39" s="177"/>
     </row>
     <row r="40" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="176"/>
-      <c r="B40" s="176"/>
-      <c r="C40" s="176"/>
-      <c r="D40" s="176"/>
-      <c r="E40" s="176"/>
-      <c r="F40" s="176"/>
-      <c r="G40" s="176"/>
+      <c r="A40" s="177"/>
+      <c r="B40" s="177"/>
+      <c r="C40" s="177"/>
+      <c r="D40" s="177"/>
+      <c r="E40" s="177"/>
+      <c r="F40" s="177"/>
+      <c r="G40" s="177"/>
     </row>
     <row r="41" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
@@ -7795,150 +7816,150 @@
       <c r="G43" s="11"/>
     </row>
     <row r="45" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="173" t="s">
+      <c r="A45" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="171" t="s">
+      <c r="B45" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="171" t="s">
+      <c r="C45" s="172" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="171"/>
-      <c r="E45" s="171"/>
-      <c r="F45" s="171"/>
-      <c r="G45" s="171"/>
-      <c r="H45" s="171">
+      <c r="D45" s="172"/>
+      <c r="E45" s="172"/>
+      <c r="F45" s="172"/>
+      <c r="G45" s="172"/>
+      <c r="H45" s="172">
         <v>2006</v>
       </c>
-      <c r="I45" s="171"/>
-      <c r="J45" s="171"/>
-      <c r="K45" s="171"/>
-      <c r="L45" s="171">
+      <c r="I45" s="172"/>
+      <c r="J45" s="172"/>
+      <c r="K45" s="172"/>
+      <c r="L45" s="172">
         <v>2007</v>
       </c>
-      <c r="M45" s="171"/>
-      <c r="N45" s="171"/>
-      <c r="O45" s="171"/>
-      <c r="P45" s="171">
+      <c r="M45" s="172"/>
+      <c r="N45" s="172"/>
+      <c r="O45" s="172"/>
+      <c r="P45" s="172">
         <v>2008</v>
       </c>
-      <c r="Q45" s="171"/>
-      <c r="R45" s="171"/>
-      <c r="S45" s="171"/>
-      <c r="T45" s="171">
+      <c r="Q45" s="172"/>
+      <c r="R45" s="172"/>
+      <c r="S45" s="172"/>
+      <c r="T45" s="172">
         <v>2009</v>
       </c>
-      <c r="U45" s="171"/>
-      <c r="V45" s="171"/>
-      <c r="W45" s="171"/>
-      <c r="X45" s="171">
+      <c r="U45" s="172"/>
+      <c r="V45" s="172"/>
+      <c r="W45" s="172"/>
+      <c r="X45" s="172">
         <v>2010</v>
       </c>
-      <c r="Y45" s="171"/>
-      <c r="Z45" s="171"/>
-      <c r="AA45" s="171"/>
-      <c r="AB45" s="171">
+      <c r="Y45" s="172"/>
+      <c r="Z45" s="172"/>
+      <c r="AA45" s="172"/>
+      <c r="AB45" s="172">
         <v>2011</v>
       </c>
-      <c r="AC45" s="171"/>
-      <c r="AD45" s="171"/>
-      <c r="AE45" s="171"/>
-      <c r="AF45" s="171">
+      <c r="AC45" s="172"/>
+      <c r="AD45" s="172"/>
+      <c r="AE45" s="172"/>
+      <c r="AF45" s="172">
         <v>2012</v>
       </c>
-      <c r="AG45" s="171"/>
-      <c r="AH45" s="171"/>
-      <c r="AI45" s="171"/>
-      <c r="AJ45" s="171">
+      <c r="AG45" s="172"/>
+      <c r="AH45" s="172"/>
+      <c r="AI45" s="172"/>
+      <c r="AJ45" s="172">
         <v>2013</v>
       </c>
-      <c r="AK45" s="171"/>
-      <c r="AL45" s="171"/>
-      <c r="AM45" s="171"/>
-      <c r="AN45" s="171">
+      <c r="AK45" s="172"/>
+      <c r="AL45" s="172"/>
+      <c r="AM45" s="172"/>
+      <c r="AN45" s="172">
         <v>2014</v>
       </c>
-      <c r="AO45" s="171"/>
-      <c r="AP45" s="171"/>
-      <c r="AQ45" s="171"/>
-      <c r="AR45" s="171">
+      <c r="AO45" s="172"/>
+      <c r="AP45" s="172"/>
+      <c r="AQ45" s="172"/>
+      <c r="AR45" s="172">
         <v>2015</v>
       </c>
-      <c r="AS45" s="171"/>
-      <c r="AT45" s="171"/>
-      <c r="AU45" s="171"/>
-      <c r="AV45" s="171">
+      <c r="AS45" s="172"/>
+      <c r="AT45" s="172"/>
+      <c r="AU45" s="172"/>
+      <c r="AV45" s="172">
         <v>2016</v>
       </c>
-      <c r="AW45" s="171"/>
-      <c r="AX45" s="171"/>
-      <c r="AY45" s="171"/>
-      <c r="AZ45" s="171">
+      <c r="AW45" s="172"/>
+      <c r="AX45" s="172"/>
+      <c r="AY45" s="172"/>
+      <c r="AZ45" s="172">
         <v>2017</v>
       </c>
-      <c r="BA45" s="171"/>
-      <c r="BB45" s="171"/>
-      <c r="BC45" s="171"/>
-      <c r="BD45" s="171">
+      <c r="BA45" s="172"/>
+      <c r="BB45" s="172"/>
+      <c r="BC45" s="172"/>
+      <c r="BD45" s="172">
         <v>2018</v>
       </c>
-      <c r="BE45" s="171"/>
-      <c r="BF45" s="171"/>
-      <c r="BG45" s="171"/>
-      <c r="BH45" s="171">
+      <c r="BE45" s="172"/>
+      <c r="BF45" s="172"/>
+      <c r="BG45" s="172"/>
+      <c r="BH45" s="172">
         <v>2019</v>
       </c>
-      <c r="BI45" s="171"/>
-      <c r="BJ45" s="171"/>
-      <c r="BK45" s="171"/>
-      <c r="BL45" s="171">
+      <c r="BI45" s="172"/>
+      <c r="BJ45" s="172"/>
+      <c r="BK45" s="172"/>
+      <c r="BL45" s="172">
         <v>2020</v>
       </c>
-      <c r="BM45" s="171"/>
-      <c r="BN45" s="171"/>
-      <c r="BO45" s="171"/>
-      <c r="BP45" s="171">
+      <c r="BM45" s="172"/>
+      <c r="BN45" s="172"/>
+      <c r="BO45" s="172"/>
+      <c r="BP45" s="172">
         <v>2021</v>
       </c>
-      <c r="BQ45" s="171"/>
-      <c r="BR45" s="171"/>
-      <c r="BS45" s="171"/>
-      <c r="BT45" s="171">
+      <c r="BQ45" s="172"/>
+      <c r="BR45" s="172"/>
+      <c r="BS45" s="172"/>
+      <c r="BT45" s="172">
         <v>2022</v>
       </c>
-      <c r="BU45" s="171"/>
-      <c r="BV45" s="171"/>
-      <c r="BW45" s="171"/>
-      <c r="BX45" s="171">
+      <c r="BU45" s="172"/>
+      <c r="BV45" s="172"/>
+      <c r="BW45" s="172"/>
+      <c r="BX45" s="172">
         <v>2023</v>
       </c>
-      <c r="BY45" s="171" t="s">
+      <c r="BY45" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="BZ45" s="171"/>
-      <c r="CA45" s="171"/>
-      <c r="CB45" s="171" t="s">
+      <c r="BZ45" s="172"/>
+      <c r="CA45" s="172"/>
+      <c r="CB45" s="172" t="s">
         <v>12</v>
       </c>
-      <c r="CC45" s="171" t="s">
+      <c r="CC45" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="CD45" s="171"/>
-      <c r="CE45" s="171"/>
-      <c r="CF45" s="171" t="s">
+      <c r="CD45" s="172"/>
+      <c r="CE45" s="172"/>
+      <c r="CF45" s="172" t="s">
         <v>13</v>
       </c>
-      <c r="CG45" s="171" t="s">
+      <c r="CG45" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="CH45" s="171"/>
-      <c r="CI45" s="172"/>
+      <c r="CH45" s="172"/>
+      <c r="CI45" s="173"/>
     </row>
     <row r="46" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="174"/>
-      <c r="B46" s="175"/>
-      <c r="C46" s="175"/>
+      <c r="A46" s="175"/>
+      <c r="B46" s="176"/>
+      <c r="C46" s="176"/>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -12072,24 +12093,24 @@
       <c r="P68" s="78"/>
     </row>
     <row r="72" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="176" t="s">
+      <c r="A72" s="177" t="s">
         <v>0</v>
       </c>
-      <c r="B72" s="176"/>
-      <c r="C72" s="176"/>
-      <c r="D72" s="176"/>
-      <c r="E72" s="176"/>
-      <c r="F72" s="176"/>
-      <c r="G72" s="176"/>
+      <c r="B72" s="177"/>
+      <c r="C72" s="177"/>
+      <c r="D72" s="177"/>
+      <c r="E72" s="177"/>
+      <c r="F72" s="177"/>
+      <c r="G72" s="177"/>
     </row>
     <row r="73" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="176"/>
-      <c r="B73" s="176"/>
-      <c r="C73" s="176"/>
-      <c r="D73" s="176"/>
-      <c r="E73" s="176"/>
-      <c r="F73" s="176"/>
-      <c r="G73" s="176"/>
+      <c r="A73" s="177"/>
+      <c r="B73" s="177"/>
+      <c r="C73" s="177"/>
+      <c r="D73" s="177"/>
+      <c r="E73" s="177"/>
+      <c r="F73" s="177"/>
+      <c r="G73" s="177"/>
     </row>
     <row r="74" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
@@ -12131,150 +12152,150 @@
       <c r="K77" s="79"/>
     </row>
     <row r="78" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="173" t="s">
+      <c r="A78" s="174" t="s">
         <v>8</v>
       </c>
-      <c r="B78" s="171" t="s">
+      <c r="B78" s="172" t="s">
         <v>9</v>
       </c>
-      <c r="C78" s="171" t="s">
+      <c r="C78" s="172" t="s">
         <v>10</v>
       </c>
-      <c r="D78" s="171"/>
-      <c r="E78" s="171"/>
-      <c r="F78" s="171"/>
-      <c r="G78" s="171"/>
-      <c r="H78" s="171">
+      <c r="D78" s="172"/>
+      <c r="E78" s="172"/>
+      <c r="F78" s="172"/>
+      <c r="G78" s="172"/>
+      <c r="H78" s="172">
         <v>2006</v>
       </c>
-      <c r="I78" s="171"/>
-      <c r="J78" s="171"/>
-      <c r="K78" s="171"/>
-      <c r="L78" s="171">
+      <c r="I78" s="172"/>
+      <c r="J78" s="172"/>
+      <c r="K78" s="172"/>
+      <c r="L78" s="172">
         <v>2007</v>
       </c>
-      <c r="M78" s="171"/>
-      <c r="N78" s="171"/>
-      <c r="O78" s="171"/>
-      <c r="P78" s="171">
+      <c r="M78" s="172"/>
+      <c r="N78" s="172"/>
+      <c r="O78" s="172"/>
+      <c r="P78" s="172">
         <v>2008</v>
       </c>
-      <c r="Q78" s="171"/>
-      <c r="R78" s="171"/>
-      <c r="S78" s="171"/>
-      <c r="T78" s="171">
+      <c r="Q78" s="172"/>
+      <c r="R78" s="172"/>
+      <c r="S78" s="172"/>
+      <c r="T78" s="172">
         <v>2009</v>
       </c>
-      <c r="U78" s="171"/>
-      <c r="V78" s="171"/>
-      <c r="W78" s="171"/>
-      <c r="X78" s="171">
+      <c r="U78" s="172"/>
+      <c r="V78" s="172"/>
+      <c r="W78" s="172"/>
+      <c r="X78" s="172">
         <v>2010</v>
       </c>
-      <c r="Y78" s="171"/>
-      <c r="Z78" s="171"/>
-      <c r="AA78" s="171"/>
-      <c r="AB78" s="171">
+      <c r="Y78" s="172"/>
+      <c r="Z78" s="172"/>
+      <c r="AA78" s="172"/>
+      <c r="AB78" s="172">
         <v>2011</v>
       </c>
-      <c r="AC78" s="171"/>
-      <c r="AD78" s="171"/>
-      <c r="AE78" s="171"/>
-      <c r="AF78" s="171">
+      <c r="AC78" s="172"/>
+      <c r="AD78" s="172"/>
+      <c r="AE78" s="172"/>
+      <c r="AF78" s="172">
         <v>2012</v>
       </c>
-      <c r="AG78" s="171"/>
-      <c r="AH78" s="171"/>
-      <c r="AI78" s="171"/>
-      <c r="AJ78" s="171">
+      <c r="AG78" s="172"/>
+      <c r="AH78" s="172"/>
+      <c r="AI78" s="172"/>
+      <c r="AJ78" s="172">
         <v>2013</v>
       </c>
-      <c r="AK78" s="171"/>
-      <c r="AL78" s="171"/>
-      <c r="AM78" s="171"/>
-      <c r="AN78" s="171">
+      <c r="AK78" s="172"/>
+      <c r="AL78" s="172"/>
+      <c r="AM78" s="172"/>
+      <c r="AN78" s="172">
         <v>2014</v>
       </c>
-      <c r="AO78" s="171"/>
-      <c r="AP78" s="171"/>
-      <c r="AQ78" s="171"/>
-      <c r="AR78" s="171">
+      <c r="AO78" s="172"/>
+      <c r="AP78" s="172"/>
+      <c r="AQ78" s="172"/>
+      <c r="AR78" s="172">
         <v>2015</v>
       </c>
-      <c r="AS78" s="171"/>
-      <c r="AT78" s="171"/>
-      <c r="AU78" s="171"/>
-      <c r="AV78" s="171">
+      <c r="AS78" s="172"/>
+      <c r="AT78" s="172"/>
+      <c r="AU78" s="172"/>
+      <c r="AV78" s="172">
         <v>2016</v>
       </c>
-      <c r="AW78" s="171"/>
-      <c r="AX78" s="171"/>
-      <c r="AY78" s="171"/>
-      <c r="AZ78" s="171">
+      <c r="AW78" s="172"/>
+      <c r="AX78" s="172"/>
+      <c r="AY78" s="172"/>
+      <c r="AZ78" s="172">
         <v>2017</v>
       </c>
-      <c r="BA78" s="171"/>
-      <c r="BB78" s="171"/>
-      <c r="BC78" s="171"/>
-      <c r="BD78" s="171">
+      <c r="BA78" s="172"/>
+      <c r="BB78" s="172"/>
+      <c r="BC78" s="172"/>
+      <c r="BD78" s="172">
         <v>2018</v>
       </c>
-      <c r="BE78" s="171"/>
-      <c r="BF78" s="171"/>
-      <c r="BG78" s="171"/>
-      <c r="BH78" s="171">
+      <c r="BE78" s="172"/>
+      <c r="BF78" s="172"/>
+      <c r="BG78" s="172"/>
+      <c r="BH78" s="172">
         <v>2019</v>
       </c>
-      <c r="BI78" s="171"/>
-      <c r="BJ78" s="171"/>
-      <c r="BK78" s="171"/>
-      <c r="BL78" s="171">
+      <c r="BI78" s="172"/>
+      <c r="BJ78" s="172"/>
+      <c r="BK78" s="172"/>
+      <c r="BL78" s="172">
         <v>2020</v>
       </c>
-      <c r="BM78" s="171"/>
-      <c r="BN78" s="171"/>
-      <c r="BO78" s="171"/>
-      <c r="BP78" s="171">
+      <c r="BM78" s="172"/>
+      <c r="BN78" s="172"/>
+      <c r="BO78" s="172"/>
+      <c r="BP78" s="172">
         <v>2021</v>
       </c>
-      <c r="BQ78" s="171"/>
-      <c r="BR78" s="171"/>
-      <c r="BS78" s="171"/>
-      <c r="BT78" s="171">
+      <c r="BQ78" s="172"/>
+      <c r="BR78" s="172"/>
+      <c r="BS78" s="172"/>
+      <c r="BT78" s="172">
         <v>2022</v>
       </c>
-      <c r="BU78" s="171"/>
-      <c r="BV78" s="171"/>
-      <c r="BW78" s="171"/>
-      <c r="BX78" s="171">
+      <c r="BU78" s="172"/>
+      <c r="BV78" s="172"/>
+      <c r="BW78" s="172"/>
+      <c r="BX78" s="172">
         <v>2023</v>
       </c>
-      <c r="BY78" s="171" t="s">
+      <c r="BY78" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="BZ78" s="171"/>
-      <c r="CA78" s="171"/>
-      <c r="CB78" s="171" t="s">
+      <c r="BZ78" s="172"/>
+      <c r="CA78" s="172"/>
+      <c r="CB78" s="172" t="s">
         <v>12</v>
       </c>
-      <c r="CC78" s="171" t="s">
+      <c r="CC78" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="CD78" s="171"/>
-      <c r="CE78" s="171"/>
-      <c r="CF78" s="171" t="s">
+      <c r="CD78" s="172"/>
+      <c r="CE78" s="172"/>
+      <c r="CF78" s="172" t="s">
         <v>13</v>
       </c>
-      <c r="CG78" s="171" t="s">
+      <c r="CG78" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="CH78" s="171"/>
-      <c r="CI78" s="172"/>
+      <c r="CH78" s="172"/>
+      <c r="CI78" s="173"/>
     </row>
     <row r="79" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="174"/>
-      <c r="B79" s="175"/>
-      <c r="C79" s="175"/>
+      <c r="A79" s="175"/>
+      <c r="B79" s="176"/>
+      <c r="C79" s="176"/>
       <c r="D79" s="14"/>
       <c r="E79" s="14"/>
       <c r="F79" s="14"/>
@@ -16726,14 +16747,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="179" t="s">
+      <c r="A1" s="180" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="179"/>
+      <c r="B1" s="180"/>
     </row>
     <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="179"/>
-      <c r="B2" s="179"/>
+      <c r="A2" s="180"/>
+      <c r="B2" s="180"/>
     </row>
     <row r="4" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="5" spans="1:28" s="144" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -16893,19 +16914,24 @@
         <v>63888.120954066384</v>
       </c>
       <c r="X6" s="146">
-        <v>0</v>
+        <f t="shared" ref="X6:X18" si="0">W6*(1+$X$20)</f>
+        <v>65216.919478487296</v>
       </c>
       <c r="Y6" s="146">
-        <v>0</v>
+        <f t="shared" ref="Y6:Y18" si="1">X6*(1+$Y$20)</f>
+        <v>66778.491991517774</v>
       </c>
       <c r="Z6" s="146">
-        <v>0</v>
+        <f t="shared" ref="Z6:Z18" si="2">Y6*(1+$Z$20)</f>
+        <v>68272.43105498128</v>
       </c>
       <c r="AA6" s="146">
-        <v>0</v>
+        <f t="shared" ref="AA6:AA18" si="3">Z6*(1+$AA$20)</f>
+        <v>69853.478737334503</v>
       </c>
       <c r="AB6" s="146">
-        <v>0</v>
+        <f t="shared" ref="AB6:AB18" si="4">AA6*(1+$AB$20)</f>
+        <v>71443.675126041009</v>
       </c>
     </row>
     <row r="7" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
@@ -16978,20 +17004,25 @@
       <c r="W7" s="147">
         <v>34868.277064090362</v>
       </c>
-      <c r="X7" s="146">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="146">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="146">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="146">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="146">
-        <v>0</v>
+      <c r="X7" s="147">
+        <f>35593.4966263493</f>
+        <v>35593.496626349297</v>
+      </c>
+      <c r="Y7" s="147">
+        <f t="shared" si="1"/>
+        <v>36445.757457109394</v>
+      </c>
+      <c r="Z7" s="147">
+        <f t="shared" si="2"/>
+        <v>37261.105919449757</v>
+      </c>
+      <c r="AA7" s="147">
+        <f t="shared" si="3"/>
+        <v>38123.995730835282</v>
+      </c>
+      <c r="AB7" s="147">
+        <f t="shared" si="4"/>
+        <v>38991.878639891242</v>
       </c>
     </row>
     <row r="8" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
@@ -17065,19 +17096,24 @@
         <v>113056.56188430529</v>
       </c>
       <c r="X8" s="146">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>115408.00672826896</v>
       </c>
       <c r="Y8" s="146">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>118171.36894365154</v>
       </c>
       <c r="Z8" s="146">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>120815.04685525074</v>
       </c>
       <c r="AA8" s="146">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>123612.8723738713</v>
       </c>
       <c r="AB8" s="146">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>126426.88746373839</v>
       </c>
     </row>
     <row r="9" spans="1:28" s="149" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -17150,20 +17186,25 @@
       <c r="W9" s="147">
         <v>30289.602434291664</v>
       </c>
-      <c r="X9" s="146">
-        <v>0</v>
-      </c>
-      <c r="Y9" s="146">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="146">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="146">
-        <v>0</v>
-      </c>
-      <c r="AB9" s="146">
-        <v>0</v>
+      <c r="X9" s="147">
+        <f t="shared" si="0"/>
+        <v>30919.590895666519</v>
+      </c>
+      <c r="Y9" s="147">
+        <f t="shared" si="1"/>
+        <v>31659.938395102567</v>
+      </c>
+      <c r="Z9" s="147">
+        <f t="shared" si="2"/>
+        <v>32368.220617487877</v>
+      </c>
+      <c r="AA9" s="147">
+        <f t="shared" si="3"/>
+        <v>33117.80136916734</v>
+      </c>
+      <c r="AB9" s="147">
+        <f t="shared" si="4"/>
+        <v>33871.719557510944</v>
       </c>
     </row>
     <row r="10" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
@@ -17237,19 +17278,24 @@
         <v>41273.053068554225</v>
       </c>
       <c r="X10" s="146">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>42131.484513975382</v>
       </c>
       <c r="Y10" s="146">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>43140.292790666448</v>
       </c>
       <c r="Z10" s="146">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>44105.408454215962</v>
       </c>
       <c r="AA10" s="146">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>45126.798094781465</v>
       </c>
       <c r="AB10" s="146">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>46154.097989666378</v>
       </c>
     </row>
     <row r="11" spans="1:28" s="149" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -17322,20 +17368,25 @@
       <c r="W11" s="147">
         <v>179021.7773381015</v>
       </c>
-      <c r="X11" s="146">
-        <v>0</v>
-      </c>
-      <c r="Y11" s="146">
-        <v>0</v>
-      </c>
-      <c r="Z11" s="146">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="146">
-        <v>0</v>
-      </c>
-      <c r="AB11" s="146">
-        <v>0</v>
+      <c r="X11" s="147">
+        <f t="shared" si="0"/>
+        <v>182745.2218535085</v>
+      </c>
+      <c r="Y11" s="147">
+        <f t="shared" si="1"/>
+        <v>187120.92554537373</v>
+      </c>
+      <c r="Z11" s="147">
+        <f t="shared" si="2"/>
+        <v>191307.11262338064</v>
+      </c>
+      <c r="AA11" s="147">
+        <f t="shared" si="3"/>
+        <v>195737.38795351062</v>
+      </c>
+      <c r="AB11" s="147">
+        <f t="shared" si="4"/>
+        <v>200193.29899881349</v>
       </c>
     </row>
     <row r="12" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
@@ -17409,19 +17460,24 @@
         <v>31269.035070523441</v>
       </c>
       <c r="X12" s="146">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>31919.394590279087</v>
       </c>
       <c r="Y12" s="146">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>32683.681674418276</v>
       </c>
       <c r="Z12" s="146">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>33414.866631356534</v>
       </c>
       <c r="AA12" s="146">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>34188.685530541516</v>
       </c>
       <c r="AB12" s="146">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>34966.982120031658</v>
       </c>
     </row>
     <row r="13" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
@@ -17494,20 +17550,25 @@
       <c r="W13" s="147">
         <v>53112.341726684856</v>
       </c>
-      <c r="X13" s="146">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="146">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="146">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="146">
-        <v>0</v>
-      </c>
-      <c r="AB13" s="146">
-        <v>0</v>
+      <c r="X13" s="147">
+        <f t="shared" si="0"/>
+        <v>54217.016590509695</v>
+      </c>
+      <c r="Y13" s="147">
+        <f t="shared" si="1"/>
+        <v>55515.204292769755</v>
+      </c>
+      <c r="Z13" s="147">
+        <f t="shared" si="2"/>
+        <v>56757.166035776179</v>
+      </c>
+      <c r="AA13" s="147">
+        <f t="shared" si="3"/>
+        <v>58071.544100701605</v>
+      </c>
+      <c r="AB13" s="147">
+        <f t="shared" si="4"/>
+        <v>59393.527792634632</v>
       </c>
     </row>
     <row r="14" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
@@ -17581,19 +17642,24 @@
         <v>90073.804942443036</v>
       </c>
       <c r="X14" s="146">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>91947.235203172546</v>
       </c>
       <c r="Y14" s="146">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>94148.846016602402</v>
       </c>
       <c r="Z14" s="146">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>96255.102606854227</v>
       </c>
       <c r="AA14" s="146">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>98484.170834535791</v>
       </c>
       <c r="AB14" s="146">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>100726.13752877475</v>
       </c>
     </row>
     <row r="15" spans="1:28" s="149" customFormat="1" ht="30" x14ac:dyDescent="0.25">
@@ -17666,20 +17732,25 @@
       <c r="W15" s="147">
         <v>70073.645866340899</v>
       </c>
-      <c r="X15" s="146">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="146">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="146">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="146">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="146">
-        <v>0</v>
+      <c r="X15" s="147">
+        <f t="shared" si="0"/>
+        <v>71531.096106502649</v>
+      </c>
+      <c r="Y15" s="147">
+        <f t="shared" si="1"/>
+        <v>73243.857064856435</v>
+      </c>
+      <c r="Z15" s="147">
+        <f t="shared" si="2"/>
+        <v>74882.436433222902</v>
+      </c>
+      <c r="AA15" s="147">
+        <f t="shared" si="3"/>
+        <v>76616.558109311532</v>
+      </c>
+      <c r="AB15" s="147">
+        <f t="shared" si="4"/>
+        <v>78360.714251895057</v>
       </c>
     </row>
     <row r="16" spans="1:28" s="149" customFormat="1" ht="45" x14ac:dyDescent="0.25">
@@ -17753,19 +17824,24 @@
         <v>166116.39565643322</v>
       </c>
       <c r="X16" s="146">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>169571.42325990729</v>
       </c>
       <c r="Y16" s="146">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>173631.68976245919</v>
       </c>
       <c r="Z16" s="146">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>177516.10158811504</v>
       </c>
       <c r="AA16" s="146">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>181627.00575044443</v>
       </c>
       <c r="AB16" s="146">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>185761.69759194847</v>
       </c>
     </row>
     <row r="17" spans="1:28" s="149" customFormat="1" ht="60" x14ac:dyDescent="0.25">
@@ -17838,20 +17914,25 @@
       <c r="W17" s="147">
         <v>47155.337358818259</v>
       </c>
-      <c r="X17" s="146">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="146">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="146">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="146">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="146">
-        <v>0</v>
+      <c r="X17" s="147">
+        <f t="shared" si="0"/>
+        <v>48136.113468136275</v>
+      </c>
+      <c r="Y17" s="147">
+        <f t="shared" si="1"/>
+        <v>49288.698292397297</v>
+      </c>
+      <c r="Z17" s="147">
+        <f t="shared" si="2"/>
+        <v>50391.363380666022</v>
+      </c>
+      <c r="AA17" s="147">
+        <f t="shared" si="3"/>
+        <v>51558.322679646604</v>
+      </c>
+      <c r="AB17" s="147">
+        <f t="shared" si="4"/>
+        <v>52732.034569375566</v>
       </c>
     </row>
     <row r="18" spans="1:28" s="149" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -17923,19 +18004,24 @@
         <v>103267.18155407908</v>
       </c>
       <c r="X18" s="146">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>105415.01868594316</v>
       </c>
       <c r="Y18" s="146">
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>107939.10594668632</v>
       </c>
       <c r="Z18" s="146">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>110353.87216916351</v>
       </c>
       <c r="AA18" s="146">
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>112909.4386128317</v>
       </c>
       <c r="AB18" s="146">
-        <v>0</v>
+        <f t="shared" si="4"/>
+        <v>115479.79279960238</v>
       </c>
     </row>
     <row r="19" spans="1:28" s="143" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -17948,99 +18034,104 @@
         <v>517438</v>
       </c>
       <c r="D19" s="169">
-        <f t="shared" ref="D19:W19" si="0">SUM(D6:D18)</f>
+        <f t="shared" ref="D19:W19" si="5">SUM(D6:D18)</f>
         <v>552139</v>
       </c>
       <c r="E19" s="169">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>588990</v>
       </c>
       <c r="F19" s="169">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>608384</v>
       </c>
       <c r="G19" s="169">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>614390</v>
       </c>
       <c r="H19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>640461</v>
       </c>
       <c r="I19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>683340</v>
       </c>
       <c r="J19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>709685</v>
       </c>
       <c r="K19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>745880</v>
       </c>
       <c r="L19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>781017</v>
       </c>
       <c r="M19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>804692</v>
       </c>
       <c r="N19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>821489</v>
       </c>
       <c r="O19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>831956</v>
       </c>
       <c r="P19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>853167</v>
       </c>
       <c r="Q19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>880280</v>
       </c>
       <c r="R19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>817375</v>
       </c>
       <c r="S19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>905132</v>
       </c>
       <c r="T19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>973165</v>
       </c>
       <c r="U19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>982221</v>
       </c>
       <c r="V19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>996471</v>
       </c>
       <c r="W19" s="167">
-        <f t="shared" si="0"/>
+        <f t="shared" si="5"/>
         <v>1023465.1349187322</v>
       </c>
-      <c r="X19" s="146">
-        <v>0</v>
-      </c>
-      <c r="Y19" s="146">
-        <v>0</v>
-      </c>
-      <c r="Z19" s="146">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="146">
-        <v>0</v>
-      </c>
-      <c r="AB19" s="146">
-        <v>0</v>
+      <c r="X19" s="187">
+        <f>W19*(1+$X$20)</f>
+        <v>1044752.0180007068</v>
+      </c>
+      <c r="Y19" s="188">
+        <f>X19*(1+$Y$20)</f>
+        <v>1069767.8581736113</v>
+      </c>
+      <c r="Z19" s="187">
+        <f>Y19*(1+$Z$20)</f>
+        <v>1093700.2343699208</v>
+      </c>
+      <c r="AA19" s="187">
+        <f>Z19*(1+$AA$20)</f>
+        <v>1119028.0598775139</v>
+      </c>
+      <c r="AB19" s="187">
+        <f>AA19*(1+$AB$20)</f>
+        <v>1144502.4444299242</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -18056,95 +18147,100 @@
         <v>6.7063107077562911E-2</v>
       </c>
       <c r="E20" s="170">
-        <f t="shared" ref="E20:W20" si="1">IFERROR((E$19/D$19)-1,"")</f>
+        <f t="shared" ref="E20:W20" si="6">IFERROR((E$19/D$19)-1,"")</f>
         <v>6.6742251498264071E-2</v>
       </c>
       <c r="F20" s="170">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.2927553948284283E-2</v>
       </c>
       <c r="G20" s="170">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>9.8720544918997621E-3</v>
       </c>
       <c r="H20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.2433958886049616E-2</v>
       </c>
       <c r="I20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>6.6950212425112454E-2</v>
       </c>
       <c r="J20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.8553282407000955E-2</v>
       </c>
       <c r="K20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>5.1001500665788235E-2</v>
       </c>
       <c r="L20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>4.7108113905722115E-2</v>
       </c>
       <c r="M20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.0313040561217086E-2</v>
       </c>
       <c r="N20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>2.0873825016279435E-2</v>
       </c>
       <c r="O20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.2741497451578709E-2</v>
       </c>
       <c r="P20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>2.5495338695796343E-2</v>
       </c>
       <c r="Q20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>3.1779241344308984E-2</v>
       </c>
       <c r="R20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>-7.146021720361706E-2</v>
       </c>
       <c r="S20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>0.10736442881174502</v>
       </c>
       <c r="T20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>7.5163622543452213E-2</v>
       </c>
       <c r="U20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>9.3057189685201713E-3</v>
       </c>
       <c r="V20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>1.4507936604898575E-2</v>
       </c>
       <c r="W20" s="168">
-        <f t="shared" si="1"/>
+        <f t="shared" si="6"/>
         <v>2.7089734592107728E-2</v>
       </c>
-      <c r="X20" s="146">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="146">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="146">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="146">
-        <v>0</v>
-      </c>
-      <c r="AB20" s="146">
-        <v>0</v>
+      <c r="X20" s="171">
+        <f>AVERAGE(V20:W20)</f>
+        <v>2.0798835598503151E-2</v>
+      </c>
+      <c r="Y20" s="171">
+        <f t="shared" ref="Y20:AB20" si="7">AVERAGE(W20:X20)</f>
+        <v>2.394428509530544E-2</v>
+      </c>
+      <c r="Z20" s="171">
+        <f t="shared" si="7"/>
+        <v>2.2371560346904296E-2</v>
+      </c>
+      <c r="AA20" s="171">
+        <f t="shared" si="7"/>
+        <v>2.3157922721104868E-2</v>
+      </c>
+      <c r="AB20" s="171">
+        <f t="shared" si="7"/>
+        <v>2.2764741534004582E-2</v>
       </c>
     </row>
   </sheetData>
@@ -18170,13 +18266,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:86" s="81" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="185"/>
-      <c r="B1" s="185"/>
-      <c r="C1" s="185"/>
-      <c r="D1" s="185"/>
-      <c r="E1" s="185"/>
-      <c r="F1" s="185"/>
-      <c r="G1" s="185"/>
+      <c r="A1" s="186"/>
+      <c r="B1" s="186"/>
+      <c r="C1" s="186"/>
+      <c r="D1" s="186"/>
+      <c r="E1" s="186"/>
+      <c r="F1" s="186"/>
+      <c r="G1" s="186"/>
     </row>
     <row r="2" spans="1:86" s="81" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="82"/>
@@ -18188,24 +18284,24 @@
       <c r="G2" s="82"/>
     </row>
     <row r="3" spans="1:86" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="178" t="s">
+      <c r="A3" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="178"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
+      <c r="B3" s="179"/>
+      <c r="C3" s="179"/>
+      <c r="D3" s="179"/>
+      <c r="E3" s="179"/>
+      <c r="F3" s="179"/>
+      <c r="G3" s="179"/>
     </row>
     <row r="4" spans="1:86" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="178"/>
-      <c r="B4" s="178"/>
-      <c r="C4" s="178"/>
-      <c r="D4" s="178"/>
-      <c r="E4" s="178"/>
-      <c r="F4" s="178"/>
-      <c r="G4" s="178"/>
+      <c r="A4" s="179"/>
+      <c r="B4" s="179"/>
+      <c r="C4" s="179"/>
+      <c r="D4" s="179"/>
+      <c r="E4" s="179"/>
+      <c r="F4" s="179"/>
+      <c r="G4" s="179"/>
     </row>
     <row r="5" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -18268,142 +18364,142 @@
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="182" t="s">
+      <c r="A10" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="180" t="s">
+      <c r="B10" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="180">
+      <c r="C10" s="181">
         <v>2005</v>
       </c>
-      <c r="D10" s="180"/>
-      <c r="E10" s="180"/>
-      <c r="F10" s="180"/>
-      <c r="G10" s="180">
+      <c r="D10" s="181"/>
+      <c r="E10" s="181"/>
+      <c r="F10" s="181"/>
+      <c r="G10" s="181">
         <v>2006</v>
       </c>
-      <c r="H10" s="180"/>
-      <c r="I10" s="180"/>
-      <c r="J10" s="180"/>
-      <c r="K10" s="180">
+      <c r="H10" s="181"/>
+      <c r="I10" s="181"/>
+      <c r="J10" s="181"/>
+      <c r="K10" s="181">
         <v>2007</v>
       </c>
-      <c r="L10" s="180"/>
-      <c r="M10" s="180"/>
-      <c r="N10" s="180"/>
-      <c r="O10" s="180">
+      <c r="L10" s="181"/>
+      <c r="M10" s="181"/>
+      <c r="N10" s="181"/>
+      <c r="O10" s="181">
         <v>2008</v>
       </c>
-      <c r="P10" s="180"/>
-      <c r="Q10" s="180"/>
-      <c r="R10" s="180"/>
-      <c r="S10" s="180">
+      <c r="P10" s="181"/>
+      <c r="Q10" s="181"/>
+      <c r="R10" s="181"/>
+      <c r="S10" s="181">
         <v>2009</v>
       </c>
-      <c r="T10" s="180"/>
-      <c r="U10" s="180"/>
-      <c r="V10" s="180"/>
-      <c r="W10" s="180">
+      <c r="T10" s="181"/>
+      <c r="U10" s="181"/>
+      <c r="V10" s="181"/>
+      <c r="W10" s="181">
         <v>2010</v>
       </c>
-      <c r="X10" s="180"/>
-      <c r="Y10" s="180"/>
-      <c r="Z10" s="180"/>
-      <c r="AA10" s="180">
+      <c r="X10" s="181"/>
+      <c r="Y10" s="181"/>
+      <c r="Z10" s="181"/>
+      <c r="AA10" s="181">
         <v>2011</v>
       </c>
-      <c r="AB10" s="180"/>
-      <c r="AC10" s="180"/>
-      <c r="AD10" s="180"/>
-      <c r="AE10" s="180">
+      <c r="AB10" s="181"/>
+      <c r="AC10" s="181"/>
+      <c r="AD10" s="181"/>
+      <c r="AE10" s="181">
         <v>2012</v>
       </c>
-      <c r="AF10" s="180"/>
-      <c r="AG10" s="180"/>
-      <c r="AH10" s="180"/>
-      <c r="AI10" s="180">
+      <c r="AF10" s="181"/>
+      <c r="AG10" s="181"/>
+      <c r="AH10" s="181"/>
+      <c r="AI10" s="181">
         <v>2013</v>
       </c>
-      <c r="AJ10" s="180"/>
-      <c r="AK10" s="180"/>
-      <c r="AL10" s="180"/>
-      <c r="AM10" s="180">
+      <c r="AJ10" s="181"/>
+      <c r="AK10" s="181"/>
+      <c r="AL10" s="181"/>
+      <c r="AM10" s="181">
         <v>2014</v>
       </c>
-      <c r="AN10" s="180"/>
-      <c r="AO10" s="180"/>
-      <c r="AP10" s="180"/>
-      <c r="AQ10" s="180">
+      <c r="AN10" s="181"/>
+      <c r="AO10" s="181"/>
+      <c r="AP10" s="181"/>
+      <c r="AQ10" s="181">
         <v>2015</v>
       </c>
-      <c r="AR10" s="180"/>
-      <c r="AS10" s="180"/>
-      <c r="AT10" s="180"/>
-      <c r="AU10" s="180">
+      <c r="AR10" s="181"/>
+      <c r="AS10" s="181"/>
+      <c r="AT10" s="181"/>
+      <c r="AU10" s="181">
         <v>2016</v>
       </c>
-      <c r="AV10" s="180"/>
-      <c r="AW10" s="180"/>
-      <c r="AX10" s="180"/>
-      <c r="AY10" s="180">
+      <c r="AV10" s="181"/>
+      <c r="AW10" s="181"/>
+      <c r="AX10" s="181"/>
+      <c r="AY10" s="181">
         <v>2017</v>
       </c>
-      <c r="AZ10" s="180"/>
-      <c r="BA10" s="180"/>
-      <c r="BB10" s="180"/>
-      <c r="BC10" s="180">
+      <c r="AZ10" s="181"/>
+      <c r="BA10" s="181"/>
+      <c r="BB10" s="181"/>
+      <c r="BC10" s="181">
         <v>2018</v>
       </c>
-      <c r="BD10" s="180"/>
-      <c r="BE10" s="180"/>
-      <c r="BF10" s="180"/>
-      <c r="BG10" s="180">
+      <c r="BD10" s="181"/>
+      <c r="BE10" s="181"/>
+      <c r="BF10" s="181"/>
+      <c r="BG10" s="181">
         <v>2019</v>
       </c>
-      <c r="BH10" s="180"/>
-      <c r="BI10" s="180"/>
-      <c r="BJ10" s="180"/>
-      <c r="BK10" s="180">
+      <c r="BH10" s="181"/>
+      <c r="BI10" s="181"/>
+      <c r="BJ10" s="181"/>
+      <c r="BK10" s="181">
         <v>2020</v>
       </c>
-      <c r="BL10" s="180"/>
-      <c r="BM10" s="180"/>
-      <c r="BN10" s="180"/>
-      <c r="BO10" s="180">
+      <c r="BL10" s="181"/>
+      <c r="BM10" s="181"/>
+      <c r="BN10" s="181"/>
+      <c r="BO10" s="181">
         <v>2021</v>
       </c>
-      <c r="BP10" s="180"/>
-      <c r="BQ10" s="180"/>
-      <c r="BR10" s="180"/>
-      <c r="BS10" s="180">
+      <c r="BP10" s="181"/>
+      <c r="BQ10" s="181"/>
+      <c r="BR10" s="181"/>
+      <c r="BS10" s="181">
         <v>2022</v>
       </c>
-      <c r="BT10" s="180"/>
-      <c r="BU10" s="180"/>
-      <c r="BV10" s="180"/>
-      <c r="BW10" s="180">
+      <c r="BT10" s="181"/>
+      <c r="BU10" s="181"/>
+      <c r="BV10" s="181"/>
+      <c r="BW10" s="181">
         <v>2023</v>
       </c>
-      <c r="BX10" s="180"/>
-      <c r="BY10" s="180"/>
-      <c r="BZ10" s="180"/>
-      <c r="CA10" s="180" t="s">
+      <c r="BX10" s="181"/>
+      <c r="BY10" s="181"/>
+      <c r="BZ10" s="181"/>
+      <c r="CA10" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="CB10" s="180"/>
-      <c r="CC10" s="180"/>
-      <c r="CD10" s="180"/>
-      <c r="CE10" s="180" t="s">
+      <c r="CB10" s="181"/>
+      <c r="CC10" s="181"/>
+      <c r="CD10" s="181"/>
+      <c r="CE10" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="CF10" s="180"/>
-      <c r="CG10" s="180"/>
-      <c r="CH10" s="181"/>
+      <c r="CF10" s="181"/>
+      <c r="CG10" s="181"/>
+      <c r="CH10" s="182"/>
     </row>
     <row r="11" spans="1:86" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="183"/>
-      <c r="B11" s="184"/>
+      <c r="A11" s="184"/>
+      <c r="B11" s="185"/>
       <c r="C11" s="84" t="s">
         <v>14</v>
       </c>
@@ -21217,25 +21313,25 @@
       <c r="Q30" s="25"/>
     </row>
     <row r="31" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="178" t="s">
+      <c r="A31" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="178"/>
-      <c r="C31" s="178"/>
-      <c r="D31" s="178"/>
-      <c r="E31" s="178"/>
-      <c r="F31" s="178"/>
-      <c r="G31" s="178"/>
+      <c r="B31" s="179"/>
+      <c r="C31" s="179"/>
+      <c r="D31" s="179"/>
+      <c r="E31" s="179"/>
+      <c r="F31" s="179"/>
+      <c r="G31" s="179"/>
       <c r="BH31" s="1"/>
     </row>
     <row r="32" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="178"/>
-      <c r="B32" s="178"/>
-      <c r="C32" s="178"/>
-      <c r="D32" s="178"/>
-      <c r="E32" s="178"/>
-      <c r="F32" s="178"/>
-      <c r="G32" s="178"/>
+      <c r="A32" s="179"/>
+      <c r="B32" s="179"/>
+      <c r="C32" s="179"/>
+      <c r="D32" s="179"/>
+      <c r="E32" s="179"/>
+      <c r="F32" s="179"/>
+      <c r="G32" s="179"/>
     </row>
     <row r="33" spans="1:86" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
@@ -21274,140 +21370,140 @@
       <c r="BH36" s="2"/>
     </row>
     <row r="37" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="182" t="s">
+      <c r="A37" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="180" t="s">
+      <c r="B37" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="180"/>
-      <c r="D37" s="180"/>
-      <c r="E37" s="180"/>
-      <c r="F37" s="180"/>
-      <c r="G37" s="180">
+      <c r="C37" s="181"/>
+      <c r="D37" s="181"/>
+      <c r="E37" s="181"/>
+      <c r="F37" s="181"/>
+      <c r="G37" s="181">
         <v>2006</v>
       </c>
-      <c r="H37" s="180"/>
-      <c r="I37" s="180"/>
-      <c r="J37" s="180"/>
-      <c r="K37" s="180">
+      <c r="H37" s="181"/>
+      <c r="I37" s="181"/>
+      <c r="J37" s="181"/>
+      <c r="K37" s="181">
         <v>2007</v>
       </c>
-      <c r="L37" s="180"/>
-      <c r="M37" s="180"/>
-      <c r="N37" s="180"/>
-      <c r="O37" s="180">
+      <c r="L37" s="181"/>
+      <c r="M37" s="181"/>
+      <c r="N37" s="181"/>
+      <c r="O37" s="181">
         <v>2008</v>
       </c>
-      <c r="P37" s="180"/>
-      <c r="Q37" s="180"/>
-      <c r="R37" s="180"/>
-      <c r="S37" s="180">
+      <c r="P37" s="181"/>
+      <c r="Q37" s="181"/>
+      <c r="R37" s="181"/>
+      <c r="S37" s="181">
         <v>2009</v>
       </c>
-      <c r="T37" s="180"/>
-      <c r="U37" s="180"/>
-      <c r="V37" s="180"/>
-      <c r="W37" s="180">
+      <c r="T37" s="181"/>
+      <c r="U37" s="181"/>
+      <c r="V37" s="181"/>
+      <c r="W37" s="181">
         <v>2010</v>
       </c>
-      <c r="X37" s="180"/>
-      <c r="Y37" s="180"/>
-      <c r="Z37" s="180"/>
-      <c r="AA37" s="180">
+      <c r="X37" s="181"/>
+      <c r="Y37" s="181"/>
+      <c r="Z37" s="181"/>
+      <c r="AA37" s="181">
         <v>2011</v>
       </c>
-      <c r="AB37" s="180"/>
-      <c r="AC37" s="180"/>
-      <c r="AD37" s="180"/>
-      <c r="AE37" s="180">
+      <c r="AB37" s="181"/>
+      <c r="AC37" s="181"/>
+      <c r="AD37" s="181"/>
+      <c r="AE37" s="181">
         <v>2012</v>
       </c>
-      <c r="AF37" s="180"/>
-      <c r="AG37" s="180"/>
-      <c r="AH37" s="180"/>
-      <c r="AI37" s="180">
+      <c r="AF37" s="181"/>
+      <c r="AG37" s="181"/>
+      <c r="AH37" s="181"/>
+      <c r="AI37" s="181">
         <v>2013</v>
       </c>
-      <c r="AJ37" s="180"/>
-      <c r="AK37" s="180"/>
-      <c r="AL37" s="180"/>
-      <c r="AM37" s="180">
+      <c r="AJ37" s="181"/>
+      <c r="AK37" s="181"/>
+      <c r="AL37" s="181"/>
+      <c r="AM37" s="181">
         <v>2014</v>
       </c>
-      <c r="AN37" s="180"/>
-      <c r="AO37" s="180"/>
-      <c r="AP37" s="180"/>
-      <c r="AQ37" s="180">
+      <c r="AN37" s="181"/>
+      <c r="AO37" s="181"/>
+      <c r="AP37" s="181"/>
+      <c r="AQ37" s="181">
         <v>2015</v>
       </c>
-      <c r="AR37" s="180"/>
-      <c r="AS37" s="180"/>
-      <c r="AT37" s="180"/>
-      <c r="AU37" s="180">
+      <c r="AR37" s="181"/>
+      <c r="AS37" s="181"/>
+      <c r="AT37" s="181"/>
+      <c r="AU37" s="181">
         <v>2016</v>
       </c>
-      <c r="AV37" s="180"/>
-      <c r="AW37" s="180"/>
-      <c r="AX37" s="180"/>
-      <c r="AY37" s="180">
+      <c r="AV37" s="181"/>
+      <c r="AW37" s="181"/>
+      <c r="AX37" s="181"/>
+      <c r="AY37" s="181">
         <v>2017</v>
       </c>
-      <c r="AZ37" s="180"/>
-      <c r="BA37" s="180"/>
-      <c r="BB37" s="180"/>
-      <c r="BC37" s="180">
+      <c r="AZ37" s="181"/>
+      <c r="BA37" s="181"/>
+      <c r="BB37" s="181"/>
+      <c r="BC37" s="181">
         <v>2018</v>
       </c>
-      <c r="BD37" s="180"/>
-      <c r="BE37" s="180"/>
-      <c r="BF37" s="180"/>
-      <c r="BG37" s="180">
+      <c r="BD37" s="181"/>
+      <c r="BE37" s="181"/>
+      <c r="BF37" s="181"/>
+      <c r="BG37" s="181">
         <v>2019</v>
       </c>
-      <c r="BH37" s="180"/>
-      <c r="BI37" s="180"/>
-      <c r="BJ37" s="180"/>
-      <c r="BK37" s="180">
+      <c r="BH37" s="181"/>
+      <c r="BI37" s="181"/>
+      <c r="BJ37" s="181"/>
+      <c r="BK37" s="181">
         <v>2020</v>
       </c>
-      <c r="BL37" s="180"/>
-      <c r="BM37" s="180"/>
-      <c r="BN37" s="180"/>
-      <c r="BO37" s="180">
+      <c r="BL37" s="181"/>
+      <c r="BM37" s="181"/>
+      <c r="BN37" s="181"/>
+      <c r="BO37" s="181">
         <v>2021</v>
       </c>
-      <c r="BP37" s="180"/>
-      <c r="BQ37" s="180"/>
-      <c r="BR37" s="180"/>
-      <c r="BS37" s="180">
+      <c r="BP37" s="181"/>
+      <c r="BQ37" s="181"/>
+      <c r="BR37" s="181"/>
+      <c r="BS37" s="181">
         <v>2022</v>
       </c>
-      <c r="BT37" s="180"/>
-      <c r="BU37" s="180"/>
-      <c r="BV37" s="180"/>
-      <c r="BW37" s="180">
+      <c r="BT37" s="181"/>
+      <c r="BU37" s="181"/>
+      <c r="BV37" s="181"/>
+      <c r="BW37" s="181">
         <v>2023</v>
       </c>
-      <c r="BX37" s="180"/>
-      <c r="BY37" s="180"/>
-      <c r="BZ37" s="180"/>
-      <c r="CA37" s="180" t="s">
+      <c r="BX37" s="181"/>
+      <c r="BY37" s="181"/>
+      <c r="BZ37" s="181"/>
+      <c r="CA37" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="CB37" s="180"/>
-      <c r="CC37" s="180"/>
-      <c r="CD37" s="180"/>
-      <c r="CE37" s="180" t="s">
+      <c r="CB37" s="181"/>
+      <c r="CC37" s="181"/>
+      <c r="CD37" s="181"/>
+      <c r="CE37" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="CF37" s="180"/>
-      <c r="CG37" s="180"/>
-      <c r="CH37" s="181"/>
+      <c r="CF37" s="181"/>
+      <c r="CG37" s="181"/>
+      <c r="CH37" s="182"/>
     </row>
     <row r="38" spans="1:86" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="183"/>
-      <c r="B38" s="184"/>
+      <c r="A38" s="184"/>
+      <c r="B38" s="185"/>
       <c r="C38" s="84"/>
       <c r="D38" s="84"/>
       <c r="E38" s="84"/>
@@ -24507,15 +24603,15 @@
       <c r="BF57" s="25"/>
     </row>
     <row r="58" spans="1:86" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="178" t="s">
+      <c r="A58" s="179" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="178"/>
-      <c r="C58" s="178"/>
-      <c r="D58" s="178"/>
-      <c r="E58" s="178"/>
-      <c r="F58" s="178"/>
-      <c r="G58" s="178"/>
+      <c r="B58" s="179"/>
+      <c r="C58" s="179"/>
+      <c r="D58" s="179"/>
+      <c r="E58" s="179"/>
+      <c r="F58" s="179"/>
+      <c r="G58" s="179"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -24569,13 +24665,13 @@
       <c r="BF58" s="2"/>
     </row>
     <row r="59" spans="1:86" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="178"/>
-      <c r="B59" s="178"/>
-      <c r="C59" s="178"/>
-      <c r="D59" s="178"/>
-      <c r="E59" s="178"/>
-      <c r="F59" s="178"/>
-      <c r="G59" s="178"/>
+      <c r="A59" s="179"/>
+      <c r="B59" s="179"/>
+      <c r="C59" s="179"/>
+      <c r="D59" s="179"/>
+      <c r="E59" s="179"/>
+      <c r="F59" s="179"/>
+      <c r="G59" s="179"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -24815,140 +24911,140 @@
       <c r="BF62" s="2"/>
     </row>
     <row r="64" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="182" t="s">
+      <c r="A64" s="183" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="180" t="s">
+      <c r="B64" s="181" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="180"/>
-      <c r="D64" s="180"/>
-      <c r="E64" s="180"/>
-      <c r="F64" s="180"/>
-      <c r="G64" s="180">
+      <c r="C64" s="181"/>
+      <c r="D64" s="181"/>
+      <c r="E64" s="181"/>
+      <c r="F64" s="181"/>
+      <c r="G64" s="181">
         <v>2006</v>
       </c>
-      <c r="H64" s="180"/>
-      <c r="I64" s="180"/>
-      <c r="J64" s="180"/>
-      <c r="K64" s="180">
+      <c r="H64" s="181"/>
+      <c r="I64" s="181"/>
+      <c r="J64" s="181"/>
+      <c r="K64" s="181">
         <v>2007</v>
       </c>
-      <c r="L64" s="180"/>
-      <c r="M64" s="180"/>
-      <c r="N64" s="180"/>
-      <c r="O64" s="180">
+      <c r="L64" s="181"/>
+      <c r="M64" s="181"/>
+      <c r="N64" s="181"/>
+      <c r="O64" s="181">
         <v>2008</v>
       </c>
-      <c r="P64" s="180"/>
-      <c r="Q64" s="180"/>
-      <c r="R64" s="180"/>
-      <c r="S64" s="180">
+      <c r="P64" s="181"/>
+      <c r="Q64" s="181"/>
+      <c r="R64" s="181"/>
+      <c r="S64" s="181">
         <v>2009</v>
       </c>
-      <c r="T64" s="180"/>
-      <c r="U64" s="180"/>
-      <c r="V64" s="180"/>
-      <c r="W64" s="180">
+      <c r="T64" s="181"/>
+      <c r="U64" s="181"/>
+      <c r="V64" s="181"/>
+      <c r="W64" s="181">
         <v>2010</v>
       </c>
-      <c r="X64" s="180"/>
-      <c r="Y64" s="180"/>
-      <c r="Z64" s="180"/>
-      <c r="AA64" s="180">
+      <c r="X64" s="181"/>
+      <c r="Y64" s="181"/>
+      <c r="Z64" s="181"/>
+      <c r="AA64" s="181">
         <v>2011</v>
       </c>
-      <c r="AB64" s="180"/>
-      <c r="AC64" s="180"/>
-      <c r="AD64" s="180"/>
-      <c r="AE64" s="180">
+      <c r="AB64" s="181"/>
+      <c r="AC64" s="181"/>
+      <c r="AD64" s="181"/>
+      <c r="AE64" s="181">
         <v>2012</v>
       </c>
-      <c r="AF64" s="180"/>
-      <c r="AG64" s="180"/>
-      <c r="AH64" s="180"/>
-      <c r="AI64" s="180">
+      <c r="AF64" s="181"/>
+      <c r="AG64" s="181"/>
+      <c r="AH64" s="181"/>
+      <c r="AI64" s="181">
         <v>2013</v>
       </c>
-      <c r="AJ64" s="180"/>
-      <c r="AK64" s="180"/>
-      <c r="AL64" s="180"/>
-      <c r="AM64" s="180">
+      <c r="AJ64" s="181"/>
+      <c r="AK64" s="181"/>
+      <c r="AL64" s="181"/>
+      <c r="AM64" s="181">
         <v>2014</v>
       </c>
-      <c r="AN64" s="180"/>
-      <c r="AO64" s="180"/>
-      <c r="AP64" s="180"/>
-      <c r="AQ64" s="180">
+      <c r="AN64" s="181"/>
+      <c r="AO64" s="181"/>
+      <c r="AP64" s="181"/>
+      <c r="AQ64" s="181">
         <v>2015</v>
       </c>
-      <c r="AR64" s="180"/>
-      <c r="AS64" s="180"/>
-      <c r="AT64" s="180"/>
-      <c r="AU64" s="180">
+      <c r="AR64" s="181"/>
+      <c r="AS64" s="181"/>
+      <c r="AT64" s="181"/>
+      <c r="AU64" s="181">
         <v>2016</v>
       </c>
-      <c r="AV64" s="180"/>
-      <c r="AW64" s="180"/>
-      <c r="AX64" s="180"/>
-      <c r="AY64" s="180">
+      <c r="AV64" s="181"/>
+      <c r="AW64" s="181"/>
+      <c r="AX64" s="181"/>
+      <c r="AY64" s="181">
         <v>2017</v>
       </c>
-      <c r="AZ64" s="180"/>
-      <c r="BA64" s="180"/>
-      <c r="BB64" s="180"/>
-      <c r="BC64" s="180">
+      <c r="AZ64" s="181"/>
+      <c r="BA64" s="181"/>
+      <c r="BB64" s="181"/>
+      <c r="BC64" s="181">
         <v>2018</v>
       </c>
-      <c r="BD64" s="180"/>
-      <c r="BE64" s="180"/>
-      <c r="BF64" s="180"/>
-      <c r="BG64" s="180">
+      <c r="BD64" s="181"/>
+      <c r="BE64" s="181"/>
+      <c r="BF64" s="181"/>
+      <c r="BG64" s="181">
         <v>2019</v>
       </c>
-      <c r="BH64" s="180"/>
-      <c r="BI64" s="180"/>
-      <c r="BJ64" s="180"/>
-      <c r="BK64" s="180">
+      <c r="BH64" s="181"/>
+      <c r="BI64" s="181"/>
+      <c r="BJ64" s="181"/>
+      <c r="BK64" s="181">
         <v>2020</v>
       </c>
-      <c r="BL64" s="180"/>
-      <c r="BM64" s="180"/>
-      <c r="BN64" s="180"/>
-      <c r="BO64" s="180">
+      <c r="BL64" s="181"/>
+      <c r="BM64" s="181"/>
+      <c r="BN64" s="181"/>
+      <c r="BO64" s="181">
         <v>2021</v>
       </c>
-      <c r="BP64" s="180"/>
-      <c r="BQ64" s="180"/>
-      <c r="BR64" s="180"/>
-      <c r="BS64" s="180">
+      <c r="BP64" s="181"/>
+      <c r="BQ64" s="181"/>
+      <c r="BR64" s="181"/>
+      <c r="BS64" s="181">
         <v>2022</v>
       </c>
-      <c r="BT64" s="180"/>
-      <c r="BU64" s="180"/>
-      <c r="BV64" s="180"/>
-      <c r="BW64" s="180">
+      <c r="BT64" s="181"/>
+      <c r="BU64" s="181"/>
+      <c r="BV64" s="181"/>
+      <c r="BW64" s="181">
         <v>2023</v>
       </c>
-      <c r="BX64" s="180"/>
-      <c r="BY64" s="180"/>
-      <c r="BZ64" s="180"/>
-      <c r="CA64" s="180" t="s">
+      <c r="BX64" s="181"/>
+      <c r="BY64" s="181"/>
+      <c r="BZ64" s="181"/>
+      <c r="CA64" s="181" t="s">
         <v>12</v>
       </c>
-      <c r="CB64" s="180"/>
-      <c r="CC64" s="180"/>
-      <c r="CD64" s="180"/>
-      <c r="CE64" s="180" t="s">
+      <c r="CB64" s="181"/>
+      <c r="CC64" s="181"/>
+      <c r="CD64" s="181"/>
+      <c r="CE64" s="181" t="s">
         <v>13</v>
       </c>
-      <c r="CF64" s="180"/>
-      <c r="CG64" s="180"/>
-      <c r="CH64" s="181"/>
+      <c r="CF64" s="181"/>
+      <c r="CG64" s="181"/>
+      <c r="CH64" s="182"/>
     </row>
     <row r="65" spans="1:86" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="183"/>
-      <c r="B65" s="184"/>
+      <c r="A65" s="184"/>
+      <c r="B65" s="185"/>
       <c r="C65" s="84"/>
       <c r="D65" s="84"/>
       <c r="E65" s="84"/>

--- a/Cuadros_Prod_Gasto.xlsx
+++ b/Cuadros_Prod_Gasto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\WTF IS PROGRAMMING 2.0\UR CLASES\7_SEMESTRE\ICE\Proyecciones\ICE_Proyecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23A9EE4B-3EB2-410A-B035-D0F488DDBC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A763D71A-2DBB-4A52-8D38-F690C352A26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{A3B4AD7B-0ED6-4521-BD6B-44541A0DC533}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="80">
   <si>
     <t>Producto Interno Bruto (PIB)</t>
   </si>
@@ -493,17 +493,24 @@
     <t>Suma Agregada PIB por Oferta Anual</t>
   </si>
   <si>
-    <t>PIB ANUAL POR LA OFERTA</t>
+    <t>Tasas de Crecimiento</t>
   </si>
   <si>
-    <t>Tasas de Crecimiento</t>
+    <t>PROYECCIÓN OFERTA ANUAL</t>
+  </si>
+  <si>
+    <t>Tasa de crecimiento Inercial</t>
+  </si>
+  <si>
+    <t>PIB</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="5">
+  <numFmts count="6">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
@@ -704,7 +711,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -771,8 +778,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="21">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -996,14 +1009,48 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="199">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1403,9 +1450,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1421,14 +1465,8 @@
     <xf numFmtId="168" fontId="0" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="168" fontId="0" fillId="9" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="9" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1475,15 +1513,55 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="0" fillId="11" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="11" borderId="10" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="1" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
+  <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
+    <cellStyle name="Millares" xfId="4" builtinId="3"/>
     <cellStyle name="Millares 2" xfId="3" xr:uid="{B5FA09B4-307C-4159-B091-F5BB2993442C}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
@@ -1499,1043 +1577,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="es-MX"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="es-CO"/>
-              <a:t>Tasa de Crecimiento</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="es-CO" baseline="0"/>
-              <a:t> PIB anual</a:t>
-            </a:r>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="es-CO"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="9.4164506090278155E-2"/>
-          <c:y val="8.6512179934492478E-2"/>
-          <c:w val="0.88924563456647421"/>
-          <c:h val="0.88472234045304121"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent6"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dPt>
-            <c:idx val="14"/>
-            <c:invertIfNegative val="0"/>
-            <c:bubble3D val="0"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:extLst>
-              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                <c16:uniqueId val="{00000002-0864-4C6A-8AE8-C83F5C3D6FD7}"/>
-              </c:ext>
-            </c:extLst>
-          </c:dPt>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="es-CO"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="inEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:numRef>
-              <c:f>'PIB oferta anual NORMAL'!$D$5:$W$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>2006</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2007</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2008</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2009</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2010</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2011</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>2012</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2013</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>2014</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>2019</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>2020</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>2021</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>2022</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>2023</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>2024</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2025</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'PIB oferta anual NORMAL'!$D$20:$W$20</c:f>
-              <c:numCache>
-                <c:formatCode>0.000%</c:formatCode>
-                <c:ptCount val="20"/>
-                <c:pt idx="0">
-                  <c:v>6.7063107077562911E-2</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>6.6742251498264071E-2</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3.2927553948284283E-2</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>9.8720544918997621E-3</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4.2433958886049616E-2</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6.6950212425112454E-2</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3.8553282407000955E-2</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>5.1001500665788235E-2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>4.7108113905722115E-2</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>3.0313040561217086E-2</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>2.0873825016279435E-2</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>1.2741497451578709E-2</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>2.5495338695796343E-2</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>3.1779241344308984E-2</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>-7.146021720361706E-2</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>0.10736442881174502</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7.5163622543452213E-2</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>9.3057189685201713E-3</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>1.4507936604898575E-2</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>2.7089734592107728E-2</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0864-4C6A-8AE8-C83F5C3D6FD7}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="75"/>
-        <c:overlap val="40"/>
-        <c:axId val="617491776"/>
-        <c:axId val="624963072"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="617491776"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="624963072"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="624963072"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="0.000%" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="es-CO"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="617491776"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="es-CO"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
-  <a:schemeClr val="accent6"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent4"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2692,47 +1733,6 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>211665</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>78315</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>42333</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>42332</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Gráfico 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{22652190-ACCB-448D-9DD0-D0B77E4E879F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -3201,31 +2201,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:87" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="178"/>
-      <c r="B1" s="178"/>
-      <c r="C1" s="178"/>
-      <c r="D1" s="178"/>
-      <c r="E1" s="178"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="178"/>
+      <c r="A1" s="175"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
     </row>
     <row r="2" spans="1:87" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="178"/>
-      <c r="B2" s="178"/>
-      <c r="C2" s="178"/>
-      <c r="D2" s="178"/>
-      <c r="E2" s="178"/>
-      <c r="F2" s="178"/>
-      <c r="G2" s="178"/>
+      <c r="A2" s="175"/>
+      <c r="B2" s="175"/>
+      <c r="C2" s="175"/>
+      <c r="D2" s="175"/>
+      <c r="E2" s="175"/>
+      <c r="F2" s="175"/>
+      <c r="G2" s="175"/>
     </row>
     <row r="3" spans="1:87" s="3" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="178"/>
-      <c r="B3" s="178"/>
-      <c r="C3" s="178"/>
-      <c r="D3" s="178"/>
-      <c r="E3" s="178"/>
-      <c r="F3" s="178"/>
-      <c r="G3" s="178"/>
+      <c r="A3" s="175"/>
+      <c r="B3" s="175"/>
+      <c r="C3" s="175"/>
+      <c r="D3" s="175"/>
+      <c r="E3" s="175"/>
+      <c r="F3" s="175"/>
+      <c r="G3" s="175"/>
       <c r="H3" s="151">
         <f>SUM(D15:G15)</f>
         <v>37909</v>
@@ -3255,28 +2255,28 @@
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:87" s="4" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="179" t="s">
+      <c r="A5" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="179"/>
-      <c r="C5" s="179"/>
-      <c r="D5" s="179"/>
-      <c r="E5" s="179"/>
-      <c r="F5" s="179"/>
-      <c r="G5" s="179"/>
+      <c r="B5" s="176"/>
+      <c r="C5" s="176"/>
+      <c r="D5" s="176"/>
+      <c r="E5" s="176"/>
+      <c r="F5" s="176"/>
+      <c r="G5" s="176"/>
       <c r="CF5" s="152">
         <f>SUM(CF15:CI15)</f>
         <v>63888.120954066384</v>
       </c>
     </row>
     <row r="6" spans="1:87" s="4" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="179"/>
-      <c r="B6" s="179"/>
-      <c r="C6" s="179"/>
-      <c r="D6" s="179"/>
-      <c r="E6" s="179"/>
-      <c r="F6" s="179"/>
-      <c r="G6" s="179"/>
+      <c r="A6" s="176"/>
+      <c r="B6" s="176"/>
+      <c r="C6" s="176"/>
+      <c r="D6" s="176"/>
+      <c r="E6" s="176"/>
+      <c r="F6" s="176"/>
+      <c r="G6" s="176"/>
     </row>
     <row r="7" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -3343,152 +2343,152 @@
       </c>
     </row>
     <row r="12" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="174" t="s">
+      <c r="A12" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="172" t="s">
+      <c r="B12" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="172" t="s">
+      <c r="C12" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="172">
+      <c r="D12" s="169">
         <v>2005</v>
       </c>
-      <c r="E12" s="172"/>
-      <c r="F12" s="172"/>
-      <c r="G12" s="172"/>
-      <c r="H12" s="172">
+      <c r="E12" s="169"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="169"/>
+      <c r="H12" s="169">
         <v>2006</v>
       </c>
-      <c r="I12" s="172"/>
-      <c r="J12" s="172"/>
-      <c r="K12" s="172"/>
-      <c r="L12" s="172">
+      <c r="I12" s="169"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="169"/>
+      <c r="L12" s="169">
         <v>2007</v>
       </c>
-      <c r="M12" s="172"/>
-      <c r="N12" s="172"/>
-      <c r="O12" s="172"/>
-      <c r="P12" s="172">
+      <c r="M12" s="169"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169">
         <v>2008</v>
       </c>
-      <c r="Q12" s="172"/>
-      <c r="R12" s="172"/>
-      <c r="S12" s="172"/>
-      <c r="T12" s="172">
+      <c r="Q12" s="169"/>
+      <c r="R12" s="169"/>
+      <c r="S12" s="169"/>
+      <c r="T12" s="169">
         <v>2009</v>
       </c>
-      <c r="U12" s="172"/>
-      <c r="V12" s="172"/>
-      <c r="W12" s="172"/>
-      <c r="X12" s="172">
+      <c r="U12" s="169"/>
+      <c r="V12" s="169"/>
+      <c r="W12" s="169"/>
+      <c r="X12" s="169">
         <v>2010</v>
       </c>
-      <c r="Y12" s="172"/>
-      <c r="Z12" s="172"/>
-      <c r="AA12" s="172"/>
-      <c r="AB12" s="172">
+      <c r="Y12" s="169"/>
+      <c r="Z12" s="169"/>
+      <c r="AA12" s="169"/>
+      <c r="AB12" s="169">
         <v>2011</v>
       </c>
-      <c r="AC12" s="172"/>
-      <c r="AD12" s="172"/>
-      <c r="AE12" s="172"/>
-      <c r="AF12" s="172">
+      <c r="AC12" s="169"/>
+      <c r="AD12" s="169"/>
+      <c r="AE12" s="169"/>
+      <c r="AF12" s="169">
         <v>2012</v>
       </c>
-      <c r="AG12" s="172"/>
-      <c r="AH12" s="172"/>
-      <c r="AI12" s="172"/>
-      <c r="AJ12" s="172">
+      <c r="AG12" s="169"/>
+      <c r="AH12" s="169"/>
+      <c r="AI12" s="169"/>
+      <c r="AJ12" s="169">
         <v>2013</v>
       </c>
-      <c r="AK12" s="172"/>
-      <c r="AL12" s="172"/>
-      <c r="AM12" s="172"/>
-      <c r="AN12" s="172">
+      <c r="AK12" s="169"/>
+      <c r="AL12" s="169"/>
+      <c r="AM12" s="169"/>
+      <c r="AN12" s="169">
         <v>2014</v>
       </c>
-      <c r="AO12" s="172"/>
-      <c r="AP12" s="172"/>
-      <c r="AQ12" s="172"/>
-      <c r="AR12" s="172">
+      <c r="AO12" s="169"/>
+      <c r="AP12" s="169"/>
+      <c r="AQ12" s="169"/>
+      <c r="AR12" s="169">
         <v>2015</v>
       </c>
-      <c r="AS12" s="172"/>
-      <c r="AT12" s="172"/>
-      <c r="AU12" s="172"/>
-      <c r="AV12" s="172">
+      <c r="AS12" s="169"/>
+      <c r="AT12" s="169"/>
+      <c r="AU12" s="169"/>
+      <c r="AV12" s="169">
         <v>2016</v>
       </c>
-      <c r="AW12" s="172"/>
-      <c r="AX12" s="172"/>
-      <c r="AY12" s="172"/>
-      <c r="AZ12" s="172">
+      <c r="AW12" s="169"/>
+      <c r="AX12" s="169"/>
+      <c r="AY12" s="169"/>
+      <c r="AZ12" s="169">
         <v>2017</v>
       </c>
-      <c r="BA12" s="172"/>
-      <c r="BB12" s="172"/>
-      <c r="BC12" s="172"/>
-      <c r="BD12" s="172">
+      <c r="BA12" s="169"/>
+      <c r="BB12" s="169"/>
+      <c r="BC12" s="169"/>
+      <c r="BD12" s="169">
         <v>2018</v>
       </c>
-      <c r="BE12" s="172"/>
-      <c r="BF12" s="172"/>
-      <c r="BG12" s="172"/>
-      <c r="BH12" s="172">
+      <c r="BE12" s="169"/>
+      <c r="BF12" s="169"/>
+      <c r="BG12" s="169"/>
+      <c r="BH12" s="169">
         <v>2019</v>
       </c>
-      <c r="BI12" s="172"/>
-      <c r="BJ12" s="172"/>
-      <c r="BK12" s="172"/>
-      <c r="BL12" s="172">
+      <c r="BI12" s="169"/>
+      <c r="BJ12" s="169"/>
+      <c r="BK12" s="169"/>
+      <c r="BL12" s="169">
         <v>2020</v>
       </c>
-      <c r="BM12" s="172"/>
-      <c r="BN12" s="172"/>
-      <c r="BO12" s="172"/>
-      <c r="BP12" s="172">
+      <c r="BM12" s="169"/>
+      <c r="BN12" s="169"/>
+      <c r="BO12" s="169"/>
+      <c r="BP12" s="169">
         <v>2021</v>
       </c>
-      <c r="BQ12" s="172"/>
-      <c r="BR12" s="172"/>
-      <c r="BS12" s="172"/>
-      <c r="BT12" s="172">
+      <c r="BQ12" s="169"/>
+      <c r="BR12" s="169"/>
+      <c r="BS12" s="169"/>
+      <c r="BT12" s="169">
         <v>2022</v>
       </c>
-      <c r="BU12" s="172"/>
-      <c r="BV12" s="172"/>
-      <c r="BW12" s="172"/>
-      <c r="BX12" s="172">
+      <c r="BU12" s="169"/>
+      <c r="BV12" s="169"/>
+      <c r="BW12" s="169"/>
+      <c r="BX12" s="169">
         <v>2023</v>
       </c>
-      <c r="BY12" s="172" t="s">
+      <c r="BY12" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="BZ12" s="172"/>
-      <c r="CA12" s="172"/>
-      <c r="CB12" s="172" t="s">
+      <c r="BZ12" s="169"/>
+      <c r="CA12" s="169"/>
+      <c r="CB12" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="CC12" s="172" t="s">
+      <c r="CC12" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="CD12" s="172"/>
-      <c r="CE12" s="172"/>
-      <c r="CF12" s="172" t="s">
+      <c r="CD12" s="169"/>
+      <c r="CE12" s="169"/>
+      <c r="CF12" s="169" t="s">
         <v>13</v>
       </c>
-      <c r="CG12" s="172" t="s">
+      <c r="CG12" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="CH12" s="172"/>
-      <c r="CI12" s="173"/>
+      <c r="CH12" s="169"/>
+      <c r="CI12" s="170"/>
     </row>
     <row r="13" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="175"/>
-      <c r="B13" s="176"/>
-      <c r="C13" s="176"/>
+      <c r="A13" s="172"/>
+      <c r="B13" s="173"/>
+      <c r="C13" s="173"/>
       <c r="D13" s="14" t="s">
         <v>14</v>
       </c>
@@ -7763,24 +6763,24 @@
       <c r="Q37" s="25"/>
     </row>
     <row r="39" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="177" t="s">
+      <c r="A39" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="177"/>
-      <c r="C39" s="177"/>
-      <c r="D39" s="177"/>
-      <c r="E39" s="177"/>
-      <c r="F39" s="177"/>
-      <c r="G39" s="177"/>
+      <c r="B39" s="174"/>
+      <c r="C39" s="174"/>
+      <c r="D39" s="174"/>
+      <c r="E39" s="174"/>
+      <c r="F39" s="174"/>
+      <c r="G39" s="174"/>
     </row>
     <row r="40" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="177"/>
-      <c r="B40" s="177"/>
-      <c r="C40" s="177"/>
-      <c r="D40" s="177"/>
-      <c r="E40" s="177"/>
-      <c r="F40" s="177"/>
-      <c r="G40" s="177"/>
+      <c r="A40" s="174"/>
+      <c r="B40" s="174"/>
+      <c r="C40" s="174"/>
+      <c r="D40" s="174"/>
+      <c r="E40" s="174"/>
+      <c r="F40" s="174"/>
+      <c r="G40" s="174"/>
     </row>
     <row r="41" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
@@ -7816,150 +6816,150 @@
       <c r="G43" s="11"/>
     </row>
     <row r="45" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="174" t="s">
+      <c r="A45" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="172" t="s">
+      <c r="B45" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="172" t="s">
+      <c r="C45" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="172"/>
-      <c r="E45" s="172"/>
-      <c r="F45" s="172"/>
-      <c r="G45" s="172"/>
-      <c r="H45" s="172">
+      <c r="D45" s="169"/>
+      <c r="E45" s="169"/>
+      <c r="F45" s="169"/>
+      <c r="G45" s="169"/>
+      <c r="H45" s="169">
         <v>2006</v>
       </c>
-      <c r="I45" s="172"/>
-      <c r="J45" s="172"/>
-      <c r="K45" s="172"/>
-      <c r="L45" s="172">
+      <c r="I45" s="169"/>
+      <c r="J45" s="169"/>
+      <c r="K45" s="169"/>
+      <c r="L45" s="169">
         <v>2007</v>
       </c>
-      <c r="M45" s="172"/>
-      <c r="N45" s="172"/>
-      <c r="O45" s="172"/>
-      <c r="P45" s="172">
+      <c r="M45" s="169"/>
+      <c r="N45" s="169"/>
+      <c r="O45" s="169"/>
+      <c r="P45" s="169">
         <v>2008</v>
       </c>
-      <c r="Q45" s="172"/>
-      <c r="R45" s="172"/>
-      <c r="S45" s="172"/>
-      <c r="T45" s="172">
+      <c r="Q45" s="169"/>
+      <c r="R45" s="169"/>
+      <c r="S45" s="169"/>
+      <c r="T45" s="169">
         <v>2009</v>
       </c>
-      <c r="U45" s="172"/>
-      <c r="V45" s="172"/>
-      <c r="W45" s="172"/>
-      <c r="X45" s="172">
+      <c r="U45" s="169"/>
+      <c r="V45" s="169"/>
+      <c r="W45" s="169"/>
+      <c r="X45" s="169">
         <v>2010</v>
       </c>
-      <c r="Y45" s="172"/>
-      <c r="Z45" s="172"/>
-      <c r="AA45" s="172"/>
-      <c r="AB45" s="172">
+      <c r="Y45" s="169"/>
+      <c r="Z45" s="169"/>
+      <c r="AA45" s="169"/>
+      <c r="AB45" s="169">
         <v>2011</v>
       </c>
-      <c r="AC45" s="172"/>
-      <c r="AD45" s="172"/>
-      <c r="AE45" s="172"/>
-      <c r="AF45" s="172">
+      <c r="AC45" s="169"/>
+      <c r="AD45" s="169"/>
+      <c r="AE45" s="169"/>
+      <c r="AF45" s="169">
         <v>2012</v>
       </c>
-      <c r="AG45" s="172"/>
-      <c r="AH45" s="172"/>
-      <c r="AI45" s="172"/>
-      <c r="AJ45" s="172">
+      <c r="AG45" s="169"/>
+      <c r="AH45" s="169"/>
+      <c r="AI45" s="169"/>
+      <c r="AJ45" s="169">
         <v>2013</v>
       </c>
-      <c r="AK45" s="172"/>
-      <c r="AL45" s="172"/>
-      <c r="AM45" s="172"/>
-      <c r="AN45" s="172">
+      <c r="AK45" s="169"/>
+      <c r="AL45" s="169"/>
+      <c r="AM45" s="169"/>
+      <c r="AN45" s="169">
         <v>2014</v>
       </c>
-      <c r="AO45" s="172"/>
-      <c r="AP45" s="172"/>
-      <c r="AQ45" s="172"/>
-      <c r="AR45" s="172">
+      <c r="AO45" s="169"/>
+      <c r="AP45" s="169"/>
+      <c r="AQ45" s="169"/>
+      <c r="AR45" s="169">
         <v>2015</v>
       </c>
-      <c r="AS45" s="172"/>
-      <c r="AT45" s="172"/>
-      <c r="AU45" s="172"/>
-      <c r="AV45" s="172">
+      <c r="AS45" s="169"/>
+      <c r="AT45" s="169"/>
+      <c r="AU45" s="169"/>
+      <c r="AV45" s="169">
         <v>2016</v>
       </c>
-      <c r="AW45" s="172"/>
-      <c r="AX45" s="172"/>
-      <c r="AY45" s="172"/>
-      <c r="AZ45" s="172">
+      <c r="AW45" s="169"/>
+      <c r="AX45" s="169"/>
+      <c r="AY45" s="169"/>
+      <c r="AZ45" s="169">
         <v>2017</v>
       </c>
-      <c r="BA45" s="172"/>
-      <c r="BB45" s="172"/>
-      <c r="BC45" s="172"/>
-      <c r="BD45" s="172">
+      <c r="BA45" s="169"/>
+      <c r="BB45" s="169"/>
+      <c r="BC45" s="169"/>
+      <c r="BD45" s="169">
         <v>2018</v>
       </c>
-      <c r="BE45" s="172"/>
-      <c r="BF45" s="172"/>
-      <c r="BG45" s="172"/>
-      <c r="BH45" s="172">
+      <c r="BE45" s="169"/>
+      <c r="BF45" s="169"/>
+      <c r="BG45" s="169"/>
+      <c r="BH45" s="169">
         <v>2019</v>
       </c>
-      <c r="BI45" s="172"/>
-      <c r="BJ45" s="172"/>
-      <c r="BK45" s="172"/>
-      <c r="BL45" s="172">
+      <c r="BI45" s="169"/>
+      <c r="BJ45" s="169"/>
+      <c r="BK45" s="169"/>
+      <c r="BL45" s="169">
         <v>2020</v>
       </c>
-      <c r="BM45" s="172"/>
-      <c r="BN45" s="172"/>
-      <c r="BO45" s="172"/>
-      <c r="BP45" s="172">
+      <c r="BM45" s="169"/>
+      <c r="BN45" s="169"/>
+      <c r="BO45" s="169"/>
+      <c r="BP45" s="169">
         <v>2021</v>
       </c>
-      <c r="BQ45" s="172"/>
-      <c r="BR45" s="172"/>
-      <c r="BS45" s="172"/>
-      <c r="BT45" s="172">
+      <c r="BQ45" s="169"/>
+      <c r="BR45" s="169"/>
+      <c r="BS45" s="169"/>
+      <c r="BT45" s="169">
         <v>2022</v>
       </c>
-      <c r="BU45" s="172"/>
-      <c r="BV45" s="172"/>
-      <c r="BW45" s="172"/>
-      <c r="BX45" s="172">
+      <c r="BU45" s="169"/>
+      <c r="BV45" s="169"/>
+      <c r="BW45" s="169"/>
+      <c r="BX45" s="169">
         <v>2023</v>
       </c>
-      <c r="BY45" s="172" t="s">
+      <c r="BY45" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="BZ45" s="172"/>
-      <c r="CA45" s="172"/>
-      <c r="CB45" s="172" t="s">
+      <c r="BZ45" s="169"/>
+      <c r="CA45" s="169"/>
+      <c r="CB45" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="CC45" s="172" t="s">
+      <c r="CC45" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="CD45" s="172"/>
-      <c r="CE45" s="172"/>
-      <c r="CF45" s="172" t="s">
+      <c r="CD45" s="169"/>
+      <c r="CE45" s="169"/>
+      <c r="CF45" s="169" t="s">
         <v>13</v>
       </c>
-      <c r="CG45" s="172" t="s">
+      <c r="CG45" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="CH45" s="172"/>
-      <c r="CI45" s="173"/>
+      <c r="CH45" s="169"/>
+      <c r="CI45" s="170"/>
     </row>
     <row r="46" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="175"/>
-      <c r="B46" s="176"/>
-      <c r="C46" s="176"/>
+      <c r="A46" s="172"/>
+      <c r="B46" s="173"/>
+      <c r="C46" s="173"/>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -12093,24 +11093,24 @@
       <c r="P68" s="78"/>
     </row>
     <row r="72" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="177" t="s">
+      <c r="A72" s="174" t="s">
         <v>0</v>
       </c>
-      <c r="B72" s="177"/>
-      <c r="C72" s="177"/>
-      <c r="D72" s="177"/>
-      <c r="E72" s="177"/>
-      <c r="F72" s="177"/>
-      <c r="G72" s="177"/>
+      <c r="B72" s="174"/>
+      <c r="C72" s="174"/>
+      <c r="D72" s="174"/>
+      <c r="E72" s="174"/>
+      <c r="F72" s="174"/>
+      <c r="G72" s="174"/>
     </row>
     <row r="73" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="177"/>
-      <c r="B73" s="177"/>
-      <c r="C73" s="177"/>
-      <c r="D73" s="177"/>
-      <c r="E73" s="177"/>
-      <c r="F73" s="177"/>
-      <c r="G73" s="177"/>
+      <c r="A73" s="174"/>
+      <c r="B73" s="174"/>
+      <c r="C73" s="174"/>
+      <c r="D73" s="174"/>
+      <c r="E73" s="174"/>
+      <c r="F73" s="174"/>
+      <c r="G73" s="174"/>
     </row>
     <row r="74" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
@@ -12152,150 +11152,150 @@
       <c r="K77" s="79"/>
     </row>
     <row r="78" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="174" t="s">
+      <c r="A78" s="171" t="s">
         <v>8</v>
       </c>
-      <c r="B78" s="172" t="s">
+      <c r="B78" s="169" t="s">
         <v>9</v>
       </c>
-      <c r="C78" s="172" t="s">
+      <c r="C78" s="169" t="s">
         <v>10</v>
       </c>
-      <c r="D78" s="172"/>
-      <c r="E78" s="172"/>
-      <c r="F78" s="172"/>
-      <c r="G78" s="172"/>
-      <c r="H78" s="172">
+      <c r="D78" s="169"/>
+      <c r="E78" s="169"/>
+      <c r="F78" s="169"/>
+      <c r="G78" s="169"/>
+      <c r="H78" s="169">
         <v>2006</v>
       </c>
-      <c r="I78" s="172"/>
-      <c r="J78" s="172"/>
-      <c r="K78" s="172"/>
-      <c r="L78" s="172">
+      <c r="I78" s="169"/>
+      <c r="J78" s="169"/>
+      <c r="K78" s="169"/>
+      <c r="L78" s="169">
         <v>2007</v>
       </c>
-      <c r="M78" s="172"/>
-      <c r="N78" s="172"/>
-      <c r="O78" s="172"/>
-      <c r="P78" s="172">
+      <c r="M78" s="169"/>
+      <c r="N78" s="169"/>
+      <c r="O78" s="169"/>
+      <c r="P78" s="169">
         <v>2008</v>
       </c>
-      <c r="Q78" s="172"/>
-      <c r="R78" s="172"/>
-      <c r="S78" s="172"/>
-      <c r="T78" s="172">
+      <c r="Q78" s="169"/>
+      <c r="R78" s="169"/>
+      <c r="S78" s="169"/>
+      <c r="T78" s="169">
         <v>2009</v>
       </c>
-      <c r="U78" s="172"/>
-      <c r="V78" s="172"/>
-      <c r="W78" s="172"/>
-      <c r="X78" s="172">
+      <c r="U78" s="169"/>
+      <c r="V78" s="169"/>
+      <c r="W78" s="169"/>
+      <c r="X78" s="169">
         <v>2010</v>
       </c>
-      <c r="Y78" s="172"/>
-      <c r="Z78" s="172"/>
-      <c r="AA78" s="172"/>
-      <c r="AB78" s="172">
+      <c r="Y78" s="169"/>
+      <c r="Z78" s="169"/>
+      <c r="AA78" s="169"/>
+      <c r="AB78" s="169">
         <v>2011</v>
       </c>
-      <c r="AC78" s="172"/>
-      <c r="AD78" s="172"/>
-      <c r="AE78" s="172"/>
-      <c r="AF78" s="172">
+      <c r="AC78" s="169"/>
+      <c r="AD78" s="169"/>
+      <c r="AE78" s="169"/>
+      <c r="AF78" s="169">
         <v>2012</v>
       </c>
-      <c r="AG78" s="172"/>
-      <c r="AH78" s="172"/>
-      <c r="AI78" s="172"/>
-      <c r="AJ78" s="172">
+      <c r="AG78" s="169"/>
+      <c r="AH78" s="169"/>
+      <c r="AI78" s="169"/>
+      <c r="AJ78" s="169">
         <v>2013</v>
       </c>
-      <c r="AK78" s="172"/>
-      <c r="AL78" s="172"/>
-      <c r="AM78" s="172"/>
-      <c r="AN78" s="172">
+      <c r="AK78" s="169"/>
+      <c r="AL78" s="169"/>
+      <c r="AM78" s="169"/>
+      <c r="AN78" s="169">
         <v>2014</v>
       </c>
-      <c r="AO78" s="172"/>
-      <c r="AP78" s="172"/>
-      <c r="AQ78" s="172"/>
-      <c r="AR78" s="172">
+      <c r="AO78" s="169"/>
+      <c r="AP78" s="169"/>
+      <c r="AQ78" s="169"/>
+      <c r="AR78" s="169">
         <v>2015</v>
       </c>
-      <c r="AS78" s="172"/>
-      <c r="AT78" s="172"/>
-      <c r="AU78" s="172"/>
-      <c r="AV78" s="172">
+      <c r="AS78" s="169"/>
+      <c r="AT78" s="169"/>
+      <c r="AU78" s="169"/>
+      <c r="AV78" s="169">
         <v>2016</v>
       </c>
-      <c r="AW78" s="172"/>
-      <c r="AX78" s="172"/>
-      <c r="AY78" s="172"/>
-      <c r="AZ78" s="172">
+      <c r="AW78" s="169"/>
+      <c r="AX78" s="169"/>
+      <c r="AY78" s="169"/>
+      <c r="AZ78" s="169">
         <v>2017</v>
       </c>
-      <c r="BA78" s="172"/>
-      <c r="BB78" s="172"/>
-      <c r="BC78" s="172"/>
-      <c r="BD78" s="172">
+      <c r="BA78" s="169"/>
+      <c r="BB78" s="169"/>
+      <c r="BC78" s="169"/>
+      <c r="BD78" s="169">
         <v>2018</v>
       </c>
-      <c r="BE78" s="172"/>
-      <c r="BF78" s="172"/>
-      <c r="BG78" s="172"/>
-      <c r="BH78" s="172">
+      <c r="BE78" s="169"/>
+      <c r="BF78" s="169"/>
+      <c r="BG78" s="169"/>
+      <c r="BH78" s="169">
         <v>2019</v>
       </c>
-      <c r="BI78" s="172"/>
-      <c r="BJ78" s="172"/>
-      <c r="BK78" s="172"/>
-      <c r="BL78" s="172">
+      <c r="BI78" s="169"/>
+      <c r="BJ78" s="169"/>
+      <c r="BK78" s="169"/>
+      <c r="BL78" s="169">
         <v>2020</v>
       </c>
-      <c r="BM78" s="172"/>
-      <c r="BN78" s="172"/>
-      <c r="BO78" s="172"/>
-      <c r="BP78" s="172">
+      <c r="BM78" s="169"/>
+      <c r="BN78" s="169"/>
+      <c r="BO78" s="169"/>
+      <c r="BP78" s="169">
         <v>2021</v>
       </c>
-      <c r="BQ78" s="172"/>
-      <c r="BR78" s="172"/>
-      <c r="BS78" s="172"/>
-      <c r="BT78" s="172">
+      <c r="BQ78" s="169"/>
+      <c r="BR78" s="169"/>
+      <c r="BS78" s="169"/>
+      <c r="BT78" s="169">
         <v>2022</v>
       </c>
-      <c r="BU78" s="172"/>
-      <c r="BV78" s="172"/>
-      <c r="BW78" s="172"/>
-      <c r="BX78" s="172">
+      <c r="BU78" s="169"/>
+      <c r="BV78" s="169"/>
+      <c r="BW78" s="169"/>
+      <c r="BX78" s="169">
         <v>2023</v>
       </c>
-      <c r="BY78" s="172" t="s">
+      <c r="BY78" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="BZ78" s="172"/>
-      <c r="CA78" s="172"/>
-      <c r="CB78" s="172" t="s">
+      <c r="BZ78" s="169"/>
+      <c r="CA78" s="169"/>
+      <c r="CB78" s="169" t="s">
         <v>12</v>
       </c>
-      <c r="CC78" s="172" t="s">
+      <c r="CC78" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="CD78" s="172"/>
-      <c r="CE78" s="172"/>
-      <c r="CF78" s="172" t="s">
+      <c r="CD78" s="169"/>
+      <c r="CE78" s="169"/>
+      <c r="CF78" s="169" t="s">
         <v>13</v>
       </c>
-      <c r="CG78" s="172" t="s">
+      <c r="CG78" s="169" t="s">
         <v>11</v>
       </c>
-      <c r="CH78" s="172"/>
-      <c r="CI78" s="173"/>
+      <c r="CH78" s="169"/>
+      <c r="CI78" s="170"/>
     </row>
     <row r="79" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="175"/>
-      <c r="B79" s="176"/>
-      <c r="C79" s="176"/>
+      <c r="A79" s="172"/>
+      <c r="B79" s="173"/>
+      <c r="C79" s="173"/>
       <c r="D79" s="14"/>
       <c r="E79" s="14"/>
       <c r="F79" s="14"/>
@@ -16739,24 +15739,41 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD938B3-C5B5-4D9D-B2F4-3C2CC8354395}">
-  <dimension ref="A1:AB20"/>
+  <dimension ref="A1:AB23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="66.5703125" style="142" customWidth="1"/>
+    <col min="3" max="22" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="180" t="s">
+      <c r="A1" s="177" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="180"/>
-    </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A2" s="180"/>
-      <c r="B2" s="180"/>
-    </row>
-    <row r="4" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="B1" s="177"/>
+    </row>
+    <row r="2" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="177"/>
+      <c r="B2" s="177"/>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="X3" s="188" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y3" s="189"/>
+      <c r="Z3" s="189"/>
+      <c r="AA3" s="189"/>
+      <c r="AB3" s="190"/>
+    </row>
+    <row r="4" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X4" s="191"/>
+      <c r="Y4" s="192"/>
+      <c r="Z4" s="192"/>
+      <c r="AA4" s="192"/>
+      <c r="AB4" s="193"/>
+    </row>
     <row r="5" spans="1:28" s="144" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="145" t="s">
         <v>9</v>
@@ -18025,230 +17042,243 @@
       </c>
     </row>
     <row r="19" spans="1:28" s="143" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="167"/>
-      <c r="B19" s="165" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="163">
+      <c r="A19" s="166"/>
+      <c r="B19" s="164" t="s">
+        <v>79</v>
+      </c>
+      <c r="C19" s="184">
         <f>SUM(C6:C18)</f>
         <v>517438</v>
       </c>
-      <c r="D19" s="169">
+      <c r="D19" s="185">
         <f t="shared" ref="D19:W19" si="5">SUM(D6:D18)</f>
         <v>552139</v>
       </c>
-      <c r="E19" s="169">
+      <c r="E19" s="185">
         <f t="shared" si="5"/>
         <v>588990</v>
       </c>
-      <c r="F19" s="169">
+      <c r="F19" s="185">
         <f t="shared" si="5"/>
         <v>608384</v>
       </c>
-      <c r="G19" s="169">
+      <c r="G19" s="185">
         <f t="shared" si="5"/>
         <v>614390</v>
       </c>
-      <c r="H19" s="167">
+      <c r="H19" s="186">
         <f t="shared" si="5"/>
         <v>640461</v>
       </c>
-      <c r="I19" s="167">
+      <c r="I19" s="186">
         <f t="shared" si="5"/>
         <v>683340</v>
       </c>
-      <c r="J19" s="167">
+      <c r="J19" s="186">
         <f t="shared" si="5"/>
         <v>709685</v>
       </c>
-      <c r="K19" s="167">
+      <c r="K19" s="186">
         <f t="shared" si="5"/>
         <v>745880</v>
       </c>
-      <c r="L19" s="167">
+      <c r="L19" s="186">
         <f t="shared" si="5"/>
         <v>781017</v>
       </c>
-      <c r="M19" s="167">
+      <c r="M19" s="186">
         <f t="shared" si="5"/>
         <v>804692</v>
       </c>
-      <c r="N19" s="167">
+      <c r="N19" s="186">
         <f t="shared" si="5"/>
         <v>821489</v>
       </c>
-      <c r="O19" s="167">
+      <c r="O19" s="186">
         <f t="shared" si="5"/>
         <v>831956</v>
       </c>
-      <c r="P19" s="167">
+      <c r="P19" s="186">
         <f t="shared" si="5"/>
         <v>853167</v>
       </c>
-      <c r="Q19" s="167">
+      <c r="Q19" s="186">
         <f t="shared" si="5"/>
         <v>880280</v>
       </c>
-      <c r="R19" s="167">
+      <c r="R19" s="186">
         <f t="shared" si="5"/>
         <v>817375</v>
       </c>
-      <c r="S19" s="167">
+      <c r="S19" s="186">
         <f t="shared" si="5"/>
         <v>905132</v>
       </c>
-      <c r="T19" s="167">
+      <c r="T19" s="186">
         <f t="shared" si="5"/>
         <v>973165</v>
       </c>
-      <c r="U19" s="167">
+      <c r="U19" s="186">
         <f t="shared" si="5"/>
         <v>982221</v>
       </c>
-      <c r="V19" s="167">
+      <c r="V19" s="186">
         <f t="shared" si="5"/>
         <v>996471</v>
       </c>
-      <c r="W19" s="167">
+      <c r="W19" s="186">
         <f t="shared" si="5"/>
         <v>1023465.1349187322</v>
       </c>
-      <c r="X19" s="187">
-        <f>W19*(1+$X$20)</f>
+      <c r="X19" s="186">
+        <f>SUM(X6:X18)</f>
         <v>1044752.0180007068</v>
       </c>
-      <c r="Y19" s="188">
-        <f>X19*(1+$Y$20)</f>
-        <v>1069767.8581736113</v>
-      </c>
-      <c r="Z19" s="187">
-        <f>Y19*(1+$Z$20)</f>
-        <v>1093700.2343699208</v>
-      </c>
-      <c r="AA19" s="187">
-        <f>Z19*(1+$AA$20)</f>
-        <v>1119028.0598775139</v>
-      </c>
-      <c r="AB19" s="187">
-        <f>AA19*(1+$AB$20)</f>
-        <v>1144502.4444299242</v>
+      <c r="Y19" s="186">
+        <f t="shared" ref="Y19:AB19" si="6">SUM(Y6:Y18)</f>
+        <v>1069767.8581736111</v>
+      </c>
+      <c r="Z19" s="186">
+        <f t="shared" si="6"/>
+        <v>1093700.2343699206</v>
+      </c>
+      <c r="AA19" s="186">
+        <f t="shared" si="6"/>
+        <v>1119028.0598775134</v>
+      </c>
+      <c r="AB19" s="186">
+        <f t="shared" si="6"/>
+        <v>1144502.444429924</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="164"/>
-      <c r="B20" s="166" t="s">
-        <v>77</v>
+      <c r="A20" s="163"/>
+      <c r="B20" s="165" t="s">
+        <v>76</v>
       </c>
       <c r="C20" s="162">
         <v>0</v>
       </c>
-      <c r="D20" s="170">
+      <c r="D20" s="168">
         <f>IFERROR((D$19/C$19)-1,"")</f>
         <v>6.7063107077562911E-2</v>
       </c>
-      <c r="E20" s="170">
-        <f t="shared" ref="E20:W20" si="6">IFERROR((E$19/D$19)-1,"")</f>
+      <c r="E20" s="168">
+        <f t="shared" ref="E20:W20" si="7">IFERROR((E$19/D$19)-1,"")</f>
         <v>6.6742251498264071E-2</v>
       </c>
-      <c r="F20" s="170">
-        <f t="shared" si="6"/>
+      <c r="F20" s="168">
+        <f t="shared" si="7"/>
         <v>3.2927553948284283E-2</v>
       </c>
-      <c r="G20" s="170">
-        <f t="shared" si="6"/>
+      <c r="G20" s="168">
+        <f t="shared" si="7"/>
         <v>9.8720544918997621E-3</v>
       </c>
-      <c r="H20" s="168">
-        <f t="shared" si="6"/>
+      <c r="H20" s="167">
+        <f t="shared" si="7"/>
         <v>4.2433958886049616E-2</v>
       </c>
-      <c r="I20" s="168">
-        <f t="shared" si="6"/>
+      <c r="I20" s="167">
+        <f t="shared" si="7"/>
         <v>6.6950212425112454E-2</v>
       </c>
-      <c r="J20" s="168">
-        <f t="shared" si="6"/>
+      <c r="J20" s="167">
+        <f t="shared" si="7"/>
         <v>3.8553282407000955E-2</v>
       </c>
-      <c r="K20" s="168">
-        <f t="shared" si="6"/>
+      <c r="K20" s="197">
+        <f t="shared" si="7"/>
         <v>5.1001500665788235E-2</v>
       </c>
-      <c r="L20" s="168">
-        <f t="shared" si="6"/>
+      <c r="L20" s="167">
+        <f t="shared" si="7"/>
         <v>4.7108113905722115E-2</v>
       </c>
-      <c r="M20" s="168">
-        <f t="shared" si="6"/>
+      <c r="M20" s="167">
+        <f t="shared" si="7"/>
         <v>3.0313040561217086E-2</v>
       </c>
-      <c r="N20" s="168">
-        <f t="shared" si="6"/>
+      <c r="N20" s="167">
+        <f t="shared" si="7"/>
         <v>2.0873825016279435E-2</v>
       </c>
-      <c r="O20" s="168">
-        <f t="shared" si="6"/>
+      <c r="O20" s="167">
+        <f t="shared" si="7"/>
         <v>1.2741497451578709E-2</v>
       </c>
-      <c r="P20" s="168">
-        <f t="shared" si="6"/>
+      <c r="P20" s="167">
+        <f t="shared" si="7"/>
         <v>2.5495338695796343E-2</v>
       </c>
-      <c r="Q20" s="168">
-        <f t="shared" si="6"/>
+      <c r="Q20" s="167">
+        <f t="shared" si="7"/>
         <v>3.1779241344308984E-2</v>
       </c>
-      <c r="R20" s="168">
-        <f t="shared" si="6"/>
+      <c r="R20" s="167">
+        <f t="shared" si="7"/>
         <v>-7.146021720361706E-2</v>
       </c>
-      <c r="S20" s="168">
-        <f t="shared" si="6"/>
+      <c r="S20" s="167">
+        <f t="shared" si="7"/>
         <v>0.10736442881174502</v>
       </c>
-      <c r="T20" s="168">
-        <f t="shared" si="6"/>
+      <c r="T20" s="167">
+        <f t="shared" si="7"/>
         <v>7.5163622543452213E-2</v>
       </c>
-      <c r="U20" s="168">
-        <f t="shared" si="6"/>
+      <c r="U20" s="167">
+        <f t="shared" si="7"/>
         <v>9.3057189685201713E-3</v>
       </c>
-      <c r="V20" s="168">
-        <f t="shared" si="6"/>
+      <c r="V20" s="167">
+        <f t="shared" si="7"/>
         <v>1.4507936604898575E-2</v>
       </c>
-      <c r="W20" s="168">
-        <f t="shared" si="6"/>
+      <c r="W20" s="167">
+        <f t="shared" si="7"/>
         <v>2.7089734592107728E-2</v>
       </c>
-      <c r="X20" s="171">
+      <c r="X20" s="187">
         <f>AVERAGE(V20:W20)</f>
         <v>2.0798835598503151E-2</v>
       </c>
-      <c r="Y20" s="171">
-        <f t="shared" ref="Y20:AB20" si="7">AVERAGE(W20:X20)</f>
+      <c r="Y20" s="187">
+        <f t="shared" ref="Y20:AB20" si="8">AVERAGE(W20:X20)</f>
         <v>2.394428509530544E-2</v>
       </c>
-      <c r="Z20" s="171">
-        <f t="shared" si="7"/>
+      <c r="Z20" s="187">
+        <f t="shared" si="8"/>
         <v>2.2371560346904296E-2</v>
       </c>
-      <c r="AA20" s="171">
-        <f t="shared" si="7"/>
+      <c r="AA20" s="187">
+        <f t="shared" si="8"/>
         <v>2.3157922721104868E-2</v>
       </c>
-      <c r="AB20" s="171">
-        <f t="shared" si="7"/>
+      <c r="AB20" s="187">
+        <f t="shared" si="8"/>
         <v>2.2764741534004582E-2</v>
       </c>
     </row>
+    <row r="21" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="X21" s="194" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y21" s="195"/>
+      <c r="Z21" s="195"/>
+      <c r="AA21" s="195"/>
+      <c r="AB21" s="196"/>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="B23" s="198"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:B2"/>
+    <mergeCell ref="X3:AB4"/>
+    <mergeCell ref="X21:AB21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18266,13 +17296,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:86" s="81" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="186"/>
-      <c r="B1" s="186"/>
-      <c r="C1" s="186"/>
-      <c r="D1" s="186"/>
-      <c r="E1" s="186"/>
-      <c r="F1" s="186"/>
-      <c r="G1" s="186"/>
+      <c r="A1" s="183"/>
+      <c r="B1" s="183"/>
+      <c r="C1" s="183"/>
+      <c r="D1" s="183"/>
+      <c r="E1" s="183"/>
+      <c r="F1" s="183"/>
+      <c r="G1" s="183"/>
     </row>
     <row r="2" spans="1:86" s="81" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="82"/>
@@ -18284,24 +17314,24 @@
       <c r="G2" s="82"/>
     </row>
     <row r="3" spans="1:86" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="179" t="s">
+      <c r="A3" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="179"/>
-      <c r="C3" s="179"/>
-      <c r="D3" s="179"/>
-      <c r="E3" s="179"/>
-      <c r="F3" s="179"/>
-      <c r="G3" s="179"/>
+      <c r="B3" s="176"/>
+      <c r="C3" s="176"/>
+      <c r="D3" s="176"/>
+      <c r="E3" s="176"/>
+      <c r="F3" s="176"/>
+      <c r="G3" s="176"/>
     </row>
     <row r="4" spans="1:86" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="179"/>
-      <c r="B4" s="179"/>
-      <c r="C4" s="179"/>
-      <c r="D4" s="179"/>
-      <c r="E4" s="179"/>
-      <c r="F4" s="179"/>
-      <c r="G4" s="179"/>
+      <c r="A4" s="176"/>
+      <c r="B4" s="176"/>
+      <c r="C4" s="176"/>
+      <c r="D4" s="176"/>
+      <c r="E4" s="176"/>
+      <c r="F4" s="176"/>
+      <c r="G4" s="176"/>
     </row>
     <row r="5" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -18364,142 +17394,142 @@
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="183" t="s">
+      <c r="A10" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="181" t="s">
+      <c r="B10" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="181">
+      <c r="C10" s="178">
         <v>2005</v>
       </c>
-      <c r="D10" s="181"/>
-      <c r="E10" s="181"/>
-      <c r="F10" s="181"/>
-      <c r="G10" s="181">
+      <c r="D10" s="178"/>
+      <c r="E10" s="178"/>
+      <c r="F10" s="178"/>
+      <c r="G10" s="178">
         <v>2006</v>
       </c>
-      <c r="H10" s="181"/>
-      <c r="I10" s="181"/>
-      <c r="J10" s="181"/>
-      <c r="K10" s="181">
+      <c r="H10" s="178"/>
+      <c r="I10" s="178"/>
+      <c r="J10" s="178"/>
+      <c r="K10" s="178">
         <v>2007</v>
       </c>
-      <c r="L10" s="181"/>
-      <c r="M10" s="181"/>
-      <c r="N10" s="181"/>
-      <c r="O10" s="181">
+      <c r="L10" s="178"/>
+      <c r="M10" s="178"/>
+      <c r="N10" s="178"/>
+      <c r="O10" s="178">
         <v>2008</v>
       </c>
-      <c r="P10" s="181"/>
-      <c r="Q10" s="181"/>
-      <c r="R10" s="181"/>
-      <c r="S10" s="181">
+      <c r="P10" s="178"/>
+      <c r="Q10" s="178"/>
+      <c r="R10" s="178"/>
+      <c r="S10" s="178">
         <v>2009</v>
       </c>
-      <c r="T10" s="181"/>
-      <c r="U10" s="181"/>
-      <c r="V10" s="181"/>
-      <c r="W10" s="181">
+      <c r="T10" s="178"/>
+      <c r="U10" s="178"/>
+      <c r="V10" s="178"/>
+      <c r="W10" s="178">
         <v>2010</v>
       </c>
-      <c r="X10" s="181"/>
-      <c r="Y10" s="181"/>
-      <c r="Z10" s="181"/>
-      <c r="AA10" s="181">
+      <c r="X10" s="178"/>
+      <c r="Y10" s="178"/>
+      <c r="Z10" s="178"/>
+      <c r="AA10" s="178">
         <v>2011</v>
       </c>
-      <c r="AB10" s="181"/>
-      <c r="AC10" s="181"/>
-      <c r="AD10" s="181"/>
-      <c r="AE10" s="181">
+      <c r="AB10" s="178"/>
+      <c r="AC10" s="178"/>
+      <c r="AD10" s="178"/>
+      <c r="AE10" s="178">
         <v>2012</v>
       </c>
-      <c r="AF10" s="181"/>
-      <c r="AG10" s="181"/>
-      <c r="AH10" s="181"/>
-      <c r="AI10" s="181">
+      <c r="AF10" s="178"/>
+      <c r="AG10" s="178"/>
+      <c r="AH10" s="178"/>
+      <c r="AI10" s="178">
         <v>2013</v>
       </c>
-      <c r="AJ10" s="181"/>
-      <c r="AK10" s="181"/>
-      <c r="AL10" s="181"/>
-      <c r="AM10" s="181">
+      <c r="AJ10" s="178"/>
+      <c r="AK10" s="178"/>
+      <c r="AL10" s="178"/>
+      <c r="AM10" s="178">
         <v>2014</v>
       </c>
-      <c r="AN10" s="181"/>
-      <c r="AO10" s="181"/>
-      <c r="AP10" s="181"/>
-      <c r="AQ10" s="181">
+      <c r="AN10" s="178"/>
+      <c r="AO10" s="178"/>
+      <c r="AP10" s="178"/>
+      <c r="AQ10" s="178">
         <v>2015</v>
       </c>
-      <c r="AR10" s="181"/>
-      <c r="AS10" s="181"/>
-      <c r="AT10" s="181"/>
-      <c r="AU10" s="181">
+      <c r="AR10" s="178"/>
+      <c r="AS10" s="178"/>
+      <c r="AT10" s="178"/>
+      <c r="AU10" s="178">
         <v>2016</v>
       </c>
-      <c r="AV10" s="181"/>
-      <c r="AW10" s="181"/>
-      <c r="AX10" s="181"/>
-      <c r="AY10" s="181">
+      <c r="AV10" s="178"/>
+      <c r="AW10" s="178"/>
+      <c r="AX10" s="178"/>
+      <c r="AY10" s="178">
         <v>2017</v>
       </c>
-      <c r="AZ10" s="181"/>
-      <c r="BA10" s="181"/>
-      <c r="BB10" s="181"/>
-      <c r="BC10" s="181">
+      <c r="AZ10" s="178"/>
+      <c r="BA10" s="178"/>
+      <c r="BB10" s="178"/>
+      <c r="BC10" s="178">
         <v>2018</v>
       </c>
-      <c r="BD10" s="181"/>
-      <c r="BE10" s="181"/>
-      <c r="BF10" s="181"/>
-      <c r="BG10" s="181">
+      <c r="BD10" s="178"/>
+      <c r="BE10" s="178"/>
+      <c r="BF10" s="178"/>
+      <c r="BG10" s="178">
         <v>2019</v>
       </c>
-      <c r="BH10" s="181"/>
-      <c r="BI10" s="181"/>
-      <c r="BJ10" s="181"/>
-      <c r="BK10" s="181">
+      <c r="BH10" s="178"/>
+      <c r="BI10" s="178"/>
+      <c r="BJ10" s="178"/>
+      <c r="BK10" s="178">
         <v>2020</v>
       </c>
-      <c r="BL10" s="181"/>
-      <c r="BM10" s="181"/>
-      <c r="BN10" s="181"/>
-      <c r="BO10" s="181">
+      <c r="BL10" s="178"/>
+      <c r="BM10" s="178"/>
+      <c r="BN10" s="178"/>
+      <c r="BO10" s="178">
         <v>2021</v>
       </c>
-      <c r="BP10" s="181"/>
-      <c r="BQ10" s="181"/>
-      <c r="BR10" s="181"/>
-      <c r="BS10" s="181">
+      <c r="BP10" s="178"/>
+      <c r="BQ10" s="178"/>
+      <c r="BR10" s="178"/>
+      <c r="BS10" s="178">
         <v>2022</v>
       </c>
-      <c r="BT10" s="181"/>
-      <c r="BU10" s="181"/>
-      <c r="BV10" s="181"/>
-      <c r="BW10" s="181">
+      <c r="BT10" s="178"/>
+      <c r="BU10" s="178"/>
+      <c r="BV10" s="178"/>
+      <c r="BW10" s="178">
         <v>2023</v>
       </c>
-      <c r="BX10" s="181"/>
-      <c r="BY10" s="181"/>
-      <c r="BZ10" s="181"/>
-      <c r="CA10" s="181" t="s">
+      <c r="BX10" s="178"/>
+      <c r="BY10" s="178"/>
+      <c r="BZ10" s="178"/>
+      <c r="CA10" s="178" t="s">
         <v>12</v>
       </c>
-      <c r="CB10" s="181"/>
-      <c r="CC10" s="181"/>
-      <c r="CD10" s="181"/>
-      <c r="CE10" s="181" t="s">
+      <c r="CB10" s="178"/>
+      <c r="CC10" s="178"/>
+      <c r="CD10" s="178"/>
+      <c r="CE10" s="178" t="s">
         <v>13</v>
       </c>
-      <c r="CF10" s="181"/>
-      <c r="CG10" s="181"/>
-      <c r="CH10" s="182"/>
+      <c r="CF10" s="178"/>
+      <c r="CG10" s="178"/>
+      <c r="CH10" s="179"/>
     </row>
     <row r="11" spans="1:86" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="184"/>
-      <c r="B11" s="185"/>
+      <c r="A11" s="181"/>
+      <c r="B11" s="182"/>
       <c r="C11" s="84" t="s">
         <v>14</v>
       </c>
@@ -21313,25 +20343,25 @@
       <c r="Q30" s="25"/>
     </row>
     <row r="31" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="179" t="s">
+      <c r="A31" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="B31" s="179"/>
-      <c r="C31" s="179"/>
-      <c r="D31" s="179"/>
-      <c r="E31" s="179"/>
-      <c r="F31" s="179"/>
-      <c r="G31" s="179"/>
+      <c r="B31" s="176"/>
+      <c r="C31" s="176"/>
+      <c r="D31" s="176"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="176"/>
       <c r="BH31" s="1"/>
     </row>
     <row r="32" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="179"/>
-      <c r="B32" s="179"/>
-      <c r="C32" s="179"/>
-      <c r="D32" s="179"/>
-      <c r="E32" s="179"/>
-      <c r="F32" s="179"/>
-      <c r="G32" s="179"/>
+      <c r="A32" s="176"/>
+      <c r="B32" s="176"/>
+      <c r="C32" s="176"/>
+      <c r="D32" s="176"/>
+      <c r="E32" s="176"/>
+      <c r="F32" s="176"/>
+      <c r="G32" s="176"/>
     </row>
     <row r="33" spans="1:86" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
@@ -21370,140 +20400,140 @@
       <c r="BH36" s="2"/>
     </row>
     <row r="37" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="183" t="s">
+      <c r="A37" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="B37" s="181" t="s">
+      <c r="B37" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="C37" s="181"/>
-      <c r="D37" s="181"/>
-      <c r="E37" s="181"/>
-      <c r="F37" s="181"/>
-      <c r="G37" s="181">
+      <c r="C37" s="178"/>
+      <c r="D37" s="178"/>
+      <c r="E37" s="178"/>
+      <c r="F37" s="178"/>
+      <c r="G37" s="178">
         <v>2006</v>
       </c>
-      <c r="H37" s="181"/>
-      <c r="I37" s="181"/>
-      <c r="J37" s="181"/>
-      <c r="K37" s="181">
+      <c r="H37" s="178"/>
+      <c r="I37" s="178"/>
+      <c r="J37" s="178"/>
+      <c r="K37" s="178">
         <v>2007</v>
       </c>
-      <c r="L37" s="181"/>
-      <c r="M37" s="181"/>
-      <c r="N37" s="181"/>
-      <c r="O37" s="181">
+      <c r="L37" s="178"/>
+      <c r="M37" s="178"/>
+      <c r="N37" s="178"/>
+      <c r="O37" s="178">
         <v>2008</v>
       </c>
-      <c r="P37" s="181"/>
-      <c r="Q37" s="181"/>
-      <c r="R37" s="181"/>
-      <c r="S37" s="181">
+      <c r="P37" s="178"/>
+      <c r="Q37" s="178"/>
+      <c r="R37" s="178"/>
+      <c r="S37" s="178">
         <v>2009</v>
       </c>
-      <c r="T37" s="181"/>
-      <c r="U37" s="181"/>
-      <c r="V37" s="181"/>
-      <c r="W37" s="181">
+      <c r="T37" s="178"/>
+      <c r="U37" s="178"/>
+      <c r="V37" s="178"/>
+      <c r="W37" s="178">
         <v>2010</v>
       </c>
-      <c r="X37" s="181"/>
-      <c r="Y37" s="181"/>
-      <c r="Z37" s="181"/>
-      <c r="AA37" s="181">
+      <c r="X37" s="178"/>
+      <c r="Y37" s="178"/>
+      <c r="Z37" s="178"/>
+      <c r="AA37" s="178">
         <v>2011</v>
       </c>
-      <c r="AB37" s="181"/>
-      <c r="AC37" s="181"/>
-      <c r="AD37" s="181"/>
-      <c r="AE37" s="181">
+      <c r="AB37" s="178"/>
+      <c r="AC37" s="178"/>
+      <c r="AD37" s="178"/>
+      <c r="AE37" s="178">
         <v>2012</v>
       </c>
-      <c r="AF37" s="181"/>
-      <c r="AG37" s="181"/>
-      <c r="AH37" s="181"/>
-      <c r="AI37" s="181">
+      <c r="AF37" s="178"/>
+      <c r="AG37" s="178"/>
+      <c r="AH37" s="178"/>
+      <c r="AI37" s="178">
         <v>2013</v>
       </c>
-      <c r="AJ37" s="181"/>
-      <c r="AK37" s="181"/>
-      <c r="AL37" s="181"/>
-      <c r="AM37" s="181">
+      <c r="AJ37" s="178"/>
+      <c r="AK37" s="178"/>
+      <c r="AL37" s="178"/>
+      <c r="AM37" s="178">
         <v>2014</v>
       </c>
-      <c r="AN37" s="181"/>
-      <c r="AO37" s="181"/>
-      <c r="AP37" s="181"/>
-      <c r="AQ37" s="181">
+      <c r="AN37" s="178"/>
+      <c r="AO37" s="178"/>
+      <c r="AP37" s="178"/>
+      <c r="AQ37" s="178">
         <v>2015</v>
       </c>
-      <c r="AR37" s="181"/>
-      <c r="AS37" s="181"/>
-      <c r="AT37" s="181"/>
-      <c r="AU37" s="181">
+      <c r="AR37" s="178"/>
+      <c r="AS37" s="178"/>
+      <c r="AT37" s="178"/>
+      <c r="AU37" s="178">
         <v>2016</v>
       </c>
-      <c r="AV37" s="181"/>
-      <c r="AW37" s="181"/>
-      <c r="AX37" s="181"/>
-      <c r="AY37" s="181">
+      <c r="AV37" s="178"/>
+      <c r="AW37" s="178"/>
+      <c r="AX37" s="178"/>
+      <c r="AY37" s="178">
         <v>2017</v>
       </c>
-      <c r="AZ37" s="181"/>
-      <c r="BA37" s="181"/>
-      <c r="BB37" s="181"/>
-      <c r="BC37" s="181">
+      <c r="AZ37" s="178"/>
+      <c r="BA37" s="178"/>
+      <c r="BB37" s="178"/>
+      <c r="BC37" s="178">
         <v>2018</v>
       </c>
-      <c r="BD37" s="181"/>
-      <c r="BE37" s="181"/>
-      <c r="BF37" s="181"/>
-      <c r="BG37" s="181">
+      <c r="BD37" s="178"/>
+      <c r="BE37" s="178"/>
+      <c r="BF37" s="178"/>
+      <c r="BG37" s="178">
         <v>2019</v>
       </c>
-      <c r="BH37" s="181"/>
-      <c r="BI37" s="181"/>
-      <c r="BJ37" s="181"/>
-      <c r="BK37" s="181">
+      <c r="BH37" s="178"/>
+      <c r="BI37" s="178"/>
+      <c r="BJ37" s="178"/>
+      <c r="BK37" s="178">
         <v>2020</v>
       </c>
-      <c r="BL37" s="181"/>
-      <c r="BM37" s="181"/>
-      <c r="BN37" s="181"/>
-      <c r="BO37" s="181">
+      <c r="BL37" s="178"/>
+      <c r="BM37" s="178"/>
+      <c r="BN37" s="178"/>
+      <c r="BO37" s="178">
         <v>2021</v>
       </c>
-      <c r="BP37" s="181"/>
-      <c r="BQ37" s="181"/>
-      <c r="BR37" s="181"/>
-      <c r="BS37" s="181">
+      <c r="BP37" s="178"/>
+      <c r="BQ37" s="178"/>
+      <c r="BR37" s="178"/>
+      <c r="BS37" s="178">
         <v>2022</v>
       </c>
-      <c r="BT37" s="181"/>
-      <c r="BU37" s="181"/>
-      <c r="BV37" s="181"/>
-      <c r="BW37" s="181">
+      <c r="BT37" s="178"/>
+      <c r="BU37" s="178"/>
+      <c r="BV37" s="178"/>
+      <c r="BW37" s="178">
         <v>2023</v>
       </c>
-      <c r="BX37" s="181"/>
-      <c r="BY37" s="181"/>
-      <c r="BZ37" s="181"/>
-      <c r="CA37" s="181" t="s">
+      <c r="BX37" s="178"/>
+      <c r="BY37" s="178"/>
+      <c r="BZ37" s="178"/>
+      <c r="CA37" s="178" t="s">
         <v>12</v>
       </c>
-      <c r="CB37" s="181"/>
-      <c r="CC37" s="181"/>
-      <c r="CD37" s="181"/>
-      <c r="CE37" s="181" t="s">
+      <c r="CB37" s="178"/>
+      <c r="CC37" s="178"/>
+      <c r="CD37" s="178"/>
+      <c r="CE37" s="178" t="s">
         <v>13</v>
       </c>
-      <c r="CF37" s="181"/>
-      <c r="CG37" s="181"/>
-      <c r="CH37" s="182"/>
+      <c r="CF37" s="178"/>
+      <c r="CG37" s="178"/>
+      <c r="CH37" s="179"/>
     </row>
     <row r="38" spans="1:86" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="184"/>
-      <c r="B38" s="185"/>
+      <c r="A38" s="181"/>
+      <c r="B38" s="182"/>
       <c r="C38" s="84"/>
       <c r="D38" s="84"/>
       <c r="E38" s="84"/>
@@ -24603,15 +23633,15 @@
       <c r="BF57" s="25"/>
     </row>
     <row r="58" spans="1:86" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="179" t="s">
+      <c r="A58" s="176" t="s">
         <v>0</v>
       </c>
-      <c r="B58" s="179"/>
-      <c r="C58" s="179"/>
-      <c r="D58" s="179"/>
-      <c r="E58" s="179"/>
-      <c r="F58" s="179"/>
-      <c r="G58" s="179"/>
+      <c r="B58" s="176"/>
+      <c r="C58" s="176"/>
+      <c r="D58" s="176"/>
+      <c r="E58" s="176"/>
+      <c r="F58" s="176"/>
+      <c r="G58" s="176"/>
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
       <c r="J58" s="2"/>
@@ -24665,13 +23695,13 @@
       <c r="BF58" s="2"/>
     </row>
     <row r="59" spans="1:86" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="179"/>
-      <c r="B59" s="179"/>
-      <c r="C59" s="179"/>
-      <c r="D59" s="179"/>
-      <c r="E59" s="179"/>
-      <c r="F59" s="179"/>
-      <c r="G59" s="179"/>
+      <c r="A59" s="176"/>
+      <c r="B59" s="176"/>
+      <c r="C59" s="176"/>
+      <c r="D59" s="176"/>
+      <c r="E59" s="176"/>
+      <c r="F59" s="176"/>
+      <c r="G59" s="176"/>
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
       <c r="J59" s="2"/>
@@ -24911,140 +23941,140 @@
       <c r="BF62" s="2"/>
     </row>
     <row r="64" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="183" t="s">
+      <c r="A64" s="180" t="s">
         <v>8</v>
       </c>
-      <c r="B64" s="181" t="s">
+      <c r="B64" s="178" t="s">
         <v>10</v>
       </c>
-      <c r="C64" s="181"/>
-      <c r="D64" s="181"/>
-      <c r="E64" s="181"/>
-      <c r="F64" s="181"/>
-      <c r="G64" s="181">
+      <c r="C64" s="178"/>
+      <c r="D64" s="178"/>
+      <c r="E64" s="178"/>
+      <c r="F64" s="178"/>
+      <c r="G64" s="178">
         <v>2006</v>
       </c>
-      <c r="H64" s="181"/>
-      <c r="I64" s="181"/>
-      <c r="J64" s="181"/>
-      <c r="K64" s="181">
+      <c r="H64" s="178"/>
+      <c r="I64" s="178"/>
+      <c r="J64" s="178"/>
+      <c r="K64" s="178">
         <v>2007</v>
       </c>
-      <c r="L64" s="181"/>
-      <c r="M64" s="181"/>
-      <c r="N64" s="181"/>
-      <c r="O64" s="181">
+      <c r="L64" s="178"/>
+      <c r="M64" s="178"/>
+      <c r="N64" s="178"/>
+      <c r="O64" s="178">
         <v>2008</v>
       </c>
-      <c r="P64" s="181"/>
-      <c r="Q64" s="181"/>
-      <c r="R64" s="181"/>
-      <c r="S64" s="181">
+      <c r="P64" s="178"/>
+      <c r="Q64" s="178"/>
+      <c r="R64" s="178"/>
+      <c r="S64" s="178">
         <v>2009</v>
       </c>
-      <c r="T64" s="181"/>
-      <c r="U64" s="181"/>
-      <c r="V64" s="181"/>
-      <c r="W64" s="181">
+      <c r="T64" s="178"/>
+      <c r="U64" s="178"/>
+      <c r="V64" s="178"/>
+      <c r="W64" s="178">
         <v>2010</v>
       </c>
-      <c r="X64" s="181"/>
-      <c r="Y64" s="181"/>
-      <c r="Z64" s="181"/>
-      <c r="AA64" s="181">
+      <c r="X64" s="178"/>
+      <c r="Y64" s="178"/>
+      <c r="Z64" s="178"/>
+      <c r="AA64" s="178">
         <v>2011</v>
       </c>
-      <c r="AB64" s="181"/>
-      <c r="AC64" s="181"/>
-      <c r="AD64" s="181"/>
-      <c r="AE64" s="181">
+      <c r="AB64" s="178"/>
+      <c r="AC64" s="178"/>
+      <c r="AD64" s="178"/>
+      <c r="AE64" s="178">
         <v>2012</v>
       </c>
-      <c r="AF64" s="181"/>
-      <c r="AG64" s="181"/>
-      <c r="AH64" s="181"/>
-      <c r="AI64" s="181">
+      <c r="AF64" s="178"/>
+      <c r="AG64" s="178"/>
+      <c r="AH64" s="178"/>
+      <c r="AI64" s="178">
         <v>2013</v>
       </c>
-      <c r="AJ64" s="181"/>
-      <c r="AK64" s="181"/>
-      <c r="AL64" s="181"/>
-      <c r="AM64" s="181">
+      <c r="AJ64" s="178"/>
+      <c r="AK64" s="178"/>
+      <c r="AL64" s="178"/>
+      <c r="AM64" s="178">
         <v>2014</v>
       </c>
-      <c r="AN64" s="181"/>
-      <c r="AO64" s="181"/>
-      <c r="AP64" s="181"/>
-      <c r="AQ64" s="181">
+      <c r="AN64" s="178"/>
+      <c r="AO64" s="178"/>
+      <c r="AP64" s="178"/>
+      <c r="AQ64" s="178">
         <v>2015</v>
       </c>
-      <c r="AR64" s="181"/>
-      <c r="AS64" s="181"/>
-      <c r="AT64" s="181"/>
-      <c r="AU64" s="181">
+      <c r="AR64" s="178"/>
+      <c r="AS64" s="178"/>
+      <c r="AT64" s="178"/>
+      <c r="AU64" s="178">
         <v>2016</v>
       </c>
-      <c r="AV64" s="181"/>
-      <c r="AW64" s="181"/>
-      <c r="AX64" s="181"/>
-      <c r="AY64" s="181">
+      <c r="AV64" s="178"/>
+      <c r="AW64" s="178"/>
+      <c r="AX64" s="178"/>
+      <c r="AY64" s="178">
         <v>2017</v>
       </c>
-      <c r="AZ64" s="181"/>
-      <c r="BA64" s="181"/>
-      <c r="BB64" s="181"/>
-      <c r="BC64" s="181">
+      <c r="AZ64" s="178"/>
+      <c r="BA64" s="178"/>
+      <c r="BB64" s="178"/>
+      <c r="BC64" s="178">
         <v>2018</v>
       </c>
-      <c r="BD64" s="181"/>
-      <c r="BE64" s="181"/>
-      <c r="BF64" s="181"/>
-      <c r="BG64" s="181">
+      <c r="BD64" s="178"/>
+      <c r="BE64" s="178"/>
+      <c r="BF64" s="178"/>
+      <c r="BG64" s="178">
         <v>2019</v>
       </c>
-      <c r="BH64" s="181"/>
-      <c r="BI64" s="181"/>
-      <c r="BJ64" s="181"/>
-      <c r="BK64" s="181">
+      <c r="BH64" s="178"/>
+      <c r="BI64" s="178"/>
+      <c r="BJ64" s="178"/>
+      <c r="BK64" s="178">
         <v>2020</v>
       </c>
-      <c r="BL64" s="181"/>
-      <c r="BM64" s="181"/>
-      <c r="BN64" s="181"/>
-      <c r="BO64" s="181">
+      <c r="BL64" s="178"/>
+      <c r="BM64" s="178"/>
+      <c r="BN64" s="178"/>
+      <c r="BO64" s="178">
         <v>2021</v>
       </c>
-      <c r="BP64" s="181"/>
-      <c r="BQ64" s="181"/>
-      <c r="BR64" s="181"/>
-      <c r="BS64" s="181">
+      <c r="BP64" s="178"/>
+      <c r="BQ64" s="178"/>
+      <c r="BR64" s="178"/>
+      <c r="BS64" s="178">
         <v>2022</v>
       </c>
-      <c r="BT64" s="181"/>
-      <c r="BU64" s="181"/>
-      <c r="BV64" s="181"/>
-      <c r="BW64" s="181">
+      <c r="BT64" s="178"/>
+      <c r="BU64" s="178"/>
+      <c r="BV64" s="178"/>
+      <c r="BW64" s="178">
         <v>2023</v>
       </c>
-      <c r="BX64" s="181"/>
-      <c r="BY64" s="181"/>
-      <c r="BZ64" s="181"/>
-      <c r="CA64" s="181" t="s">
+      <c r="BX64" s="178"/>
+      <c r="BY64" s="178"/>
+      <c r="BZ64" s="178"/>
+      <c r="CA64" s="178" t="s">
         <v>12</v>
       </c>
-      <c r="CB64" s="181"/>
-      <c r="CC64" s="181"/>
-      <c r="CD64" s="181"/>
-      <c r="CE64" s="181" t="s">
+      <c r="CB64" s="178"/>
+      <c r="CC64" s="178"/>
+      <c r="CD64" s="178"/>
+      <c r="CE64" s="178" t="s">
         <v>13</v>
       </c>
-      <c r="CF64" s="181"/>
-      <c r="CG64" s="181"/>
-      <c r="CH64" s="182"/>
+      <c r="CF64" s="178"/>
+      <c r="CG64" s="178"/>
+      <c r="CH64" s="179"/>
     </row>
     <row r="65" spans="1:86" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="184"/>
-      <c r="B65" s="185"/>
+      <c r="A65" s="181"/>
+      <c r="B65" s="182"/>
       <c r="C65" s="84"/>
       <c r="D65" s="84"/>
       <c r="E65" s="84"/>

--- a/Cuadros_Prod_Gasto.xlsx
+++ b/Cuadros_Prod_Gasto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\WTF IS PROGRAMMING 2.0\UR CLASES\7_SEMESTRE\ICE\Proyecciones\ICE_Proyecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E77ABF4-56CD-43DC-8B22-0A227955B8FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBCB42D-3E6E-4E9B-ABC4-8D7002EB7668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="2" xr2:uid="{A3B4AD7B-0ED6-4521-BD6B-44541A0DC533}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{A3B4AD7B-0ED6-4521-BD6B-44541A0DC533}"/>
   </bookViews>
   <sheets>
     <sheet name="C1P" sheetId="2" state="hidden" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="87">
   <si>
     <t>Producto Interno Bruto (PIB)</t>
   </si>
@@ -491,12 +491,6 @@
     </r>
   </si>
   <si>
-    <t>Suma Agregada PIB por Oferta Anual</t>
-  </si>
-  <si>
-    <t>Tasas de Crecimiento</t>
-  </si>
-  <si>
     <t>PROYECCIÓN OFERTA ANUAL</t>
   </si>
   <si>
@@ -539,6 +533,12 @@
   <si>
     <t>Tasa de Crecimiento por Variable Desagregada</t>
   </si>
+  <si>
+    <t>Tasa de Crecimiento</t>
+  </si>
+  <si>
+    <t>Suma Agregada por Oferta Annual</t>
+  </si>
 </sst>
 </file>
 
@@ -552,7 +552,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000%"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -733,6 +733,12 @@
       <u/>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1095,7 +1101,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="266">
+  <cellXfs count="257">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1447,9 +1453,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1460,9 +1463,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1483,29 +1483,11 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="0" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1653,16 +1635,7 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1697,18 +1670,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1785,6 +1746,24 @@
     </xf>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="27" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -2429,36 +2408,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:87" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="175"/>
-      <c r="B1" s="175"/>
-      <c r="C1" s="175"/>
-      <c r="D1" s="175"/>
-      <c r="E1" s="175"/>
-      <c r="F1" s="175"/>
-      <c r="G1" s="175"/>
+      <c r="A1" s="167"/>
+      <c r="B1" s="167"/>
+      <c r="C1" s="167"/>
+      <c r="D1" s="167"/>
+      <c r="E1" s="167"/>
+      <c r="F1" s="167"/>
+      <c r="G1" s="167"/>
     </row>
     <row r="2" spans="1:87" ht="9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="175"/>
-      <c r="B2" s="175"/>
-      <c r="C2" s="175"/>
-      <c r="D2" s="175"/>
-      <c r="E2" s="175"/>
-      <c r="F2" s="175"/>
-      <c r="G2" s="175"/>
+      <c r="A2" s="167"/>
+      <c r="B2" s="167"/>
+      <c r="C2" s="167"/>
+      <c r="D2" s="167"/>
+      <c r="E2" s="167"/>
+      <c r="F2" s="167"/>
+      <c r="G2" s="167"/>
     </row>
     <row r="3" spans="1:87" s="3" customFormat="1" ht="42" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="175"/>
-      <c r="B3" s="175"/>
-      <c r="C3" s="175"/>
-      <c r="D3" s="175"/>
-      <c r="E3" s="175"/>
-      <c r="F3" s="175"/>
-      <c r="G3" s="175"/>
-      <c r="H3" s="151">
+      <c r="A3" s="167"/>
+      <c r="B3" s="167"/>
+      <c r="C3" s="167"/>
+      <c r="D3" s="167"/>
+      <c r="E3" s="167"/>
+      <c r="F3" s="167"/>
+      <c r="G3" s="167"/>
+      <c r="H3" s="149">
         <f>SUM(D15:G15)</f>
         <v>37909</v>
       </c>
-      <c r="I3" s="151">
+      <c r="I3" s="149">
         <f>SUM(H15:K15)</f>
         <v>38717</v>
       </c>
@@ -2483,28 +2462,28 @@
       <c r="M4" s="2"/>
     </row>
     <row r="5" spans="1:87" s="4" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="176" t="s">
+      <c r="A5" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="176"/>
-      <c r="C5" s="176"/>
-      <c r="D5" s="176"/>
-      <c r="E5" s="176"/>
-      <c r="F5" s="176"/>
-      <c r="G5" s="176"/>
-      <c r="CF5" s="152">
+      <c r="B5" s="168"/>
+      <c r="C5" s="168"/>
+      <c r="D5" s="168"/>
+      <c r="E5" s="168"/>
+      <c r="F5" s="168"/>
+      <c r="G5" s="168"/>
+      <c r="CF5" s="150">
         <f>SUM(CF15:CI15)</f>
         <v>63888.120954066384</v>
       </c>
     </row>
     <row r="6" spans="1:87" s="4" customFormat="1" ht="14.45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="176"/>
-      <c r="B6" s="176"/>
-      <c r="C6" s="176"/>
-      <c r="D6" s="176"/>
-      <c r="E6" s="176"/>
-      <c r="F6" s="176"/>
-      <c r="G6" s="176"/>
+      <c r="A6" s="168"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="168"/>
+      <c r="D6" s="168"/>
+      <c r="E6" s="168"/>
+      <c r="F6" s="168"/>
+      <c r="G6" s="168"/>
     </row>
     <row r="7" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
@@ -2571,152 +2550,152 @@
       </c>
     </row>
     <row r="12" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="171" t="s">
+      <c r="A12" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="169" t="s">
+      <c r="B12" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="169" t="s">
+      <c r="C12" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="169">
+      <c r="D12" s="161">
         <v>2005</v>
       </c>
-      <c r="E12" s="169"/>
-      <c r="F12" s="169"/>
-      <c r="G12" s="169"/>
-      <c r="H12" s="169">
+      <c r="E12" s="161"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="161"/>
+      <c r="H12" s="161">
         <v>2006</v>
       </c>
-      <c r="I12" s="169"/>
-      <c r="J12" s="169"/>
-      <c r="K12" s="169"/>
-      <c r="L12" s="169">
+      <c r="I12" s="161"/>
+      <c r="J12" s="161"/>
+      <c r="K12" s="161"/>
+      <c r="L12" s="161">
         <v>2007</v>
       </c>
-      <c r="M12" s="169"/>
-      <c r="N12" s="169"/>
-      <c r="O12" s="169"/>
-      <c r="P12" s="169">
+      <c r="M12" s="161"/>
+      <c r="N12" s="161"/>
+      <c r="O12" s="161"/>
+      <c r="P12" s="161">
         <v>2008</v>
       </c>
-      <c r="Q12" s="169"/>
-      <c r="R12" s="169"/>
-      <c r="S12" s="169"/>
-      <c r="T12" s="169">
+      <c r="Q12" s="161"/>
+      <c r="R12" s="161"/>
+      <c r="S12" s="161"/>
+      <c r="T12" s="161">
         <v>2009</v>
       </c>
-      <c r="U12" s="169"/>
-      <c r="V12" s="169"/>
-      <c r="W12" s="169"/>
-      <c r="X12" s="169">
+      <c r="U12" s="161"/>
+      <c r="V12" s="161"/>
+      <c r="W12" s="161"/>
+      <c r="X12" s="161">
         <v>2010</v>
       </c>
-      <c r="Y12" s="169"/>
-      <c r="Z12" s="169"/>
-      <c r="AA12" s="169"/>
-      <c r="AB12" s="169">
+      <c r="Y12" s="161"/>
+      <c r="Z12" s="161"/>
+      <c r="AA12" s="161"/>
+      <c r="AB12" s="161">
         <v>2011</v>
       </c>
-      <c r="AC12" s="169"/>
-      <c r="AD12" s="169"/>
-      <c r="AE12" s="169"/>
-      <c r="AF12" s="169">
+      <c r="AC12" s="161"/>
+      <c r="AD12" s="161"/>
+      <c r="AE12" s="161"/>
+      <c r="AF12" s="161">
         <v>2012</v>
       </c>
-      <c r="AG12" s="169"/>
-      <c r="AH12" s="169"/>
-      <c r="AI12" s="169"/>
-      <c r="AJ12" s="169">
+      <c r="AG12" s="161"/>
+      <c r="AH12" s="161"/>
+      <c r="AI12" s="161"/>
+      <c r="AJ12" s="161">
         <v>2013</v>
       </c>
-      <c r="AK12" s="169"/>
-      <c r="AL12" s="169"/>
-      <c r="AM12" s="169"/>
-      <c r="AN12" s="169">
+      <c r="AK12" s="161"/>
+      <c r="AL12" s="161"/>
+      <c r="AM12" s="161"/>
+      <c r="AN12" s="161">
         <v>2014</v>
       </c>
-      <c r="AO12" s="169"/>
-      <c r="AP12" s="169"/>
-      <c r="AQ12" s="169"/>
-      <c r="AR12" s="169">
+      <c r="AO12" s="161"/>
+      <c r="AP12" s="161"/>
+      <c r="AQ12" s="161"/>
+      <c r="AR12" s="161">
         <v>2015</v>
       </c>
-      <c r="AS12" s="169"/>
-      <c r="AT12" s="169"/>
-      <c r="AU12" s="169"/>
-      <c r="AV12" s="169">
+      <c r="AS12" s="161"/>
+      <c r="AT12" s="161"/>
+      <c r="AU12" s="161"/>
+      <c r="AV12" s="161">
         <v>2016</v>
       </c>
-      <c r="AW12" s="169"/>
-      <c r="AX12" s="169"/>
-      <c r="AY12" s="169"/>
-      <c r="AZ12" s="169">
+      <c r="AW12" s="161"/>
+      <c r="AX12" s="161"/>
+      <c r="AY12" s="161"/>
+      <c r="AZ12" s="161">
         <v>2017</v>
       </c>
-      <c r="BA12" s="169"/>
-      <c r="BB12" s="169"/>
-      <c r="BC12" s="169"/>
-      <c r="BD12" s="169">
+      <c r="BA12" s="161"/>
+      <c r="BB12" s="161"/>
+      <c r="BC12" s="161"/>
+      <c r="BD12" s="161">
         <v>2018</v>
       </c>
-      <c r="BE12" s="169"/>
-      <c r="BF12" s="169"/>
-      <c r="BG12" s="169"/>
-      <c r="BH12" s="169">
+      <c r="BE12" s="161"/>
+      <c r="BF12" s="161"/>
+      <c r="BG12" s="161"/>
+      <c r="BH12" s="161">
         <v>2019</v>
       </c>
-      <c r="BI12" s="169"/>
-      <c r="BJ12" s="169"/>
-      <c r="BK12" s="169"/>
-      <c r="BL12" s="169">
+      <c r="BI12" s="161"/>
+      <c r="BJ12" s="161"/>
+      <c r="BK12" s="161"/>
+      <c r="BL12" s="161">
         <v>2020</v>
       </c>
-      <c r="BM12" s="169"/>
-      <c r="BN12" s="169"/>
-      <c r="BO12" s="169"/>
-      <c r="BP12" s="169">
+      <c r="BM12" s="161"/>
+      <c r="BN12" s="161"/>
+      <c r="BO12" s="161"/>
+      <c r="BP12" s="161">
         <v>2021</v>
       </c>
-      <c r="BQ12" s="169"/>
-      <c r="BR12" s="169"/>
-      <c r="BS12" s="169"/>
-      <c r="BT12" s="169">
+      <c r="BQ12" s="161"/>
+      <c r="BR12" s="161"/>
+      <c r="BS12" s="161"/>
+      <c r="BT12" s="161">
         <v>2022</v>
       </c>
-      <c r="BU12" s="169"/>
-      <c r="BV12" s="169"/>
-      <c r="BW12" s="169"/>
-      <c r="BX12" s="169">
+      <c r="BU12" s="161"/>
+      <c r="BV12" s="161"/>
+      <c r="BW12" s="161"/>
+      <c r="BX12" s="161">
         <v>2023</v>
       </c>
-      <c r="BY12" s="169" t="s">
+      <c r="BY12" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="BZ12" s="169"/>
-      <c r="CA12" s="169"/>
-      <c r="CB12" s="169" t="s">
+      <c r="BZ12" s="161"/>
+      <c r="CA12" s="161"/>
+      <c r="CB12" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="CC12" s="169" t="s">
+      <c r="CC12" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="CD12" s="169"/>
-      <c r="CE12" s="169"/>
-      <c r="CF12" s="169" t="s">
+      <c r="CD12" s="161"/>
+      <c r="CE12" s="161"/>
+      <c r="CF12" s="161" t="s">
         <v>13</v>
       </c>
-      <c r="CG12" s="169" t="s">
+      <c r="CG12" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="CH12" s="169"/>
-      <c r="CI12" s="170"/>
+      <c r="CH12" s="161"/>
+      <c r="CI12" s="162"/>
     </row>
     <row r="13" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="172"/>
-      <c r="B13" s="173"/>
-      <c r="C13" s="173"/>
+      <c r="A13" s="164"/>
+      <c r="B13" s="165"/>
+      <c r="C13" s="165"/>
       <c r="D13" s="14" t="s">
         <v>14</v>
       </c>
@@ -6991,24 +6970,24 @@
       <c r="Q37" s="25"/>
     </row>
     <row r="39" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="174" t="s">
+      <c r="A39" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="174"/>
-      <c r="C39" s="174"/>
-      <c r="D39" s="174"/>
-      <c r="E39" s="174"/>
-      <c r="F39" s="174"/>
-      <c r="G39" s="174"/>
+      <c r="B39" s="166"/>
+      <c r="C39" s="166"/>
+      <c r="D39" s="166"/>
+      <c r="E39" s="166"/>
+      <c r="F39" s="166"/>
+      <c r="G39" s="166"/>
     </row>
     <row r="40" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="174"/>
-      <c r="B40" s="174"/>
-      <c r="C40" s="174"/>
-      <c r="D40" s="174"/>
-      <c r="E40" s="174"/>
-      <c r="F40" s="174"/>
-      <c r="G40" s="174"/>
+      <c r="A40" s="166"/>
+      <c r="B40" s="166"/>
+      <c r="C40" s="166"/>
+      <c r="D40" s="166"/>
+      <c r="E40" s="166"/>
+      <c r="F40" s="166"/>
+      <c r="G40" s="166"/>
     </row>
     <row r="41" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
@@ -7044,150 +7023,150 @@
       <c r="G43" s="11"/>
     </row>
     <row r="45" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="171" t="s">
+      <c r="A45" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="B45" s="169" t="s">
+      <c r="B45" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="169" t="s">
+      <c r="C45" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="D45" s="169"/>
-      <c r="E45" s="169"/>
-      <c r="F45" s="169"/>
-      <c r="G45" s="169"/>
-      <c r="H45" s="169">
+      <c r="D45" s="161"/>
+      <c r="E45" s="161"/>
+      <c r="F45" s="161"/>
+      <c r="G45" s="161"/>
+      <c r="H45" s="161">
         <v>2006</v>
       </c>
-      <c r="I45" s="169"/>
-      <c r="J45" s="169"/>
-      <c r="K45" s="169"/>
-      <c r="L45" s="169">
+      <c r="I45" s="161"/>
+      <c r="J45" s="161"/>
+      <c r="K45" s="161"/>
+      <c r="L45" s="161">
         <v>2007</v>
       </c>
-      <c r="M45" s="169"/>
-      <c r="N45" s="169"/>
-      <c r="O45" s="169"/>
-      <c r="P45" s="169">
+      <c r="M45" s="161"/>
+      <c r="N45" s="161"/>
+      <c r="O45" s="161"/>
+      <c r="P45" s="161">
         <v>2008</v>
       </c>
-      <c r="Q45" s="169"/>
-      <c r="R45" s="169"/>
-      <c r="S45" s="169"/>
-      <c r="T45" s="169">
+      <c r="Q45" s="161"/>
+      <c r="R45" s="161"/>
+      <c r="S45" s="161"/>
+      <c r="T45" s="161">
         <v>2009</v>
       </c>
-      <c r="U45" s="169"/>
-      <c r="V45" s="169"/>
-      <c r="W45" s="169"/>
-      <c r="X45" s="169">
+      <c r="U45" s="161"/>
+      <c r="V45" s="161"/>
+      <c r="W45" s="161"/>
+      <c r="X45" s="161">
         <v>2010</v>
       </c>
-      <c r="Y45" s="169"/>
-      <c r="Z45" s="169"/>
-      <c r="AA45" s="169"/>
-      <c r="AB45" s="169">
+      <c r="Y45" s="161"/>
+      <c r="Z45" s="161"/>
+      <c r="AA45" s="161"/>
+      <c r="AB45" s="161">
         <v>2011</v>
       </c>
-      <c r="AC45" s="169"/>
-      <c r="AD45" s="169"/>
-      <c r="AE45" s="169"/>
-      <c r="AF45" s="169">
+      <c r="AC45" s="161"/>
+      <c r="AD45" s="161"/>
+      <c r="AE45" s="161"/>
+      <c r="AF45" s="161">
         <v>2012</v>
       </c>
-      <c r="AG45" s="169"/>
-      <c r="AH45" s="169"/>
-      <c r="AI45" s="169"/>
-      <c r="AJ45" s="169">
+      <c r="AG45" s="161"/>
+      <c r="AH45" s="161"/>
+      <c r="AI45" s="161"/>
+      <c r="AJ45" s="161">
         <v>2013</v>
       </c>
-      <c r="AK45" s="169"/>
-      <c r="AL45" s="169"/>
-      <c r="AM45" s="169"/>
-      <c r="AN45" s="169">
+      <c r="AK45" s="161"/>
+      <c r="AL45" s="161"/>
+      <c r="AM45" s="161"/>
+      <c r="AN45" s="161">
         <v>2014</v>
       </c>
-      <c r="AO45" s="169"/>
-      <c r="AP45" s="169"/>
-      <c r="AQ45" s="169"/>
-      <c r="AR45" s="169">
+      <c r="AO45" s="161"/>
+      <c r="AP45" s="161"/>
+      <c r="AQ45" s="161"/>
+      <c r="AR45" s="161">
         <v>2015</v>
       </c>
-      <c r="AS45" s="169"/>
-      <c r="AT45" s="169"/>
-      <c r="AU45" s="169"/>
-      <c r="AV45" s="169">
+      <c r="AS45" s="161"/>
+      <c r="AT45" s="161"/>
+      <c r="AU45" s="161"/>
+      <c r="AV45" s="161">
         <v>2016</v>
       </c>
-      <c r="AW45" s="169"/>
-      <c r="AX45" s="169"/>
-      <c r="AY45" s="169"/>
-      <c r="AZ45" s="169">
+      <c r="AW45" s="161"/>
+      <c r="AX45" s="161"/>
+      <c r="AY45" s="161"/>
+      <c r="AZ45" s="161">
         <v>2017</v>
       </c>
-      <c r="BA45" s="169"/>
-      <c r="BB45" s="169"/>
-      <c r="BC45" s="169"/>
-      <c r="BD45" s="169">
+      <c r="BA45" s="161"/>
+      <c r="BB45" s="161"/>
+      <c r="BC45" s="161"/>
+      <c r="BD45" s="161">
         <v>2018</v>
       </c>
-      <c r="BE45" s="169"/>
-      <c r="BF45" s="169"/>
-      <c r="BG45" s="169"/>
-      <c r="BH45" s="169">
+      <c r="BE45" s="161"/>
+      <c r="BF45" s="161"/>
+      <c r="BG45" s="161"/>
+      <c r="BH45" s="161">
         <v>2019</v>
       </c>
-      <c r="BI45" s="169"/>
-      <c r="BJ45" s="169"/>
-      <c r="BK45" s="169"/>
-      <c r="BL45" s="169">
+      <c r="BI45" s="161"/>
+      <c r="BJ45" s="161"/>
+      <c r="BK45" s="161"/>
+      <c r="BL45" s="161">
         <v>2020</v>
       </c>
-      <c r="BM45" s="169"/>
-      <c r="BN45" s="169"/>
-      <c r="BO45" s="169"/>
-      <c r="BP45" s="169">
+      <c r="BM45" s="161"/>
+      <c r="BN45" s="161"/>
+      <c r="BO45" s="161"/>
+      <c r="BP45" s="161">
         <v>2021</v>
       </c>
-      <c r="BQ45" s="169"/>
-      <c r="BR45" s="169"/>
-      <c r="BS45" s="169"/>
-      <c r="BT45" s="169">
+      <c r="BQ45" s="161"/>
+      <c r="BR45" s="161"/>
+      <c r="BS45" s="161"/>
+      <c r="BT45" s="161">
         <v>2022</v>
       </c>
-      <c r="BU45" s="169"/>
-      <c r="BV45" s="169"/>
-      <c r="BW45" s="169"/>
-      <c r="BX45" s="169">
+      <c r="BU45" s="161"/>
+      <c r="BV45" s="161"/>
+      <c r="BW45" s="161"/>
+      <c r="BX45" s="161">
         <v>2023</v>
       </c>
-      <c r="BY45" s="169" t="s">
+      <c r="BY45" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="BZ45" s="169"/>
-      <c r="CA45" s="169"/>
-      <c r="CB45" s="169" t="s">
+      <c r="BZ45" s="161"/>
+      <c r="CA45" s="161"/>
+      <c r="CB45" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="CC45" s="169" t="s">
+      <c r="CC45" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="CD45" s="169"/>
-      <c r="CE45" s="169"/>
-      <c r="CF45" s="169" t="s">
+      <c r="CD45" s="161"/>
+      <c r="CE45" s="161"/>
+      <c r="CF45" s="161" t="s">
         <v>13</v>
       </c>
-      <c r="CG45" s="169" t="s">
+      <c r="CG45" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="CH45" s="169"/>
-      <c r="CI45" s="170"/>
+      <c r="CH45" s="161"/>
+      <c r="CI45" s="162"/>
     </row>
     <row r="46" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="172"/>
-      <c r="B46" s="173"/>
-      <c r="C46" s="173"/>
+      <c r="A46" s="164"/>
+      <c r="B46" s="165"/>
+      <c r="C46" s="165"/>
       <c r="D46" s="14"/>
       <c r="E46" s="14"/>
       <c r="F46" s="14"/>
@@ -11321,24 +11300,24 @@
       <c r="P68" s="78"/>
     </row>
     <row r="72" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="174" t="s">
+      <c r="A72" s="166" t="s">
         <v>0</v>
       </c>
-      <c r="B72" s="174"/>
-      <c r="C72" s="174"/>
-      <c r="D72" s="174"/>
-      <c r="E72" s="174"/>
-      <c r="F72" s="174"/>
-      <c r="G72" s="174"/>
+      <c r="B72" s="166"/>
+      <c r="C72" s="166"/>
+      <c r="D72" s="166"/>
+      <c r="E72" s="166"/>
+      <c r="F72" s="166"/>
+      <c r="G72" s="166"/>
     </row>
     <row r="73" spans="1:87" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="174"/>
-      <c r="B73" s="174"/>
-      <c r="C73" s="174"/>
-      <c r="D73" s="174"/>
-      <c r="E73" s="174"/>
-      <c r="F73" s="174"/>
-      <c r="G73" s="174"/>
+      <c r="A73" s="166"/>
+      <c r="B73" s="166"/>
+      <c r="C73" s="166"/>
+      <c r="D73" s="166"/>
+      <c r="E73" s="166"/>
+      <c r="F73" s="166"/>
+      <c r="G73" s="166"/>
     </row>
     <row r="74" spans="1:87" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="5" t="s">
@@ -11380,150 +11359,150 @@
       <c r="K77" s="79"/>
     </row>
     <row r="78" spans="1:87" s="13" customFormat="1" ht="36.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="171" t="s">
+      <c r="A78" s="163" t="s">
         <v>8</v>
       </c>
-      <c r="B78" s="169" t="s">
+      <c r="B78" s="161" t="s">
         <v>9</v>
       </c>
-      <c r="C78" s="169" t="s">
+      <c r="C78" s="161" t="s">
         <v>10</v>
       </c>
-      <c r="D78" s="169"/>
-      <c r="E78" s="169"/>
-      <c r="F78" s="169"/>
-      <c r="G78" s="169"/>
-      <c r="H78" s="169">
+      <c r="D78" s="161"/>
+      <c r="E78" s="161"/>
+      <c r="F78" s="161"/>
+      <c r="G78" s="161"/>
+      <c r="H78" s="161">
         <v>2006</v>
       </c>
-      <c r="I78" s="169"/>
-      <c r="J78" s="169"/>
-      <c r="K78" s="169"/>
-      <c r="L78" s="169">
+      <c r="I78" s="161"/>
+      <c r="J78" s="161"/>
+      <c r="K78" s="161"/>
+      <c r="L78" s="161">
         <v>2007</v>
       </c>
-      <c r="M78" s="169"/>
-      <c r="N78" s="169"/>
-      <c r="O78" s="169"/>
-      <c r="P78" s="169">
+      <c r="M78" s="161"/>
+      <c r="N78" s="161"/>
+      <c r="O78" s="161"/>
+      <c r="P78" s="161">
         <v>2008</v>
       </c>
-      <c r="Q78" s="169"/>
-      <c r="R78" s="169"/>
-      <c r="S78" s="169"/>
-      <c r="T78" s="169">
+      <c r="Q78" s="161"/>
+      <c r="R78" s="161"/>
+      <c r="S78" s="161"/>
+      <c r="T78" s="161">
         <v>2009</v>
       </c>
-      <c r="U78" s="169"/>
-      <c r="V78" s="169"/>
-      <c r="W78" s="169"/>
-      <c r="X78" s="169">
+      <c r="U78" s="161"/>
+      <c r="V78" s="161"/>
+      <c r="W78" s="161"/>
+      <c r="X78" s="161">
         <v>2010</v>
       </c>
-      <c r="Y78" s="169"/>
-      <c r="Z78" s="169"/>
-      <c r="AA78" s="169"/>
-      <c r="AB78" s="169">
+      <c r="Y78" s="161"/>
+      <c r="Z78" s="161"/>
+      <c r="AA78" s="161"/>
+      <c r="AB78" s="161">
         <v>2011</v>
       </c>
-      <c r="AC78" s="169"/>
-      <c r="AD78" s="169"/>
-      <c r="AE78" s="169"/>
-      <c r="AF78" s="169">
+      <c r="AC78" s="161"/>
+      <c r="AD78" s="161"/>
+      <c r="AE78" s="161"/>
+      <c r="AF78" s="161">
         <v>2012</v>
       </c>
-      <c r="AG78" s="169"/>
-      <c r="AH78" s="169"/>
-      <c r="AI78" s="169"/>
-      <c r="AJ78" s="169">
+      <c r="AG78" s="161"/>
+      <c r="AH78" s="161"/>
+      <c r="AI78" s="161"/>
+      <c r="AJ78" s="161">
         <v>2013</v>
       </c>
-      <c r="AK78" s="169"/>
-      <c r="AL78" s="169"/>
-      <c r="AM78" s="169"/>
-      <c r="AN78" s="169">
+      <c r="AK78" s="161"/>
+      <c r="AL78" s="161"/>
+      <c r="AM78" s="161"/>
+      <c r="AN78" s="161">
         <v>2014</v>
       </c>
-      <c r="AO78" s="169"/>
-      <c r="AP78" s="169"/>
-      <c r="AQ78" s="169"/>
-      <c r="AR78" s="169">
+      <c r="AO78" s="161"/>
+      <c r="AP78" s="161"/>
+      <c r="AQ78" s="161"/>
+      <c r="AR78" s="161">
         <v>2015</v>
       </c>
-      <c r="AS78" s="169"/>
-      <c r="AT78" s="169"/>
-      <c r="AU78" s="169"/>
-      <c r="AV78" s="169">
+      <c r="AS78" s="161"/>
+      <c r="AT78" s="161"/>
+      <c r="AU78" s="161"/>
+      <c r="AV78" s="161">
         <v>2016</v>
       </c>
-      <c r="AW78" s="169"/>
-      <c r="AX78" s="169"/>
-      <c r="AY78" s="169"/>
-      <c r="AZ78" s="169">
+      <c r="AW78" s="161"/>
+      <c r="AX78" s="161"/>
+      <c r="AY78" s="161"/>
+      <c r="AZ78" s="161">
         <v>2017</v>
       </c>
-      <c r="BA78" s="169"/>
-      <c r="BB78" s="169"/>
-      <c r="BC78" s="169"/>
-      <c r="BD78" s="169">
+      <c r="BA78" s="161"/>
+      <c r="BB78" s="161"/>
+      <c r="BC78" s="161"/>
+      <c r="BD78" s="161">
         <v>2018</v>
       </c>
-      <c r="BE78" s="169"/>
-      <c r="BF78" s="169"/>
-      <c r="BG78" s="169"/>
-      <c r="BH78" s="169">
+      <c r="BE78" s="161"/>
+      <c r="BF78" s="161"/>
+      <c r="BG78" s="161"/>
+      <c r="BH78" s="161">
         <v>2019</v>
       </c>
-      <c r="BI78" s="169"/>
-      <c r="BJ78" s="169"/>
-      <c r="BK78" s="169"/>
-      <c r="BL78" s="169">
+      <c r="BI78" s="161"/>
+      <c r="BJ78" s="161"/>
+      <c r="BK78" s="161"/>
+      <c r="BL78" s="161">
         <v>2020</v>
       </c>
-      <c r="BM78" s="169"/>
-      <c r="BN78" s="169"/>
-      <c r="BO78" s="169"/>
-      <c r="BP78" s="169">
+      <c r="BM78" s="161"/>
+      <c r="BN78" s="161"/>
+      <c r="BO78" s="161"/>
+      <c r="BP78" s="161">
         <v>2021</v>
       </c>
-      <c r="BQ78" s="169"/>
-      <c r="BR78" s="169"/>
-      <c r="BS78" s="169"/>
-      <c r="BT78" s="169">
+      <c r="BQ78" s="161"/>
+      <c r="BR78" s="161"/>
+      <c r="BS78" s="161"/>
+      <c r="BT78" s="161">
         <v>2022</v>
       </c>
-      <c r="BU78" s="169"/>
-      <c r="BV78" s="169"/>
-      <c r="BW78" s="169"/>
-      <c r="BX78" s="169">
+      <c r="BU78" s="161"/>
+      <c r="BV78" s="161"/>
+      <c r="BW78" s="161"/>
+      <c r="BX78" s="161">
         <v>2023</v>
       </c>
-      <c r="BY78" s="169" t="s">
+      <c r="BY78" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="BZ78" s="169"/>
-      <c r="CA78" s="169"/>
-      <c r="CB78" s="169" t="s">
+      <c r="BZ78" s="161"/>
+      <c r="CA78" s="161"/>
+      <c r="CB78" s="161" t="s">
         <v>12</v>
       </c>
-      <c r="CC78" s="169" t="s">
+      <c r="CC78" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="CD78" s="169"/>
-      <c r="CE78" s="169"/>
-      <c r="CF78" s="169" t="s">
+      <c r="CD78" s="161"/>
+      <c r="CE78" s="161"/>
+      <c r="CF78" s="161" t="s">
         <v>13</v>
       </c>
-      <c r="CG78" s="169" t="s">
+      <c r="CG78" s="161" t="s">
         <v>11</v>
       </c>
-      <c r="CH78" s="169"/>
-      <c r="CI78" s="170"/>
+      <c r="CH78" s="161"/>
+      <c r="CI78" s="162"/>
     </row>
     <row r="79" spans="1:87" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="172"/>
-      <c r="B79" s="173"/>
-      <c r="C79" s="173"/>
+      <c r="A79" s="164"/>
+      <c r="B79" s="165"/>
+      <c r="C79" s="165"/>
       <c r="D79" s="14"/>
       <c r="E79" s="14"/>
       <c r="F79" s="14"/>
@@ -15967,3038 +15946,2991 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DD938B3-C5B5-4D9D-B2F4-3C2CC8354395}">
-  <dimension ref="A1:AB38"/>
+  <dimension ref="A1:AA38"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="66.5703125" style="142" customWidth="1"/>
-    <col min="3" max="22" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="23" max="28" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.85546875" style="142" customWidth="1"/>
+    <col min="2" max="21" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="27" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="A1" s="177" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="169" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="169"/>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="W3" s="180" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="177"/>
-    </row>
-    <row r="2" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="177"/>
-      <c r="B2" s="177"/>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="X3" s="188" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y3" s="189"/>
-      <c r="Z3" s="189"/>
-      <c r="AA3" s="189"/>
-      <c r="AB3" s="190"/>
-    </row>
-    <row r="4" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="X4" s="191"/>
-      <c r="Y4" s="192"/>
-      <c r="Z4" s="192"/>
-      <c r="AA4" s="192"/>
-      <c r="AB4" s="193"/>
-    </row>
-    <row r="5" spans="1:28" s="144" customFormat="1" ht="38.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="145" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="150" t="s">
+      <c r="X3" s="181"/>
+      <c r="Y3" s="181"/>
+      <c r="Z3" s="181"/>
+      <c r="AA3" s="182"/>
+    </row>
+    <row r="4" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="W4" s="183"/>
+      <c r="X4" s="184"/>
+      <c r="Y4" s="184"/>
+      <c r="Z4" s="184"/>
+      <c r="AA4" s="185"/>
+    </row>
+    <row r="5" spans="1:27" s="144" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="256" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="161">
+      <c r="B5" s="157">
         <v>2005</v>
       </c>
-      <c r="D5" s="158">
+      <c r="C5" s="156">
         <v>2006</v>
       </c>
-      <c r="E5" s="158">
+      <c r="D5" s="156">
         <v>2007</v>
       </c>
-      <c r="F5" s="158">
+      <c r="E5" s="156">
         <v>2008</v>
       </c>
-      <c r="G5" s="158">
+      <c r="F5" s="156">
         <v>2009</v>
       </c>
-      <c r="H5" s="158">
+      <c r="G5" s="156">
         <v>2010</v>
       </c>
-      <c r="I5" s="158">
+      <c r="H5" s="156">
         <v>2011</v>
       </c>
-      <c r="J5" s="158">
+      <c r="I5" s="156">
         <v>2012</v>
       </c>
-      <c r="K5" s="158">
+      <c r="J5" s="156">
         <v>2013</v>
       </c>
-      <c r="L5" s="158">
+      <c r="K5" s="156">
         <v>2014</v>
       </c>
-      <c r="M5" s="158">
+      <c r="L5" s="156">
         <v>2015</v>
       </c>
-      <c r="N5" s="158">
+      <c r="M5" s="156">
         <v>2016</v>
       </c>
-      <c r="O5" s="158">
+      <c r="N5" s="156">
         <v>2017</v>
       </c>
-      <c r="P5" s="158">
+      <c r="O5" s="156">
         <v>2018</v>
       </c>
-      <c r="Q5" s="158">
+      <c r="P5" s="156">
         <v>2019</v>
       </c>
-      <c r="R5" s="158">
+      <c r="Q5" s="156">
         <v>2020</v>
       </c>
-      <c r="S5" s="158">
+      <c r="R5" s="156">
         <v>2021</v>
       </c>
-      <c r="T5" s="158">
+      <c r="S5" s="156">
         <v>2022</v>
       </c>
-      <c r="U5" s="158">
+      <c r="T5" s="156">
         <v>2023</v>
       </c>
-      <c r="V5" s="158">
+      <c r="U5" s="156">
         <v>2024</v>
       </c>
-      <c r="W5" s="158">
+      <c r="V5" s="156">
         <v>2025</v>
       </c>
-      <c r="X5" s="158">
+      <c r="W5" s="156">
         <v>2026</v>
       </c>
-      <c r="Y5" s="158">
+      <c r="X5" s="156">
         <v>2027</v>
       </c>
-      <c r="Z5" s="158">
+      <c r="Y5" s="156">
         <v>2028</v>
       </c>
-      <c r="AA5" s="158">
+      <c r="Z5" s="156">
         <v>2029</v>
       </c>
-      <c r="AB5" s="158">
+      <c r="AA5" s="156">
         <v>2030</v>
       </c>
     </row>
-    <row r="6" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="146" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="159" t="s">
+    <row r="6" spans="1:27" s="148" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="224" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="153">
+      <c r="B6" s="151">
         <v>37909</v>
       </c>
-      <c r="D6" s="157">
+      <c r="C6" s="155">
         <v>38717</v>
       </c>
-      <c r="E6" s="146">
+      <c r="D6" s="145">
         <v>40239</v>
       </c>
-      <c r="F6" s="146">
+      <c r="E6" s="145">
         <v>39914.999999999993</v>
       </c>
-      <c r="G6" s="146">
+      <c r="F6" s="145">
         <v>39822</v>
       </c>
-      <c r="H6" s="146">
+      <c r="G6" s="145">
         <v>39943</v>
       </c>
-      <c r="I6" s="146">
+      <c r="H6" s="145">
         <v>40706.000000000007</v>
       </c>
-      <c r="J6" s="146">
+      <c r="I6" s="145">
         <v>41725</v>
       </c>
-      <c r="K6" s="146">
+      <c r="J6" s="145">
         <v>44834.999999999993</v>
       </c>
-      <c r="L6" s="146">
+      <c r="K6" s="145">
         <v>46140</v>
       </c>
-      <c r="M6" s="146">
+      <c r="L6" s="145">
         <v>48124</v>
       </c>
-      <c r="N6" s="146">
+      <c r="M6" s="145">
         <v>49441</v>
       </c>
-      <c r="O6" s="146">
+      <c r="N6" s="145">
         <v>52198</v>
       </c>
-      <c r="P6" s="146">
+      <c r="O6" s="145">
         <v>53030</v>
       </c>
-      <c r="Q6" s="146">
+      <c r="P6" s="145">
         <v>54471</v>
       </c>
-      <c r="R6" s="146">
+      <c r="Q6" s="145">
         <v>55539</v>
       </c>
-      <c r="S6" s="156">
+      <c r="R6" s="154">
         <v>57968</v>
       </c>
-      <c r="T6" s="146">
+      <c r="S6" s="145">
         <v>57442</v>
       </c>
-      <c r="U6" s="157">
+      <c r="T6" s="155">
         <v>58389</v>
       </c>
-      <c r="V6" s="146">
+      <c r="U6" s="145">
         <v>61966.999999999985</v>
       </c>
-      <c r="W6" s="146">
+      <c r="V6" s="145">
         <v>63888.120954066384</v>
       </c>
-      <c r="X6" s="146">
-        <f>W6*(1+X26)</f>
+      <c r="W6" s="145">
+        <f>V6*(1+W26)</f>
         <v>66835.950434092651</v>
       </c>
-      <c r="Y6" s="146">
-        <f t="shared" ref="Y6:AB6" si="0">X6*(1+Y26)</f>
+      <c r="X6" s="145">
+        <f t="shared" ref="X6:AA6" si="0">W6*(1+X26)</f>
         <v>69413.907192983272</v>
       </c>
-      <c r="Z6" s="146">
+      <c r="Y6" s="145">
         <f t="shared" si="0"/>
         <v>72353.999278498406</v>
       </c>
-      <c r="AA6" s="146">
+      <c r="Z6" s="145">
         <f t="shared" si="0"/>
         <v>75281.708358124772</v>
       </c>
-      <c r="AB6" s="146">
+      <c r="AA6" s="145">
         <f t="shared" si="0"/>
         <v>78399.110033224424</v>
       </c>
     </row>
-    <row r="7" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="147" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="160" t="s">
+    <row r="7" spans="1:27" s="148" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="223" t="s">
         <v>21</v>
       </c>
-      <c r="C7" s="147">
+      <c r="B7" s="146">
         <v>27430</v>
       </c>
-      <c r="D7" s="155">
+      <c r="C7" s="153">
         <v>28059</v>
       </c>
-      <c r="E7" s="147">
+      <c r="D7" s="146">
         <v>28434</v>
       </c>
-      <c r="F7" s="147">
+      <c r="E7" s="146">
         <v>31101</v>
       </c>
-      <c r="G7" s="147">
+      <c r="F7" s="146">
         <v>34659</v>
       </c>
-      <c r="H7" s="147">
+      <c r="G7" s="146">
         <v>38427</v>
       </c>
-      <c r="I7" s="147">
+      <c r="H7" s="146">
         <v>43974</v>
       </c>
-      <c r="J7" s="147">
+      <c r="I7" s="146">
         <v>46335</v>
       </c>
-      <c r="K7" s="147">
+      <c r="J7" s="146">
         <v>48794</v>
       </c>
-      <c r="L7" s="147">
+      <c r="K7" s="146">
         <v>48136</v>
       </c>
-      <c r="M7" s="147">
+      <c r="L7" s="146">
         <v>47626.999999999993</v>
       </c>
-      <c r="N7" s="147">
+      <c r="M7" s="146">
         <v>46253</v>
       </c>
-      <c r="O7" s="147">
+      <c r="N7" s="146">
         <v>43592</v>
       </c>
-      <c r="P7" s="147">
+      <c r="O7" s="146">
         <v>42868.000000000007</v>
       </c>
-      <c r="Q7" s="147">
+      <c r="P7" s="146">
         <v>43692.999999999993</v>
       </c>
-      <c r="R7" s="147">
+      <c r="Q7" s="146">
         <v>37056.000000000007</v>
       </c>
-      <c r="S7" s="154">
+      <c r="R7" s="152">
         <v>36980</v>
       </c>
-      <c r="T7" s="147">
+      <c r="S7" s="146">
         <v>37518</v>
       </c>
-      <c r="U7" s="155">
+      <c r="T7" s="153">
         <v>38480.999999999993</v>
       </c>
-      <c r="V7" s="147">
+      <c r="U7" s="146">
         <v>37168</v>
       </c>
-      <c r="W7" s="147">
+      <c r="V7" s="146">
         <v>34868.277064090362</v>
       </c>
-      <c r="X7" s="147">
-        <f t="shared" ref="X7:AB18" si="1">W7*(1+X27)</f>
+      <c r="W7" s="146">
+        <f t="shared" ref="W7:AA18" si="1">V7*(1+W27)</f>
         <v>33194.696199246107</v>
       </c>
-      <c r="Y7" s="147">
+      <c r="X7" s="146">
         <f t="shared" si="1"/>
         <v>31371.129496069167</v>
       </c>
-      <c r="Z7" s="147">
+      <c r="Y7" s="146">
         <f t="shared" si="1"/>
         <v>29756.571677465465</v>
       </c>
-      <c r="AA7" s="147">
+      <c r="Z7" s="146">
         <f t="shared" si="1"/>
         <v>28173.494640273962</v>
       </c>
-      <c r="AB7" s="147">
+      <c r="AA7" s="146">
         <f t="shared" si="1"/>
         <v>26699.073103066705</v>
       </c>
     </row>
-    <row r="8" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="146" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="159" t="s">
+    <row r="8" spans="1:27" s="148" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="224" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="146">
+      <c r="B8" s="145">
         <v>77252</v>
       </c>
-      <c r="D8" s="157">
+      <c r="C8" s="155">
         <v>82885</v>
       </c>
-      <c r="E8" s="146">
+      <c r="D8" s="145">
         <v>89320</v>
       </c>
-      <c r="F8" s="146">
+      <c r="E8" s="145">
         <v>89639</v>
       </c>
-      <c r="G8" s="146">
+      <c r="F8" s="145">
         <v>86354</v>
       </c>
-      <c r="H8" s="146">
+      <c r="G8" s="145">
         <v>87979.999999999985</v>
       </c>
-      <c r="I8" s="146">
+      <c r="H8" s="145">
         <v>92896</v>
       </c>
-      <c r="J8" s="146">
+      <c r="I8" s="145">
         <v>93666.999999999985</v>
       </c>
-      <c r="K8" s="146">
+      <c r="J8" s="145">
         <v>95081</v>
       </c>
-      <c r="L8" s="146">
+      <c r="K8" s="145">
         <v>97828.999999999985</v>
       </c>
-      <c r="M8" s="146">
+      <c r="L8" s="145">
         <v>99789</v>
       </c>
-      <c r="N8" s="146">
+      <c r="M8" s="145">
         <v>103005.99999999999</v>
       </c>
-      <c r="O8" s="146">
+      <c r="N8" s="145">
         <v>101135</v>
       </c>
-      <c r="P8" s="146">
+      <c r="O8" s="145">
         <v>102626.99999999997</v>
       </c>
-      <c r="Q8" s="146">
+      <c r="P8" s="145">
         <v>103860.00000000001</v>
       </c>
-      <c r="R8" s="146">
+      <c r="Q8" s="145">
         <v>94254</v>
       </c>
-      <c r="S8" s="156">
+      <c r="R8" s="154">
         <v>107066</v>
       </c>
-      <c r="T8" s="146">
+      <c r="S8" s="145">
         <v>115801.99999999999</v>
       </c>
-      <c r="U8" s="157">
+      <c r="T8" s="155">
         <v>113925.00000000001</v>
       </c>
-      <c r="V8" s="146">
+      <c r="U8" s="145">
         <v>111003</v>
       </c>
-      <c r="W8" s="146">
+      <c r="V8" s="145">
         <v>113056.56188430529</v>
       </c>
-      <c r="X8" s="146">
+      <c r="W8" s="145">
         <f t="shared" si="1"/>
         <v>112652.47538000907</v>
       </c>
-      <c r="Y8" s="146">
+      <c r="X8" s="145">
         <f t="shared" si="1"/>
         <v>113493.19290724187</v>
       </c>
-      <c r="Z8" s="146">
+      <c r="Y8" s="145">
         <f t="shared" si="1"/>
         <v>113713.86522389682</v>
       </c>
-      <c r="AA8" s="146">
+      <c r="Z8" s="145">
         <f t="shared" si="1"/>
         <v>114248.73521872904</v>
       </c>
-      <c r="AB8" s="146">
+      <c r="AA8" s="145">
         <f t="shared" si="1"/>
         <v>114628.49881999166</v>
       </c>
     </row>
-    <row r="9" spans="1:28" s="149" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="147" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="160" t="s">
+    <row r="9" spans="1:27" s="148" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="223" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="147">
+      <c r="B9" s="146">
         <v>18685</v>
       </c>
-      <c r="D9" s="155">
+      <c r="C9" s="153">
         <v>19679</v>
       </c>
-      <c r="E9" s="147">
+      <c r="D9" s="146">
         <v>20511</v>
       </c>
-      <c r="F9" s="147">
+      <c r="E9" s="146">
         <v>20619</v>
       </c>
-      <c r="G9" s="147">
+      <c r="F9" s="146">
         <v>21113.000000000004</v>
       </c>
-      <c r="H9" s="147">
+      <c r="G9" s="146">
         <v>21935.000000000004</v>
       </c>
-      <c r="I9" s="147">
+      <c r="H9" s="146">
         <v>22608</v>
       </c>
-      <c r="J9" s="147">
+      <c r="I9" s="146">
         <v>23094</v>
       </c>
-      <c r="K9" s="147">
+      <c r="J9" s="146">
         <v>23950</v>
       </c>
-      <c r="L9" s="147">
+      <c r="K9" s="146">
         <v>24772.999999999996</v>
       </c>
-      <c r="M9" s="147">
+      <c r="L9" s="146">
         <v>24598.999999999993</v>
       </c>
-      <c r="N9" s="147">
+      <c r="M9" s="146">
         <v>24597</v>
       </c>
-      <c r="O9" s="147">
+      <c r="N9" s="146">
         <v>25306.999999999996</v>
       </c>
-      <c r="P9" s="147">
+      <c r="O9" s="146">
         <v>25952.000000000004</v>
       </c>
-      <c r="Q9" s="147">
+      <c r="P9" s="146">
         <v>26606.000000000004</v>
       </c>
-      <c r="R9" s="147">
+      <c r="Q9" s="146">
         <v>25587</v>
       </c>
-      <c r="S9" s="154">
+      <c r="R9" s="152">
         <v>27079</v>
       </c>
-      <c r="T9" s="147">
+      <c r="S9" s="146">
         <v>28327</v>
       </c>
-      <c r="U9" s="155">
+      <c r="T9" s="153">
         <v>29221</v>
       </c>
-      <c r="V9" s="147">
+      <c r="U9" s="146">
         <v>29948</v>
       </c>
-      <c r="W9" s="147">
+      <c r="V9" s="146">
         <v>30289.602434291664</v>
       </c>
-      <c r="X9" s="147">
+      <c r="W9" s="146">
         <f t="shared" si="1"/>
         <v>30839.144975163603</v>
       </c>
-      <c r="Y9" s="147">
+      <c r="X9" s="146">
         <f t="shared" si="1"/>
         <v>31294.785053431708</v>
       </c>
-      <c r="Z9" s="147">
+      <c r="Y9" s="146">
         <f t="shared" si="1"/>
         <v>31809.860828502598</v>
       </c>
-      <c r="AA9" s="147">
+      <c r="Z9" s="146">
         <f t="shared" si="1"/>
         <v>32306.628562273097</v>
       </c>
-      <c r="AB9" s="147">
+      <c r="AA9" s="146">
         <f t="shared" si="1"/>
         <v>32824.756157790674</v>
       </c>
     </row>
-    <row r="10" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="146" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="159" t="s">
+    <row r="10" spans="1:27" s="148" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="224" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="146">
+      <c r="B10" s="145">
         <v>29808</v>
       </c>
-      <c r="D10" s="157">
+      <c r="C10" s="155">
         <v>33427</v>
       </c>
-      <c r="E10" s="146">
+      <c r="D10" s="145">
         <v>35747</v>
       </c>
-      <c r="F10" s="146">
+      <c r="E10" s="145">
         <v>39289</v>
       </c>
-      <c r="G10" s="146">
+      <c r="F10" s="145">
         <v>40316</v>
       </c>
-      <c r="H10" s="146">
+      <c r="G10" s="145">
         <v>40048.000000000007</v>
       </c>
-      <c r="I10" s="146">
+      <c r="H10" s="145">
         <v>42536</v>
       </c>
-      <c r="J10" s="146">
+      <c r="I10" s="145">
         <v>45051</v>
       </c>
-      <c r="K10" s="146">
+      <c r="J10" s="145">
         <v>50131</v>
       </c>
-      <c r="L10" s="146">
+      <c r="K10" s="145">
         <v>54602</v>
       </c>
-      <c r="M10" s="146">
+      <c r="L10" s="145">
         <v>58042</v>
       </c>
-      <c r="N10" s="146">
+      <c r="M10" s="145">
         <v>60124.999999999993</v>
       </c>
-      <c r="O10" s="146">
+      <c r="N10" s="145">
         <v>58907</v>
       </c>
-      <c r="P10" s="146">
+      <c r="O10" s="145">
         <v>58156</v>
       </c>
-      <c r="Q10" s="146">
+      <c r="P10" s="145">
         <v>55893</v>
       </c>
-      <c r="R10" s="146">
+      <c r="Q10" s="145">
         <v>39359</v>
       </c>
-      <c r="S10" s="156">
+      <c r="R10" s="154">
         <v>41039</v>
       </c>
-      <c r="T10" s="146">
+      <c r="S10" s="145">
         <v>43765</v>
       </c>
-      <c r="U10" s="157">
+      <c r="T10" s="155">
         <v>42412</v>
       </c>
-      <c r="V10" s="146">
+      <c r="U10" s="145">
         <v>42448</v>
       </c>
-      <c r="W10" s="146">
+      <c r="V10" s="145">
         <v>41273.053068554225</v>
       </c>
-      <c r="X10" s="146">
+      <c r="W10" s="145">
         <f t="shared" si="1"/>
         <v>40719.357300236836</v>
       </c>
-      <c r="Y10" s="146">
+      <c r="X10" s="145">
         <f t="shared" si="1"/>
         <v>39882.674119692369</v>
       </c>
-      <c r="Z10" s="146">
+      <c r="Y10" s="145">
         <f t="shared" si="1"/>
         <v>39205.406807516934</v>
       </c>
-      <c r="AA10" s="146">
+      <c r="Z10" s="145">
         <f t="shared" si="1"/>
         <v>38469.736055404705</v>
       </c>
-      <c r="AB10" s="146">
+      <c r="AA10" s="145">
         <f t="shared" si="1"/>
         <v>37782.166176811588</v>
       </c>
     </row>
-    <row r="11" spans="1:28" s="149" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="147" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="160" t="s">
+    <row r="11" spans="1:27" s="148" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="223" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="147">
+      <c r="B11" s="146">
         <v>85427</v>
       </c>
-      <c r="D11" s="155">
+      <c r="C11" s="153">
         <v>91926</v>
       </c>
-      <c r="E11" s="147">
+      <c r="D11" s="146">
         <v>99342.999999999985</v>
       </c>
-      <c r="F11" s="147">
+      <c r="E11" s="146">
         <v>102346</v>
       </c>
-      <c r="G11" s="147">
+      <c r="F11" s="146">
         <v>102185</v>
       </c>
-      <c r="H11" s="147">
+      <c r="G11" s="146">
         <v>107647</v>
       </c>
-      <c r="I11" s="147">
+      <c r="H11" s="146">
         <v>115063</v>
       </c>
-      <c r="J11" s="147">
+      <c r="I11" s="146">
         <v>119453.00000000001</v>
       </c>
-      <c r="K11" s="147">
+      <c r="J11" s="146">
         <v>125149</v>
       </c>
-      <c r="L11" s="147">
+      <c r="K11" s="146">
         <v>131063</v>
       </c>
-      <c r="M11" s="147">
+      <c r="L11" s="146">
         <v>135429</v>
       </c>
-      <c r="N11" s="147">
+      <c r="M11" s="146">
         <v>139066</v>
       </c>
-      <c r="O11" s="147">
+      <c r="N11" s="146">
         <v>141652</v>
       </c>
-      <c r="P11" s="147">
+      <c r="O11" s="146">
         <v>145438</v>
       </c>
-      <c r="Q11" s="147">
+      <c r="P11" s="146">
         <v>150890</v>
       </c>
-      <c r="R11" s="147">
+      <c r="Q11" s="146">
         <v>130235</v>
       </c>
-      <c r="S11" s="154">
+      <c r="R11" s="152">
         <v>156814.99999999997</v>
       </c>
-      <c r="T11" s="147">
+      <c r="S11" s="146">
         <v>175451</v>
       </c>
-      <c r="U11" s="155">
+      <c r="T11" s="153">
         <v>169067.00000000006</v>
       </c>
-      <c r="V11" s="147">
+      <c r="U11" s="146">
         <v>171151</v>
       </c>
-      <c r="W11" s="147">
+      <c r="V11" s="146">
         <v>179021.7773381015</v>
       </c>
-      <c r="X11" s="147">
+      <c r="W11" s="146">
         <f t="shared" si="1"/>
         <v>184241.49767305734</v>
       </c>
-      <c r="Y11" s="147">
+      <c r="X11" s="146">
         <f t="shared" si="1"/>
         <v>191163.84045685895</v>
       </c>
-      <c r="Z11" s="147">
+      <c r="Y11" s="146">
         <f t="shared" si="1"/>
         <v>197541.92801607211</v>
       </c>
-      <c r="AA11" s="147">
+      <c r="Z11" s="146">
         <f t="shared" si="1"/>
         <v>204548.40671636674</v>
       </c>
-      <c r="AB11" s="147">
+      <c r="AA11" s="146">
         <f t="shared" si="1"/>
         <v>211588.22856841571</v>
       </c>
     </row>
-    <row r="12" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="146" t="s">
-        <v>30</v>
-      </c>
-      <c r="B12" s="159" t="s">
+    <row r="12" spans="1:27" s="148" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="224" t="s">
         <v>31</v>
       </c>
-      <c r="C12" s="146">
+      <c r="B12" s="145">
         <v>12730</v>
       </c>
-      <c r="D12" s="157">
+      <c r="C12" s="155">
         <v>14629</v>
       </c>
-      <c r="E12" s="146">
+      <c r="D12" s="145">
         <v>16761</v>
       </c>
-      <c r="F12" s="146">
+      <c r="E12" s="145">
         <v>17120</v>
       </c>
-      <c r="G12" s="146">
+      <c r="F12" s="145">
         <v>15669</v>
       </c>
-      <c r="H12" s="146">
+      <c r="G12" s="145">
         <v>18256</v>
       </c>
-      <c r="I12" s="146">
+      <c r="H12" s="145">
         <v>20153</v>
       </c>
-      <c r="J12" s="146">
+      <c r="I12" s="145">
         <v>20415</v>
       </c>
-      <c r="K12" s="146">
+      <c r="J12" s="145">
         <v>22218</v>
       </c>
-      <c r="L12" s="146">
+      <c r="K12" s="145">
         <v>23654.000000000004</v>
       </c>
-      <c r="M12" s="146">
+      <c r="L12" s="145">
         <v>23961.000000000004</v>
       </c>
-      <c r="N12" s="146">
+      <c r="M12" s="145">
         <v>23803.999999999996</v>
       </c>
-      <c r="O12" s="146">
+      <c r="N12" s="145">
         <v>23758</v>
       </c>
-      <c r="P12" s="146">
+      <c r="O12" s="145">
         <v>24595</v>
       </c>
-      <c r="Q12" s="146">
+      <c r="P12" s="145">
         <v>24820.999999999996</v>
       </c>
-      <c r="R12" s="146">
+      <c r="Q12" s="145">
         <v>24132.999999999996</v>
       </c>
-      <c r="S12" s="156">
+      <c r="R12" s="154">
         <v>27210</v>
       </c>
-      <c r="T12" s="146">
+      <c r="S12" s="145">
         <v>30564</v>
       </c>
-      <c r="U12" s="157">
+      <c r="T12" s="155">
         <v>31034</v>
       </c>
-      <c r="V12" s="146">
+      <c r="U12" s="145">
         <v>30969.000000000004</v>
       </c>
-      <c r="W12" s="146">
+      <c r="V12" s="145">
         <v>31269.035070523441</v>
       </c>
-      <c r="X12" s="146">
+      <c r="W12" s="145">
         <f t="shared" si="1"/>
         <v>31387.759873728442</v>
       </c>
-      <c r="Y12" s="146">
+      <c r="X12" s="145">
         <f t="shared" si="1"/>
         <v>31599.393725413145</v>
       </c>
-      <c r="Z12" s="146">
+      <c r="Y12" s="145">
         <f t="shared" si="1"/>
         <v>31765.913696060685</v>
       </c>
-      <c r="AA12" s="146">
+      <c r="Z12" s="145">
         <f t="shared" si="1"/>
         <v>31956.704226475271</v>
       </c>
-      <c r="AB12" s="146">
+      <c r="AA12" s="145">
         <f t="shared" si="1"/>
         <v>32136.873897564514</v>
       </c>
     </row>
-    <row r="13" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="147" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="160" t="s">
+    <row r="13" spans="1:27" s="148" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="147">
+      <c r="B13" s="146">
         <v>15424</v>
       </c>
-      <c r="D13" s="155">
+      <c r="C13" s="153">
         <v>16440</v>
       </c>
-      <c r="E13" s="147">
+      <c r="D13" s="146">
         <v>18702</v>
       </c>
-      <c r="F13" s="147">
+      <c r="E13" s="146">
         <v>20598</v>
       </c>
-      <c r="G13" s="147">
+      <c r="F13" s="146">
         <v>21315</v>
       </c>
-      <c r="H13" s="147">
+      <c r="G13" s="146">
         <v>22312.000000000004</v>
       </c>
-      <c r="I13" s="147">
+      <c r="H13" s="146">
         <v>24754</v>
       </c>
-      <c r="J13" s="147">
+      <c r="I13" s="146">
         <v>26625.999999999996</v>
       </c>
-      <c r="K13" s="147">
+      <c r="J13" s="146">
         <v>29160</v>
       </c>
-      <c r="L13" s="147">
+      <c r="K13" s="146">
         <v>32139</v>
       </c>
-      <c r="M13" s="147">
+      <c r="L13" s="146">
         <v>34695.999999999993</v>
       </c>
-      <c r="N13" s="147">
+      <c r="M13" s="146">
         <v>35726</v>
       </c>
-      <c r="O13" s="147">
+      <c r="N13" s="146">
         <v>37651</v>
       </c>
-      <c r="P13" s="147">
+      <c r="O13" s="146">
         <v>39057</v>
       </c>
-      <c r="Q13" s="147">
+      <c r="P13" s="146">
         <v>41505.000000000007</v>
       </c>
-      <c r="R13" s="147">
+      <c r="Q13" s="146">
         <v>42433</v>
       </c>
-      <c r="S13" s="154">
+      <c r="R13" s="152">
         <v>44002.999999999993</v>
       </c>
-      <c r="T13" s="147">
+      <c r="S13" s="146">
         <v>46940</v>
       </c>
-      <c r="U13" s="155">
+      <c r="T13" s="153">
         <v>51134.999999999993</v>
       </c>
-      <c r="V13" s="147">
+      <c r="U13" s="146">
         <v>51684.000000000007</v>
       </c>
-      <c r="W13" s="147">
+      <c r="V13" s="146">
         <v>53112.341726684856</v>
       </c>
-      <c r="X13" s="147">
+      <c r="W13" s="146">
         <f t="shared" si="1"/>
         <v>54131.364106798661</v>
       </c>
-      <c r="Y13" s="147">
+      <c r="X13" s="146">
         <f t="shared" si="1"/>
         <v>55398.63946936612</v>
       </c>
-      <c r="Z13" s="147">
+      <c r="Y13" s="146">
         <f t="shared" si="1"/>
         <v>56578.555150443826</v>
       </c>
-      <c r="AA13" s="147">
+      <c r="Z13" s="146">
         <f t="shared" si="1"/>
         <v>57843.361702283335</v>
       </c>
-      <c r="AB13" s="147">
+      <c r="AA13" s="146">
         <f t="shared" si="1"/>
         <v>59105.894744615689</v>
       </c>
     </row>
-    <row r="14" spans="1:28" s="149" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="146" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="159" t="s">
+    <row r="14" spans="1:27" s="148" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="146">
+      <c r="B14" s="145">
         <v>50233</v>
       </c>
-      <c r="D14" s="157">
+      <c r="C14" s="155">
         <v>52265</v>
       </c>
-      <c r="E14" s="146">
+      <c r="D14" s="145">
         <v>54225</v>
       </c>
-      <c r="F14" s="146">
+      <c r="E14" s="145">
         <v>55731</v>
       </c>
-      <c r="G14" s="146">
+      <c r="F14" s="145">
         <v>57866</v>
       </c>
-      <c r="H14" s="146">
+      <c r="G14" s="145">
         <v>59932</v>
       </c>
-      <c r="I14" s="146">
+      <c r="H14" s="145">
         <v>61628</v>
       </c>
-      <c r="J14" s="146">
+      <c r="I14" s="145">
         <v>63579</v>
       </c>
-      <c r="K14" s="146">
+      <c r="J14" s="145">
         <v>65625</v>
       </c>
-      <c r="L14" s="146">
+      <c r="K14" s="145">
         <v>67664</v>
       </c>
-      <c r="M14" s="146">
+      <c r="L14" s="145">
         <v>69824.999999999985</v>
       </c>
-      <c r="N14" s="146">
+      <c r="M14" s="145">
         <v>72289</v>
       </c>
-      <c r="O14" s="146">
+      <c r="N14" s="145">
         <v>74495</v>
       </c>
-      <c r="P14" s="146">
+      <c r="O14" s="145">
         <v>77449</v>
       </c>
-      <c r="Q14" s="146">
+      <c r="P14" s="145">
         <v>79964</v>
       </c>
-      <c r="R14" s="146">
+      <c r="Q14" s="145">
         <v>81118</v>
       </c>
-      <c r="S14" s="156">
+      <c r="R14" s="154">
         <v>83143</v>
       </c>
-      <c r="T14" s="146">
+      <c r="S14" s="145">
         <v>84843</v>
       </c>
-      <c r="U14" s="157">
+      <c r="T14" s="155">
         <v>86413</v>
       </c>
-      <c r="V14" s="146">
+      <c r="U14" s="145">
         <v>88322</v>
       </c>
-      <c r="W14" s="146">
+      <c r="V14" s="145">
         <v>90073.804942443036</v>
       </c>
-      <c r="X14" s="146">
+      <c r="W14" s="145">
         <f t="shared" si="1"/>
         <v>91962.0168139624</v>
       </c>
-      <c r="Y14" s="146">
+      <c r="X14" s="145">
         <f t="shared" si="1"/>
         <v>93837.915048749011</v>
       </c>
-      <c r="Z14" s="146">
+      <c r="Y14" s="145">
         <f t="shared" si="1"/>
         <v>95778.556378827387</v>
       </c>
-      <c r="AA14" s="146">
+      <c r="Z14" s="145">
         <f t="shared" si="1"/>
         <v>97745.819220150268</v>
       </c>
-      <c r="AB14" s="146">
+      <c r="AA14" s="145">
         <f t="shared" si="1"/>
         <v>99760.384054742477</v>
       </c>
     </row>
-    <row r="15" spans="1:28" s="149" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="147" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="160" t="s">
+    <row r="15" spans="1:27" s="148" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="223" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="147">
+      <c r="B15" s="146">
         <v>36057</v>
       </c>
-      <c r="D15" s="155">
+      <c r="C15" s="153">
         <v>38592</v>
       </c>
-      <c r="E15" s="147">
+      <c r="D15" s="146">
         <v>41246</v>
       </c>
-      <c r="F15" s="147">
+      <c r="E15" s="146">
         <v>42799.999999999993</v>
       </c>
-      <c r="G15" s="147">
+      <c r="F15" s="146">
         <v>43998</v>
       </c>
-      <c r="H15" s="147">
+      <c r="G15" s="146">
         <v>45354</v>
       </c>
-      <c r="I15" s="147">
+      <c r="H15" s="146">
         <v>48568</v>
       </c>
-      <c r="J15" s="147">
+      <c r="I15" s="146">
         <v>50907</v>
       </c>
-      <c r="K15" s="147">
+      <c r="J15" s="146">
         <v>53593</v>
       </c>
-      <c r="L15" s="147">
+      <c r="K15" s="146">
         <v>57500</v>
       </c>
-      <c r="M15" s="147">
+      <c r="L15" s="146">
         <v>57392</v>
       </c>
-      <c r="N15" s="147">
+      <c r="M15" s="146">
         <v>55994.999999999993</v>
       </c>
-      <c r="O15" s="147">
+      <c r="N15" s="146">
         <v>56810</v>
       </c>
-      <c r="P15" s="147">
+      <c r="O15" s="146">
         <v>59065.999999999993</v>
       </c>
-      <c r="Q15" s="147">
+      <c r="P15" s="146">
         <v>61102</v>
       </c>
-      <c r="R15" s="147">
+      <c r="Q15" s="146">
         <v>57564</v>
       </c>
-      <c r="S15" s="154">
+      <c r="R15" s="152">
         <v>63167</v>
       </c>
-      <c r="T15" s="147">
+      <c r="S15" s="146">
         <v>68132.000000000015</v>
       </c>
-      <c r="U15" s="155">
+      <c r="T15" s="153">
         <v>69437.000000000015</v>
       </c>
-      <c r="V15" s="147">
+      <c r="U15" s="146">
         <v>69146.000000000015</v>
       </c>
-      <c r="W15" s="147">
+      <c r="V15" s="146">
         <v>70073.645866340899</v>
       </c>
-      <c r="X15" s="147">
+      <c r="W15" s="146">
         <f t="shared" si="1"/>
         <v>70396.857291394525</v>
       </c>
-      <c r="Y15" s="147">
+      <c r="X15" s="146">
         <f t="shared" si="1"/>
         <v>71031.421934031372</v>
       </c>
-      <c r="Z15" s="147">
+      <c r="Y15" s="146">
         <f t="shared" si="1"/>
         <v>71515.378832675109</v>
       </c>
-      <c r="AA15" s="147">
+      <c r="Z15" s="146">
         <f t="shared" si="1"/>
         <v>72081.329505158486</v>
       </c>
-      <c r="AB15" s="147">
+      <c r="AA15" s="146">
         <f t="shared" si="1"/>
         <v>72612.099326968688</v>
       </c>
     </row>
-    <row r="16" spans="1:28" s="149" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="146" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="159" t="s">
+    <row r="16" spans="1:27" s="148" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A16" s="224" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="146">
+      <c r="B16" s="145">
         <v>71182</v>
       </c>
-      <c r="D16" s="157">
+      <c r="C16" s="155">
         <v>74469</v>
       </c>
-      <c r="E16" s="146">
+      <c r="D16" s="145">
         <v>77514</v>
       </c>
-      <c r="F16" s="146">
+      <c r="E16" s="145">
         <v>79167</v>
       </c>
-      <c r="G16" s="146">
+      <c r="F16" s="145">
         <v>81581</v>
       </c>
-      <c r="H16" s="146">
+      <c r="G16" s="145">
         <v>85362.000000000015</v>
       </c>
-      <c r="I16" s="146">
+      <c r="H16" s="145">
         <v>90265</v>
       </c>
-      <c r="J16" s="146">
+      <c r="I16" s="145">
         <v>95283</v>
       </c>
-      <c r="K16" s="146">
+      <c r="J16" s="145">
         <v>100531</v>
       </c>
-      <c r="L16" s="146">
+      <c r="K16" s="145">
         <v>106408</v>
       </c>
-      <c r="M16" s="146">
+      <c r="L16" s="145">
         <v>112077</v>
       </c>
-      <c r="N16" s="146">
+      <c r="M16" s="145">
         <v>116197.99999999999</v>
       </c>
-      <c r="O16" s="146">
+      <c r="N16" s="145">
         <v>120222</v>
       </c>
-      <c r="P16" s="146">
+      <c r="O16" s="145">
         <v>125916</v>
       </c>
-      <c r="Q16" s="146">
+      <c r="P16" s="145">
         <v>132333</v>
       </c>
-      <c r="R16" s="146">
+      <c r="Q16" s="145">
         <v>132742</v>
       </c>
-      <c r="S16" s="156">
+      <c r="R16" s="154">
         <v>143974.00000000003</v>
       </c>
-      <c r="T16" s="146">
+      <c r="S16" s="145">
         <v>145589</v>
       </c>
-      <c r="U16" s="157">
+      <c r="T16" s="155">
         <v>152772</v>
       </c>
-      <c r="V16" s="146">
+      <c r="U16" s="145">
         <v>158980</v>
       </c>
-      <c r="W16" s="146">
+      <c r="V16" s="145">
         <v>166116.39565643322</v>
       </c>
-      <c r="X16" s="146">
+      <c r="W16" s="145">
         <f t="shared" si="1"/>
         <v>173219.89457829096</v>
       </c>
-      <c r="Y16" s="146">
+      <c r="X16" s="145">
         <f t="shared" si="1"/>
         <v>180811.32714686374</v>
       </c>
-      <c r="Z16" s="146">
+      <c r="Y16" s="145">
         <f t="shared" si="1"/>
         <v>188639.33534712496</v>
       </c>
-      <c r="AA16" s="146">
+      <c r="Z16" s="145">
         <f t="shared" si="1"/>
         <v>196856.38945759783</v>
       </c>
-      <c r="AB16" s="146">
+      <c r="AA16" s="145">
         <f t="shared" si="1"/>
         <v>205405.21221519986</v>
       </c>
     </row>
-    <row r="17" spans="1:28" s="149" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="147" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="160" t="s">
+    <row r="17" spans="1:27" s="148" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A17" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="147">
+      <c r="B17" s="146">
         <v>12775.999999999998</v>
       </c>
-      <c r="D17" s="155">
+      <c r="C17" s="153">
         <v>13424</v>
       </c>
-      <c r="E17" s="147">
+      <c r="D17" s="146">
         <v>14135</v>
       </c>
-      <c r="F17" s="147">
+      <c r="E17" s="146">
         <v>14558</v>
       </c>
-      <c r="G17" s="147">
+      <c r="F17" s="146">
         <v>14897</v>
       </c>
-      <c r="H17" s="147">
+      <c r="G17" s="146">
         <v>15259</v>
       </c>
-      <c r="I17" s="147">
+      <c r="H17" s="146">
         <v>16188</v>
       </c>
-      <c r="J17" s="147">
+      <c r="I17" s="146">
         <v>16677</v>
       </c>
-      <c r="K17" s="147">
+      <c r="J17" s="146">
         <v>17718</v>
       </c>
-      <c r="L17" s="147">
+      <c r="K17" s="146">
         <v>18210</v>
       </c>
-      <c r="M17" s="147">
+      <c r="L17" s="146">
         <v>18982</v>
       </c>
-      <c r="N17" s="147">
+      <c r="M17" s="146">
         <v>20034</v>
       </c>
-      <c r="O17" s="147">
+      <c r="N17" s="146">
         <v>20456</v>
       </c>
-      <c r="P17" s="147">
+      <c r="O17" s="146">
         <v>20925</v>
       </c>
-      <c r="Q17" s="147">
+      <c r="P17" s="146">
         <v>23653</v>
       </c>
-      <c r="R17" s="147">
+      <c r="Q17" s="146">
         <v>20864.999999999996</v>
       </c>
-      <c r="S17" s="154">
+      <c r="R17" s="152">
         <v>28048</v>
       </c>
-      <c r="T17" s="147">
+      <c r="S17" s="146">
         <v>35932</v>
       </c>
-      <c r="U17" s="155">
+      <c r="T17" s="153">
         <v>39661</v>
       </c>
-      <c r="V17" s="147">
+      <c r="U17" s="146">
         <v>42910</v>
       </c>
-      <c r="W17" s="147">
+      <c r="V17" s="146">
         <v>47155.337358818259</v>
       </c>
-      <c r="X17" s="147">
+      <c r="W17" s="146">
         <f t="shared" si="1"/>
         <v>51419.479377001742</v>
       </c>
-      <c r="Y17" s="147">
+      <c r="X17" s="146">
         <f t="shared" si="1"/>
         <v>56287.963332090119</v>
       </c>
-      <c r="Z17" s="147">
+      <c r="Y17" s="146">
         <f t="shared" si="1"/>
         <v>61497.675032291809</v>
       </c>
-      <c r="AA17" s="147">
+      <c r="Z17" s="146">
         <f t="shared" si="1"/>
         <v>67254.974704848195</v>
       </c>
-      <c r="AB17" s="147">
+      <c r="AA17" s="146">
         <f t="shared" si="1"/>
         <v>73515.498162954973</v>
       </c>
     </row>
-    <row r="18" spans="1:28" s="149" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="146"/>
-      <c r="B18" s="159" t="s">
+    <row r="18" spans="1:27" s="148" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="224" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="148">
+      <c r="B18" s="147">
         <v>42525</v>
       </c>
-      <c r="D18" s="157">
+      <c r="C18" s="155">
         <v>47626.999999999993</v>
       </c>
-      <c r="E18" s="146">
+      <c r="D18" s="145">
         <v>52812.999999999993</v>
       </c>
-      <c r="F18" s="146">
+      <c r="E18" s="145">
         <v>55501</v>
       </c>
-      <c r="G18" s="146">
+      <c r="F18" s="145">
         <v>54615</v>
       </c>
-      <c r="H18" s="146">
+      <c r="G18" s="145">
         <v>58006</v>
       </c>
-      <c r="I18" s="146">
+      <c r="H18" s="145">
         <v>64001</v>
       </c>
-      <c r="J18" s="146">
+      <c r="I18" s="145">
         <v>66872.999999999985</v>
       </c>
-      <c r="K18" s="146">
+      <c r="J18" s="145">
         <v>69095</v>
       </c>
-      <c r="L18" s="146">
+      <c r="K18" s="145">
         <v>72899</v>
       </c>
-      <c r="M18" s="146">
+      <c r="L18" s="145">
         <v>74149</v>
       </c>
-      <c r="N18" s="146">
+      <c r="M18" s="145">
         <v>74955</v>
       </c>
-      <c r="O18" s="146">
+      <c r="N18" s="145">
         <v>75773</v>
       </c>
-      <c r="P18" s="146">
+      <c r="O18" s="145">
         <v>78088.000000000015</v>
       </c>
-      <c r="Q18" s="146">
+      <c r="P18" s="145">
         <v>81489</v>
       </c>
-      <c r="R18" s="146">
+      <c r="Q18" s="145">
         <v>76490</v>
       </c>
-      <c r="S18" s="156">
+      <c r="R18" s="154">
         <v>88640</v>
       </c>
-      <c r="T18" s="146">
+      <c r="S18" s="145">
         <v>102860</v>
       </c>
-      <c r="U18" s="157">
+      <c r="T18" s="155">
         <v>100274</v>
       </c>
-      <c r="V18" s="146">
+      <c r="U18" s="145">
         <v>100775</v>
       </c>
-      <c r="W18" s="146">
+      <c r="V18" s="145">
         <v>103267.18155407908</v>
       </c>
-      <c r="X18" s="146">
+      <c r="W18" s="145">
         <f t="shared" si="1"/>
         <v>104802.0657830838</v>
       </c>
-      <c r="Y18" s="146">
+      <c r="X18" s="145">
         <f t="shared" si="1"/>
         <v>106876.80033012755</v>
       </c>
-      <c r="Z18" s="146">
+      <c r="Y18" s="145">
         <f t="shared" si="1"/>
         <v>108728.97146511993</v>
       </c>
-      <c r="AA18" s="146">
+      <c r="Z18" s="145">
         <f t="shared" si="1"/>
         <v>110747.34321329654</v>
       </c>
-      <c r="AB18" s="146">
+      <c r="AA18" s="145">
         <f t="shared" si="1"/>
         <v>112734.88669002496</v>
       </c>
     </row>
-    <row r="19" spans="1:28" s="143" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="166"/>
-      <c r="B19" s="164" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" s="184">
-        <f>SUM(C6:C18)</f>
+    <row r="19" spans="1:27" s="143" customFormat="1" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="208" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="176">
+        <f>SUM(B6:B18)</f>
         <v>517438</v>
       </c>
-      <c r="D19" s="185">
-        <f t="shared" ref="D19:W19" si="2">SUM(D6:D18)</f>
+      <c r="C19" s="177">
+        <f t="shared" ref="C19:V19" si="2">SUM(C6:C18)</f>
         <v>552139</v>
       </c>
-      <c r="E19" s="185">
+      <c r="D19" s="177">
         <f t="shared" si="2"/>
         <v>588990</v>
       </c>
-      <c r="F19" s="185">
+      <c r="E19" s="177">
         <f t="shared" si="2"/>
         <v>608384</v>
       </c>
-      <c r="G19" s="185">
+      <c r="F19" s="177">
         <f t="shared" si="2"/>
         <v>614390</v>
       </c>
-      <c r="H19" s="186">
+      <c r="G19" s="178">
         <f t="shared" si="2"/>
         <v>640461</v>
       </c>
-      <c r="I19" s="186">
+      <c r="H19" s="178">
         <f t="shared" si="2"/>
         <v>683340</v>
       </c>
-      <c r="J19" s="186">
+      <c r="I19" s="178">
         <f t="shared" si="2"/>
         <v>709685</v>
       </c>
-      <c r="K19" s="186">
+      <c r="J19" s="178">
         <f t="shared" si="2"/>
         <v>745880</v>
       </c>
-      <c r="L19" s="186">
+      <c r="K19" s="178">
         <f t="shared" si="2"/>
         <v>781017</v>
       </c>
-      <c r="M19" s="186">
+      <c r="L19" s="178">
         <f t="shared" si="2"/>
         <v>804692</v>
       </c>
-      <c r="N19" s="186">
+      <c r="M19" s="178">
         <f t="shared" si="2"/>
         <v>821489</v>
       </c>
-      <c r="O19" s="186">
+      <c r="N19" s="178">
         <f t="shared" si="2"/>
         <v>831956</v>
       </c>
-      <c r="P19" s="186">
+      <c r="O19" s="178">
         <f t="shared" si="2"/>
         <v>853167</v>
       </c>
-      <c r="Q19" s="186">
+      <c r="P19" s="178">
         <f t="shared" si="2"/>
         <v>880280</v>
       </c>
-      <c r="R19" s="186">
+      <c r="Q19" s="178">
         <f t="shared" si="2"/>
         <v>817375</v>
       </c>
-      <c r="S19" s="186">
+      <c r="R19" s="178">
         <f t="shared" si="2"/>
         <v>905132</v>
       </c>
-      <c r="T19" s="186">
+      <c r="S19" s="178">
         <f t="shared" si="2"/>
         <v>973165</v>
       </c>
-      <c r="U19" s="186">
+      <c r="T19" s="178">
         <f t="shared" si="2"/>
         <v>982221</v>
       </c>
-      <c r="V19" s="186">
+      <c r="U19" s="178">
         <f t="shared" si="2"/>
         <v>996471</v>
       </c>
-      <c r="W19" s="186">
+      <c r="V19" s="178">
         <f t="shared" si="2"/>
         <v>1023465.1349187322</v>
       </c>
-      <c r="X19" s="186">
-        <f>SUM(X6:X18)</f>
+      <c r="W19" s="178">
+        <f>SUM(W6:W18)</f>
         <v>1045802.5597860662</v>
       </c>
-      <c r="Y19" s="186">
-        <f t="shared" ref="Y19:AB19" si="3">SUM(Y6:Y18)</f>
+      <c r="X19" s="178">
+        <f t="shared" ref="X19:AA19" si="3">SUM(X6:X18)</f>
         <v>1072462.9902129185</v>
       </c>
-      <c r="Z19" s="186">
+      <c r="Y19" s="178">
         <f t="shared" si="3"/>
         <v>1098886.0177344962</v>
       </c>
-      <c r="AA19" s="186">
+      <c r="Z19" s="178">
         <f t="shared" si="3"/>
         <v>1127514.6315809824</v>
       </c>
-      <c r="AB19" s="186">
+      <c r="AA19" s="178">
         <f t="shared" si="3"/>
         <v>1157192.6819513717</v>
       </c>
     </row>
-    <row r="20" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="163"/>
-      <c r="B20" s="165" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="162">
+    <row r="20" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="225" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" s="158">
         <v>0</v>
       </c>
-      <c r="D20" s="168">
-        <f>IFERROR((D$19/C$19)-1,"")</f>
+      <c r="C20" s="160">
+        <f>IFERROR((C$19/B$19)-1,"")</f>
         <v>6.7063107077562911E-2</v>
       </c>
-      <c r="E20" s="168">
-        <f t="shared" ref="E20:W20" si="4">IFERROR((E$19/D$19)-1,"")</f>
+      <c r="D20" s="160">
+        <f t="shared" ref="D20:V20" si="4">IFERROR((D$19/C$19)-1,"")</f>
         <v>6.6742251498264071E-2</v>
       </c>
-      <c r="F20" s="168">
+      <c r="E20" s="160">
         <f t="shared" si="4"/>
         <v>3.2927553948284283E-2</v>
       </c>
-      <c r="G20" s="168">
+      <c r="F20" s="160">
         <f t="shared" si="4"/>
         <v>9.8720544918997621E-3</v>
       </c>
-      <c r="H20" s="167">
+      <c r="G20" s="159">
         <f t="shared" si="4"/>
         <v>4.2433958886049616E-2</v>
       </c>
-      <c r="I20" s="167">
+      <c r="H20" s="159">
         <f t="shared" si="4"/>
         <v>6.6950212425112454E-2</v>
       </c>
-      <c r="J20" s="167">
+      <c r="I20" s="159">
         <f t="shared" si="4"/>
         <v>3.8553282407000955E-2</v>
       </c>
-      <c r="K20" s="197">
+      <c r="J20" s="189">
         <f t="shared" si="4"/>
         <v>5.1001500665788235E-2</v>
       </c>
-      <c r="L20" s="167">
+      <c r="K20" s="159">
         <f t="shared" si="4"/>
         <v>4.7108113905722115E-2</v>
       </c>
-      <c r="M20" s="167">
+      <c r="L20" s="159">
         <f t="shared" si="4"/>
         <v>3.0313040561217086E-2</v>
       </c>
-      <c r="N20" s="167">
+      <c r="M20" s="159">
         <f t="shared" si="4"/>
         <v>2.0873825016279435E-2</v>
       </c>
-      <c r="O20" s="167">
+      <c r="N20" s="159">
         <f t="shared" si="4"/>
         <v>1.2741497451578709E-2</v>
       </c>
-      <c r="P20" s="167">
+      <c r="O20" s="159">
         <f t="shared" si="4"/>
         <v>2.5495338695796343E-2</v>
       </c>
-      <c r="Q20" s="167">
+      <c r="P20" s="159">
         <f t="shared" si="4"/>
         <v>3.1779241344308984E-2</v>
       </c>
-      <c r="R20" s="167">
+      <c r="Q20" s="159">
         <f t="shared" si="4"/>
         <v>-7.146021720361706E-2</v>
       </c>
-      <c r="S20" s="167">
+      <c r="R20" s="159">
         <f t="shared" si="4"/>
         <v>0.10736442881174502</v>
       </c>
-      <c r="T20" s="167">
+      <c r="S20" s="159">
         <f t="shared" si="4"/>
         <v>7.5163622543452213E-2</v>
       </c>
-      <c r="U20" s="167">
+      <c r="T20" s="159">
         <f t="shared" si="4"/>
         <v>9.3057189685201713E-3</v>
       </c>
-      <c r="V20" s="167">
+      <c r="U20" s="159">
         <f t="shared" si="4"/>
         <v>1.4507936604898575E-2</v>
       </c>
-      <c r="W20" s="167">
+      <c r="V20" s="159">
         <f t="shared" si="4"/>
         <v>2.7089734592107728E-2</v>
       </c>
-      <c r="X20" s="187">
-        <f>AVERAGE(V20:W20)</f>
+      <c r="W20" s="179">
+        <f>AVERAGE(U20:V20)</f>
         <v>2.0798835598503151E-2</v>
       </c>
-      <c r="Y20" s="187">
-        <f t="shared" ref="Y20:AB20" si="5">AVERAGE(W20:X20)</f>
+      <c r="X20" s="179">
+        <f t="shared" ref="X20:AA20" si="5">AVERAGE(V20:W20)</f>
         <v>2.394428509530544E-2</v>
       </c>
-      <c r="Z20" s="187">
+      <c r="Y20" s="179">
         <f t="shared" si="5"/>
         <v>2.2371560346904296E-2</v>
       </c>
-      <c r="AA20" s="187">
+      <c r="Z20" s="179">
         <f t="shared" si="5"/>
         <v>2.3157922721104868E-2</v>
       </c>
-      <c r="AB20" s="187">
+      <c r="AA20" s="179">
         <f t="shared" si="5"/>
         <v>2.2764741534004582E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="23" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="233" t="s">
-        <v>85</v>
-      </c>
-      <c r="B23" s="234"/>
-    </row>
-    <row r="24" spans="1:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="235"/>
-      <c r="B24" s="236"/>
-      <c r="X24" s="194" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y24" s="195"/>
-      <c r="Z24" s="195"/>
-      <c r="AA24" s="195"/>
-      <c r="AB24" s="196"/>
-    </row>
-    <row r="25" spans="1:28" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="241" t="s">
+    <row r="22" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="254" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="255"/>
+      <c r="W24" s="186" t="s">
+        <v>76</v>
+      </c>
+      <c r="X24" s="187"/>
+      <c r="Y24" s="187"/>
+      <c r="Z24" s="187"/>
+      <c r="AA24" s="188"/>
+    </row>
+    <row r="25" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="226" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="161">
+      <c r="B25" s="157">
         <v>2005</v>
       </c>
-      <c r="D25" s="158">
+      <c r="C25" s="156">
         <v>2006</v>
       </c>
-      <c r="E25" s="158">
+      <c r="D25" s="156">
         <v>2007</v>
       </c>
-      <c r="F25" s="158">
+      <c r="E25" s="156">
         <v>2008</v>
       </c>
-      <c r="G25" s="158">
+      <c r="F25" s="156">
         <v>2009</v>
       </c>
-      <c r="H25" s="158">
+      <c r="G25" s="156">
         <v>2010</v>
       </c>
-      <c r="I25" s="158">
+      <c r="H25" s="156">
         <v>2011</v>
       </c>
-      <c r="J25" s="158">
+      <c r="I25" s="156">
         <v>2012</v>
       </c>
-      <c r="K25" s="158">
+      <c r="J25" s="156">
         <v>2013</v>
       </c>
-      <c r="L25" s="242">
+      <c r="K25" s="227">
         <v>2014</v>
       </c>
-      <c r="M25" s="158">
+      <c r="L25" s="156">
         <v>2015</v>
       </c>
-      <c r="N25" s="158">
+      <c r="M25" s="156">
         <v>2016</v>
       </c>
-      <c r="O25" s="158">
+      <c r="N25" s="156">
         <v>2017</v>
       </c>
-      <c r="P25" s="158">
+      <c r="O25" s="156">
         <v>2018</v>
       </c>
-      <c r="Q25" s="158">
+      <c r="P25" s="156">
         <v>2019</v>
       </c>
-      <c r="R25" s="158">
+      <c r="Q25" s="156">
         <v>2020</v>
       </c>
-      <c r="S25" s="158">
+      <c r="R25" s="156">
         <v>2021</v>
       </c>
-      <c r="T25" s="158">
+      <c r="S25" s="156">
         <v>2022</v>
       </c>
-      <c r="U25" s="161">
+      <c r="T25" s="157">
         <v>2023</v>
       </c>
-      <c r="V25" s="158">
+      <c r="U25" s="156">
         <v>2024</v>
       </c>
-      <c r="W25" s="158">
+      <c r="V25" s="156">
         <v>2025</v>
       </c>
-      <c r="X25" s="158">
+      <c r="W25" s="156">
         <v>2026</v>
       </c>
-      <c r="Y25" s="158">
+      <c r="X25" s="156">
         <v>2027</v>
       </c>
-      <c r="Z25" s="158">
+      <c r="Y25" s="156">
         <v>2028</v>
       </c>
-      <c r="AA25" s="158">
+      <c r="Z25" s="156">
         <v>2029</v>
       </c>
-      <c r="AB25" s="158">
+      <c r="AA25" s="156">
         <v>2030</v>
       </c>
     </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B26" s="237" t="s">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A26" s="222" t="s">
         <v>19</v>
       </c>
-      <c r="C26" s="243">
+      <c r="B26" s="228">
         <v>0</v>
       </c>
-      <c r="D26" s="243">
+      <c r="C26" s="228">
+        <f>(C6/B6)-1</f>
+        <v>2.1314199794244093E-2</v>
+      </c>
+      <c r="D26" s="228">
         <f>(D6/C6)-1</f>
-        <v>2.1314199794244093E-2</v>
-      </c>
-      <c r="E26" s="243">
-        <f>(E6/D6)-1</f>
         <v>3.9310897021979985E-2</v>
       </c>
-      <c r="F26" s="244">
-        <f t="shared" ref="E26:W37" si="6">(F6/E6)-1</f>
+      <c r="E26" s="229">
+        <f t="shared" ref="D26:V37" si="6">(E6/D6)-1</f>
         <v>-8.0518899575040548E-3</v>
       </c>
-      <c r="G26" s="244">
+      <c r="F26" s="229">
         <f t="shared" si="6"/>
         <v>-2.3299511461855049E-3</v>
       </c>
-      <c r="H26" s="244">
+      <c r="G26" s="229">
         <f t="shared" si="6"/>
         <v>3.0385214203203503E-3</v>
       </c>
-      <c r="I26" s="244">
+      <c r="H26" s="229">
         <f t="shared" si="6"/>
         <v>1.9102220664447112E-2</v>
       </c>
-      <c r="J26" s="244">
-        <f>(J6/I6)-1</f>
+      <c r="I26" s="229">
+        <f>(I6/H6)-1</f>
         <v>2.5033164644032713E-2</v>
       </c>
-      <c r="K26" s="244">
+      <c r="J26" s="229">
         <f t="shared" si="6"/>
         <v>7.453565008987395E-2</v>
       </c>
-      <c r="L26" s="243">
+      <c r="K26" s="228">
         <f t="shared" si="6"/>
         <v>2.9106724657076199E-2</v>
       </c>
-      <c r="M26" s="243">
+      <c r="L26" s="228">
         <f t="shared" si="6"/>
         <v>4.299956653662762E-2</v>
       </c>
-      <c r="N26" s="243">
+      <c r="M26" s="228">
         <f t="shared" si="6"/>
         <v>2.7366802427063464E-2</v>
       </c>
-      <c r="O26" s="243">
+      <c r="N26" s="228">
         <f t="shared" si="6"/>
         <v>5.5763435205598677E-2</v>
       </c>
-      <c r="P26" s="243">
+      <c r="O26" s="228">
         <f t="shared" si="6"/>
         <v>1.5939308019464304E-2</v>
       </c>
-      <c r="Q26" s="243">
+      <c r="P26" s="228">
         <f t="shared" si="6"/>
         <v>2.7173298133132295E-2</v>
       </c>
-      <c r="R26" s="243">
+      <c r="Q26" s="228">
         <f t="shared" si="6"/>
         <v>1.9606763231811319E-2</v>
       </c>
-      <c r="S26" s="243">
+      <c r="R26" s="228">
         <f t="shared" si="6"/>
         <v>4.3735033039845828E-2</v>
       </c>
-      <c r="T26" s="246">
+      <c r="S26" s="231">
         <f t="shared" si="6"/>
         <v>-9.073971846536022E-3</v>
       </c>
-      <c r="U26" s="243">
+      <c r="T26" s="228">
         <f t="shared" si="6"/>
         <v>1.6486194770377161E-2</v>
       </c>
-      <c r="V26" s="243">
+      <c r="U26" s="228">
         <f t="shared" si="6"/>
         <v>6.1278665502063401E-2</v>
       </c>
-      <c r="W26" s="243">
+      <c r="V26" s="228">
         <f t="shared" si="6"/>
         <v>3.100232307625661E-2</v>
       </c>
-      <c r="X26" s="243">
-        <f>AVERAGE(V26:W26)</f>
+      <c r="W26" s="228">
+        <f>AVERAGE(U26:V26)</f>
         <v>4.6140494289160006E-2</v>
       </c>
-      <c r="Y26" s="243">
-        <f t="shared" ref="Y26:AB38" si="7">AVERAGE(W26:X26)</f>
+      <c r="X26" s="228">
+        <f t="shared" ref="X26:AA38" si="7">AVERAGE(V26:W26)</f>
         <v>3.8571408682708308E-2</v>
       </c>
-      <c r="Z26" s="243">
+      <c r="Y26" s="228">
         <f t="shared" si="7"/>
         <v>4.2355951485934157E-2</v>
       </c>
-      <c r="AA26" s="243">
+      <c r="Z26" s="228">
         <f t="shared" si="7"/>
         <v>4.0463680084321232E-2</v>
       </c>
-      <c r="AB26" s="243">
+      <c r="AA26" s="228">
         <f t="shared" si="7"/>
         <v>4.1409815785127695E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B27" s="238" t="s">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A27" s="223" t="s">
         <v>21</v>
       </c>
-      <c r="C27" s="244">
+      <c r="B27" s="229">
         <v>0</v>
       </c>
-      <c r="D27" s="244">
-        <f t="shared" ref="D27:S29" si="8">(D7/C7)-1</f>
+      <c r="C27" s="229">
+        <f t="shared" ref="C27:R29" si="8">(C7/B7)-1</f>
         <v>2.2931097338680262E-2</v>
       </c>
-      <c r="E27" s="244">
+      <c r="D27" s="229">
         <f t="shared" si="8"/>
         <v>1.3364695819523043E-2</v>
       </c>
-      <c r="F27" s="244">
+      <c r="E27" s="229">
         <f t="shared" si="8"/>
         <v>9.379615952732645E-2</v>
       </c>
-      <c r="G27" s="244">
+      <c r="F27" s="229">
         <f t="shared" si="8"/>
         <v>0.11440146619079772</v>
       </c>
-      <c r="H27" s="244">
+      <c r="G27" s="229">
         <f t="shared" si="8"/>
         <v>0.10871635073141173</v>
       </c>
-      <c r="I27" s="244">
+      <c r="H27" s="229">
         <f t="shared" si="8"/>
         <v>0.14435162776173005</v>
       </c>
-      <c r="J27" s="244">
+      <c r="I27" s="229">
         <f t="shared" si="8"/>
         <v>5.3690817301132565E-2</v>
       </c>
-      <c r="K27" s="244">
+      <c r="J27" s="229">
         <f t="shared" si="8"/>
         <v>5.3070033452034204E-2</v>
       </c>
-      <c r="L27" s="244">
+      <c r="K27" s="229">
         <f t="shared" si="8"/>
         <v>-1.3485264581710843E-2</v>
       </c>
-      <c r="M27" s="244">
+      <c r="L27" s="229">
         <f t="shared" si="8"/>
         <v>-1.0574206415157161E-2</v>
       </c>
-      <c r="N27" s="244">
+      <c r="M27" s="229">
         <f t="shared" si="8"/>
         <v>-2.8849182186574729E-2</v>
       </c>
-      <c r="O27" s="244">
+      <c r="N27" s="229">
         <f t="shared" si="8"/>
         <v>-5.7531403368430101E-2</v>
       </c>
-      <c r="P27" s="244">
+      <c r="O27" s="229">
         <f t="shared" si="8"/>
         <v>-1.6608552027894907E-2</v>
       </c>
-      <c r="Q27" s="244">
+      <c r="P27" s="229">
         <f t="shared" si="8"/>
         <v>1.9245124568442407E-2</v>
       </c>
-      <c r="R27" s="244">
+      <c r="Q27" s="229">
         <f t="shared" si="8"/>
         <v>-0.15190076213581094</v>
       </c>
-      <c r="S27" s="244">
+      <c r="R27" s="229">
         <f t="shared" si="8"/>
         <v>-2.0509499136444065E-3</v>
       </c>
-      <c r="T27" s="247">
+      <c r="S27" s="232">
         <f t="shared" si="6"/>
         <v>1.4548404542996218E-2</v>
       </c>
-      <c r="U27" s="244">
+      <c r="T27" s="229">
         <f t="shared" si="6"/>
         <v>2.5667679513833086E-2</v>
       </c>
-      <c r="V27" s="244">
+      <c r="U27" s="229">
         <f t="shared" si="6"/>
         <v>-3.4120734908136274E-2</v>
       </c>
-      <c r="W27" s="244">
+      <c r="V27" s="229">
         <f t="shared" si="6"/>
         <v>-6.1873733747030757E-2</v>
       </c>
-      <c r="X27" s="244">
-        <f t="shared" ref="X27:X38" si="9">AVERAGE(V27:W27)</f>
+      <c r="W27" s="229">
+        <f t="shared" ref="W27:W38" si="9">AVERAGE(U27:V27)</f>
         <v>-4.7997234327583516E-2</v>
       </c>
-      <c r="Y27" s="244">
+      <c r="X27" s="229">
         <f t="shared" si="7"/>
         <v>-5.4935484037307136E-2</v>
       </c>
-      <c r="Z27" s="244">
+      <c r="Y27" s="229">
         <f t="shared" si="7"/>
         <v>-5.1466359182445326E-2</v>
       </c>
-      <c r="AA27" s="244">
+      <c r="Z27" s="229">
         <f t="shared" si="7"/>
         <v>-5.3200921609876231E-2</v>
       </c>
-      <c r="AB27" s="244">
+      <c r="AA27" s="229">
         <f t="shared" si="7"/>
         <v>-5.2333640396160779E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B28" s="239" t="s">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A28" s="224" t="s">
         <v>23</v>
       </c>
-      <c r="C28" s="244">
+      <c r="B28" s="229">
         <v>0</v>
       </c>
-      <c r="D28" s="244">
+      <c r="C28" s="229">
         <f t="shared" si="8"/>
         <v>7.2917206027028447E-2</v>
       </c>
-      <c r="E28" s="244">
+      <c r="D28" s="229">
         <f t="shared" si="8"/>
         <v>7.7637690776376944E-2</v>
       </c>
-      <c r="F28" s="244">
+      <c r="E28" s="229">
         <f t="shared" si="8"/>
         <v>3.5714285714285587E-3</v>
       </c>
-      <c r="G28" s="244">
+      <c r="F28" s="229">
         <f t="shared" si="8"/>
         <v>-3.6646995169513308E-2</v>
       </c>
-      <c r="H28" s="244">
+      <c r="G28" s="229">
         <f t="shared" si="8"/>
         <v>1.8829469393426779E-2</v>
       </c>
-      <c r="I28" s="244">
+      <c r="H28" s="229">
         <f t="shared" si="8"/>
         <v>5.5876335530802734E-2</v>
       </c>
-      <c r="J28" s="244">
+      <c r="I28" s="229">
         <f t="shared" si="8"/>
         <v>8.2996038580775977E-3</v>
       </c>
-      <c r="K28" s="244">
+      <c r="J28" s="229">
         <f t="shared" si="8"/>
         <v>1.5096031686720135E-2</v>
       </c>
-      <c r="L28" s="244">
+      <c r="K28" s="229">
         <f t="shared" si="8"/>
         <v>2.8901673310124831E-2</v>
       </c>
-      <c r="M28" s="244">
+      <c r="L28" s="229">
         <f t="shared" si="8"/>
         <v>2.0034958959000093E-2</v>
       </c>
-      <c r="N28" s="244">
+      <c r="M28" s="229">
         <f t="shared" si="8"/>
         <v>3.2238022226898533E-2</v>
       </c>
-      <c r="O28" s="244">
+      <c r="N28" s="229">
         <f t="shared" si="8"/>
         <v>-1.8163990447158329E-2</v>
       </c>
-      <c r="P28" s="244">
+      <c r="O28" s="229">
         <f t="shared" si="8"/>
         <v>1.4752558461462062E-2</v>
       </c>
-      <c r="Q28" s="244">
+      <c r="P28" s="229">
         <f t="shared" si="8"/>
         <v>1.2014382180128402E-2</v>
       </c>
-      <c r="R28" s="244">
+      <c r="Q28" s="229">
         <f t="shared" si="8"/>
         <v>-9.2489890236857386E-2</v>
       </c>
-      <c r="S28" s="244">
+      <c r="R28" s="229">
         <f t="shared" si="8"/>
         <v>0.13593057058586377</v>
       </c>
-      <c r="T28" s="247">
+      <c r="S28" s="232">
         <f t="shared" si="6"/>
         <v>8.1594530476528426E-2</v>
       </c>
-      <c r="U28" s="244">
+      <c r="T28" s="229">
         <f t="shared" si="6"/>
         <v>-1.6208701058703423E-2</v>
       </c>
-      <c r="V28" s="244">
+      <c r="U28" s="229">
         <f t="shared" si="6"/>
         <v>-2.5648452929559085E-2</v>
       </c>
-      <c r="W28" s="244">
+      <c r="V28" s="229">
         <f t="shared" si="6"/>
         <v>1.85000575147094E-2</v>
       </c>
-      <c r="X28" s="244">
+      <c r="W28" s="229">
         <f t="shared" si="9"/>
         <v>-3.5741977074248421E-3</v>
       </c>
-      <c r="Y28" s="244">
+      <c r="X28" s="229">
         <f t="shared" si="7"/>
         <v>7.4629299036422792E-3</v>
       </c>
-      <c r="Z28" s="244">
+      <c r="Y28" s="229">
         <f t="shared" si="7"/>
         <v>1.9443660981087185E-3</v>
       </c>
-      <c r="AA28" s="244">
+      <c r="Z28" s="229">
         <f t="shared" si="7"/>
         <v>4.7036480008754988E-3</v>
       </c>
-      <c r="AB28" s="244">
+      <c r="AA28" s="229">
         <f t="shared" si="7"/>
         <v>3.3240070494921087E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="B29" s="238" t="s">
+    <row r="29" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A29" s="223" t="s">
         <v>25</v>
       </c>
-      <c r="C29" s="244">
+      <c r="B29" s="229">
         <v>0</v>
       </c>
-      <c r="D29" s="244">
+      <c r="C29" s="229">
         <f t="shared" si="8"/>
         <v>5.3197752207653215E-2</v>
       </c>
-      <c r="E29" s="244">
+      <c r="D29" s="229">
         <f t="shared" si="8"/>
         <v>4.2278571065602844E-2</v>
       </c>
-      <c r="F29" s="244">
+      <c r="E29" s="229">
         <f t="shared" si="8"/>
         <v>5.2654673102237037E-3</v>
       </c>
-      <c r="G29" s="244">
+      <c r="F29" s="229">
         <f t="shared" si="8"/>
         <v>2.3958484892574905E-2</v>
       </c>
-      <c r="H29" s="244">
+      <c r="G29" s="229">
         <f t="shared" si="8"/>
         <v>3.8933358594231082E-2</v>
       </c>
-      <c r="I29" s="244">
+      <c r="H29" s="229">
         <f t="shared" si="8"/>
         <v>3.0681559152039961E-2</v>
       </c>
-      <c r="J29" s="244">
+      <c r="I29" s="229">
         <f t="shared" si="8"/>
         <v>2.1496815286624171E-2</v>
       </c>
-      <c r="K29" s="244">
+      <c r="J29" s="229">
         <f t="shared" si="8"/>
         <v>3.7065904563956087E-2</v>
       </c>
-      <c r="L29" s="244">
+      <c r="K29" s="229">
         <f t="shared" si="8"/>
         <v>3.4363256784968543E-2</v>
       </c>
-      <c r="M29" s="244">
+      <c r="L29" s="229">
         <f t="shared" si="8"/>
         <v>-7.0237758850362209E-3</v>
       </c>
-      <c r="N29" s="244">
+      <c r="M29" s="229">
         <f t="shared" si="8"/>
         <v>-8.1304118053293628E-5</v>
       </c>
-      <c r="O29" s="244">
+      <c r="N29" s="229">
         <f t="shared" si="8"/>
         <v>2.8865308777493048E-2</v>
       </c>
-      <c r="P29" s="244">
+      <c r="O29" s="229">
         <f t="shared" si="8"/>
         <v>2.5487019401746913E-2</v>
       </c>
-      <c r="Q29" s="244">
+      <c r="P29" s="229">
         <f t="shared" si="8"/>
         <v>2.5200369913686904E-2</v>
       </c>
-      <c r="R29" s="244">
+      <c r="Q29" s="229">
         <f t="shared" si="8"/>
         <v>-3.8299631662031208E-2</v>
       </c>
-      <c r="S29" s="244">
+      <c r="R29" s="229">
         <f t="shared" si="8"/>
         <v>5.8310860984093438E-2</v>
       </c>
-      <c r="T29" s="247">
+      <c r="S29" s="232">
         <f t="shared" si="6"/>
         <v>4.6087373979836865E-2</v>
       </c>
-      <c r="U29" s="244">
+      <c r="T29" s="229">
         <f t="shared" si="6"/>
         <v>3.1559995763758897E-2</v>
       </c>
-      <c r="V29" s="244">
+      <c r="U29" s="229">
         <f t="shared" si="6"/>
         <v>2.48793675781116E-2</v>
       </c>
-      <c r="W29" s="244">
+      <c r="V29" s="229">
         <f t="shared" si="6"/>
         <v>1.140651910951207E-2</v>
       </c>
-      <c r="X29" s="244">
+      <c r="W29" s="229">
         <f t="shared" si="9"/>
         <v>1.8142943343811835E-2</v>
       </c>
-      <c r="Y29" s="244">
+      <c r="X29" s="229">
         <f t="shared" si="7"/>
         <v>1.4774731226661952E-2</v>
       </c>
-      <c r="Z29" s="244">
+      <c r="Y29" s="229">
         <f t="shared" si="7"/>
         <v>1.6458837285236894E-2</v>
       </c>
-      <c r="AA29" s="244">
+      <c r="Z29" s="229">
         <f t="shared" si="7"/>
         <v>1.5616784255949423E-2</v>
       </c>
-      <c r="AB29" s="244">
+      <c r="AA29" s="229">
         <f t="shared" si="7"/>
         <v>1.6037810770593158E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B30" s="239" t="s">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A30" s="224" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="244">
+      <c r="B30" s="229">
         <v>0</v>
       </c>
-      <c r="D30" s="244">
-        <f t="shared" ref="D30:S38" si="10">(D10/C10)-1</f>
+      <c r="C30" s="229">
+        <f t="shared" ref="C30:R38" si="10">(C10/B10)-1</f>
         <v>0.12141035963499736</v>
       </c>
-      <c r="E30" s="244">
+      <c r="D30" s="229">
         <f t="shared" si="10"/>
         <v>6.9404972028599632E-2</v>
       </c>
-      <c r="F30" s="244">
+      <c r="E30" s="229">
         <f t="shared" si="10"/>
         <v>9.9085237922063474E-2</v>
       </c>
-      <c r="G30" s="244">
+      <c r="F30" s="229">
         <f t="shared" si="10"/>
         <v>2.6139631958054466E-2</v>
       </c>
-      <c r="H30" s="244">
+      <c r="G30" s="229">
         <f t="shared" si="10"/>
         <v>-6.6474848695304845E-3</v>
       </c>
-      <c r="I30" s="244">
+      <c r="H30" s="229">
         <f t="shared" si="10"/>
         <v>6.2125449460647131E-2</v>
       </c>
-      <c r="J30" s="244">
+      <c r="I30" s="229">
         <f t="shared" si="10"/>
         <v>5.9126387060372432E-2</v>
       </c>
-      <c r="K30" s="244">
+      <c r="J30" s="229">
         <f t="shared" si="10"/>
         <v>0.11276109298350767</v>
       </c>
-      <c r="L30" s="244">
+      <c r="K30" s="229">
         <f t="shared" si="10"/>
         <v>8.918633181065605E-2</v>
       </c>
-      <c r="M30" s="244">
+      <c r="L30" s="229">
         <f t="shared" si="10"/>
         <v>6.3001355261712133E-2</v>
       </c>
-      <c r="N30" s="244">
+      <c r="M30" s="229">
         <f t="shared" si="10"/>
         <v>3.588780538230929E-2</v>
       </c>
-      <c r="O30" s="244">
+      <c r="N30" s="229">
         <f t="shared" si="10"/>
         <v>-2.0257796257796112E-2</v>
       </c>
-      <c r="P30" s="244">
+      <c r="O30" s="229">
         <f t="shared" si="10"/>
         <v>-1.2748909297706557E-2</v>
       </c>
-      <c r="Q30" s="244">
+      <c r="P30" s="229">
         <f t="shared" si="10"/>
         <v>-3.8912579957356086E-2</v>
       </c>
-      <c r="R30" s="244">
+      <c r="Q30" s="229">
         <f t="shared" si="10"/>
         <v>-0.29581521836365909</v>
       </c>
-      <c r="S30" s="244">
+      <c r="R30" s="229">
         <f t="shared" si="10"/>
         <v>4.2684011280774481E-2</v>
       </c>
-      <c r="T30" s="247">
+      <c r="S30" s="232">
         <f t="shared" si="6"/>
         <v>6.6424620482955277E-2</v>
       </c>
-      <c r="U30" s="244">
+      <c r="T30" s="229">
         <f t="shared" si="6"/>
         <v>-3.0915114817776757E-2</v>
       </c>
-      <c r="V30" s="244">
+      <c r="U30" s="229">
         <f t="shared" si="6"/>
         <v>8.4881637272471444E-4</v>
       </c>
-      <c r="W30" s="244">
+      <c r="V30" s="229">
         <f t="shared" si="6"/>
         <v>-2.7679677050644891E-2</v>
       </c>
-      <c r="X30" s="244">
+      <c r="W30" s="229">
         <f t="shared" si="9"/>
         <v>-1.3415430338960088E-2</v>
       </c>
-      <c r="Y30" s="244">
+      <c r="X30" s="229">
         <f t="shared" si="7"/>
         <v>-2.0547553694802489E-2</v>
       </c>
-      <c r="Z30" s="244">
+      <c r="Y30" s="229">
         <f t="shared" si="7"/>
         <v>-1.6981492016881289E-2</v>
       </c>
-      <c r="AA30" s="244">
+      <c r="Z30" s="229">
         <f t="shared" si="7"/>
         <v>-1.8764522855841889E-2</v>
       </c>
-      <c r="AB30" s="244">
+      <c r="AA30" s="229">
         <f t="shared" si="7"/>
         <v>-1.7873007436361589E-2</v>
       </c>
     </row>
-    <row r="31" spans="1:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="B31" s="238" t="s">
+    <row r="31" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="223" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="244">
+      <c r="B31" s="229">
         <v>0</v>
       </c>
-      <c r="D31" s="244">
+      <c r="C31" s="229">
         <f t="shared" si="10"/>
         <v>7.6076650239385701E-2</v>
       </c>
-      <c r="E31" s="244">
+      <c r="D31" s="229">
         <f t="shared" si="10"/>
         <v>8.0684463590279032E-2</v>
       </c>
-      <c r="F31" s="244">
+      <c r="E31" s="229">
         <f t="shared" si="10"/>
         <v>3.022860191457899E-2</v>
       </c>
-      <c r="G31" s="244">
+      <c r="F31" s="229">
         <f t="shared" si="10"/>
         <v>-1.5730951869149523E-3</v>
       </c>
-      <c r="H31" s="244">
+      <c r="G31" s="229">
         <f t="shared" si="10"/>
         <v>5.3452072221950475E-2</v>
       </c>
-      <c r="I31" s="244">
+      <c r="H31" s="229">
         <f t="shared" si="10"/>
         <v>6.8891840924503178E-2</v>
       </c>
-      <c r="J31" s="244">
+      <c r="I31" s="229">
         <f t="shared" si="10"/>
         <v>3.8153011828302885E-2</v>
       </c>
-      <c r="K31" s="244">
+      <c r="J31" s="229">
         <f t="shared" si="10"/>
         <v>4.7684026353461029E-2</v>
       </c>
-      <c r="L31" s="244">
+      <c r="K31" s="229">
         <f t="shared" si="10"/>
         <v>4.7255671239882169E-2</v>
       </c>
-      <c r="M31" s="244">
+      <c r="L31" s="229">
         <f t="shared" si="10"/>
         <v>3.3312223892326687E-2</v>
       </c>
-      <c r="N31" s="244">
+      <c r="M31" s="229">
         <f t="shared" si="10"/>
         <v>2.6855400246623695E-2</v>
       </c>
-      <c r="O31" s="244">
+      <c r="N31" s="229">
         <f t="shared" si="10"/>
         <v>1.8595487034932967E-2</v>
       </c>
-      <c r="P31" s="244">
+      <c r="O31" s="229">
         <f t="shared" si="10"/>
         <v>2.6727472961906695E-2</v>
       </c>
-      <c r="Q31" s="244">
+      <c r="P31" s="229">
         <f t="shared" si="10"/>
         <v>3.7486764119418536E-2</v>
       </c>
-      <c r="R31" s="244">
+      <c r="Q31" s="229">
         <f t="shared" si="10"/>
         <v>-0.13688779905891713</v>
       </c>
-      <c r="S31" s="244">
+      <c r="R31" s="229">
         <f t="shared" si="10"/>
         <v>0.20409260183514388</v>
       </c>
-      <c r="T31" s="247">
+      <c r="S31" s="232">
         <f t="shared" si="6"/>
         <v>0.11884067212957961</v>
       </c>
-      <c r="U31" s="244">
+      <c r="T31" s="229">
         <f t="shared" si="6"/>
         <v>-3.6386227493715895E-2</v>
       </c>
-      <c r="V31" s="244">
+      <c r="U31" s="229">
         <f t="shared" si="6"/>
         <v>1.2326474119727315E-2</v>
       </c>
-      <c r="W31" s="244">
+      <c r="V31" s="229">
         <f t="shared" si="6"/>
         <v>4.5987328955726214E-2</v>
       </c>
-      <c r="X31" s="244">
+      <c r="W31" s="229">
         <f t="shared" si="9"/>
         <v>2.9156901537726765E-2</v>
       </c>
-      <c r="Y31" s="244">
+      <c r="X31" s="229">
         <f t="shared" si="7"/>
         <v>3.757211524672649E-2</v>
       </c>
-      <c r="Z31" s="244">
+      <c r="Y31" s="229">
         <f t="shared" si="7"/>
         <v>3.3364508392226627E-2</v>
       </c>
-      <c r="AA31" s="244">
+      <c r="Z31" s="229">
         <f t="shared" si="7"/>
         <v>3.5468311819476558E-2</v>
       </c>
-      <c r="AB31" s="244">
+      <c r="AA31" s="229">
         <f t="shared" si="7"/>
         <v>3.4416410105851593E-2</v>
       </c>
     </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
-      <c r="B32" s="239" t="s">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A32" s="224" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="244">
+      <c r="B32" s="229">
         <v>0</v>
       </c>
-      <c r="D32" s="244">
+      <c r="C32" s="229">
         <f t="shared" si="10"/>
         <v>0.14917517674783976</v>
       </c>
-      <c r="E32" s="244">
+      <c r="D32" s="229">
         <f t="shared" si="10"/>
         <v>0.14573791783443846</v>
       </c>
-      <c r="F32" s="244">
+      <c r="E32" s="229">
         <f t="shared" si="10"/>
         <v>2.1418769763140721E-2</v>
       </c>
-      <c r="G32" s="244">
+      <c r="F32" s="229">
         <f t="shared" si="10"/>
         <v>-8.4754672897196293E-2</v>
       </c>
-      <c r="H32" s="244">
+      <c r="G32" s="229">
         <f t="shared" si="10"/>
         <v>0.16510306975556821</v>
       </c>
-      <c r="I32" s="244">
+      <c r="H32" s="229">
         <f t="shared" si="10"/>
         <v>0.10391104294478537</v>
       </c>
-      <c r="J32" s="244">
+      <c r="I32" s="229">
         <f t="shared" si="10"/>
         <v>1.3000545824443099E-2</v>
       </c>
-      <c r="K32" s="244">
+      <c r="J32" s="229">
         <f t="shared" si="10"/>
         <v>8.8317413666421762E-2</v>
       </c>
-      <c r="L32" s="244">
+      <c r="K32" s="229">
         <f t="shared" si="10"/>
         <v>6.4632280133225528E-2</v>
       </c>
-      <c r="M32" s="244">
+      <c r="L32" s="229">
         <f t="shared" si="10"/>
         <v>1.2978777373805706E-2</v>
       </c>
-      <c r="N32" s="244">
+      <c r="M32" s="229">
         <f t="shared" si="10"/>
         <v>-6.5523141772049209E-3</v>
       </c>
-      <c r="O32" s="244">
+      <c r="N32" s="229">
         <f t="shared" si="10"/>
         <v>-1.932448328011982E-3</v>
       </c>
-      <c r="P32" s="244">
+      <c r="O32" s="229">
         <f t="shared" si="10"/>
         <v>3.5230238235541611E-2</v>
       </c>
-      <c r="Q32" s="244">
+      <c r="P32" s="229">
         <f t="shared" si="10"/>
         <v>9.1888595242934912E-3</v>
       </c>
-      <c r="R32" s="244">
+      <c r="Q32" s="229">
         <f t="shared" si="10"/>
         <v>-2.7718464203698501E-2</v>
       </c>
-      <c r="S32" s="244">
+      <c r="R32" s="229">
         <f t="shared" si="10"/>
         <v>0.12750176107404809</v>
       </c>
-      <c r="T32" s="247">
+      <c r="S32" s="232">
         <f t="shared" si="6"/>
         <v>0.12326350606394709</v>
       </c>
-      <c r="U32" s="244">
+      <c r="T32" s="229">
         <f t="shared" si="6"/>
         <v>1.5377568381101936E-2</v>
       </c>
-      <c r="V32" s="244">
+      <c r="U32" s="229">
         <f t="shared" si="6"/>
         <v>-2.0944770251980493E-3</v>
       </c>
-      <c r="W32" s="244">
+      <c r="V32" s="229">
         <f t="shared" si="6"/>
         <v>9.6882389009473879E-3</v>
       </c>
-      <c r="X32" s="244">
+      <c r="W32" s="229">
         <f t="shared" si="9"/>
         <v>3.7968809378746693E-3</v>
       </c>
-      <c r="Y32" s="244">
+      <c r="X32" s="229">
         <f t="shared" si="7"/>
         <v>6.7425599194110286E-3</v>
       </c>
-      <c r="Z32" s="244">
+      <c r="Y32" s="229">
         <f t="shared" si="7"/>
         <v>5.269720428642849E-3</v>
       </c>
-      <c r="AA32" s="244">
+      <c r="Z32" s="229">
         <f t="shared" si="7"/>
         <v>6.0061401740269388E-3</v>
       </c>
-      <c r="AB32" s="244">
+      <c r="AA32" s="229">
         <f t="shared" si="7"/>
         <v>5.6379303013348939E-3</v>
       </c>
     </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B33" s="238" t="s">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A33" s="223" t="s">
         <v>33</v>
       </c>
-      <c r="C33" s="244">
+      <c r="B33" s="229">
         <v>0</v>
       </c>
-      <c r="D33" s="244">
+      <c r="C33" s="229">
         <f t="shared" si="10"/>
         <v>6.5871369294605797E-2</v>
       </c>
-      <c r="E33" s="244">
+      <c r="D33" s="229">
         <f t="shared" si="10"/>
         <v>0.13759124087591235</v>
       </c>
-      <c r="F33" s="244">
+      <c r="E33" s="229">
         <f t="shared" si="10"/>
         <v>0.1013795316008983</v>
       </c>
-      <c r="G33" s="244">
+      <c r="F33" s="229">
         <f t="shared" si="10"/>
         <v>3.4809204777162872E-2</v>
       </c>
-      <c r="H33" s="244">
+      <c r="G33" s="229">
         <f t="shared" si="10"/>
         <v>4.6774571897724826E-2</v>
       </c>
-      <c r="I33" s="244">
+      <c r="H33" s="229">
         <f t="shared" si="10"/>
         <v>0.10944783076371434</v>
       </c>
-      <c r="J33" s="244">
+      <c r="I33" s="229">
         <f t="shared" si="10"/>
         <v>7.562414155288022E-2</v>
       </c>
-      <c r="K33" s="244">
+      <c r="J33" s="229">
         <f t="shared" si="10"/>
         <v>9.5170134455044186E-2</v>
       </c>
-      <c r="L33" s="244">
+      <c r="K33" s="229">
         <f t="shared" si="10"/>
         <v>0.10216049382716053</v>
       </c>
-      <c r="M33" s="244">
+      <c r="L33" s="229">
         <f t="shared" si="10"/>
         <v>7.9560658390117611E-2</v>
       </c>
-      <c r="N33" s="244">
+      <c r="M33" s="229">
         <f t="shared" si="10"/>
         <v>2.9686419183767798E-2</v>
       </c>
-      <c r="O33" s="244">
+      <c r="N33" s="229">
         <f t="shared" si="10"/>
         <v>5.3882326596876196E-2</v>
       </c>
-      <c r="P33" s="244">
+      <c r="O33" s="229">
         <f t="shared" si="10"/>
         <v>3.7342965658282656E-2</v>
       </c>
-      <c r="Q33" s="244">
+      <c r="P33" s="229">
         <f t="shared" si="10"/>
         <v>6.2677625009601501E-2</v>
       </c>
-      <c r="R33" s="244">
+      <c r="Q33" s="229">
         <f t="shared" si="10"/>
         <v>2.2358751957595402E-2</v>
       </c>
-      <c r="S33" s="244">
+      <c r="R33" s="229">
         <f t="shared" si="10"/>
         <v>3.699950510216099E-2</v>
       </c>
-      <c r="T33" s="247">
+      <c r="S33" s="232">
         <f t="shared" si="6"/>
         <v>6.6745449173920113E-2</v>
       </c>
-      <c r="U33" s="244">
+      <c r="T33" s="229">
         <f t="shared" si="6"/>
         <v>8.9369407754580132E-2</v>
       </c>
-      <c r="V33" s="244">
+      <c r="U33" s="229">
         <f t="shared" si="6"/>
         <v>1.0736286300968345E-2</v>
       </c>
-      <c r="W33" s="244">
+      <c r="V33" s="229">
         <f t="shared" si="6"/>
         <v>2.7636052292486113E-2</v>
       </c>
-      <c r="X33" s="244">
+      <c r="W33" s="229">
         <f t="shared" si="9"/>
         <v>1.9186169296727229E-2</v>
       </c>
-      <c r="Y33" s="244">
+      <c r="X33" s="229">
         <f t="shared" si="7"/>
         <v>2.3411110794606671E-2</v>
       </c>
-      <c r="Z33" s="244">
+      <c r="Y33" s="229">
         <f t="shared" si="7"/>
         <v>2.129864004566695E-2</v>
       </c>
-      <c r="AA33" s="244">
+      <c r="Z33" s="229">
         <f t="shared" si="7"/>
         <v>2.2354875420136811E-2</v>
       </c>
-      <c r="AB33" s="244">
+      <c r="AA33" s="229">
         <f t="shared" si="7"/>
         <v>2.182675773290188E-2</v>
       </c>
     </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.25">
-      <c r="B34" s="239" t="s">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A34" s="224" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="244">
+      <c r="B34" s="229">
         <v>0</v>
       </c>
-      <c r="D34" s="244">
+      <c r="C34" s="229">
         <f t="shared" si="10"/>
         <v>4.0451496028507172E-2</v>
       </c>
-      <c r="E34" s="244">
+      <c r="D34" s="229">
         <f t="shared" si="10"/>
         <v>3.7501195828948619E-2</v>
       </c>
-      <c r="F34" s="244">
+      <c r="E34" s="229">
         <f t="shared" si="10"/>
         <v>2.7773167358229545E-2</v>
       </c>
-      <c r="G34" s="244">
+      <c r="F34" s="229">
         <f t="shared" si="10"/>
         <v>3.8309020114478454E-2</v>
       </c>
-      <c r="H34" s="244">
+      <c r="G34" s="229">
         <f t="shared" si="10"/>
         <v>3.5703176303874429E-2</v>
       </c>
-      <c r="I34" s="244">
+      <c r="H34" s="229">
         <f t="shared" si="10"/>
         <v>2.8298738570379678E-2</v>
       </c>
-      <c r="J34" s="244">
+      <c r="I34" s="229">
         <f t="shared" si="10"/>
         <v>3.165768806386704E-2</v>
       </c>
-      <c r="K34" s="244">
+      <c r="J34" s="229">
         <f t="shared" si="10"/>
         <v>3.2180436936724455E-2</v>
       </c>
-      <c r="L34" s="244">
+      <c r="K34" s="229">
         <f t="shared" si="10"/>
         <v>3.1070476190476093E-2</v>
       </c>
-      <c r="M34" s="244">
+      <c r="L34" s="229">
         <f t="shared" si="10"/>
         <v>3.1937219200756539E-2</v>
       </c>
-      <c r="N34" s="244">
+      <c r="M34" s="229">
         <f t="shared" si="10"/>
         <v>3.5288220551378702E-2</v>
       </c>
-      <c r="O34" s="244">
+      <c r="N34" s="229">
         <f t="shared" si="10"/>
         <v>3.0516399452198861E-2</v>
       </c>
-      <c r="P34" s="244">
+      <c r="O34" s="229">
         <f t="shared" si="10"/>
         <v>3.965366803141146E-2</v>
       </c>
-      <c r="Q34" s="244">
+      <c r="P34" s="229">
         <f t="shared" si="10"/>
         <v>3.2472982220558055E-2</v>
       </c>
-      <c r="R34" s="244">
+      <c r="Q34" s="229">
         <f t="shared" si="10"/>
         <v>1.4431494172377546E-2</v>
       </c>
-      <c r="S34" s="244">
+      <c r="R34" s="229">
         <f t="shared" si="10"/>
         <v>2.49636332256713E-2</v>
       </c>
-      <c r="T34" s="247">
+      <c r="S34" s="232">
         <f t="shared" si="6"/>
         <v>2.0446700263401674E-2</v>
       </c>
-      <c r="U34" s="244">
+      <c r="T34" s="229">
         <f t="shared" si="6"/>
         <v>1.8504767629621721E-2</v>
       </c>
-      <c r="V34" s="244">
+      <c r="U34" s="229">
         <f t="shared" si="6"/>
         <v>2.2091583442306106E-2</v>
       </c>
-      <c r="W34" s="244">
+      <c r="V34" s="229">
         <f t="shared" si="6"/>
         <v>1.9834298843357745E-2</v>
       </c>
-      <c r="X34" s="244">
+      <c r="W34" s="229">
         <f t="shared" si="9"/>
         <v>2.0962941142831926E-2</v>
       </c>
-      <c r="Y34" s="244">
+      <c r="X34" s="229">
         <f t="shared" si="7"/>
         <v>2.0398619993094835E-2</v>
       </c>
-      <c r="Z34" s="244">
+      <c r="Y34" s="229">
         <f t="shared" si="7"/>
         <v>2.068078056796338E-2</v>
       </c>
-      <c r="AA34" s="244">
+      <c r="Z34" s="229">
         <f t="shared" si="7"/>
         <v>2.0539700280529108E-2</v>
       </c>
-      <c r="AB34" s="244">
+      <c r="AA34" s="229">
         <f t="shared" si="7"/>
         <v>2.0610240424246244E-2</v>
       </c>
     </row>
-    <row r="35" spans="2:28" ht="30" x14ac:dyDescent="0.25">
-      <c r="B35" s="238" t="s">
+    <row r="35" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="223" t="s">
         <v>37</v>
       </c>
-      <c r="C35" s="244">
+      <c r="B35" s="229">
         <v>0</v>
       </c>
-      <c r="D35" s="244">
+      <c r="C35" s="229">
         <f t="shared" si="10"/>
         <v>7.0305349862717303E-2</v>
       </c>
-      <c r="E35" s="244">
+      <c r="D35" s="229">
         <f t="shared" si="10"/>
         <v>6.8770729684908716E-2</v>
       </c>
-      <c r="F35" s="244">
+      <c r="E35" s="229">
         <f t="shared" si="10"/>
         <v>3.7676380739950277E-2</v>
       </c>
-      <c r="G35" s="244">
+      <c r="F35" s="229">
         <f t="shared" si="10"/>
         <v>2.7990654205607646E-2</v>
       </c>
-      <c r="H35" s="244">
+      <c r="G35" s="229">
         <f t="shared" si="10"/>
         <v>3.0819582708304871E-2</v>
       </c>
-      <c r="I35" s="244">
+      <c r="H35" s="229">
         <f t="shared" si="10"/>
         <v>7.0864752833267097E-2</v>
       </c>
-      <c r="J35" s="244">
+      <c r="I35" s="229">
         <f t="shared" si="10"/>
         <v>4.815928183165874E-2</v>
       </c>
-      <c r="K35" s="244">
+      <c r="J35" s="229">
         <f t="shared" si="10"/>
         <v>5.2762881332626188E-2</v>
       </c>
-      <c r="L35" s="244">
+      <c r="K35" s="229">
         <f t="shared" si="10"/>
         <v>7.2901311738473362E-2</v>
       </c>
-      <c r="M35" s="244">
+      <c r="L35" s="229">
         <f t="shared" si="10"/>
         <v>-1.8782608695652181E-3</v>
       </c>
-      <c r="N35" s="244">
+      <c r="M35" s="229">
         <f t="shared" si="10"/>
         <v>-2.4341371619738039E-2</v>
       </c>
-      <c r="O35" s="244">
+      <c r="N35" s="229">
         <f t="shared" si="10"/>
         <v>1.4554870970622469E-2</v>
       </c>
-      <c r="P35" s="244">
+      <c r="O35" s="229">
         <f t="shared" si="10"/>
         <v>3.971131842985387E-2</v>
       </c>
-      <c r="Q35" s="244">
+      <c r="P35" s="229">
         <f t="shared" si="10"/>
         <v>3.446991501032759E-2</v>
       </c>
-      <c r="R35" s="244">
+      <c r="Q35" s="229">
         <f t="shared" si="10"/>
         <v>-5.7903178292036284E-2</v>
       </c>
-      <c r="S35" s="244">
+      <c r="R35" s="229">
         <f t="shared" si="10"/>
         <v>9.7335140018066868E-2</v>
       </c>
-      <c r="T35" s="247">
+      <c r="S35" s="232">
         <f t="shared" si="6"/>
         <v>7.8601168331565718E-2</v>
       </c>
-      <c r="U35" s="244">
+      <c r="T35" s="229">
         <f t="shared" si="6"/>
         <v>1.9153995185815731E-2</v>
       </c>
-      <c r="V35" s="244">
+      <c r="U35" s="229">
         <f t="shared" si="6"/>
         <v>-4.1908492590405633E-3</v>
       </c>
-      <c r="W35" s="244">
+      <c r="V35" s="229">
         <f t="shared" si="6"/>
         <v>1.3415756028416492E-2</v>
       </c>
-      <c r="X35" s="244">
+      <c r="W35" s="229">
         <f t="shared" si="9"/>
         <v>4.6124533846879645E-3</v>
       </c>
-      <c r="Y35" s="244">
+      <c r="X35" s="229">
         <f t="shared" si="7"/>
         <v>9.0141047065522284E-3</v>
       </c>
-      <c r="Z35" s="244">
+      <c r="Y35" s="229">
         <f t="shared" si="7"/>
         <v>6.8132790456200965E-3</v>
       </c>
-      <c r="AA35" s="244">
+      <c r="Z35" s="229">
         <f t="shared" si="7"/>
         <v>7.9136918760861624E-3</v>
       </c>
-      <c r="AB35" s="244">
+      <c r="AA35" s="229">
         <f t="shared" si="7"/>
         <v>7.3634854608531294E-3</v>
       </c>
     </row>
-    <row r="36" spans="2:28" ht="45" x14ac:dyDescent="0.25">
-      <c r="B36" s="239" t="s">
+    <row r="36" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A36" s="224" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="244">
+      <c r="B36" s="229">
         <v>0</v>
       </c>
-      <c r="D36" s="244">
+      <c r="C36" s="229">
         <f t="shared" si="10"/>
         <v>4.6177404399988742E-2</v>
       </c>
-      <c r="E36" s="244">
+      <c r="D36" s="229">
         <f t="shared" si="10"/>
         <v>4.0889497643314732E-2</v>
       </c>
-      <c r="F36" s="244">
+      <c r="E36" s="229">
         <f t="shared" si="10"/>
         <v>2.1325179967489838E-2</v>
       </c>
-      <c r="G36" s="244">
+      <c r="F36" s="229">
         <f t="shared" si="10"/>
         <v>3.0492503189460285E-2</v>
       </c>
-      <c r="H36" s="244">
+      <c r="G36" s="229">
         <f t="shared" si="10"/>
         <v>4.634657579583501E-2</v>
       </c>
-      <c r="I36" s="244">
+      <c r="H36" s="229">
         <f t="shared" si="10"/>
         <v>5.7437735760642816E-2</v>
       </c>
-      <c r="J36" s="244">
+      <c r="I36" s="229">
         <f t="shared" si="10"/>
         <v>5.5591868387525611E-2</v>
       </c>
-      <c r="K36" s="244">
+      <c r="J36" s="229">
         <f t="shared" si="10"/>
         <v>5.507803070852102E-2</v>
       </c>
-      <c r="L36" s="244">
+      <c r="K36" s="229">
         <f t="shared" si="10"/>
         <v>5.8459579632153202E-2</v>
       </c>
-      <c r="M36" s="244">
+      <c r="L36" s="229">
         <f t="shared" si="10"/>
         <v>5.3276069468461085E-2</v>
       </c>
-      <c r="N36" s="244">
+      <c r="M36" s="229">
         <f t="shared" si="10"/>
         <v>3.6769363919448184E-2</v>
       </c>
-      <c r="O36" s="244">
+      <c r="N36" s="229">
         <f t="shared" si="10"/>
         <v>3.4630544415566566E-2</v>
       </c>
-      <c r="P36" s="244">
+      <c r="O36" s="229">
         <f t="shared" si="10"/>
         <v>4.7362379597744253E-2</v>
       </c>
-      <c r="Q36" s="244">
+      <c r="P36" s="229">
         <f t="shared" si="10"/>
         <v>5.0962546459544456E-2</v>
       </c>
-      <c r="R36" s="244">
+      <c r="Q36" s="229">
         <f t="shared" si="10"/>
         <v>3.0906878858636411E-3</v>
       </c>
-      <c r="S36" s="244">
+      <c r="R36" s="229">
         <f t="shared" si="10"/>
         <v>8.4615268716758951E-2</v>
       </c>
-      <c r="T36" s="247">
+      <c r="S36" s="232">
         <f t="shared" si="6"/>
         <v>1.1217303124174904E-2</v>
       </c>
-      <c r="U36" s="244">
+      <c r="T36" s="229">
         <f t="shared" si="6"/>
         <v>4.9337518631215271E-2</v>
       </c>
-      <c r="V36" s="244">
+      <c r="U36" s="229">
         <f t="shared" si="6"/>
         <v>4.063571858717574E-2</v>
       </c>
-      <c r="W36" s="244">
+      <c r="V36" s="229">
         <f t="shared" si="6"/>
         <v>4.4888637919443974E-2</v>
       </c>
-      <c r="X36" s="244">
+      <c r="W36" s="229">
         <f t="shared" si="9"/>
         <v>4.2762178253309857E-2</v>
       </c>
-      <c r="Y36" s="244">
+      <c r="X36" s="229">
         <f t="shared" si="7"/>
         <v>4.3825408086376916E-2</v>
       </c>
-      <c r="Z36" s="244">
+      <c r="Y36" s="229">
         <f t="shared" si="7"/>
         <v>4.3293793169843386E-2</v>
       </c>
-      <c r="AA36" s="244">
+      <c r="Z36" s="229">
         <f t="shared" si="7"/>
         <v>4.3559600628110151E-2</v>
       </c>
-      <c r="AB36" s="244">
+      <c r="AA36" s="229">
         <f t="shared" si="7"/>
         <v>4.3426696898976769E-2</v>
       </c>
     </row>
-    <row r="37" spans="2:28" ht="60" x14ac:dyDescent="0.25">
-      <c r="B37" s="238" t="s">
+    <row r="37" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+      <c r="A37" s="223" t="s">
         <v>41</v>
       </c>
-      <c r="C37" s="244">
+      <c r="B37" s="229">
         <v>0</v>
       </c>
-      <c r="D37" s="244">
+      <c r="C37" s="229">
         <f t="shared" si="10"/>
         <v>5.0720100187852335E-2</v>
       </c>
-      <c r="E37" s="244">
+      <c r="D37" s="229">
         <f t="shared" si="10"/>
         <v>5.2964839094159721E-2</v>
       </c>
-      <c r="F37" s="244">
+      <c r="E37" s="229">
         <f t="shared" si="10"/>
         <v>2.9925716307039218E-2</v>
       </c>
-      <c r="G37" s="244">
+      <c r="F37" s="229">
         <f t="shared" si="10"/>
         <v>2.3286165682099291E-2</v>
       </c>
-      <c r="H37" s="244">
+      <c r="G37" s="229">
         <f t="shared" si="10"/>
         <v>2.4300194670067832E-2</v>
       </c>
-      <c r="I37" s="244">
+      <c r="H37" s="229">
         <f t="shared" si="10"/>
         <v>6.0882102365816815E-2</v>
       </c>
-      <c r="J37" s="244">
+      <c r="I37" s="229">
         <f t="shared" si="10"/>
         <v>3.0207561156412099E-2</v>
       </c>
-      <c r="K37" s="244">
+      <c r="J37" s="229">
         <f t="shared" si="10"/>
         <v>6.2421298794747226E-2</v>
       </c>
-      <c r="L37" s="244">
+      <c r="K37" s="229">
         <f t="shared" si="10"/>
         <v>2.7768371147985027E-2</v>
       </c>
-      <c r="M37" s="244">
+      <c r="L37" s="229">
         <f t="shared" si="10"/>
         <v>4.2394288852279027E-2</v>
       </c>
-      <c r="N37" s="244">
+      <c r="M37" s="229">
         <f t="shared" si="10"/>
         <v>5.5420925086924422E-2</v>
       </c>
-      <c r="O37" s="244">
+      <c r="N37" s="229">
         <f t="shared" si="10"/>
         <v>2.106419087551159E-2</v>
       </c>
-      <c r="P37" s="244">
+      <c r="O37" s="229">
         <f t="shared" si="10"/>
         <v>2.2927258506061809E-2</v>
       </c>
-      <c r="Q37" s="244">
+      <c r="P37" s="229">
         <f t="shared" si="10"/>
         <v>0.13037037037037047</v>
       </c>
-      <c r="R37" s="244">
+      <c r="Q37" s="229">
         <f t="shared" si="10"/>
         <v>-0.11787088318606531</v>
       </c>
-      <c r="S37" s="244">
+      <c r="R37" s="229">
         <f t="shared" si="10"/>
         <v>0.34426072369997618</v>
       </c>
-      <c r="T37" s="247">
+      <c r="S37" s="232">
         <f t="shared" si="6"/>
         <v>0.28108956075299485</v>
       </c>
-      <c r="U37" s="244">
+      <c r="T37" s="229">
         <f t="shared" si="6"/>
         <v>0.10377936101525109</v>
       </c>
-      <c r="V37" s="244">
+      <c r="U37" s="229">
         <f t="shared" si="6"/>
         <v>8.1919265777464112E-2</v>
       </c>
-      <c r="W37" s="244">
+      <c r="V37" s="229">
         <f t="shared" si="6"/>
         <v>9.8935850823077542E-2</v>
       </c>
-      <c r="X37" s="244">
+      <c r="W37" s="229">
         <f t="shared" si="9"/>
         <v>9.0427558300270827E-2</v>
       </c>
-      <c r="Y37" s="244">
+      <c r="X37" s="229">
         <f t="shared" si="7"/>
         <v>9.4681704561674185E-2</v>
       </c>
-      <c r="Z37" s="244">
+      <c r="Y37" s="229">
         <f t="shared" si="7"/>
         <v>9.2554631430972506E-2</v>
       </c>
-      <c r="AA37" s="244">
+      <c r="Z37" s="229">
         <f t="shared" si="7"/>
         <v>9.3618167996323345E-2</v>
       </c>
-      <c r="AB37" s="244">
+      <c r="AA37" s="229">
         <f t="shared" si="7"/>
         <v>9.3086399713647933E-2</v>
       </c>
     </row>
-    <row r="38" spans="2:28" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B38" s="240" t="s">
+    <row r="38" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="225" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="245">
+      <c r="B38" s="230">
         <v>0</v>
       </c>
-      <c r="D38" s="245">
+      <c r="C38" s="230">
         <f t="shared" si="10"/>
         <v>0.11997648442092879</v>
       </c>
-      <c r="E38" s="245">
+      <c r="D38" s="230">
         <f t="shared" si="10"/>
         <v>0.10888781573477235</v>
       </c>
-      <c r="F38" s="245">
+      <c r="E38" s="230">
         <f t="shared" si="10"/>
         <v>5.0896559559199694E-2</v>
       </c>
-      <c r="G38" s="245">
+      <c r="F38" s="230">
         <f t="shared" si="10"/>
         <v>-1.5963676330156162E-2</v>
       </c>
-      <c r="H38" s="245">
+      <c r="G38" s="230">
         <f t="shared" si="10"/>
         <v>6.208916964203981E-2</v>
       </c>
-      <c r="I38" s="245">
+      <c r="H38" s="230">
         <f t="shared" si="10"/>
         <v>0.1033513774437127</v>
       </c>
-      <c r="J38" s="245">
-        <f>(J18/I18)-1</f>
+      <c r="I38" s="230">
+        <f>(I18/H18)-1</f>
         <v>4.4874298839080451E-2</v>
       </c>
-      <c r="K38" s="245">
-        <f t="shared" ref="K38:W38" si="11">(K18/J18)-1</f>
+      <c r="J38" s="230">
+        <f t="shared" ref="J38:V38" si="11">(J18/I18)-1</f>
         <v>3.3227161933815141E-2</v>
       </c>
-      <c r="L38" s="245">
+      <c r="K38" s="230">
         <f t="shared" si="11"/>
         <v>5.5054634922932166E-2</v>
       </c>
-      <c r="M38" s="245">
+      <c r="L38" s="230">
         <f t="shared" si="11"/>
         <v>1.7147011618815045E-2</v>
       </c>
-      <c r="N38" s="245">
+      <c r="M38" s="230">
         <f t="shared" si="11"/>
         <v>1.0870004989952609E-2</v>
       </c>
-      <c r="O38" s="245">
+      <c r="N38" s="230">
         <f t="shared" si="11"/>
         <v>1.0913214595423826E-2</v>
       </c>
-      <c r="P38" s="245">
+      <c r="O38" s="230">
         <f t="shared" si="11"/>
         <v>3.0551779657661982E-2</v>
       </c>
-      <c r="Q38" s="245">
+      <c r="P38" s="230">
         <f t="shared" si="11"/>
         <v>4.3553426902981141E-2</v>
       </c>
-      <c r="R38" s="245">
+      <c r="Q38" s="230">
         <f t="shared" si="11"/>
         <v>-6.1345703101032045E-2</v>
       </c>
-      <c r="S38" s="245">
+      <c r="R38" s="230">
         <f t="shared" si="11"/>
         <v>0.15884429337168249</v>
       </c>
-      <c r="T38" s="248">
+      <c r="S38" s="233">
         <f t="shared" si="11"/>
         <v>0.16042418772563183</v>
       </c>
-      <c r="U38" s="245">
+      <c r="T38" s="230">
         <f t="shared" si="11"/>
         <v>-2.5140968306435973E-2</v>
       </c>
-      <c r="V38" s="245">
+      <c r="U38" s="230">
         <f t="shared" si="11"/>
         <v>4.9963101102978857E-3</v>
       </c>
-      <c r="W38" s="245">
+      <c r="V38" s="230">
         <f t="shared" si="11"/>
         <v>2.4730156825394145E-2</v>
       </c>
-      <c r="X38" s="245">
+      <c r="W38" s="230">
         <f t="shared" si="9"/>
         <v>1.4863233467846015E-2</v>
       </c>
-      <c r="Y38" s="245">
+      <c r="X38" s="230">
         <f t="shared" si="7"/>
         <v>1.979669514662008E-2</v>
       </c>
-      <c r="Z38" s="245">
+      <c r="Y38" s="230">
         <f t="shared" si="7"/>
         <v>1.7329964307233048E-2</v>
       </c>
-      <c r="AA38" s="245">
+      <c r="Z38" s="230">
         <f t="shared" si="7"/>
         <v>1.8563329726926564E-2</v>
       </c>
-      <c r="AB38" s="245">
+      <c r="AA38" s="230">
         <f t="shared" si="7"/>
         <v>1.7946647017079806E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A1:B2"/>
-    <mergeCell ref="X3:AB4"/>
-    <mergeCell ref="X24:AB24"/>
-    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="W3:AA4"/>
+    <mergeCell ref="W24:AA24"/>
+    <mergeCell ref="A23:A24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -19022,807 +18954,807 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="209" t="s">
-        <v>80</v>
+      <c r="A1" s="201" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="209"/>
+      <c r="A2" s="201"/>
     </row>
     <row r="3" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="142"/>
-      <c r="W3" s="188" t="s">
-        <v>83</v>
-      </c>
-      <c r="X3" s="189"/>
-      <c r="Y3" s="189"/>
-      <c r="Z3" s="189"/>
-      <c r="AA3" s="190"/>
+      <c r="W3" s="180" t="s">
+        <v>81</v>
+      </c>
+      <c r="X3" s="181"/>
+      <c r="Y3" s="181"/>
+      <c r="Z3" s="181"/>
+      <c r="AA3" s="182"/>
     </row>
     <row r="4" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="142"/>
-      <c r="W4" s="191"/>
-      <c r="X4" s="192"/>
-      <c r="Y4" s="192"/>
-      <c r="Z4" s="192"/>
-      <c r="AA4" s="193"/>
-    </row>
-    <row r="5" spans="1:28" s="207" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="208" t="s">
+      <c r="W4" s="183"/>
+      <c r="X4" s="184"/>
+      <c r="Y4" s="184"/>
+      <c r="Z4" s="184"/>
+      <c r="AA4" s="185"/>
+    </row>
+    <row r="5" spans="1:28" s="199" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="200" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="161">
+      <c r="B5" s="157">
         <v>2005</v>
       </c>
-      <c r="C5" s="161">
+      <c r="C5" s="157">
         <v>2006</v>
       </c>
-      <c r="D5" s="158">
+      <c r="D5" s="156">
         <v>2007</v>
       </c>
-      <c r="E5" s="158">
+      <c r="E5" s="156">
         <v>2008</v>
       </c>
-      <c r="F5" s="158">
+      <c r="F5" s="156">
         <v>2009</v>
       </c>
-      <c r="G5" s="158">
+      <c r="G5" s="156">
         <v>2010</v>
       </c>
-      <c r="H5" s="158">
+      <c r="H5" s="156">
         <v>2011</v>
       </c>
-      <c r="I5" s="158">
+      <c r="I5" s="156">
         <v>2012</v>
       </c>
-      <c r="J5" s="158">
+      <c r="J5" s="156">
         <v>2013</v>
       </c>
-      <c r="K5" s="158">
+      <c r="K5" s="156">
         <v>2014</v>
       </c>
-      <c r="L5" s="158">
+      <c r="L5" s="156">
         <v>2015</v>
       </c>
-      <c r="M5" s="158">
+      <c r="M5" s="156">
         <v>2016</v>
       </c>
-      <c r="N5" s="158">
+      <c r="N5" s="156">
         <v>2017</v>
       </c>
-      <c r="O5" s="158">
+      <c r="O5" s="156">
         <v>2018</v>
       </c>
-      <c r="P5" s="158">
+      <c r="P5" s="156">
         <v>2019</v>
       </c>
-      <c r="Q5" s="158">
+      <c r="Q5" s="156">
         <v>2020</v>
       </c>
-      <c r="R5" s="158">
+      <c r="R5" s="156">
         <v>2021</v>
       </c>
-      <c r="S5" s="158">
+      <c r="S5" s="156">
         <v>2022</v>
       </c>
-      <c r="T5" s="158">
+      <c r="T5" s="156">
         <v>2023</v>
       </c>
-      <c r="U5" s="158">
+      <c r="U5" s="156">
         <v>2024</v>
       </c>
-      <c r="V5" s="158">
+      <c r="V5" s="156">
         <v>2025</v>
       </c>
-      <c r="W5" s="158">
+      <c r="W5" s="156">
         <v>2026</v>
       </c>
-      <c r="X5" s="158">
+      <c r="X5" s="156">
         <v>2027</v>
       </c>
-      <c r="Y5" s="158">
+      <c r="Y5" s="156">
         <v>2028</v>
       </c>
-      <c r="Z5" s="158">
+      <c r="Z5" s="156">
         <v>2029</v>
       </c>
-      <c r="AA5" s="158">
+      <c r="AA5" s="156">
         <v>2030</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="213" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="215">
+      <c r="A6" s="205" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="207">
         <v>348741</v>
       </c>
-      <c r="C6" s="212">
+      <c r="C6" s="204">
         <v>370953</v>
       </c>
-      <c r="D6" s="201">
+      <c r="D6" s="193">
         <v>395261.00000000006</v>
       </c>
-      <c r="E6" s="200">
+      <c r="E6" s="192">
         <v>411526.00000000006</v>
       </c>
-      <c r="F6" s="200">
+      <c r="F6" s="192">
         <v>418556.00000000006</v>
       </c>
-      <c r="G6" s="200">
+      <c r="G6" s="192">
         <v>439704.00000000006</v>
       </c>
-      <c r="H6" s="200">
+      <c r="H6" s="192">
         <v>463891</v>
       </c>
-      <c r="I6" s="200">
+      <c r="I6" s="192">
         <v>490025.99999999988</v>
       </c>
-      <c r="J6" s="200">
+      <c r="J6" s="192">
         <v>512698.99999999994</v>
       </c>
-      <c r="K6" s="200">
+      <c r="K6" s="192">
         <v>534484</v>
       </c>
-      <c r="L6" s="200">
+      <c r="L6" s="192">
         <v>551013</v>
       </c>
-      <c r="M6" s="200">
+      <c r="M6" s="192">
         <v>559739</v>
       </c>
-      <c r="N6" s="200">
+      <c r="N6" s="192">
         <v>571234.99999999988</v>
       </c>
-      <c r="O6" s="200">
+      <c r="O6" s="192">
         <v>589723</v>
       </c>
-      <c r="P6" s="200">
+      <c r="P6" s="192">
         <v>613728</v>
       </c>
-      <c r="Q6" s="200">
+      <c r="Q6" s="192">
         <v>582997</v>
       </c>
-      <c r="R6" s="202">
+      <c r="R6" s="194">
         <v>668838</v>
       </c>
-      <c r="S6" s="200">
+      <c r="S6" s="192">
         <v>741003.99999999988</v>
       </c>
-      <c r="T6" s="201">
+      <c r="T6" s="193">
         <v>744807</v>
       </c>
-      <c r="U6" s="200">
+      <c r="U6" s="192">
         <v>757023</v>
       </c>
-      <c r="V6" s="200">
+      <c r="V6" s="192">
         <v>784516.15422914457</v>
       </c>
-      <c r="W6" s="200">
+      <c r="W6" s="192">
         <f>V6*(1+W16)</f>
         <v>805195.61826503684</v>
       </c>
-      <c r="X6" s="200">
+      <c r="X6" s="192">
         <f t="shared" ref="X6:AA6" si="0">W6*(1+X16)</f>
         <v>830429.23132445221</v>
       </c>
-      <c r="Y6" s="200">
+      <c r="Y6" s="192">
         <f t="shared" si="0"/>
         <v>854386.28469378524</v>
       </c>
-      <c r="Z6" s="200">
+      <c r="Z6" s="192">
         <f t="shared" si="0"/>
         <v>880097.96698120434</v>
       </c>
-      <c r="AA6" s="200">
+      <c r="AA6" s="192">
         <f t="shared" si="0"/>
         <v>906035.66189593379</v>
       </c>
-      <c r="AB6" s="199"/>
+      <c r="AB6" s="191"/>
     </row>
     <row r="7" spans="1:28" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="214" t="s">
+      <c r="A7" s="206" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="211">
+      <c r="B7" s="203">
         <v>70375</v>
       </c>
-      <c r="C7" s="204">
+      <c r="C7" s="196">
         <v>74044</v>
       </c>
-      <c r="D7" s="205">
+      <c r="D7" s="197">
         <v>77427.000000000015</v>
       </c>
-      <c r="E7" s="204">
+      <c r="E7" s="196">
         <v>81064</v>
       </c>
-      <c r="F7" s="204">
+      <c r="F7" s="196">
         <v>84925</v>
       </c>
-      <c r="G7" s="204">
+      <c r="G7" s="196">
         <v>89363</v>
       </c>
-      <c r="H7" s="204">
+      <c r="H7" s="196">
         <v>95151</v>
       </c>
-      <c r="I7" s="204">
+      <c r="I7" s="196">
         <v>99725</v>
       </c>
-      <c r="J7" s="204">
+      <c r="J7" s="196">
         <v>108596.00000000003</v>
       </c>
-      <c r="K7" s="204">
+      <c r="K7" s="196">
         <v>113674</v>
       </c>
-      <c r="L7" s="204">
+      <c r="L7" s="196">
         <v>119188</v>
       </c>
-      <c r="M7" s="204">
+      <c r="M7" s="196">
         <v>121362.00000000001</v>
       </c>
-      <c r="N7" s="204">
+      <c r="N7" s="196">
         <v>125783</v>
       </c>
-      <c r="O7" s="204">
+      <c r="O7" s="196">
         <v>135030</v>
       </c>
-      <c r="P7" s="204">
+      <c r="P7" s="196">
         <v>142152</v>
       </c>
-      <c r="Q7" s="204">
+      <c r="Q7" s="196">
         <v>141071</v>
       </c>
-      <c r="R7" s="206">
+      <c r="R7" s="198">
         <v>154922</v>
       </c>
-      <c r="S7" s="204">
+      <c r="S7" s="196">
         <v>156452</v>
       </c>
-      <c r="T7" s="223">
+      <c r="T7" s="212">
         <v>158878</v>
       </c>
-      <c r="U7" s="203">
+      <c r="U7" s="195">
         <v>159810.99999999997</v>
       </c>
-      <c r="V7" s="204">
+      <c r="V7" s="196">
         <v>171226.2309509097</v>
       </c>
-      <c r="W7" s="203">
+      <c r="W7" s="195">
         <f t="shared" ref="W7:AA10" si="1">V7*(1+W17)</f>
         <v>177844.29600687011</v>
       </c>
-      <c r="X7" s="203">
+      <c r="X7" s="195">
         <f t="shared" si="1"/>
         <v>187632.89671293247</v>
       </c>
-      <c r="Y7" s="203">
+      <c r="Y7" s="195">
         <f t="shared" si="1"/>
         <v>196422.68029872622</v>
       </c>
-      <c r="Z7" s="203">
+      <c r="Z7" s="195">
         <f t="shared" si="1"/>
         <v>206429.03375553418</v>
       </c>
-      <c r="AA7" s="203">
+      <c r="AA7" s="195">
         <f t="shared" si="1"/>
         <v>216522.23748429489</v>
       </c>
-      <c r="AB7" s="199"/>
-    </row>
-    <row r="8" spans="1:28" s="149" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="228" t="s">
+      <c r="AB7" s="191"/>
+    </row>
+    <row r="8" spans="1:28" s="148" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="217" t="s">
         <v>65</v>
       </c>
-      <c r="B8" s="210">
+      <c r="B8" s="202">
         <v>86720.000000000015</v>
       </c>
-      <c r="C8" s="200">
+      <c r="C8" s="192">
         <v>101405</v>
       </c>
-      <c r="D8" s="201">
+      <c r="D8" s="193">
         <v>117424</v>
       </c>
-      <c r="E8" s="200">
+      <c r="E8" s="192">
         <v>128090</v>
       </c>
-      <c r="F8" s="200">
+      <c r="F8" s="192">
         <v>120026</v>
       </c>
-      <c r="G8" s="200">
+      <c r="G8" s="192">
         <v>131503</v>
       </c>
-      <c r="H8" s="200">
+      <c r="H8" s="192">
         <v>155852</v>
       </c>
-      <c r="I8" s="200">
+      <c r="I8" s="192">
         <v>160351</v>
       </c>
-      <c r="J8" s="200">
+      <c r="J8" s="192">
         <v>172869</v>
       </c>
-      <c r="K8" s="200">
+      <c r="K8" s="192">
         <v>193533</v>
       </c>
-      <c r="L8" s="200">
+      <c r="L8" s="192">
         <v>191305</v>
       </c>
-      <c r="M8" s="200">
+      <c r="M8" s="192">
         <v>190994</v>
       </c>
-      <c r="N8" s="200">
+      <c r="N8" s="192">
         <v>184828</v>
       </c>
-      <c r="O8" s="200">
+      <c r="O8" s="192">
         <v>187607.99999999997</v>
       </c>
-      <c r="P8" s="200">
+      <c r="P8" s="192">
         <v>193147</v>
       </c>
-      <c r="Q8" s="200">
+      <c r="Q8" s="192">
         <v>153203</v>
       </c>
-      <c r="R8" s="202">
+      <c r="R8" s="194">
         <v>170923</v>
       </c>
-      <c r="S8" s="200">
+      <c r="S8" s="192">
         <v>198344</v>
       </c>
-      <c r="T8" s="201">
+      <c r="T8" s="193">
         <v>166406</v>
       </c>
-      <c r="U8" s="200">
+      <c r="U8" s="192">
         <v>170387.99999999997</v>
       </c>
-      <c r="V8" s="200">
+      <c r="V8" s="192">
         <v>173947.39176549573</v>
       </c>
-      <c r="W8" s="200">
+      <c r="W8" s="192">
         <f t="shared" si="1"/>
         <v>177845.49594032613</v>
       </c>
-      <c r="X8" s="200">
+      <c r="X8" s="192">
         <f t="shared" si="1"/>
         <v>181695.81477896898</v>
       </c>
-      <c r="Y8" s="200">
+      <c r="Y8" s="192">
         <f t="shared" si="1"/>
         <v>185698.5254089665</v>
       </c>
-      <c r="Z8" s="200">
+      <c r="Z8" s="192">
         <f t="shared" si="1"/>
         <v>189754.13771619822</v>
       </c>
-      <c r="AA8" s="200">
+      <c r="AA8" s="192">
         <f t="shared" si="1"/>
         <v>193916.34735530525</v>
       </c>
-      <c r="AB8" s="229"/>
-    </row>
-    <row r="9" spans="1:28" s="149" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="221" t="s">
+      <c r="AB8" s="218"/>
+    </row>
+    <row r="9" spans="1:28" s="148" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="210" t="s">
         <v>69</v>
       </c>
-      <c r="B9" s="222">
+      <c r="B9" s="211">
         <v>88125</v>
       </c>
-      <c r="C9" s="203">
+      <c r="C9" s="195">
         <v>96513.000000000015</v>
       </c>
-      <c r="D9" s="223">
+      <c r="D9" s="212">
         <v>102516</v>
       </c>
-      <c r="E9" s="203">
+      <c r="E9" s="195">
         <v>104603.99999999999</v>
       </c>
-      <c r="F9" s="203">
+      <c r="F9" s="195">
         <v>99158.000000000015</v>
       </c>
-      <c r="G9" s="203">
+      <c r="G9" s="195">
         <v>101203</v>
       </c>
-      <c r="H9" s="203">
+      <c r="H9" s="195">
         <v>113608</v>
       </c>
-      <c r="I9" s="203">
+      <c r="I9" s="195">
         <v>118690</v>
       </c>
-      <c r="J9" s="203">
+      <c r="J9" s="195">
         <v>124241</v>
       </c>
-      <c r="K9" s="203">
+      <c r="K9" s="195">
         <v>123882.00000000001</v>
       </c>
-      <c r="L9" s="203">
+      <c r="L9" s="195">
         <v>125936</v>
       </c>
-      <c r="M9" s="203">
+      <c r="M9" s="195">
         <v>125673</v>
       </c>
-      <c r="N9" s="203">
+      <c r="N9" s="195">
         <v>128902</v>
       </c>
-      <c r="O9" s="203">
+      <c r="O9" s="195">
         <v>129730</v>
       </c>
-      <c r="P9" s="203">
+      <c r="P9" s="195">
         <v>133731</v>
       </c>
-      <c r="Q9" s="203">
+      <c r="Q9" s="195">
         <v>103696</v>
       </c>
-      <c r="R9" s="224">
+      <c r="R9" s="213">
         <v>118871</v>
       </c>
-      <c r="S9" s="203">
+      <c r="S9" s="195">
         <v>133683</v>
       </c>
-      <c r="T9" s="223">
+      <c r="T9" s="212">
         <v>137845</v>
       </c>
-      <c r="U9" s="203">
+      <c r="U9" s="195">
         <v>138383</v>
       </c>
-      <c r="V9" s="203">
+      <c r="V9" s="195">
         <v>140934.00773097412</v>
       </c>
-      <c r="W9" s="203">
+      <c r="W9" s="195">
         <f t="shared" si="1"/>
         <v>142508.05284370799</v>
       </c>
-      <c r="X9" s="203">
+      <c r="X9" s="195">
         <f t="shared" si="1"/>
         <v>144617.39069843045</v>
       </c>
-      <c r="Y9" s="203">
+      <c r="Y9" s="195">
         <f t="shared" si="1"/>
         <v>146495.26214098319</v>
       </c>
-      <c r="Z9" s="203">
+      <c r="Z9" s="195">
         <f t="shared" si="1"/>
         <v>148530.56737281344</v>
       </c>
-      <c r="AA9" s="203">
+      <c r="AA9" s="195">
         <f t="shared" si="1"/>
         <v>150526.70077861598</v>
       </c>
-      <c r="AB9" s="229"/>
-    </row>
-    <row r="10" spans="1:28" s="149" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="225" t="s">
+      <c r="AB9" s="218"/>
+    </row>
+    <row r="10" spans="1:28" s="148" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="214" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="226">
+      <c r="B10" s="215">
         <v>78708</v>
       </c>
-      <c r="C10" s="227">
+      <c r="C10" s="216">
         <v>92625</v>
       </c>
-      <c r="D10" s="201">
+      <c r="D10" s="193">
         <v>105460.99999999999</v>
       </c>
-      <c r="E10" s="200">
+      <c r="E10" s="192">
         <v>118656</v>
       </c>
-      <c r="F10" s="200">
+      <c r="F10" s="192">
         <v>108395</v>
       </c>
-      <c r="G10" s="200">
+      <c r="G10" s="192">
         <v>120134</v>
       </c>
-      <c r="H10" s="200">
+      <c r="H10" s="192">
         <v>144435.99999999997</v>
       </c>
-      <c r="I10" s="200">
+      <c r="I10" s="192">
         <v>157977</v>
       </c>
-      <c r="J10" s="200">
+      <c r="J10" s="192">
         <v>171443</v>
       </c>
-      <c r="K10" s="200">
+      <c r="K10" s="192">
         <v>184747</v>
       </c>
-      <c r="L10" s="200">
+      <c r="L10" s="192">
         <v>182750.00000000003</v>
       </c>
-      <c r="M10" s="200">
+      <c r="M10" s="192">
         <v>176279</v>
       </c>
-      <c r="N10" s="200">
+      <c r="N10" s="192">
         <v>178075</v>
       </c>
-      <c r="O10" s="200">
+      <c r="O10" s="192">
         <v>188413</v>
       </c>
-      <c r="P10" s="200">
+      <c r="P10" s="192">
         <v>202250.00000000003</v>
       </c>
-      <c r="Q10" s="200">
+      <c r="Q10" s="192">
         <v>161613</v>
       </c>
-      <c r="R10" s="202">
+      <c r="R10" s="194">
         <v>204810</v>
       </c>
-      <c r="S10" s="200">
+      <c r="S10" s="192">
         <v>253971.00000000003</v>
       </c>
-      <c r="T10" s="201">
+      <c r="T10" s="193">
         <v>228498.00000000003</v>
       </c>
-      <c r="U10" s="200">
+      <c r="U10" s="192">
         <v>231157</v>
       </c>
-      <c r="V10" s="200">
+      <c r="V10" s="192">
         <v>250618.83208520326</v>
       </c>
-      <c r="W10" s="200">
+      <c r="W10" s="192">
         <f t="shared" si="1"/>
         <v>262627.23298808624</v>
       </c>
-      <c r="X10" s="200">
+      <c r="X10" s="192">
         <f t="shared" si="1"/>
         <v>279974.82949480147</v>
       </c>
-      <c r="Y10" s="200">
+      <c r="Y10" s="192">
         <f t="shared" si="1"/>
         <v>295929.0641218159</v>
       </c>
-      <c r="Z10" s="200">
+      <c r="Z10" s="192">
         <f t="shared" si="1"/>
         <v>314134.41265649174</v>
       </c>
-      <c r="AA10" s="200">
+      <c r="AA10" s="192">
         <f t="shared" si="1"/>
         <v>332747.47830561764</v>
       </c>
-      <c r="AB10" s="229"/>
-    </row>
-    <row r="11" spans="1:28" s="149" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="216" t="s">
-        <v>79</v>
-      </c>
-      <c r="B11" s="218">
+      <c r="AB10" s="218"/>
+    </row>
+    <row r="11" spans="1:28" s="148" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="208" t="s">
+        <v>77</v>
+      </c>
+      <c r="B11" s="209">
         <f>SUM(B6:B9)-B10</f>
         <v>515253</v>
       </c>
-      <c r="C11" s="218">
+      <c r="C11" s="209">
         <f>SUM(C6:C9)-C10</f>
         <v>550290</v>
       </c>
-      <c r="D11" s="218">
+      <c r="D11" s="209">
         <f>SUM(D6:D9)-D10</f>
         <v>587167</v>
       </c>
-      <c r="E11" s="218">
+      <c r="E11" s="209">
         <f>SUM(E6:E9)-E10</f>
         <v>606628</v>
       </c>
-      <c r="F11" s="218">
+      <c r="F11" s="209">
         <f>SUM(F6:F9)-F10</f>
         <v>614270</v>
       </c>
-      <c r="G11" s="218">
+      <c r="G11" s="209">
         <f>SUM(G6:G9)-G10</f>
         <v>641639</v>
       </c>
-      <c r="H11" s="218">
+      <c r="H11" s="209">
         <f>SUM(H6:H9)-H10</f>
         <v>684066</v>
       </c>
-      <c r="I11" s="218">
+      <c r="I11" s="209">
         <f>SUM(I6:I9)-I10</f>
         <v>710814.99999999988</v>
       </c>
-      <c r="J11" s="218">
+      <c r="J11" s="209">
         <f>SUM(J6:J9)-J10</f>
         <v>746962</v>
       </c>
-      <c r="K11" s="218">
+      <c r="K11" s="209">
         <f>SUM(K6:K9)-K10</f>
         <v>780826</v>
       </c>
-      <c r="L11" s="218">
+      <c r="L11" s="209">
         <f>SUM(L6:L9)-L10</f>
         <v>804692</v>
       </c>
-      <c r="M11" s="218">
+      <c r="M11" s="209">
         <f>SUM(M6:M9)-M10</f>
         <v>821489</v>
       </c>
-      <c r="N11" s="218">
+      <c r="N11" s="209">
         <f>SUM(N6:N9)-N10</f>
         <v>832672.99999999988</v>
       </c>
-      <c r="O11" s="218">
+      <c r="O11" s="209">
         <f>SUM(O6:O9)-O10</f>
         <v>853678</v>
       </c>
-      <c r="P11" s="218">
+      <c r="P11" s="209">
         <f>SUM(P6:P9)-P10</f>
         <v>880508</v>
       </c>
-      <c r="Q11" s="218">
+      <c r="Q11" s="209">
         <f>SUM(Q6:Q9)-Q10</f>
         <v>819354</v>
       </c>
-      <c r="R11" s="218">
+      <c r="R11" s="209">
         <f>SUM(R6:R9)-R10</f>
         <v>908744</v>
       </c>
-      <c r="S11" s="218">
+      <c r="S11" s="209">
         <f>SUM(S6:S9)-S10</f>
         <v>975512</v>
       </c>
-      <c r="T11" s="218">
+      <c r="T11" s="209">
         <f>SUM(T6:T9)-T10</f>
         <v>979438</v>
       </c>
-      <c r="U11" s="218">
+      <c r="U11" s="209">
         <f>SUM(U6:U9)-U10</f>
         <v>994448</v>
       </c>
-      <c r="V11" s="218">
+      <c r="V11" s="209">
         <f>SUM(V6:V9)-V10</f>
         <v>1020004.9525913208</v>
       </c>
-      <c r="W11" s="218">
+      <c r="W11" s="209">
         <f t="shared" ref="W11:AA11" si="2">SUM(W6:W9)-W10</f>
         <v>1040766.230067855</v>
       </c>
-      <c r="X11" s="218">
+      <c r="X11" s="209">
         <f t="shared" si="2"/>
         <v>1064400.5040199826</v>
       </c>
-      <c r="Y11" s="218">
+      <c r="Y11" s="209">
         <f t="shared" si="2"/>
         <v>1087073.6884206454</v>
       </c>
-      <c r="Z11" s="218">
+      <c r="Z11" s="209">
         <f t="shared" si="2"/>
         <v>1110677.2931692586</v>
       </c>
-      <c r="AA11" s="218">
+      <c r="AA11" s="209">
         <f t="shared" si="2"/>
         <v>1134253.4692085322</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="217" t="s">
-        <v>82</v>
-      </c>
-      <c r="B12" s="219">
+      <c r="A12" s="251" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="252">
         <v>0</v>
       </c>
-      <c r="C12" s="220">
+      <c r="C12" s="253">
         <f>(C11/B11)-1</f>
         <v>6.7999604077996656E-2</v>
       </c>
-      <c r="D12" s="220">
+      <c r="D12" s="253">
         <f t="shared" ref="D12:V12" si="3">(D11/C11)-1</f>
         <v>6.7013756382998002E-2</v>
       </c>
-      <c r="E12" s="220">
+      <c r="E12" s="253">
         <f t="shared" si="3"/>
         <v>3.3143892623393345E-2</v>
       </c>
-      <c r="F12" s="220">
+      <c r="F12" s="253">
         <f t="shared" si="3"/>
         <v>1.2597506214681919E-2</v>
       </c>
-      <c r="G12" s="220">
+      <c r="G12" s="253">
         <f t="shared" si="3"/>
         <v>4.4555325833916637E-2</v>
       </c>
-      <c r="H12" s="220">
+      <c r="H12" s="253">
         <f t="shared" si="3"/>
         <v>6.6122851011238382E-2</v>
       </c>
-      <c r="I12" s="220">
+      <c r="I12" s="253">
         <f t="shared" si="3"/>
         <v>3.9102952054333784E-2</v>
       </c>
-      <c r="J12" s="220">
+      <c r="J12" s="253">
         <f t="shared" si="3"/>
         <v>5.0852894212981115E-2</v>
       </c>
-      <c r="K12" s="220">
+      <c r="K12" s="253">
         <f t="shared" si="3"/>
         <v>4.533563956399389E-2</v>
       </c>
-      <c r="L12" s="220">
+      <c r="L12" s="253">
         <f t="shared" si="3"/>
         <v>3.0565068273853635E-2</v>
       </c>
-      <c r="M12" s="220">
+      <c r="M12" s="253">
         <f t="shared" si="3"/>
         <v>2.0873825016279435E-2</v>
       </c>
-      <c r="N12" s="220">
+      <c r="N12" s="253">
         <f t="shared" si="3"/>
         <v>1.3614302808680145E-2</v>
       </c>
-      <c r="O12" s="220">
+      <c r="O12" s="253">
         <f t="shared" si="3"/>
         <v>2.5225989073742072E-2</v>
       </c>
-      <c r="P12" s="220">
+      <c r="P12" s="253">
         <f t="shared" si="3"/>
         <v>3.1428711996795089E-2</v>
       </c>
-      <c r="Q12" s="220">
+      <c r="Q12" s="253">
         <f t="shared" si="3"/>
         <v>-6.9453088444398015E-2</v>
       </c>
-      <c r="R12" s="220">
+      <c r="R12" s="253">
         <f t="shared" si="3"/>
         <v>0.1090981431713276</v>
       </c>
-      <c r="S12" s="220">
+      <c r="S12" s="253">
         <f t="shared" si="3"/>
         <v>7.347283723468867E-2</v>
       </c>
-      <c r="T12" s="220">
+      <c r="T12" s="253">
         <f t="shared" si="3"/>
         <v>4.0245532602367629E-3</v>
       </c>
-      <c r="U12" s="220">
+      <c r="U12" s="253">
         <f t="shared" si="3"/>
         <v>1.5325115014937163E-2</v>
       </c>
-      <c r="V12" s="220">
+      <c r="V12" s="253">
         <f t="shared" si="3"/>
         <v>2.5699636975810458E-2</v>
       </c>
-      <c r="W12" s="220">
+      <c r="W12" s="253">
         <f t="shared" ref="W12" si="4">(W11/V11)-1</f>
         <v>2.0354094775510756E-2</v>
       </c>
-      <c r="X12" s="220">
+      <c r="X12" s="253">
         <f t="shared" ref="X12" si="5">(X11/W11)-1</f>
         <v>2.2708532684219351E-2</v>
       </c>
-      <c r="Y12" s="220">
+      <c r="Y12" s="253">
         <f t="shared" ref="Y12" si="6">(Y11/X11)-1</f>
         <v>2.1301365712466103E-2</v>
       </c>
-      <c r="Z12" s="220">
+      <c r="Z12" s="253">
         <f t="shared" ref="Z12" si="7">(Z11/Y11)-1</f>
         <v>2.1712975854383698E-2</v>
       </c>
-      <c r="AA12" s="220">
+      <c r="AA12" s="253">
         <f t="shared" ref="AA12" si="8">(AA11/Z11)-1</f>
         <v>2.1226846163389324E-2</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="263"/>
-      <c r="B13" s="264"/>
-      <c r="C13" s="265"/>
-      <c r="D13" s="265"/>
-      <c r="E13" s="265"/>
-      <c r="F13" s="265"/>
-      <c r="G13" s="265"/>
-      <c r="H13" s="265"/>
-      <c r="I13" s="265"/>
-      <c r="J13" s="265"/>
-      <c r="K13" s="265"/>
-      <c r="L13" s="265"/>
-      <c r="M13" s="265"/>
-      <c r="N13" s="265"/>
-      <c r="O13" s="265"/>
-      <c r="P13" s="265"/>
-      <c r="Q13" s="265"/>
-      <c r="R13" s="265"/>
-      <c r="S13" s="265"/>
-      <c r="T13" s="265"/>
-      <c r="U13" s="265"/>
-      <c r="V13" s="265"/>
-      <c r="W13" s="265"/>
-      <c r="X13" s="265"/>
-      <c r="Y13" s="265"/>
-      <c r="Z13" s="265"/>
-      <c r="AA13" s="265"/>
+      <c r="A13" s="248"/>
+      <c r="B13" s="249"/>
+      <c r="C13" s="250"/>
+      <c r="D13" s="250"/>
+      <c r="E13" s="250"/>
+      <c r="F13" s="250"/>
+      <c r="G13" s="250"/>
+      <c r="H13" s="250"/>
+      <c r="I13" s="250"/>
+      <c r="J13" s="250"/>
+      <c r="K13" s="250"/>
+      <c r="L13" s="250"/>
+      <c r="M13" s="250"/>
+      <c r="N13" s="250"/>
+      <c r="O13" s="250"/>
+      <c r="P13" s="250"/>
+      <c r="Q13" s="250"/>
+      <c r="R13" s="250"/>
+      <c r="S13" s="250"/>
+      <c r="T13" s="250"/>
+      <c r="U13" s="250"/>
+      <c r="V13" s="250"/>
+      <c r="W13" s="250"/>
+      <c r="X13" s="250"/>
+      <c r="Y13" s="250"/>
+      <c r="Z13" s="250"/>
+      <c r="AA13" s="250"/>
     </row>
     <row r="14" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="198"/>
+      <c r="A14" s="190"/>
       <c r="B14" s="143"/>
       <c r="C14" s="143"/>
       <c r="D14" s="143"/>
@@ -19844,633 +19776,633 @@
       <c r="T14" s="143"/>
       <c r="U14" s="143"/>
       <c r="V14" s="143"/>
-      <c r="W14" s="230" t="s">
+      <c r="W14" s="219" t="s">
+        <v>82</v>
+      </c>
+      <c r="X14" s="220"/>
+      <c r="Y14" s="220"/>
+      <c r="Z14" s="220"/>
+      <c r="AA14" s="221"/>
+    </row>
+    <row r="15" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="234" t="s">
         <v>84</v>
       </c>
-      <c r="X14" s="231"/>
-      <c r="Y14" s="231"/>
-      <c r="Z14" s="231"/>
-      <c r="AA14" s="232"/>
-    </row>
-    <row r="15" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="249" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="161">
+      <c r="B15" s="157">
         <v>2005</v>
       </c>
-      <c r="C15" s="161">
+      <c r="C15" s="157">
         <v>2006</v>
       </c>
-      <c r="D15" s="161">
+      <c r="D15" s="157">
         <v>2007</v>
       </c>
-      <c r="E15" s="161">
+      <c r="E15" s="157">
         <v>2008</v>
       </c>
-      <c r="F15" s="161">
+      <c r="F15" s="157">
         <v>2009</v>
       </c>
-      <c r="G15" s="161">
+      <c r="G15" s="157">
         <v>2010</v>
       </c>
-      <c r="H15" s="161">
+      <c r="H15" s="157">
         <v>2011</v>
       </c>
-      <c r="I15" s="161">
+      <c r="I15" s="157">
         <v>2012</v>
       </c>
-      <c r="J15" s="161">
+      <c r="J15" s="157">
         <v>2013</v>
       </c>
-      <c r="K15" s="161">
+      <c r="K15" s="157">
         <v>2014</v>
       </c>
-      <c r="L15" s="161">
+      <c r="L15" s="157">
         <v>2015</v>
       </c>
-      <c r="M15" s="161">
+      <c r="M15" s="157">
         <v>2016</v>
       </c>
-      <c r="N15" s="161">
+      <c r="N15" s="157">
         <v>2017</v>
       </c>
-      <c r="O15" s="161">
+      <c r="O15" s="157">
         <v>2018</v>
       </c>
-      <c r="P15" s="161">
+      <c r="P15" s="157">
         <v>2019</v>
       </c>
-      <c r="Q15" s="161">
+      <c r="Q15" s="157">
         <v>2020</v>
       </c>
-      <c r="R15" s="161">
+      <c r="R15" s="157">
         <v>2021</v>
       </c>
-      <c r="S15" s="161">
+      <c r="S15" s="157">
         <v>2022</v>
       </c>
-      <c r="T15" s="161">
+      <c r="T15" s="157">
         <v>2023</v>
       </c>
-      <c r="U15" s="161">
+      <c r="U15" s="157">
         <v>2024</v>
       </c>
-      <c r="V15" s="161">
+      <c r="V15" s="157">
         <v>2025</v>
       </c>
-      <c r="W15" s="158">
+      <c r="W15" s="156">
         <v>2026</v>
       </c>
-      <c r="X15" s="158">
+      <c r="X15" s="156">
         <v>2027</v>
       </c>
-      <c r="Y15" s="158">
+      <c r="Y15" s="156">
         <v>2028</v>
       </c>
-      <c r="Z15" s="158">
+      <c r="Z15" s="156">
         <v>2029</v>
       </c>
-      <c r="AA15" s="158">
+      <c r="AA15" s="156">
         <v>2030</v>
       </c>
     </row>
     <row r="16" spans="1:28" s="143" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="213" t="s">
-        <v>81</v>
-      </c>
-      <c r="B16" s="250">
+      <c r="A16" s="205" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="235">
         <v>0</v>
       </c>
-      <c r="C16" s="251">
+      <c r="C16" s="236">
         <f>(C6/B6)-1</f>
         <v>6.3691966244290077E-2</v>
       </c>
-      <c r="D16" s="251">
+      <c r="D16" s="236">
         <f>(D6/C6)-1</f>
         <v>6.5528517089766147E-2</v>
       </c>
-      <c r="E16" s="251">
+      <c r="E16" s="236">
         <f>(E6/D6)-1</f>
         <v>4.1150024920242556E-2</v>
       </c>
-      <c r="F16" s="251">
+      <c r="F16" s="236">
         <f>(F6/E6)-1</f>
         <v>1.7082760263021024E-2</v>
       </c>
-      <c r="G16" s="251">
+      <c r="G16" s="236">
         <f>(G6/F6)-1</f>
         <v>5.0526094477202577E-2</v>
       </c>
-      <c r="H16" s="257">
+      <c r="H16" s="242">
         <f>(H6/G6)-1</f>
         <v>5.5007459563706451E-2</v>
       </c>
-      <c r="I16" s="257">
+      <c r="I16" s="242">
         <f>(I6/H6)-1</f>
         <v>5.6338665764155582E-2</v>
       </c>
-      <c r="J16" s="257">
+      <c r="J16" s="242">
         <f>(J6/I6)-1</f>
         <v>4.626897348303971E-2</v>
       </c>
-      <c r="K16" s="257">
+      <c r="K16" s="242">
         <f>(K6/J6)-1</f>
         <v>4.2490818199372393E-2</v>
       </c>
-      <c r="L16" s="257">
+      <c r="L16" s="242">
         <f>(L6/K6)-1</f>
         <v>3.0925153980287501E-2</v>
       </c>
-      <c r="M16" s="257">
+      <c r="M16" s="242">
         <f>(M6/L6)-1</f>
         <v>1.5836286984154624E-2</v>
       </c>
-      <c r="N16" s="257">
+      <c r="N16" s="242">
         <f>(N6/M6)-1</f>
         <v>2.0538143670531861E-2</v>
       </c>
-      <c r="O16" s="257">
+      <c r="O16" s="242">
         <f>(O6/N6)-1</f>
         <v>3.2364963631430266E-2</v>
       </c>
-      <c r="P16" s="257">
+      <c r="P16" s="242">
         <f>(P6/O6)-1</f>
         <v>4.0705551589474975E-2</v>
       </c>
-      <c r="Q16" s="257">
+      <c r="Q16" s="242">
         <f>(Q6/P6)-1</f>
         <v>-5.0072670629334182E-2</v>
       </c>
-      <c r="R16" s="257">
+      <c r="R16" s="242">
         <f>(R6/Q6)-1</f>
         <v>0.14724089489311276</v>
       </c>
-      <c r="S16" s="257">
+      <c r="S16" s="242">
         <f>(S6/R6)-1</f>
         <v>0.10789757758978991</v>
       </c>
-      <c r="T16" s="257">
+      <c r="T16" s="242">
         <f>(T6/S6)-1</f>
         <v>5.1322260068773495E-3</v>
       </c>
-      <c r="U16" s="257">
+      <c r="U16" s="242">
         <f>(U6/T6)-1</f>
         <v>1.6401564432128035E-2</v>
       </c>
-      <c r="V16" s="257">
+      <c r="V16" s="242">
         <f>(V6/U6)-1</f>
         <v>3.6317462255631039E-2</v>
       </c>
-      <c r="W16" s="260">
+      <c r="W16" s="245">
         <f>AVERAGE(U16:V16)</f>
         <v>2.6359513343879537E-2</v>
       </c>
-      <c r="X16" s="260">
+      <c r="X16" s="245">
         <f t="shared" ref="X16:AA20" si="9">AVERAGE(V16:W16)</f>
         <v>3.1338487799755288E-2</v>
       </c>
-      <c r="Y16" s="260">
+      <c r="Y16" s="245">
         <f t="shared" si="9"/>
         <v>2.8849000571817413E-2</v>
       </c>
-      <c r="Z16" s="260">
+      <c r="Z16" s="245">
         <f t="shared" si="9"/>
         <v>3.009374418578635E-2</v>
       </c>
-      <c r="AA16" s="260">
+      <c r="AA16" s="245">
         <f t="shared" si="9"/>
         <v>2.9471372378801881E-2</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="214" t="s">
+      <c r="A17" s="206" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="252">
+      <c r="B17" s="237">
         <v>0</v>
       </c>
-      <c r="C17" s="253">
+      <c r="C17" s="238">
         <f>(C7/B7)-1</f>
         <v>5.2134991119005436E-2</v>
       </c>
-      <c r="D17" s="253">
+      <c r="D17" s="238">
         <f>(D7/C7)-1</f>
         <v>4.5689049754200406E-2</v>
       </c>
-      <c r="E17" s="253">
+      <c r="E17" s="238">
         <f>(E7/D7)-1</f>
         <v>4.6973278055458589E-2</v>
       </c>
-      <c r="F17" s="253">
+      <c r="F17" s="238">
         <f>(F7/E7)-1</f>
         <v>4.7629033849797775E-2</v>
       </c>
-      <c r="G17" s="253">
+      <c r="G17" s="238">
         <f>(G7/F7)-1</f>
         <v>5.2257874595231124E-2</v>
       </c>
-      <c r="H17" s="258">
+      <c r="H17" s="243">
         <f>(H7/G7)-1</f>
         <v>6.4769535490079688E-2</v>
       </c>
-      <c r="I17" s="258">
+      <c r="I17" s="243">
         <f>(I7/H7)-1</f>
         <v>4.8070960893737302E-2</v>
       </c>
-      <c r="J17" s="258">
+      <c r="J17" s="243">
         <f>(J7/I7)-1</f>
         <v>8.89546252193536E-2</v>
       </c>
-      <c r="K17" s="258">
+      <c r="K17" s="243">
         <f>(K7/J7)-1</f>
         <v>4.6760469998894605E-2</v>
       </c>
-      <c r="L17" s="258">
+      <c r="L17" s="243">
         <f>(L7/K7)-1</f>
         <v>4.850713443707444E-2</v>
       </c>
-      <c r="M17" s="258">
+      <c r="M17" s="243">
         <f>(M7/L7)-1</f>
         <v>1.8240091284357662E-2</v>
       </c>
-      <c r="N17" s="258">
+      <c r="N17" s="243">
         <f>(N7/M7)-1</f>
         <v>3.6428206522634676E-2</v>
       </c>
-      <c r="O17" s="258">
+      <c r="O17" s="243">
         <f>(O7/N7)-1</f>
         <v>7.3515498914797694E-2</v>
       </c>
-      <c r="P17" s="258">
+      <c r="P17" s="243">
         <f>(P7/O7)-1</f>
         <v>5.2743834703399273E-2</v>
       </c>
-      <c r="Q17" s="258">
+      <c r="Q17" s="243">
         <f>(Q7/P7)-1</f>
         <v>-7.6045359896448339E-3</v>
       </c>
-      <c r="R17" s="258">
+      <c r="R17" s="243">
         <f>(R7/Q7)-1</f>
         <v>9.818460207980384E-2</v>
       </c>
-      <c r="S17" s="258">
+      <c r="S17" s="243">
         <f>(S7/R7)-1</f>
         <v>9.8759375685828488E-3</v>
       </c>
-      <c r="T17" s="258">
+      <c r="T17" s="243">
         <f>(T7/S7)-1</f>
         <v>1.5506353386342209E-2</v>
       </c>
-      <c r="U17" s="258">
+      <c r="U17" s="243">
         <f>(U7/T7)-1</f>
         <v>5.8724304183082054E-3</v>
       </c>
-      <c r="V17" s="258">
+      <c r="V17" s="243">
         <f>(V7/U7)-1</f>
         <v>7.142956962230218E-2</v>
       </c>
-      <c r="W17" s="261">
+      <c r="W17" s="246">
         <f t="shared" ref="W17:W20" si="10">AVERAGE(U17:V17)</f>
         <v>3.8651000020305193E-2</v>
       </c>
-      <c r="X17" s="261">
+      <c r="X17" s="246">
         <f t="shared" si="9"/>
         <v>5.5040284821303687E-2</v>
       </c>
-      <c r="Y17" s="261">
+      <c r="Y17" s="246">
         <f t="shared" si="9"/>
         <v>4.684564242080444E-2</v>
       </c>
-      <c r="Z17" s="261">
+      <c r="Z17" s="246">
         <f t="shared" si="9"/>
         <v>5.0942963621054063E-2</v>
       </c>
-      <c r="AA17" s="261">
+      <c r="AA17" s="246">
         <f t="shared" si="9"/>
         <v>4.8894303020929251E-2</v>
       </c>
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A18" s="228" t="s">
+      <c r="A18" s="217" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="254">
+      <c r="B18" s="239">
         <v>0</v>
       </c>
-      <c r="C18" s="253">
+      <c r="C18" s="238">
         <f>(C8/B8)-1</f>
         <v>0.16933809963099611</v>
       </c>
-      <c r="D18" s="253">
+      <c r="D18" s="238">
         <f>(D8/C8)-1</f>
         <v>0.15797051427444408</v>
       </c>
-      <c r="E18" s="253">
+      <c r="E18" s="238">
         <f>(E8/D8)-1</f>
         <v>9.0833219784711705E-2</v>
       </c>
-      <c r="F18" s="253">
+      <c r="F18" s="238">
         <f>(F8/E8)-1</f>
         <v>-6.2955734249355966E-2</v>
       </c>
-      <c r="G18" s="253">
+      <c r="G18" s="238">
         <f>(G8/F8)-1</f>
         <v>9.5620948794427951E-2</v>
       </c>
-      <c r="H18" s="258">
+      <c r="H18" s="243">
         <f>(H8/G8)-1</f>
         <v>0.18515927393291398</v>
       </c>
-      <c r="I18" s="258">
+      <c r="I18" s="243">
         <f>(I8/H8)-1</f>
         <v>2.8867130354438775E-2</v>
       </c>
-      <c r="J18" s="258">
+      <c r="J18" s="243">
         <f>(J8/I8)-1</f>
         <v>7.8066242181215051E-2</v>
       </c>
-      <c r="K18" s="258">
+      <c r="K18" s="243">
         <f>(K8/J8)-1</f>
         <v>0.1195356021033267</v>
       </c>
-      <c r="L18" s="258">
+      <c r="L18" s="243">
         <f>(L8/K8)-1</f>
         <v>-1.1512248557093652E-2</v>
       </c>
-      <c r="M18" s="258">
+      <c r="M18" s="243">
         <f>(M8/L8)-1</f>
         <v>-1.6256762761035493E-3</v>
       </c>
-      <c r="N18" s="258">
+      <c r="N18" s="243">
         <f>(N8/M8)-1</f>
         <v>-3.2283736661884666E-2</v>
       </c>
-      <c r="O18" s="258">
+      <c r="O18" s="243">
         <f>(O8/N8)-1</f>
         <v>1.5041011102213897E-2</v>
       </c>
-      <c r="P18" s="258">
+      <c r="P18" s="243">
         <f>(P8/O8)-1</f>
         <v>2.9524327320796795E-2</v>
       </c>
-      <c r="Q18" s="258">
+      <c r="Q18" s="243">
         <f>(Q8/P8)-1</f>
         <v>-0.20680621495544849</v>
       </c>
-      <c r="R18" s="258">
+      <c r="R18" s="243">
         <f>(R8/Q8)-1</f>
         <v>0.11566353139298835</v>
       </c>
-      <c r="S18" s="258">
+      <c r="S18" s="243">
         <f>(S8/R8)-1</f>
         <v>0.16042896508954319</v>
       </c>
-      <c r="T18" s="258">
+      <c r="T18" s="243">
         <f>(T8/S8)-1</f>
         <v>-0.16102327269793892</v>
       </c>
-      <c r="U18" s="258">
+      <c r="U18" s="243">
         <f>(U8/T8)-1</f>
         <v>2.3929425621672218E-2</v>
       </c>
-      <c r="V18" s="258">
+      <c r="V18" s="243">
         <f>(V8/U8)-1</f>
         <v>2.0889920449185251E-2</v>
       </c>
-      <c r="W18" s="261">
+      <c r="W18" s="246">
         <f t="shared" si="10"/>
         <v>2.2409673035428734E-2</v>
       </c>
-      <c r="X18" s="261">
+      <c r="X18" s="246">
         <f t="shared" si="9"/>
         <v>2.1649796742306993E-2</v>
       </c>
-      <c r="Y18" s="261">
+      <c r="Y18" s="246">
         <f t="shared" si="9"/>
         <v>2.2029734888867863E-2</v>
       </c>
-      <c r="Z18" s="261">
+      <c r="Z18" s="246">
         <f t="shared" si="9"/>
         <v>2.1839765815587428E-2</v>
       </c>
-      <c r="AA18" s="261">
+      <c r="AA18" s="246">
         <f t="shared" si="9"/>
         <v>2.1934750352227646E-2</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A19" s="221" t="s">
+      <c r="A19" s="210" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="254">
+      <c r="B19" s="239">
         <v>0</v>
       </c>
-      <c r="C19" s="253">
+      <c r="C19" s="238">
         <f>(C9/B9)-1</f>
         <v>9.5182978723404421E-2</v>
       </c>
-      <c r="D19" s="253">
+      <c r="D19" s="238">
         <f>(D9/C9)-1</f>
         <v>6.2198874762985135E-2</v>
       </c>
-      <c r="E19" s="253">
+      <c r="E19" s="238">
         <f>(E9/D9)-1</f>
         <v>2.0367552382067E-2</v>
       </c>
-      <c r="F19" s="253">
+      <c r="F19" s="238">
         <f>(F9/E9)-1</f>
         <v>-5.2063018622614532E-2</v>
       </c>
-      <c r="G19" s="253">
+      <c r="G19" s="238">
         <f>(G9/F9)-1</f>
         <v>2.0623651142620769E-2</v>
       </c>
-      <c r="H19" s="258">
+      <c r="H19" s="243">
         <f>(H9/G9)-1</f>
         <v>0.1225754177247711</v>
       </c>
-      <c r="I19" s="258">
+      <c r="I19" s="243">
         <f>(I9/H9)-1</f>
         <v>4.4732765298218347E-2</v>
       </c>
-      <c r="J19" s="258">
+      <c r="J19" s="243">
         <f>(J9/I9)-1</f>
         <v>4.6768893756845564E-2</v>
       </c>
-      <c r="K19" s="258">
+      <c r="K19" s="243">
         <f>(K9/J9)-1</f>
         <v>-2.8895453191779552E-3</v>
       </c>
-      <c r="L19" s="258">
+      <c r="L19" s="243">
         <f>(L9/K9)-1</f>
         <v>1.6580294150885466E-2</v>
       </c>
-      <c r="M19" s="258">
+      <c r="M19" s="243">
         <f>(M9/L9)-1</f>
         <v>-2.0883623427773168E-3</v>
       </c>
-      <c r="N19" s="258">
+      <c r="N19" s="243">
         <f>(N9/M9)-1</f>
         <v>2.5693665305992486E-2</v>
       </c>
-      <c r="O19" s="258">
+      <c r="O19" s="243">
         <f>(O9/N9)-1</f>
         <v>6.423484507610322E-3</v>
       </c>
-      <c r="P19" s="258">
+      <c r="P19" s="243">
         <f>(P9/O9)-1</f>
         <v>3.0840977414630322E-2</v>
       </c>
-      <c r="Q19" s="258">
+      <c r="Q19" s="243">
         <f>(Q9/P9)-1</f>
         <v>-0.2245926524141747</v>
       </c>
-      <c r="R19" s="258">
+      <c r="R19" s="243">
         <f>(R9/Q9)-1</f>
         <v>0.14634122820552387</v>
       </c>
-      <c r="S19" s="258">
+      <c r="S19" s="243">
         <f>(S9/R9)-1</f>
         <v>0.12460566496454129</v>
       </c>
-      <c r="T19" s="258">
+      <c r="T19" s="243">
         <f>(T9/S9)-1</f>
         <v>3.1133352782328316E-2</v>
       </c>
-      <c r="U19" s="258">
+      <c r="U19" s="243">
         <f>(U9/T9)-1</f>
         <v>3.9029344553664913E-3</v>
       </c>
-      <c r="V19" s="258">
+      <c r="V19" s="243">
         <f>(V9/U9)-1</f>
         <v>1.8434401125673849E-2</v>
       </c>
-      <c r="W19" s="261">
+      <c r="W19" s="246">
         <f t="shared" si="10"/>
         <v>1.116866779052017E-2</v>
       </c>
-      <c r="X19" s="261">
+      <c r="X19" s="246">
         <f t="shared" si="9"/>
         <v>1.480153445809701E-2</v>
       </c>
-      <c r="Y19" s="261">
+      <c r="Y19" s="246">
         <f t="shared" si="9"/>
         <v>1.298510112430859E-2</v>
       </c>
-      <c r="Z19" s="261">
+      <c r="Z19" s="246">
         <f t="shared" si="9"/>
         <v>1.38933177912028E-2</v>
       </c>
-      <c r="AA19" s="261">
+      <c r="AA19" s="246">
         <f t="shared" si="9"/>
         <v>1.3439209457755695E-2</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="225" t="s">
+      <c r="A20" s="214" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="255">
+      <c r="B20" s="240">
         <v>0</v>
       </c>
-      <c r="C20" s="256">
+      <c r="C20" s="241">
         <f>(C10/B10)-1</f>
         <v>0.17681811251715196</v>
       </c>
-      <c r="D20" s="256">
+      <c r="D20" s="241">
         <f>(D10/C10)-1</f>
         <v>0.13858029689608631</v>
       </c>
-      <c r="E20" s="256">
+      <c r="E20" s="241">
         <f>(E10/D10)-1</f>
         <v>0.12511734195579427</v>
       </c>
-      <c r="F20" s="256">
+      <c r="F20" s="241">
         <f>(F10/E10)-1</f>
         <v>-8.6476874325782105E-2</v>
       </c>
-      <c r="G20" s="256">
+      <c r="G20" s="241">
         <f>(G10/F10)-1</f>
         <v>0.10829835324507586</v>
       </c>
-      <c r="H20" s="259">
+      <c r="H20" s="244">
         <f>(H10/G10)-1</f>
         <v>0.20229077530091377</v>
       </c>
-      <c r="I20" s="259">
+      <c r="I20" s="244">
         <f>(I10/H10)-1</f>
         <v>9.3750865435210384E-2</v>
       </c>
-      <c r="J20" s="259">
+      <c r="J20" s="244">
         <f>(J10/I10)-1</f>
         <v>8.5240256493033906E-2</v>
       </c>
-      <c r="K20" s="259">
+      <c r="K20" s="244">
         <f>(K10/J10)-1</f>
         <v>7.7600135321943764E-2</v>
       </c>
-      <c r="L20" s="259">
+      <c r="L20" s="244">
         <f>(L10/K10)-1</f>
         <v>-1.0809377148207955E-2</v>
       </c>
-      <c r="M20" s="259">
+      <c r="M20" s="244">
         <f>(M10/L10)-1</f>
         <v>-3.5409028727770298E-2</v>
       </c>
-      <c r="N20" s="259">
+      <c r="N20" s="244">
         <f>(N10/M10)-1</f>
         <v>1.0188394533665379E-2</v>
       </c>
-      <c r="O20" s="259">
+      <c r="O20" s="244">
         <f>(O10/N10)-1</f>
         <v>5.8054190650006943E-2</v>
       </c>
-      <c r="P20" s="259">
+      <c r="P20" s="244">
         <f>(P10/O10)-1</f>
         <v>7.3439730804137904E-2</v>
       </c>
-      <c r="Q20" s="259">
+      <c r="Q20" s="244">
         <f>(Q10/P10)-1</f>
         <v>-0.20092459826946862</v>
       </c>
-      <c r="R20" s="259">
+      <c r="R20" s="244">
         <f>(R10/Q10)-1</f>
         <v>0.26728666629540943</v>
       </c>
-      <c r="S20" s="259">
+      <c r="S20" s="244">
         <f>(S10/R10)-1</f>
         <v>0.24003222498901433</v>
       </c>
-      <c r="T20" s="259">
+      <c r="T20" s="244">
         <f>(T10/S10)-1</f>
         <v>-0.10029885301865171</v>
       </c>
-      <c r="U20" s="259">
+      <c r="U20" s="244">
         <f>(U10/T10)-1</f>
         <v>1.1636863342348702E-2</v>
       </c>
-      <c r="V20" s="259">
+      <c r="V20" s="244">
         <f>(V10/U10)-1</f>
         <v>8.4193133174436774E-2</v>
       </c>
-      <c r="W20" s="262">
+      <c r="W20" s="247">
         <f t="shared" si="10"/>
         <v>4.7914998258392738E-2</v>
       </c>
-      <c r="X20" s="262">
+      <c r="X20" s="247">
         <f t="shared" si="9"/>
         <v>6.6054065716414756E-2</v>
       </c>
-      <c r="Y20" s="262">
+      <c r="Y20" s="247">
         <f t="shared" si="9"/>
         <v>5.6984531987403747E-2</v>
       </c>
-      <c r="Z20" s="262">
+      <c r="Z20" s="247">
         <f t="shared" si="9"/>
         <v>6.1519298851909252E-2</v>
       </c>
-      <c r="AA20" s="262">
+      <c r="AA20" s="247">
         <f t="shared" si="9"/>
         <v>5.9251915419656499E-2</v>
       </c>
@@ -20502,13 +20434,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:86" s="81" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="183"/>
-      <c r="B1" s="183"/>
-      <c r="C1" s="183"/>
-      <c r="D1" s="183"/>
-      <c r="E1" s="183"/>
-      <c r="F1" s="183"/>
-      <c r="G1" s="183"/>
+      <c r="A1" s="175"/>
+      <c r="B1" s="175"/>
+      <c r="C1" s="175"/>
+      <c r="D1" s="175"/>
+      <c r="E1" s="175"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="175"/>
     </row>
     <row r="2" spans="1:86" s="81" customFormat="1" ht="8.4499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="82"/>
@@ -20520,24 +20452,24 @@
       <c r="G2" s="82"/>
     </row>
     <row r="3" spans="1:86" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="176" t="s">
+      <c r="A3" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="176"/>
-      <c r="C3" s="176"/>
-      <c r="D3" s="176"/>
-      <c r="E3" s="176"/>
-      <c r="F3" s="176"/>
-      <c r="G3" s="176"/>
+      <c r="B3" s="168"/>
+      <c r="C3" s="168"/>
+      <c r="D3" s="168"/>
+      <c r="E3" s="168"/>
+      <c r="F3" s="168"/>
+      <c r="G3" s="168"/>
     </row>
     <row r="4" spans="1:86" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="176"/>
-      <c r="B4" s="176"/>
-      <c r="C4" s="176"/>
-      <c r="D4" s="176"/>
-      <c r="E4" s="176"/>
-      <c r="F4" s="176"/>
-      <c r="G4" s="176"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="168"/>
+      <c r="C4" s="168"/>
+      <c r="D4" s="168"/>
+      <c r="E4" s="168"/>
+      <c r="F4" s="168"/>
+      <c r="G4" s="168"/>
     </row>
     <row r="5" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
@@ -20600,142 +20532,142 @@
       <c r="D9" s="13"/>
     </row>
     <row r="10" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="180" t="s">
+      <c r="A10" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="178" t="s">
+      <c r="B10" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="178">
+      <c r="C10" s="170">
         <v>2005</v>
       </c>
-      <c r="D10" s="178"/>
-      <c r="E10" s="178"/>
-      <c r="F10" s="178"/>
-      <c r="G10" s="178">
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="170"/>
+      <c r="G10" s="170">
         <v>2006</v>
       </c>
-      <c r="H10" s="178"/>
-      <c r="I10" s="178"/>
-      <c r="J10" s="178"/>
-      <c r="K10" s="178">
+      <c r="H10" s="170"/>
+      <c r="I10" s="170"/>
+      <c r="J10" s="170"/>
+      <c r="K10" s="170">
         <v>2007</v>
       </c>
-      <c r="L10" s="178"/>
-      <c r="M10" s="178"/>
-      <c r="N10" s="178"/>
-      <c r="O10" s="178">
+      <c r="L10" s="170"/>
+      <c r="M10" s="170"/>
+      <c r="N10" s="170"/>
+      <c r="O10" s="170">
         <v>2008</v>
       </c>
-      <c r="P10" s="178"/>
-      <c r="Q10" s="178"/>
-      <c r="R10" s="178"/>
-      <c r="S10" s="178">
+      <c r="P10" s="170"/>
+      <c r="Q10" s="170"/>
+      <c r="R10" s="170"/>
+      <c r="S10" s="170">
         <v>2009</v>
       </c>
-      <c r="T10" s="178"/>
-      <c r="U10" s="178"/>
-      <c r="V10" s="178"/>
-      <c r="W10" s="178">
+      <c r="T10" s="170"/>
+      <c r="U10" s="170"/>
+      <c r="V10" s="170"/>
+      <c r="W10" s="170">
         <v>2010</v>
       </c>
-      <c r="X10" s="178"/>
-      <c r="Y10" s="178"/>
-      <c r="Z10" s="178"/>
-      <c r="AA10" s="178">
+      <c r="X10" s="170"/>
+      <c r="Y10" s="170"/>
+      <c r="Z10" s="170"/>
+      <c r="AA10" s="170">
         <v>2011</v>
       </c>
-      <c r="AB10" s="178"/>
-      <c r="AC10" s="178"/>
-      <c r="AD10" s="178"/>
-      <c r="AE10" s="178">
+      <c r="AB10" s="170"/>
+      <c r="AC10" s="170"/>
+      <c r="AD10" s="170"/>
+      <c r="AE10" s="170">
         <v>2012</v>
       </c>
-      <c r="AF10" s="178"/>
-      <c r="AG10" s="178"/>
-      <c r="AH10" s="178"/>
-      <c r="AI10" s="178">
+      <c r="AF10" s="170"/>
+      <c r="AG10" s="170"/>
+      <c r="AH10" s="170"/>
+      <c r="AI10" s="170">
         <v>2013</v>
       </c>
-      <c r="AJ10" s="178"/>
-      <c r="AK10" s="178"/>
-      <c r="AL10" s="178"/>
-      <c r="AM10" s="178">
+      <c r="AJ10" s="170"/>
+      <c r="AK10" s="170"/>
+      <c r="AL10" s="170"/>
+      <c r="AM10" s="170">
         <v>2014</v>
       </c>
-      <c r="AN10" s="178"/>
-      <c r="AO10" s="178"/>
-      <c r="AP10" s="178"/>
-      <c r="AQ10" s="178">
+      <c r="AN10" s="170"/>
+      <c r="AO10" s="170"/>
+      <c r="AP10" s="170"/>
+      <c r="AQ10" s="170">
         <v>2015</v>
       </c>
-      <c r="AR10" s="178"/>
-      <c r="AS10" s="178"/>
-      <c r="AT10" s="178"/>
-      <c r="AU10" s="178">
+      <c r="AR10" s="170"/>
+      <c r="AS10" s="170"/>
+      <c r="AT10" s="170"/>
+      <c r="AU10" s="170">
         <v>2016</v>
       </c>
-      <c r="AV10" s="178"/>
-      <c r="AW10" s="178"/>
-      <c r="AX10" s="178"/>
-      <c r="AY10" s="178">
+      <c r="AV10" s="170"/>
+      <c r="AW10" s="170"/>
+      <c r="AX10" s="170"/>
+      <c r="AY10" s="170">
         <v>2017</v>
       </c>
-      <c r="AZ10" s="178"/>
-      <c r="BA10" s="178"/>
-      <c r="BB10" s="178"/>
-      <c r="BC10" s="178">
+      <c r="AZ10" s="170"/>
+      <c r="BA10" s="170"/>
+      <c r="BB10" s="170"/>
+      <c r="BC10" s="170">
         <v>2018</v>
       </c>
-      <c r="BD10" s="178"/>
-      <c r="BE10" s="178"/>
-      <c r="BF10" s="178"/>
-      <c r="BG10" s="178">
+      <c r="BD10" s="170"/>
+      <c r="BE10" s="170"/>
+      <c r="BF10" s="170"/>
+      <c r="BG10" s="170">
         <v>2019</v>
       </c>
-      <c r="BH10" s="178"/>
-      <c r="BI10" s="178"/>
-      <c r="BJ10" s="178"/>
-      <c r="BK10" s="178">
+      <c r="BH10" s="170"/>
+      <c r="BI10" s="170"/>
+      <c r="BJ10" s="170"/>
+      <c r="BK10" s="170">
         <v>2020</v>
       </c>
-      <c r="BL10" s="178"/>
-      <c r="BM10" s="178"/>
-      <c r="BN10" s="178"/>
-      <c r="BO10" s="178">
+      <c r="BL10" s="170"/>
+      <c r="BM10" s="170"/>
+      <c r="BN10" s="170"/>
+      <c r="BO10" s="170">
         <v>2021</v>
       </c>
-      <c r="BP10" s="178"/>
-      <c r="BQ10" s="178"/>
-      <c r="BR10" s="178"/>
-      <c r="BS10" s="178">
+      <c r="BP10" s="170"/>
+      <c r="BQ10" s="170"/>
+      <c r="BR10" s="170"/>
+      <c r="BS10" s="170">
         <v>2022</v>
       </c>
-      <c r="BT10" s="178"/>
-      <c r="BU10" s="178"/>
-      <c r="BV10" s="178"/>
-      <c r="BW10" s="178">
+      <c r="BT10" s="170"/>
+      <c r="BU10" s="170"/>
+      <c r="BV10" s="170"/>
+      <c r="BW10" s="170">
         <v>2023</v>
       </c>
-      <c r="BX10" s="178"/>
-      <c r="BY10" s="178"/>
-      <c r="BZ10" s="178"/>
-      <c r="CA10" s="178" t="s">
+      <c r="BX10" s="170"/>
+      <c r="BY10" s="170"/>
+      <c r="BZ10" s="170"/>
+      <c r="CA10" s="170" t="s">
         <v>12</v>
       </c>
-      <c r="CB10" s="178"/>
-      <c r="CC10" s="178"/>
-      <c r="CD10" s="178"/>
-      <c r="CE10" s="178" t="s">
+      <c r="CB10" s="170"/>
+      <c r="CC10" s="170"/>
+      <c r="CD10" s="170"/>
+      <c r="CE10" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="CF10" s="178"/>
-      <c r="CG10" s="178"/>
-      <c r="CH10" s="179"/>
+      <c r="CF10" s="170"/>
+      <c r="CG10" s="170"/>
+      <c r="CH10" s="171"/>
     </row>
     <row r="11" spans="1:86" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="181"/>
-      <c r="B11" s="182"/>
+      <c r="A11" s="173"/>
+      <c r="B11" s="174"/>
       <c r="C11" s="84" t="s">
         <v>14</v>
       </c>
@@ -22769,25 +22701,25 @@
       <c r="Q27" s="25"/>
     </row>
     <row r="28" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="176" t="s">
+      <c r="A28" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B28" s="176"/>
-      <c r="C28" s="176"/>
-      <c r="D28" s="176"/>
-      <c r="E28" s="176"/>
-      <c r="F28" s="176"/>
-      <c r="G28" s="176"/>
+      <c r="B28" s="168"/>
+      <c r="C28" s="168"/>
+      <c r="D28" s="168"/>
+      <c r="E28" s="168"/>
+      <c r="F28" s="168"/>
+      <c r="G28" s="168"/>
       <c r="BH28" s="1"/>
     </row>
     <row r="29" spans="1:86" s="2" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="176"/>
-      <c r="B29" s="176"/>
-      <c r="C29" s="176"/>
-      <c r="D29" s="176"/>
-      <c r="E29" s="176"/>
-      <c r="F29" s="176"/>
-      <c r="G29" s="176"/>
+      <c r="A29" s="168"/>
+      <c r="B29" s="168"/>
+      <c r="C29" s="168"/>
+      <c r="D29" s="168"/>
+      <c r="E29" s="168"/>
+      <c r="F29" s="168"/>
+      <c r="G29" s="168"/>
     </row>
     <row r="30" spans="1:86" s="2" customFormat="1" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
@@ -22826,140 +22758,140 @@
       <c r="BH33" s="2"/>
     </row>
     <row r="34" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="180" t="s">
+      <c r="A34" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="B34" s="178" t="s">
+      <c r="B34" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="178"/>
-      <c r="D34" s="178"/>
-      <c r="E34" s="178"/>
-      <c r="F34" s="178"/>
-      <c r="G34" s="178">
+      <c r="C34" s="170"/>
+      <c r="D34" s="170"/>
+      <c r="E34" s="170"/>
+      <c r="F34" s="170"/>
+      <c r="G34" s="170">
         <v>2006</v>
       </c>
-      <c r="H34" s="178"/>
-      <c r="I34" s="178"/>
-      <c r="J34" s="178"/>
-      <c r="K34" s="178">
+      <c r="H34" s="170"/>
+      <c r="I34" s="170"/>
+      <c r="J34" s="170"/>
+      <c r="K34" s="170">
         <v>2007</v>
       </c>
-      <c r="L34" s="178"/>
-      <c r="M34" s="178"/>
-      <c r="N34" s="178"/>
-      <c r="O34" s="178">
+      <c r="L34" s="170"/>
+      <c r="M34" s="170"/>
+      <c r="N34" s="170"/>
+      <c r="O34" s="170">
         <v>2008</v>
       </c>
-      <c r="P34" s="178"/>
-      <c r="Q34" s="178"/>
-      <c r="R34" s="178"/>
-      <c r="S34" s="178">
+      <c r="P34" s="170"/>
+      <c r="Q34" s="170"/>
+      <c r="R34" s="170"/>
+      <c r="S34" s="170">
         <v>2009</v>
       </c>
-      <c r="T34" s="178"/>
-      <c r="U34" s="178"/>
-      <c r="V34" s="178"/>
-      <c r="W34" s="178">
+      <c r="T34" s="170"/>
+      <c r="U34" s="170"/>
+      <c r="V34" s="170"/>
+      <c r="W34" s="170">
         <v>2010</v>
       </c>
-      <c r="X34" s="178"/>
-      <c r="Y34" s="178"/>
-      <c r="Z34" s="178"/>
-      <c r="AA34" s="178">
+      <c r="X34" s="170"/>
+      <c r="Y34" s="170"/>
+      <c r="Z34" s="170"/>
+      <c r="AA34" s="170">
         <v>2011</v>
       </c>
-      <c r="AB34" s="178"/>
-      <c r="AC34" s="178"/>
-      <c r="AD34" s="178"/>
-      <c r="AE34" s="178">
+      <c r="AB34" s="170"/>
+      <c r="AC34" s="170"/>
+      <c r="AD34" s="170"/>
+      <c r="AE34" s="170">
         <v>2012</v>
       </c>
-      <c r="AF34" s="178"/>
-      <c r="AG34" s="178"/>
-      <c r="AH34" s="178"/>
-      <c r="AI34" s="178">
+      <c r="AF34" s="170"/>
+      <c r="AG34" s="170"/>
+      <c r="AH34" s="170"/>
+      <c r="AI34" s="170">
         <v>2013</v>
       </c>
-      <c r="AJ34" s="178"/>
-      <c r="AK34" s="178"/>
-      <c r="AL34" s="178"/>
-      <c r="AM34" s="178">
+      <c r="AJ34" s="170"/>
+      <c r="AK34" s="170"/>
+      <c r="AL34" s="170"/>
+      <c r="AM34" s="170">
         <v>2014</v>
       </c>
-      <c r="AN34" s="178"/>
-      <c r="AO34" s="178"/>
-      <c r="AP34" s="178"/>
-      <c r="AQ34" s="178">
+      <c r="AN34" s="170"/>
+      <c r="AO34" s="170"/>
+      <c r="AP34" s="170"/>
+      <c r="AQ34" s="170">
         <v>2015</v>
       </c>
-      <c r="AR34" s="178"/>
-      <c r="AS34" s="178"/>
-      <c r="AT34" s="178"/>
-      <c r="AU34" s="178">
+      <c r="AR34" s="170"/>
+      <c r="AS34" s="170"/>
+      <c r="AT34" s="170"/>
+      <c r="AU34" s="170">
         <v>2016</v>
       </c>
-      <c r="AV34" s="178"/>
-      <c r="AW34" s="178"/>
-      <c r="AX34" s="178"/>
-      <c r="AY34" s="178">
+      <c r="AV34" s="170"/>
+      <c r="AW34" s="170"/>
+      <c r="AX34" s="170"/>
+      <c r="AY34" s="170">
         <v>2017</v>
       </c>
-      <c r="AZ34" s="178"/>
-      <c r="BA34" s="178"/>
-      <c r="BB34" s="178"/>
-      <c r="BC34" s="178">
+      <c r="AZ34" s="170"/>
+      <c r="BA34" s="170"/>
+      <c r="BB34" s="170"/>
+      <c r="BC34" s="170">
         <v>2018</v>
       </c>
-      <c r="BD34" s="178"/>
-      <c r="BE34" s="178"/>
-      <c r="BF34" s="178"/>
-      <c r="BG34" s="178">
+      <c r="BD34" s="170"/>
+      <c r="BE34" s="170"/>
+      <c r="BF34" s="170"/>
+      <c r="BG34" s="170">
         <v>2019</v>
       </c>
-      <c r="BH34" s="178"/>
-      <c r="BI34" s="178"/>
-      <c r="BJ34" s="178"/>
-      <c r="BK34" s="178">
+      <c r="BH34" s="170"/>
+      <c r="BI34" s="170"/>
+      <c r="BJ34" s="170"/>
+      <c r="BK34" s="170">
         <v>2020</v>
       </c>
-      <c r="BL34" s="178"/>
-      <c r="BM34" s="178"/>
-      <c r="BN34" s="178"/>
-      <c r="BO34" s="178">
+      <c r="BL34" s="170"/>
+      <c r="BM34" s="170"/>
+      <c r="BN34" s="170"/>
+      <c r="BO34" s="170">
         <v>2021</v>
       </c>
-      <c r="BP34" s="178"/>
-      <c r="BQ34" s="178"/>
-      <c r="BR34" s="178"/>
-      <c r="BS34" s="178">
+      <c r="BP34" s="170"/>
+      <c r="BQ34" s="170"/>
+      <c r="BR34" s="170"/>
+      <c r="BS34" s="170">
         <v>2022</v>
       </c>
-      <c r="BT34" s="178"/>
-      <c r="BU34" s="178"/>
-      <c r="BV34" s="178"/>
-      <c r="BW34" s="178">
+      <c r="BT34" s="170"/>
+      <c r="BU34" s="170"/>
+      <c r="BV34" s="170"/>
+      <c r="BW34" s="170">
         <v>2023</v>
       </c>
-      <c r="BX34" s="178"/>
-      <c r="BY34" s="178"/>
-      <c r="BZ34" s="178"/>
-      <c r="CA34" s="178" t="s">
+      <c r="BX34" s="170"/>
+      <c r="BY34" s="170"/>
+      <c r="BZ34" s="170"/>
+      <c r="CA34" s="170" t="s">
         <v>12</v>
       </c>
-      <c r="CB34" s="178"/>
-      <c r="CC34" s="178"/>
-      <c r="CD34" s="178"/>
-      <c r="CE34" s="178" t="s">
+      <c r="CB34" s="170"/>
+      <c r="CC34" s="170"/>
+      <c r="CD34" s="170"/>
+      <c r="CE34" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="CF34" s="178"/>
-      <c r="CG34" s="178"/>
-      <c r="CH34" s="179"/>
+      <c r="CF34" s="170"/>
+      <c r="CG34" s="170"/>
+      <c r="CH34" s="171"/>
     </row>
     <row r="35" spans="1:86" s="13" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="181"/>
-      <c r="B35" s="182"/>
+      <c r="A35" s="173"/>
+      <c r="B35" s="174"/>
       <c r="C35" s="84"/>
       <c r="D35" s="84"/>
       <c r="E35" s="84"/>
@@ -26059,15 +25991,15 @@
       <c r="BF54" s="25"/>
     </row>
     <row r="55" spans="1:86" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="176" t="s">
+      <c r="A55" s="168" t="s">
         <v>0</v>
       </c>
-      <c r="B55" s="176"/>
-      <c r="C55" s="176"/>
-      <c r="D55" s="176"/>
-      <c r="E55" s="176"/>
-      <c r="F55" s="176"/>
-      <c r="G55" s="176"/>
+      <c r="B55" s="168"/>
+      <c r="C55" s="168"/>
+      <c r="D55" s="168"/>
+      <c r="E55" s="168"/>
+      <c r="F55" s="168"/>
+      <c r="G55" s="168"/>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
@@ -26121,13 +26053,13 @@
       <c r="BF55" s="2"/>
     </row>
     <row r="56" spans="1:86" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="176"/>
-      <c r="B56" s="176"/>
-      <c r="C56" s="176"/>
-      <c r="D56" s="176"/>
-      <c r="E56" s="176"/>
-      <c r="F56" s="176"/>
-      <c r="G56" s="176"/>
+      <c r="A56" s="168"/>
+      <c r="B56" s="168"/>
+      <c r="C56" s="168"/>
+      <c r="D56" s="168"/>
+      <c r="E56" s="168"/>
+      <c r="F56" s="168"/>
+      <c r="G56" s="168"/>
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
       <c r="J56" s="2"/>
@@ -26367,140 +26299,140 @@
       <c r="BF59" s="2"/>
     </row>
     <row r="61" spans="1:86" s="13" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="180" t="s">
+      <c r="A61" s="172" t="s">
         <v>8</v>
       </c>
-      <c r="B61" s="178" t="s">
+      <c r="B61" s="170" t="s">
         <v>10</v>
       </c>
-      <c r="C61" s="178"/>
-      <c r="D61" s="178"/>
-      <c r="E61" s="178"/>
-      <c r="F61" s="178"/>
-      <c r="G61" s="178">
+      <c r="C61" s="170"/>
+      <c r="D61" s="170"/>
+      <c r="E61" s="170"/>
+      <c r="F61" s="170"/>
+      <c r="G61" s="170">
         <v>2006</v>
       </c>
-      <c r="H61" s="178"/>
-      <c r="I61" s="178"/>
-      <c r="J61" s="178"/>
-      <c r="K61" s="178">
+      <c r="H61" s="170"/>
+      <c r="I61" s="170"/>
+      <c r="J61" s="170"/>
+      <c r="K61" s="170">
         <v>2007</v>
       </c>
-      <c r="L61" s="178"/>
-      <c r="M61" s="178"/>
-      <c r="N61" s="178"/>
-      <c r="O61" s="178">
+      <c r="L61" s="170"/>
+      <c r="M61" s="170"/>
+      <c r="N61" s="170"/>
+      <c r="O61" s="170">
         <v>2008</v>
       </c>
-      <c r="P61" s="178"/>
-      <c r="Q61" s="178"/>
-      <c r="R61" s="178"/>
-      <c r="S61" s="178">
+      <c r="P61" s="170"/>
+      <c r="Q61" s="170"/>
+      <c r="R61" s="170"/>
+      <c r="S61" s="170">
         <v>2009</v>
       </c>
-      <c r="T61" s="178"/>
-      <c r="U61" s="178"/>
-      <c r="V61" s="178"/>
-      <c r="W61" s="178">
+      <c r="T61" s="170"/>
+      <c r="U61" s="170"/>
+      <c r="V61" s="170"/>
+      <c r="W61" s="170">
         <v>2010</v>
       </c>
-      <c r="X61" s="178"/>
-      <c r="Y61" s="178"/>
-      <c r="Z61" s="178"/>
-      <c r="AA61" s="178">
+      <c r="X61" s="170"/>
+      <c r="Y61" s="170"/>
+      <c r="Z61" s="170"/>
+      <c r="AA61" s="170">
         <v>2011</v>
       </c>
-      <c r="AB61" s="178"/>
-      <c r="AC61" s="178"/>
-      <c r="AD61" s="178"/>
-      <c r="AE61" s="178">
+      <c r="AB61" s="170"/>
+      <c r="AC61" s="170"/>
+      <c r="AD61" s="170"/>
+      <c r="AE61" s="170">
         <v>2012</v>
       </c>
-      <c r="AF61" s="178"/>
-      <c r="AG61" s="178"/>
-      <c r="AH61" s="178"/>
-      <c r="AI61" s="178">
+      <c r="AF61" s="170"/>
+      <c r="AG61" s="170"/>
+      <c r="AH61" s="170"/>
+      <c r="AI61" s="170">
         <v>2013</v>
       </c>
-      <c r="AJ61" s="178"/>
-      <c r="AK61" s="178"/>
-      <c r="AL61" s="178"/>
-      <c r="AM61" s="178">
+      <c r="AJ61" s="170"/>
+      <c r="AK61" s="170"/>
+      <c r="AL61" s="170"/>
+      <c r="AM61" s="170">
         <v>2014</v>
       </c>
-      <c r="AN61" s="178"/>
-      <c r="AO61" s="178"/>
-      <c r="AP61" s="178"/>
-      <c r="AQ61" s="178">
+      <c r="AN61" s="170"/>
+      <c r="AO61" s="170"/>
+      <c r="AP61" s="170"/>
+      <c r="AQ61" s="170">
         <v>2015</v>
       </c>
-      <c r="AR61" s="178"/>
-      <c r="AS61" s="178"/>
-      <c r="AT61" s="178"/>
-      <c r="AU61" s="178">
+      <c r="AR61" s="170"/>
+      <c r="AS61" s="170"/>
+      <c r="AT61" s="170"/>
+      <c r="AU61" s="170">
         <v>2016</v>
       </c>
-      <c r="AV61" s="178"/>
-      <c r="AW61" s="178"/>
-      <c r="AX61" s="178"/>
-      <c r="AY61" s="178">
+      <c r="AV61" s="170"/>
+      <c r="AW61" s="170"/>
+      <c r="AX61" s="170"/>
+      <c r="AY61" s="170">
         <v>2017</v>
       </c>
-      <c r="AZ61" s="178"/>
-      <c r="BA61" s="178"/>
-      <c r="BB61" s="178"/>
-      <c r="BC61" s="178">
+      <c r="AZ61" s="170"/>
+      <c r="BA61" s="170"/>
+      <c r="BB61" s="170"/>
+      <c r="BC61" s="170">
         <v>2018</v>
       </c>
-      <c r="BD61" s="178"/>
-      <c r="BE61" s="178"/>
-      <c r="BF61" s="178"/>
-      <c r="BG61" s="178">
+      <c r="BD61" s="170"/>
+      <c r="BE61" s="170"/>
+      <c r="BF61" s="170"/>
+      <c r="BG61" s="170">
         <v>2019</v>
       </c>
-      <c r="BH61" s="178"/>
-      <c r="BI61" s="178"/>
-      <c r="BJ61" s="178"/>
-      <c r="BK61" s="178">
+      <c r="BH61" s="170"/>
+      <c r="BI61" s="170"/>
+      <c r="BJ61" s="170"/>
+      <c r="BK61" s="170">
         <v>2020</v>
       </c>
-      <c r="BL61" s="178"/>
-      <c r="BM61" s="178"/>
-      <c r="BN61" s="178"/>
-      <c r="BO61" s="178">
+      <c r="BL61" s="170"/>
+      <c r="BM61" s="170"/>
+      <c r="BN61" s="170"/>
+      <c r="BO61" s="170">
         <v>2021</v>
       </c>
-      <c r="BP61" s="178"/>
-      <c r="BQ61" s="178"/>
-      <c r="BR61" s="178"/>
-      <c r="BS61" s="178">
+      <c r="BP61" s="170"/>
+      <c r="BQ61" s="170"/>
+      <c r="BR61" s="170"/>
+      <c r="BS61" s="170">
         <v>2022</v>
       </c>
-      <c r="BT61" s="178"/>
-      <c r="BU61" s="178"/>
-      <c r="BV61" s="178"/>
-      <c r="BW61" s="178">
+      <c r="BT61" s="170"/>
+      <c r="BU61" s="170"/>
+      <c r="BV61" s="170"/>
+      <c r="BW61" s="170">
         <v>2023</v>
       </c>
-      <c r="BX61" s="178"/>
-      <c r="BY61" s="178"/>
-      <c r="BZ61" s="178"/>
-      <c r="CA61" s="178" t="s">
+      <c r="BX61" s="170"/>
+      <c r="BY61" s="170"/>
+      <c r="BZ61" s="170"/>
+      <c r="CA61" s="170" t="s">
         <v>12</v>
       </c>
-      <c r="CB61" s="178"/>
-      <c r="CC61" s="178"/>
-      <c r="CD61" s="178"/>
-      <c r="CE61" s="178" t="s">
+      <c r="CB61" s="170"/>
+      <c r="CC61" s="170"/>
+      <c r="CD61" s="170"/>
+      <c r="CE61" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="CF61" s="178"/>
-      <c r="CG61" s="178"/>
-      <c r="CH61" s="179"/>
+      <c r="CF61" s="170"/>
+      <c r="CG61" s="170"/>
+      <c r="CH61" s="171"/>
     </row>
     <row r="62" spans="1:86" s="13" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="181"/>
-      <c r="B62" s="182"/>
+      <c r="A62" s="173"/>
+      <c r="B62" s="174"/>
       <c r="C62" s="84"/>
       <c r="D62" s="84"/>
       <c r="E62" s="84"/>

--- a/Cuadros_Prod_Gasto.xlsx
+++ b/Cuadros_Prod_Gasto.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\WTF IS PROGRAMMING 2.0\UR CLASES\7_SEMESTRE\ICE\Proyecciones\ICE_Proyecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCBCB42D-3E6E-4E9B-ABC4-8D7002EB7668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1914E209-D874-47FD-93A4-9AEA0096BD6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="1" xr2:uid="{A3B4AD7B-0ED6-4521-BD6B-44541A0DC533}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="3" xr2:uid="{A3B4AD7B-0ED6-4521-BD6B-44541A0DC533}"/>
   </bookViews>
   <sheets>
     <sheet name="C1P" sheetId="2" state="hidden" r:id="rId1"/>
     <sheet name="PIB oferta anual" sheetId="4" r:id="rId2"/>
     <sheet name="PIB demanda anual" sheetId="6" r:id="rId3"/>
-    <sheet name="C1G" sheetId="3" state="hidden" r:id="rId4"/>
+    <sheet name="Supuestos Macro" sheetId="7" r:id="rId4"/>
+    <sheet name="C1G" sheetId="3" state="hidden" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="94">
   <si>
     <t>Producto Interno Bruto (PIB)</t>
   </si>
@@ -539,18 +540,41 @@
   <si>
     <t>Suma Agregada por Oferta Annual</t>
   </si>
+  <si>
+    <t>Verificación  Delta del PIB</t>
+  </si>
+  <si>
+    <t>Año</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>% Diferencia Of</t>
+  </si>
+  <si>
+    <t>% Diferencia De</t>
+  </si>
+  <si>
+    <t>PIB Oferta</t>
+  </si>
+  <si>
+    <t>PIB Demanda</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="6">
+  <numFmts count="8">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.000%"/>
+    <numFmt numFmtId="174" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="0.0000%"/>
   </numFmts>
   <fonts count="28" x14ac:knownFonts="1">
     <font>
@@ -836,7 +860,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1093,6 +1117,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1101,7 +1140,7 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="257">
+  <cellXfs count="271">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1672,6 +1711,18 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1747,6 +1798,9 @@
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1754,6 +1808,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="27" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1765,6 +1822,22 @@
     <xf numFmtId="0" fontId="26" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="24" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -1773,7 +1846,108 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -15979,7 +16153,7 @@
       <c r="AA4" s="185"/>
     </row>
     <row r="5" spans="1:27" s="144" customFormat="1" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="256" t="s">
+      <c r="A5" s="262" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="157">
@@ -16062,7 +16236,7 @@
       </c>
     </row>
     <row r="6" spans="1:27" s="148" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="224" t="s">
+      <c r="A6" s="228" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="151">
@@ -16150,7 +16324,7 @@
       </c>
     </row>
     <row r="7" spans="1:27" s="148" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="223" t="s">
+      <c r="A7" s="227" t="s">
         <v>21</v>
       </c>
       <c r="B7" s="146">
@@ -16238,7 +16412,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" s="148" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="224" t="s">
+      <c r="A8" s="228" t="s">
         <v>23</v>
       </c>
       <c r="B8" s="145">
@@ -16326,7 +16500,7 @@
       </c>
     </row>
     <row r="9" spans="1:27" s="148" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="223" t="s">
+      <c r="A9" s="227" t="s">
         <v>25</v>
       </c>
       <c r="B9" s="146">
@@ -16414,7 +16588,7 @@
       </c>
     </row>
     <row r="10" spans="1:27" s="148" customFormat="1" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="224" t="s">
+      <c r="A10" s="228" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="145">
@@ -16502,7 +16676,7 @@
       </c>
     </row>
     <row r="11" spans="1:27" s="148" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="223" t="s">
+      <c r="A11" s="227" t="s">
         <v>29</v>
       </c>
       <c r="B11" s="146">
@@ -16590,7 +16764,7 @@
       </c>
     </row>
     <row r="12" spans="1:27" s="148" customFormat="1" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="224" t="s">
+      <c r="A12" s="228" t="s">
         <v>31</v>
       </c>
       <c r="B12" s="145">
@@ -16678,7 +16852,7 @@
       </c>
     </row>
     <row r="13" spans="1:27" s="148" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="223" t="s">
+      <c r="A13" s="227" t="s">
         <v>33</v>
       </c>
       <c r="B13" s="146">
@@ -16766,7 +16940,7 @@
       </c>
     </row>
     <row r="14" spans="1:27" s="148" customFormat="1" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="224" t="s">
+      <c r="A14" s="228" t="s">
         <v>35</v>
       </c>
       <c r="B14" s="145">
@@ -16854,7 +17028,7 @@
       </c>
     </row>
     <row r="15" spans="1:27" s="148" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="223" t="s">
+      <c r="A15" s="227" t="s">
         <v>37</v>
       </c>
       <c r="B15" s="146">
@@ -16942,7 +17116,7 @@
       </c>
     </row>
     <row r="16" spans="1:27" s="148" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A16" s="224" t="s">
+      <c r="A16" s="228" t="s">
         <v>39</v>
       </c>
       <c r="B16" s="145">
@@ -17030,7 +17204,7 @@
       </c>
     </row>
     <row r="17" spans="1:27" s="148" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A17" s="223" t="s">
+      <c r="A17" s="227" t="s">
         <v>41</v>
       </c>
       <c r="B17" s="146">
@@ -17118,7 +17292,7 @@
       </c>
     </row>
     <row r="18" spans="1:27" s="148" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="224" t="s">
+      <c r="A18" s="228" t="s">
         <v>45</v>
       </c>
       <c r="B18" s="147">
@@ -17315,7 +17489,7 @@
       </c>
     </row>
     <row r="20" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="225" t="s">
+      <c r="A20" s="229" t="s">
         <v>85</v>
       </c>
       <c r="B20" s="158">
@@ -17424,12 +17598,12 @@
     </row>
     <row r="22" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="23" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="254" t="s">
+      <c r="A23" s="260" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="255"/>
+      <c r="A24" s="261"/>
       <c r="W24" s="186" t="s">
         <v>76</v>
       </c>
@@ -17439,7 +17613,7 @@
       <c r="AA24" s="188"/>
     </row>
     <row r="25" spans="1:27" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="226" t="s">
+      <c r="A25" s="230" t="s">
         <v>10</v>
       </c>
       <c r="B25" s="157">
@@ -17469,7 +17643,7 @@
       <c r="J25" s="156">
         <v>2013</v>
       </c>
-      <c r="K25" s="227">
+      <c r="K25" s="231">
         <v>2014</v>
       </c>
       <c r="L25" s="156">
@@ -17522,1405 +17696,1405 @@
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A26" s="222" t="s">
+      <c r="A26" s="226" t="s">
         <v>19</v>
       </c>
-      <c r="B26" s="228">
+      <c r="B26" s="232">
         <v>0</v>
       </c>
-      <c r="C26" s="228">
+      <c r="C26" s="232">
         <f>(C6/B6)-1</f>
         <v>2.1314199794244093E-2</v>
       </c>
-      <c r="D26" s="228">
+      <c r="D26" s="232">
         <f>(D6/C6)-1</f>
         <v>3.9310897021979985E-2</v>
       </c>
-      <c r="E26" s="229">
+      <c r="E26" s="233">
         <f t="shared" ref="D26:V37" si="6">(E6/D6)-1</f>
         <v>-8.0518899575040548E-3</v>
       </c>
-      <c r="F26" s="229">
+      <c r="F26" s="233">
         <f t="shared" si="6"/>
         <v>-2.3299511461855049E-3</v>
       </c>
-      <c r="G26" s="229">
+      <c r="G26" s="233">
         <f t="shared" si="6"/>
         <v>3.0385214203203503E-3</v>
       </c>
-      <c r="H26" s="229">
+      <c r="H26" s="233">
         <f t="shared" si="6"/>
         <v>1.9102220664447112E-2</v>
       </c>
-      <c r="I26" s="229">
+      <c r="I26" s="233">
         <f>(I6/H6)-1</f>
         <v>2.5033164644032713E-2</v>
       </c>
-      <c r="J26" s="229">
+      <c r="J26" s="233">
         <f t="shared" si="6"/>
         <v>7.453565008987395E-2</v>
       </c>
-      <c r="K26" s="228">
+      <c r="K26" s="232">
         <f t="shared" si="6"/>
         <v>2.9106724657076199E-2</v>
       </c>
-      <c r="L26" s="228">
+      <c r="L26" s="232">
         <f t="shared" si="6"/>
         <v>4.299956653662762E-2</v>
       </c>
-      <c r="M26" s="228">
+      <c r="M26" s="232">
         <f t="shared" si="6"/>
         <v>2.7366802427063464E-2</v>
       </c>
-      <c r="N26" s="228">
+      <c r="N26" s="232">
         <f t="shared" si="6"/>
         <v>5.5763435205598677E-2</v>
       </c>
-      <c r="O26" s="228">
+      <c r="O26" s="232">
         <f t="shared" si="6"/>
         <v>1.5939308019464304E-2</v>
       </c>
-      <c r="P26" s="228">
+      <c r="P26" s="232">
         <f t="shared" si="6"/>
         <v>2.7173298133132295E-2</v>
       </c>
-      <c r="Q26" s="228">
+      <c r="Q26" s="232">
         <f t="shared" si="6"/>
         <v>1.9606763231811319E-2</v>
       </c>
-      <c r="R26" s="228">
+      <c r="R26" s="232">
         <f t="shared" si="6"/>
         <v>4.3735033039845828E-2</v>
       </c>
-      <c r="S26" s="231">
+      <c r="S26" s="235">
         <f t="shared" si="6"/>
         <v>-9.073971846536022E-3</v>
       </c>
-      <c r="T26" s="228">
+      <c r="T26" s="232">
         <f t="shared" si="6"/>
         <v>1.6486194770377161E-2</v>
       </c>
-      <c r="U26" s="228">
+      <c r="U26" s="232">
         <f t="shared" si="6"/>
         <v>6.1278665502063401E-2</v>
       </c>
-      <c r="V26" s="228">
+      <c r="V26" s="232">
         <f t="shared" si="6"/>
         <v>3.100232307625661E-2</v>
       </c>
-      <c r="W26" s="228">
+      <c r="W26" s="232">
         <f>AVERAGE(U26:V26)</f>
         <v>4.6140494289160006E-2</v>
       </c>
-      <c r="X26" s="228">
+      <c r="X26" s="232">
         <f t="shared" ref="X26:AA38" si="7">AVERAGE(V26:W26)</f>
         <v>3.8571408682708308E-2</v>
       </c>
-      <c r="Y26" s="228">
+      <c r="Y26" s="232">
         <f t="shared" si="7"/>
         <v>4.2355951485934157E-2</v>
       </c>
-      <c r="Z26" s="228">
+      <c r="Z26" s="232">
         <f t="shared" si="7"/>
         <v>4.0463680084321232E-2</v>
       </c>
-      <c r="AA26" s="228">
+      <c r="AA26" s="232">
         <f t="shared" si="7"/>
         <v>4.1409815785127695E-2</v>
       </c>
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A27" s="223" t="s">
+      <c r="A27" s="227" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="229">
+      <c r="B27" s="233">
         <v>0</v>
       </c>
-      <c r="C27" s="229">
+      <c r="C27" s="233">
         <f t="shared" ref="C27:R29" si="8">(C7/B7)-1</f>
         <v>2.2931097338680262E-2</v>
       </c>
-      <c r="D27" s="229">
+      <c r="D27" s="233">
         <f t="shared" si="8"/>
         <v>1.3364695819523043E-2</v>
       </c>
-      <c r="E27" s="229">
+      <c r="E27" s="233">
         <f t="shared" si="8"/>
         <v>9.379615952732645E-2</v>
       </c>
-      <c r="F27" s="229">
+      <c r="F27" s="233">
         <f t="shared" si="8"/>
         <v>0.11440146619079772</v>
       </c>
-      <c r="G27" s="229">
+      <c r="G27" s="233">
         <f t="shared" si="8"/>
         <v>0.10871635073141173</v>
       </c>
-      <c r="H27" s="229">
+      <c r="H27" s="233">
         <f t="shared" si="8"/>
         <v>0.14435162776173005</v>
       </c>
-      <c r="I27" s="229">
+      <c r="I27" s="233">
         <f t="shared" si="8"/>
         <v>5.3690817301132565E-2</v>
       </c>
-      <c r="J27" s="229">
+      <c r="J27" s="233">
         <f t="shared" si="8"/>
         <v>5.3070033452034204E-2</v>
       </c>
-      <c r="K27" s="229">
+      <c r="K27" s="233">
         <f t="shared" si="8"/>
         <v>-1.3485264581710843E-2</v>
       </c>
-      <c r="L27" s="229">
+      <c r="L27" s="233">
         <f t="shared" si="8"/>
         <v>-1.0574206415157161E-2</v>
       </c>
-      <c r="M27" s="229">
+      <c r="M27" s="233">
         <f t="shared" si="8"/>
         <v>-2.8849182186574729E-2</v>
       </c>
-      <c r="N27" s="229">
+      <c r="N27" s="233">
         <f t="shared" si="8"/>
         <v>-5.7531403368430101E-2</v>
       </c>
-      <c r="O27" s="229">
+      <c r="O27" s="233">
         <f t="shared" si="8"/>
         <v>-1.6608552027894907E-2</v>
       </c>
-      <c r="P27" s="229">
+      <c r="P27" s="233">
         <f t="shared" si="8"/>
         <v>1.9245124568442407E-2</v>
       </c>
-      <c r="Q27" s="229">
+      <c r="Q27" s="233">
         <f t="shared" si="8"/>
         <v>-0.15190076213581094</v>
       </c>
-      <c r="R27" s="229">
+      <c r="R27" s="233">
         <f t="shared" si="8"/>
         <v>-2.0509499136444065E-3</v>
       </c>
-      <c r="S27" s="232">
+      <c r="S27" s="236">
         <f t="shared" si="6"/>
         <v>1.4548404542996218E-2</v>
       </c>
-      <c r="T27" s="229">
+      <c r="T27" s="233">
         <f t="shared" si="6"/>
         <v>2.5667679513833086E-2</v>
       </c>
-      <c r="U27" s="229">
+      <c r="U27" s="233">
         <f t="shared" si="6"/>
         <v>-3.4120734908136274E-2</v>
       </c>
-      <c r="V27" s="229">
+      <c r="V27" s="233">
         <f t="shared" si="6"/>
         <v>-6.1873733747030757E-2</v>
       </c>
-      <c r="W27" s="229">
+      <c r="W27" s="233">
         <f t="shared" ref="W27:W38" si="9">AVERAGE(U27:V27)</f>
         <v>-4.7997234327583516E-2</v>
       </c>
-      <c r="X27" s="229">
+      <c r="X27" s="233">
         <f t="shared" si="7"/>
         <v>-5.4935484037307136E-2</v>
       </c>
-      <c r="Y27" s="229">
+      <c r="Y27" s="233">
         <f t="shared" si="7"/>
         <v>-5.1466359182445326E-2</v>
       </c>
-      <c r="Z27" s="229">
+      <c r="Z27" s="233">
         <f t="shared" si="7"/>
         <v>-5.3200921609876231E-2</v>
       </c>
-      <c r="AA27" s="229">
+      <c r="AA27" s="233">
         <f t="shared" si="7"/>
         <v>-5.2333640396160779E-2</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A28" s="224" t="s">
+      <c r="A28" s="228" t="s">
         <v>23</v>
       </c>
-      <c r="B28" s="229">
+      <c r="B28" s="233">
         <v>0</v>
       </c>
-      <c r="C28" s="229">
+      <c r="C28" s="233">
         <f t="shared" si="8"/>
         <v>7.2917206027028447E-2</v>
       </c>
-      <c r="D28" s="229">
+      <c r="D28" s="233">
         <f t="shared" si="8"/>
         <v>7.7637690776376944E-2</v>
       </c>
-      <c r="E28" s="229">
+      <c r="E28" s="233">
         <f t="shared" si="8"/>
         <v>3.5714285714285587E-3</v>
       </c>
-      <c r="F28" s="229">
+      <c r="F28" s="233">
         <f t="shared" si="8"/>
         <v>-3.6646995169513308E-2</v>
       </c>
-      <c r="G28" s="229">
+      <c r="G28" s="233">
         <f t="shared" si="8"/>
         <v>1.8829469393426779E-2</v>
       </c>
-      <c r="H28" s="229">
+      <c r="H28" s="233">
         <f t="shared" si="8"/>
         <v>5.5876335530802734E-2</v>
       </c>
-      <c r="I28" s="229">
+      <c r="I28" s="233">
         <f t="shared" si="8"/>
         <v>8.2996038580775977E-3</v>
       </c>
-      <c r="J28" s="229">
+      <c r="J28" s="233">
         <f t="shared" si="8"/>
         <v>1.5096031686720135E-2</v>
       </c>
-      <c r="K28" s="229">
+      <c r="K28" s="233">
         <f t="shared" si="8"/>
         <v>2.8901673310124831E-2</v>
       </c>
-      <c r="L28" s="229">
+      <c r="L28" s="233">
         <f t="shared" si="8"/>
         <v>2.0034958959000093E-2</v>
       </c>
-      <c r="M28" s="229">
+      <c r="M28" s="233">
         <f t="shared" si="8"/>
         <v>3.2238022226898533E-2</v>
       </c>
-      <c r="N28" s="229">
+      <c r="N28" s="233">
         <f t="shared" si="8"/>
         <v>-1.8163990447158329E-2</v>
       </c>
-      <c r="O28" s="229">
+      <c r="O28" s="233">
         <f t="shared" si="8"/>
         <v>1.4752558461462062E-2</v>
       </c>
-      <c r="P28" s="229">
+      <c r="P28" s="233">
         <f t="shared" si="8"/>
         <v>1.2014382180128402E-2</v>
       </c>
-      <c r="Q28" s="229">
+      <c r="Q28" s="233">
         <f t="shared" si="8"/>
         <v>-9.2489890236857386E-2</v>
       </c>
-      <c r="R28" s="229">
+      <c r="R28" s="233">
         <f t="shared" si="8"/>
         <v>0.13593057058586377</v>
       </c>
-      <c r="S28" s="232">
+      <c r="S28" s="236">
         <f t="shared" si="6"/>
         <v>8.1594530476528426E-2</v>
       </c>
-      <c r="T28" s="229">
+      <c r="T28" s="233">
         <f t="shared" si="6"/>
         <v>-1.6208701058703423E-2</v>
       </c>
-      <c r="U28" s="229">
+      <c r="U28" s="233">
         <f t="shared" si="6"/>
         <v>-2.5648452929559085E-2</v>
       </c>
-      <c r="V28" s="229">
+      <c r="V28" s="233">
         <f t="shared" si="6"/>
         <v>1.85000575147094E-2</v>
       </c>
-      <c r="W28" s="229">
+      <c r="W28" s="233">
         <f t="shared" si="9"/>
         <v>-3.5741977074248421E-3</v>
       </c>
-      <c r="X28" s="229">
+      <c r="X28" s="233">
         <f t="shared" si="7"/>
         <v>7.4629299036422792E-3</v>
       </c>
-      <c r="Y28" s="229">
+      <c r="Y28" s="233">
         <f t="shared" si="7"/>
         <v>1.9443660981087185E-3</v>
       </c>
-      <c r="Z28" s="229">
+      <c r="Z28" s="233">
         <f t="shared" si="7"/>
         <v>4.7036480008754988E-3</v>
       </c>
-      <c r="AA28" s="229">
+      <c r="AA28" s="233">
         <f t="shared" si="7"/>
         <v>3.3240070494921087E-3</v>
       </c>
     </row>
     <row r="29" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A29" s="223" t="s">
+      <c r="A29" s="227" t="s">
         <v>25</v>
       </c>
-      <c r="B29" s="229">
+      <c r="B29" s="233">
         <v>0</v>
       </c>
-      <c r="C29" s="229">
+      <c r="C29" s="233">
         <f t="shared" si="8"/>
         <v>5.3197752207653215E-2</v>
       </c>
-      <c r="D29" s="229">
+      <c r="D29" s="233">
         <f t="shared" si="8"/>
         <v>4.2278571065602844E-2</v>
       </c>
-      <c r="E29" s="229">
+      <c r="E29" s="233">
         <f t="shared" si="8"/>
         <v>5.2654673102237037E-3</v>
       </c>
-      <c r="F29" s="229">
+      <c r="F29" s="233">
         <f t="shared" si="8"/>
         <v>2.3958484892574905E-2</v>
       </c>
-      <c r="G29" s="229">
+      <c r="G29" s="233">
         <f t="shared" si="8"/>
         <v>3.8933358594231082E-2</v>
       </c>
-      <c r="H29" s="229">
+      <c r="H29" s="233">
         <f t="shared" si="8"/>
         <v>3.0681559152039961E-2</v>
       </c>
-      <c r="I29" s="229">
+      <c r="I29" s="233">
         <f t="shared" si="8"/>
         <v>2.1496815286624171E-2</v>
       </c>
-      <c r="J29" s="229">
+      <c r="J29" s="233">
         <f t="shared" si="8"/>
         <v>3.7065904563956087E-2</v>
       </c>
-      <c r="K29" s="229">
+      <c r="K29" s="233">
         <f t="shared" si="8"/>
         <v>3.4363256784968543E-2</v>
       </c>
-      <c r="L29" s="229">
+      <c r="L29" s="233">
         <f t="shared" si="8"/>
         <v>-7.0237758850362209E-3</v>
       </c>
-      <c r="M29" s="229">
+      <c r="M29" s="233">
         <f t="shared" si="8"/>
         <v>-8.1304118053293628E-5</v>
       </c>
-      <c r="N29" s="229">
+      <c r="N29" s="233">
         <f t="shared" si="8"/>
         <v>2.8865308777493048E-2</v>
       </c>
-      <c r="O29" s="229">
+      <c r="O29" s="233">
         <f t="shared" si="8"/>
         <v>2.5487019401746913E-2</v>
       </c>
-      <c r="P29" s="229">
+      <c r="P29" s="233">
         <f t="shared" si="8"/>
         <v>2.5200369913686904E-2</v>
       </c>
-      <c r="Q29" s="229">
+      <c r="Q29" s="233">
         <f t="shared" si="8"/>
         <v>-3.8299631662031208E-2</v>
       </c>
-      <c r="R29" s="229">
+      <c r="R29" s="233">
         <f t="shared" si="8"/>
         <v>5.8310860984093438E-2</v>
       </c>
-      <c r="S29" s="232">
+      <c r="S29" s="236">
         <f t="shared" si="6"/>
         <v>4.6087373979836865E-2</v>
       </c>
-      <c r="T29" s="229">
+      <c r="T29" s="233">
         <f t="shared" si="6"/>
         <v>3.1559995763758897E-2</v>
       </c>
-      <c r="U29" s="229">
+      <c r="U29" s="233">
         <f t="shared" si="6"/>
         <v>2.48793675781116E-2</v>
       </c>
-      <c r="V29" s="229">
+      <c r="V29" s="233">
         <f t="shared" si="6"/>
         <v>1.140651910951207E-2</v>
       </c>
-      <c r="W29" s="229">
+      <c r="W29" s="233">
         <f t="shared" si="9"/>
         <v>1.8142943343811835E-2</v>
       </c>
-      <c r="X29" s="229">
+      <c r="X29" s="233">
         <f t="shared" si="7"/>
         <v>1.4774731226661952E-2</v>
       </c>
-      <c r="Y29" s="229">
+      <c r="Y29" s="233">
         <f t="shared" si="7"/>
         <v>1.6458837285236894E-2</v>
       </c>
-      <c r="Z29" s="229">
+      <c r="Z29" s="233">
         <f t="shared" si="7"/>
         <v>1.5616784255949423E-2</v>
       </c>
-      <c r="AA29" s="229">
+      <c r="AA29" s="233">
         <f t="shared" si="7"/>
         <v>1.6037810770593158E-2</v>
       </c>
     </row>
     <row r="30" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A30" s="224" t="s">
+      <c r="A30" s="228" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="229">
+      <c r="B30" s="233">
         <v>0</v>
       </c>
-      <c r="C30" s="229">
+      <c r="C30" s="233">
         <f t="shared" ref="C30:R38" si="10">(C10/B10)-1</f>
         <v>0.12141035963499736</v>
       </c>
-      <c r="D30" s="229">
+      <c r="D30" s="233">
         <f t="shared" si="10"/>
         <v>6.9404972028599632E-2</v>
       </c>
-      <c r="E30" s="229">
+      <c r="E30" s="233">
         <f t="shared" si="10"/>
         <v>9.9085237922063474E-2</v>
       </c>
-      <c r="F30" s="229">
+      <c r="F30" s="233">
         <f t="shared" si="10"/>
         <v>2.6139631958054466E-2</v>
       </c>
-      <c r="G30" s="229">
+      <c r="G30" s="233">
         <f t="shared" si="10"/>
         <v>-6.6474848695304845E-3</v>
       </c>
-      <c r="H30" s="229">
+      <c r="H30" s="233">
         <f t="shared" si="10"/>
         <v>6.2125449460647131E-2</v>
       </c>
-      <c r="I30" s="229">
+      <c r="I30" s="233">
         <f t="shared" si="10"/>
         <v>5.9126387060372432E-2</v>
       </c>
-      <c r="J30" s="229">
+      <c r="J30" s="233">
         <f t="shared" si="10"/>
         <v>0.11276109298350767</v>
       </c>
-      <c r="K30" s="229">
+      <c r="K30" s="233">
         <f t="shared" si="10"/>
         <v>8.918633181065605E-2</v>
       </c>
-      <c r="L30" s="229">
+      <c r="L30" s="233">
         <f t="shared" si="10"/>
         <v>6.3001355261712133E-2</v>
       </c>
-      <c r="M30" s="229">
+      <c r="M30" s="233">
         <f t="shared" si="10"/>
         <v>3.588780538230929E-2</v>
       </c>
-      <c r="N30" s="229">
+      <c r="N30" s="233">
         <f t="shared" si="10"/>
         <v>-2.0257796257796112E-2</v>
       </c>
-      <c r="O30" s="229">
+      <c r="O30" s="233">
         <f t="shared" si="10"/>
         <v>-1.2748909297706557E-2</v>
       </c>
-      <c r="P30" s="229">
+      <c r="P30" s="233">
         <f t="shared" si="10"/>
         <v>-3.8912579957356086E-2</v>
       </c>
-      <c r="Q30" s="229">
+      <c r="Q30" s="233">
         <f t="shared" si="10"/>
         <v>-0.29581521836365909</v>
       </c>
-      <c r="R30" s="229">
+      <c r="R30" s="233">
         <f t="shared" si="10"/>
         <v>4.2684011280774481E-2</v>
       </c>
-      <c r="S30" s="232">
+      <c r="S30" s="236">
         <f t="shared" si="6"/>
         <v>6.6424620482955277E-2</v>
       </c>
-      <c r="T30" s="229">
+      <c r="T30" s="233">
         <f t="shared" si="6"/>
         <v>-3.0915114817776757E-2</v>
       </c>
-      <c r="U30" s="229">
+      <c r="U30" s="233">
         <f t="shared" si="6"/>
         <v>8.4881637272471444E-4</v>
       </c>
-      <c r="V30" s="229">
+      <c r="V30" s="233">
         <f t="shared" si="6"/>
         <v>-2.7679677050644891E-2</v>
       </c>
-      <c r="W30" s="229">
+      <c r="W30" s="233">
         <f t="shared" si="9"/>
         <v>-1.3415430338960088E-2</v>
       </c>
-      <c r="X30" s="229">
+      <c r="X30" s="233">
         <f t="shared" si="7"/>
         <v>-2.0547553694802489E-2</v>
       </c>
-      <c r="Y30" s="229">
+      <c r="Y30" s="233">
         <f t="shared" si="7"/>
         <v>-1.6981492016881289E-2</v>
       </c>
-      <c r="Z30" s="229">
+      <c r="Z30" s="233">
         <f t="shared" si="7"/>
         <v>-1.8764522855841889E-2</v>
       </c>
-      <c r="AA30" s="229">
+      <c r="AA30" s="233">
         <f t="shared" si="7"/>
         <v>-1.7873007436361589E-2</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="223" t="s">
+      <c r="A31" s="227" t="s">
         <v>29</v>
       </c>
-      <c r="B31" s="229">
+      <c r="B31" s="233">
         <v>0</v>
       </c>
-      <c r="C31" s="229">
+      <c r="C31" s="233">
         <f t="shared" si="10"/>
         <v>7.6076650239385701E-2</v>
       </c>
-      <c r="D31" s="229">
+      <c r="D31" s="233">
         <f t="shared" si="10"/>
         <v>8.0684463590279032E-2</v>
       </c>
-      <c r="E31" s="229">
+      <c r="E31" s="233">
         <f t="shared" si="10"/>
         <v>3.022860191457899E-2</v>
       </c>
-      <c r="F31" s="229">
+      <c r="F31" s="233">
         <f t="shared" si="10"/>
         <v>-1.5730951869149523E-3</v>
       </c>
-      <c r="G31" s="229">
+      <c r="G31" s="233">
         <f t="shared" si="10"/>
         <v>5.3452072221950475E-2</v>
       </c>
-      <c r="H31" s="229">
+      <c r="H31" s="233">
         <f t="shared" si="10"/>
         <v>6.8891840924503178E-2</v>
       </c>
-      <c r="I31" s="229">
+      <c r="I31" s="233">
         <f t="shared" si="10"/>
         <v>3.8153011828302885E-2</v>
       </c>
-      <c r="J31" s="229">
+      <c r="J31" s="233">
         <f t="shared" si="10"/>
         <v>4.7684026353461029E-2</v>
       </c>
-      <c r="K31" s="229">
+      <c r="K31" s="233">
         <f t="shared" si="10"/>
         <v>4.7255671239882169E-2</v>
       </c>
-      <c r="L31" s="229">
+      <c r="L31" s="233">
         <f t="shared" si="10"/>
         <v>3.3312223892326687E-2</v>
       </c>
-      <c r="M31" s="229">
+      <c r="M31" s="233">
         <f t="shared" si="10"/>
         <v>2.6855400246623695E-2</v>
       </c>
-      <c r="N31" s="229">
+      <c r="N31" s="233">
         <f t="shared" si="10"/>
         <v>1.8595487034932967E-2</v>
       </c>
-      <c r="O31" s="229">
+      <c r="O31" s="233">
         <f t="shared" si="10"/>
         <v>2.6727472961906695E-2</v>
       </c>
-      <c r="P31" s="229">
+      <c r="P31" s="233">
         <f t="shared" si="10"/>
         <v>3.7486764119418536E-2</v>
       </c>
-      <c r="Q31" s="229">
+      <c r="Q31" s="233">
         <f t="shared" si="10"/>
         <v>-0.13688779905891713</v>
       </c>
-      <c r="R31" s="229">
+      <c r="R31" s="233">
         <f t="shared" si="10"/>
         <v>0.20409260183514388</v>
       </c>
-      <c r="S31" s="232">
+      <c r="S31" s="236">
         <f t="shared" si="6"/>
         <v>0.11884067212957961</v>
       </c>
-      <c r="T31" s="229">
+      <c r="T31" s="233">
         <f t="shared" si="6"/>
         <v>-3.6386227493715895E-2</v>
       </c>
-      <c r="U31" s="229">
+      <c r="U31" s="233">
         <f t="shared" si="6"/>
         <v>1.2326474119727315E-2</v>
       </c>
-      <c r="V31" s="229">
+      <c r="V31" s="233">
         <f t="shared" si="6"/>
         <v>4.5987328955726214E-2</v>
       </c>
-      <c r="W31" s="229">
+      <c r="W31" s="233">
         <f t="shared" si="9"/>
         <v>2.9156901537726765E-2</v>
       </c>
-      <c r="X31" s="229">
+      <c r="X31" s="233">
         <f t="shared" si="7"/>
         <v>3.757211524672649E-2</v>
       </c>
-      <c r="Y31" s="229">
+      <c r="Y31" s="233">
         <f t="shared" si="7"/>
         <v>3.3364508392226627E-2</v>
       </c>
-      <c r="Z31" s="229">
+      <c r="Z31" s="233">
         <f t="shared" si="7"/>
         <v>3.5468311819476558E-2</v>
       </c>
-      <c r="AA31" s="229">
+      <c r="AA31" s="233">
         <f t="shared" si="7"/>
         <v>3.4416410105851593E-2</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A32" s="224" t="s">
+      <c r="A32" s="228" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="229">
+      <c r="B32" s="233">
         <v>0</v>
       </c>
-      <c r="C32" s="229">
+      <c r="C32" s="233">
         <f t="shared" si="10"/>
         <v>0.14917517674783976</v>
       </c>
-      <c r="D32" s="229">
+      <c r="D32" s="233">
         <f t="shared" si="10"/>
         <v>0.14573791783443846</v>
       </c>
-      <c r="E32" s="229">
+      <c r="E32" s="233">
         <f t="shared" si="10"/>
         <v>2.1418769763140721E-2</v>
       </c>
-      <c r="F32" s="229">
+      <c r="F32" s="233">
         <f t="shared" si="10"/>
         <v>-8.4754672897196293E-2</v>
       </c>
-      <c r="G32" s="229">
+      <c r="G32" s="233">
         <f t="shared" si="10"/>
         <v>0.16510306975556821</v>
       </c>
-      <c r="H32" s="229">
+      <c r="H32" s="233">
         <f t="shared" si="10"/>
         <v>0.10391104294478537</v>
       </c>
-      <c r="I32" s="229">
+      <c r="I32" s="233">
         <f t="shared" si="10"/>
         <v>1.3000545824443099E-2</v>
       </c>
-      <c r="J32" s="229">
+      <c r="J32" s="233">
         <f t="shared" si="10"/>
         <v>8.8317413666421762E-2</v>
       </c>
-      <c r="K32" s="229">
+      <c r="K32" s="233">
         <f t="shared" si="10"/>
         <v>6.4632280133225528E-2</v>
       </c>
-      <c r="L32" s="229">
+      <c r="L32" s="233">
         <f t="shared" si="10"/>
         <v>1.2978777373805706E-2</v>
       </c>
-      <c r="M32" s="229">
+      <c r="M32" s="233">
         <f t="shared" si="10"/>
         <v>-6.5523141772049209E-3</v>
       </c>
-      <c r="N32" s="229">
+      <c r="N32" s="233">
         <f t="shared" si="10"/>
         <v>-1.932448328011982E-3</v>
       </c>
-      <c r="O32" s="229">
+      <c r="O32" s="233">
         <f t="shared" si="10"/>
         <v>3.5230238235541611E-2</v>
       </c>
-      <c r="P32" s="229">
+      <c r="P32" s="233">
         <f t="shared" si="10"/>
         <v>9.1888595242934912E-3</v>
       </c>
-      <c r="Q32" s="229">
+      <c r="Q32" s="233">
         <f t="shared" si="10"/>
         <v>-2.7718464203698501E-2</v>
       </c>
-      <c r="R32" s="229">
+      <c r="R32" s="233">
         <f t="shared" si="10"/>
         <v>0.12750176107404809</v>
       </c>
-      <c r="S32" s="232">
+      <c r="S32" s="236">
         <f t="shared" si="6"/>
         <v>0.12326350606394709</v>
       </c>
-      <c r="T32" s="229">
+      <c r="T32" s="233">
         <f t="shared" si="6"/>
         <v>1.5377568381101936E-2</v>
       </c>
-      <c r="U32" s="229">
+      <c r="U32" s="233">
         <f t="shared" si="6"/>
         <v>-2.0944770251980493E-3</v>
       </c>
-      <c r="V32" s="229">
+      <c r="V32" s="233">
         <f t="shared" si="6"/>
         <v>9.6882389009473879E-3</v>
       </c>
-      <c r="W32" s="229">
+      <c r="W32" s="233">
         <f t="shared" si="9"/>
         <v>3.7968809378746693E-3</v>
       </c>
-      <c r="X32" s="229">
+      <c r="X32" s="233">
         <f t="shared" si="7"/>
         <v>6.7425599194110286E-3</v>
       </c>
-      <c r="Y32" s="229">
+      <c r="Y32" s="233">
         <f t="shared" si="7"/>
         <v>5.269720428642849E-3</v>
       </c>
-      <c r="Z32" s="229">
+      <c r="Z32" s="233">
         <f t="shared" si="7"/>
         <v>6.0061401740269388E-3</v>
       </c>
-      <c r="AA32" s="229">
+      <c r="AA32" s="233">
         <f t="shared" si="7"/>
         <v>5.6379303013348939E-3</v>
       </c>
     </row>
     <row r="33" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A33" s="223" t="s">
+      <c r="A33" s="227" t="s">
         <v>33</v>
       </c>
-      <c r="B33" s="229">
+      <c r="B33" s="233">
         <v>0</v>
       </c>
-      <c r="C33" s="229">
+      <c r="C33" s="233">
         <f t="shared" si="10"/>
         <v>6.5871369294605797E-2</v>
       </c>
-      <c r="D33" s="229">
+      <c r="D33" s="233">
         <f t="shared" si="10"/>
         <v>0.13759124087591235</v>
       </c>
-      <c r="E33" s="229">
+      <c r="E33" s="233">
         <f t="shared" si="10"/>
         <v>0.1013795316008983</v>
       </c>
-      <c r="F33" s="229">
+      <c r="F33" s="233">
         <f t="shared" si="10"/>
         <v>3.4809204777162872E-2</v>
       </c>
-      <c r="G33" s="229">
+      <c r="G33" s="233">
         <f t="shared" si="10"/>
         <v>4.6774571897724826E-2</v>
       </c>
-      <c r="H33" s="229">
+      <c r="H33" s="233">
         <f t="shared" si="10"/>
         <v>0.10944783076371434</v>
       </c>
-      <c r="I33" s="229">
+      <c r="I33" s="233">
         <f t="shared" si="10"/>
         <v>7.562414155288022E-2</v>
       </c>
-      <c r="J33" s="229">
+      <c r="J33" s="233">
         <f t="shared" si="10"/>
         <v>9.5170134455044186E-2</v>
       </c>
-      <c r="K33" s="229">
+      <c r="K33" s="233">
         <f t="shared" si="10"/>
         <v>0.10216049382716053</v>
       </c>
-      <c r="L33" s="229">
+      <c r="L33" s="233">
         <f t="shared" si="10"/>
         <v>7.9560658390117611E-2</v>
       </c>
-      <c r="M33" s="229">
+      <c r="M33" s="233">
         <f t="shared" si="10"/>
         <v>2.9686419183767798E-2</v>
       </c>
-      <c r="N33" s="229">
+      <c r="N33" s="233">
         <f t="shared" si="10"/>
         <v>5.3882326596876196E-2</v>
       </c>
-      <c r="O33" s="229">
+      <c r="O33" s="233">
         <f t="shared" si="10"/>
         <v>3.7342965658282656E-2</v>
       </c>
-      <c r="P33" s="229">
+      <c r="P33" s="233">
         <f t="shared" si="10"/>
         <v>6.2677625009601501E-2</v>
       </c>
-      <c r="Q33" s="229">
+      <c r="Q33" s="233">
         <f t="shared" si="10"/>
         <v>2.2358751957595402E-2</v>
       </c>
-      <c r="R33" s="229">
+      <c r="R33" s="233">
         <f t="shared" si="10"/>
         <v>3.699950510216099E-2</v>
       </c>
-      <c r="S33" s="232">
+      <c r="S33" s="236">
         <f t="shared" si="6"/>
         <v>6.6745449173920113E-2</v>
       </c>
-      <c r="T33" s="229">
+      <c r="T33" s="233">
         <f t="shared" si="6"/>
         <v>8.9369407754580132E-2</v>
       </c>
-      <c r="U33" s="229">
+      <c r="U33" s="233">
         <f t="shared" si="6"/>
         <v>1.0736286300968345E-2</v>
       </c>
-      <c r="V33" s="229">
+      <c r="V33" s="233">
         <f t="shared" si="6"/>
         <v>2.7636052292486113E-2</v>
       </c>
-      <c r="W33" s="229">
+      <c r="W33" s="233">
         <f t="shared" si="9"/>
         <v>1.9186169296727229E-2</v>
       </c>
-      <c r="X33" s="229">
+      <c r="X33" s="233">
         <f t="shared" si="7"/>
         <v>2.3411110794606671E-2</v>
       </c>
-      <c r="Y33" s="229">
+      <c r="Y33" s="233">
         <f t="shared" si="7"/>
         <v>2.129864004566695E-2</v>
       </c>
-      <c r="Z33" s="229">
+      <c r="Z33" s="233">
         <f t="shared" si="7"/>
         <v>2.2354875420136811E-2</v>
       </c>
-      <c r="AA33" s="229">
+      <c r="AA33" s="233">
         <f t="shared" si="7"/>
         <v>2.182675773290188E-2</v>
       </c>
     </row>
     <row r="34" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A34" s="224" t="s">
+      <c r="A34" s="228" t="s">
         <v>35</v>
       </c>
-      <c r="B34" s="229">
+      <c r="B34" s="233">
         <v>0</v>
       </c>
-      <c r="C34" s="229">
+      <c r="C34" s="233">
         <f t="shared" si="10"/>
         <v>4.0451496028507172E-2</v>
       </c>
-      <c r="D34" s="229">
+      <c r="D34" s="233">
         <f t="shared" si="10"/>
         <v>3.7501195828948619E-2</v>
       </c>
-      <c r="E34" s="229">
+      <c r="E34" s="233">
         <f t="shared" si="10"/>
         <v>2.7773167358229545E-2</v>
       </c>
-      <c r="F34" s="229">
+      <c r="F34" s="233">
         <f t="shared" si="10"/>
         <v>3.8309020114478454E-2</v>
       </c>
-      <c r="G34" s="229">
+      <c r="G34" s="233">
         <f t="shared" si="10"/>
         <v>3.5703176303874429E-2</v>
       </c>
-      <c r="H34" s="229">
+      <c r="H34" s="233">
         <f t="shared" si="10"/>
         <v>2.8298738570379678E-2</v>
       </c>
-      <c r="I34" s="229">
+      <c r="I34" s="233">
         <f t="shared" si="10"/>
         <v>3.165768806386704E-2</v>
       </c>
-      <c r="J34" s="229">
+      <c r="J34" s="233">
         <f t="shared" si="10"/>
         <v>3.2180436936724455E-2</v>
       </c>
-      <c r="K34" s="229">
+      <c r="K34" s="233">
         <f t="shared" si="10"/>
         <v>3.1070476190476093E-2</v>
       </c>
-      <c r="L34" s="229">
+      <c r="L34" s="233">
         <f t="shared" si="10"/>
         <v>3.1937219200756539E-2</v>
       </c>
-      <c r="M34" s="229">
+      <c r="M34" s="233">
         <f t="shared" si="10"/>
         <v>3.5288220551378702E-2</v>
       </c>
-      <c r="N34" s="229">
+      <c r="N34" s="233">
         <f t="shared" si="10"/>
         <v>3.0516399452198861E-2</v>
       </c>
-      <c r="O34" s="229">
+      <c r="O34" s="233">
         <f t="shared" si="10"/>
         <v>3.965366803141146E-2</v>
       </c>
-      <c r="P34" s="229">
+      <c r="P34" s="233">
         <f t="shared" si="10"/>
         <v>3.2472982220558055E-2</v>
       </c>
-      <c r="Q34" s="229">
+      <c r="Q34" s="233">
         <f t="shared" si="10"/>
         <v>1.4431494172377546E-2</v>
       </c>
-      <c r="R34" s="229">
+      <c r="R34" s="233">
         <f t="shared" si="10"/>
         <v>2.49636332256713E-2</v>
       </c>
-      <c r="S34" s="232">
+      <c r="S34" s="236">
         <f t="shared" si="6"/>
         <v>2.0446700263401674E-2</v>
       </c>
-      <c r="T34" s="229">
+      <c r="T34" s="233">
         <f t="shared" si="6"/>
         <v>1.8504767629621721E-2</v>
       </c>
-      <c r="U34" s="229">
+      <c r="U34" s="233">
         <f t="shared" si="6"/>
         <v>2.2091583442306106E-2</v>
       </c>
-      <c r="V34" s="229">
+      <c r="V34" s="233">
         <f t="shared" si="6"/>
         <v>1.9834298843357745E-2</v>
       </c>
-      <c r="W34" s="229">
+      <c r="W34" s="233">
         <f t="shared" si="9"/>
         <v>2.0962941142831926E-2</v>
       </c>
-      <c r="X34" s="229">
+      <c r="X34" s="233">
         <f t="shared" si="7"/>
         <v>2.0398619993094835E-2</v>
       </c>
-      <c r="Y34" s="229">
+      <c r="Y34" s="233">
         <f t="shared" si="7"/>
         <v>2.068078056796338E-2</v>
       </c>
-      <c r="Z34" s="229">
+      <c r="Z34" s="233">
         <f t="shared" si="7"/>
         <v>2.0539700280529108E-2</v>
       </c>
-      <c r="AA34" s="229">
+      <c r="AA34" s="233">
         <f t="shared" si="7"/>
         <v>2.0610240424246244E-2</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="223" t="s">
+      <c r="A35" s="227" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="229">
+      <c r="B35" s="233">
         <v>0</v>
       </c>
-      <c r="C35" s="229">
+      <c r="C35" s="233">
         <f t="shared" si="10"/>
         <v>7.0305349862717303E-2</v>
       </c>
-      <c r="D35" s="229">
+      <c r="D35" s="233">
         <f t="shared" si="10"/>
         <v>6.8770729684908716E-2</v>
       </c>
-      <c r="E35" s="229">
+      <c r="E35" s="233">
         <f t="shared" si="10"/>
         <v>3.7676380739950277E-2</v>
       </c>
-      <c r="F35" s="229">
+      <c r="F35" s="233">
         <f t="shared" si="10"/>
         <v>2.7990654205607646E-2</v>
       </c>
-      <c r="G35" s="229">
+      <c r="G35" s="233">
         <f t="shared" si="10"/>
         <v>3.0819582708304871E-2</v>
       </c>
-      <c r="H35" s="229">
+      <c r="H35" s="233">
         <f t="shared" si="10"/>
         <v>7.0864752833267097E-2</v>
       </c>
-      <c r="I35" s="229">
+      <c r="I35" s="233">
         <f t="shared" si="10"/>
         <v>4.815928183165874E-2</v>
       </c>
-      <c r="J35" s="229">
+      <c r="J35" s="233">
         <f t="shared" si="10"/>
         <v>5.2762881332626188E-2</v>
       </c>
-      <c r="K35" s="229">
+      <c r="K35" s="233">
         <f t="shared" si="10"/>
         <v>7.2901311738473362E-2</v>
       </c>
-      <c r="L35" s="229">
+      <c r="L35" s="233">
         <f t="shared" si="10"/>
         <v>-1.8782608695652181E-3</v>
       </c>
-      <c r="M35" s="229">
+      <c r="M35" s="233">
         <f t="shared" si="10"/>
         <v>-2.4341371619738039E-2</v>
       </c>
-      <c r="N35" s="229">
+      <c r="N35" s="233">
         <f t="shared" si="10"/>
         <v>1.4554870970622469E-2</v>
       </c>
-      <c r="O35" s="229">
+      <c r="O35" s="233">
         <f t="shared" si="10"/>
         <v>3.971131842985387E-2</v>
       </c>
-      <c r="P35" s="229">
+      <c r="P35" s="233">
         <f t="shared" si="10"/>
         <v>3.446991501032759E-2</v>
       </c>
-      <c r="Q35" s="229">
+      <c r="Q35" s="233">
         <f t="shared" si="10"/>
         <v>-5.7903178292036284E-2</v>
       </c>
-      <c r="R35" s="229">
+      <c r="R35" s="233">
         <f t="shared" si="10"/>
         <v>9.7335140018066868E-2</v>
       </c>
-      <c r="S35" s="232">
+      <c r="S35" s="236">
         <f t="shared" si="6"/>
         <v>7.8601168331565718E-2</v>
       </c>
-      <c r="T35" s="229">
+      <c r="T35" s="233">
         <f t="shared" si="6"/>
         <v>1.9153995185815731E-2</v>
       </c>
-      <c r="U35" s="229">
+      <c r="U35" s="233">
         <f t="shared" si="6"/>
         <v>-4.1908492590405633E-3</v>
       </c>
-      <c r="V35" s="229">
+      <c r="V35" s="233">
         <f t="shared" si="6"/>
         <v>1.3415756028416492E-2</v>
       </c>
-      <c r="W35" s="229">
+      <c r="W35" s="233">
         <f t="shared" si="9"/>
         <v>4.6124533846879645E-3</v>
       </c>
-      <c r="X35" s="229">
+      <c r="X35" s="233">
         <f t="shared" si="7"/>
         <v>9.0141047065522284E-3</v>
       </c>
-      <c r="Y35" s="229">
+      <c r="Y35" s="233">
         <f t="shared" si="7"/>
         <v>6.8132790456200965E-3</v>
       </c>
-      <c r="Z35" s="229">
+      <c r="Z35" s="233">
         <f t="shared" si="7"/>
         <v>7.9136918760861624E-3</v>
       </c>
-      <c r="AA35" s="229">
+      <c r="AA35" s="233">
         <f t="shared" si="7"/>
         <v>7.3634854608531294E-3</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A36" s="224" t="s">
+      <c r="A36" s="228" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="229">
+      <c r="B36" s="233">
         <v>0</v>
       </c>
-      <c r="C36" s="229">
+      <c r="C36" s="233">
         <f t="shared" si="10"/>
         <v>4.6177404399988742E-2</v>
       </c>
-      <c r="D36" s="229">
+      <c r="D36" s="233">
         <f t="shared" si="10"/>
         <v>4.0889497643314732E-2</v>
       </c>
-      <c r="E36" s="229">
+      <c r="E36" s="233">
         <f t="shared" si="10"/>
         <v>2.1325179967489838E-2</v>
       </c>
-      <c r="F36" s="229">
+      <c r="F36" s="233">
         <f t="shared" si="10"/>
         <v>3.0492503189460285E-2</v>
       </c>
-      <c r="G36" s="229">
+      <c r="G36" s="233">
         <f t="shared" si="10"/>
         <v>4.634657579583501E-2</v>
       </c>
-      <c r="H36" s="229">
+      <c r="H36" s="233">
         <f t="shared" si="10"/>
         <v>5.7437735760642816E-2</v>
       </c>
-      <c r="I36" s="229">
+      <c r="I36" s="233">
         <f t="shared" si="10"/>
         <v>5.5591868387525611E-2</v>
       </c>
-      <c r="J36" s="229">
+      <c r="J36" s="233">
         <f t="shared" si="10"/>
         <v>5.507803070852102E-2</v>
       </c>
-      <c r="K36" s="229">
+      <c r="K36" s="233">
         <f t="shared" si="10"/>
         <v>5.8459579632153202E-2</v>
       </c>
-      <c r="L36" s="229">
+      <c r="L36" s="233">
         <f t="shared" si="10"/>
         <v>5.3276069468461085E-2</v>
       </c>
-      <c r="M36" s="229">
+      <c r="M36" s="233">
         <f t="shared" si="10"/>
         <v>3.6769363919448184E-2</v>
       </c>
-      <c r="N36" s="229">
+      <c r="N36" s="233">
         <f t="shared" si="10"/>
         <v>3.4630544415566566E-2</v>
       </c>
-      <c r="O36" s="229">
+      <c r="O36" s="233">
         <f t="shared" si="10"/>
         <v>4.7362379597744253E-2</v>
       </c>
-      <c r="P36" s="229">
+      <c r="P36" s="233">
         <f t="shared" si="10"/>
         <v>5.0962546459544456E-2</v>
       </c>
-      <c r="Q36" s="229">
+      <c r="Q36" s="233">
         <f t="shared" si="10"/>
         <v>3.0906878858636411E-3</v>
       </c>
-      <c r="R36" s="229">
+      <c r="R36" s="233">
         <f t="shared" si="10"/>
         <v>8.4615268716758951E-2</v>
       </c>
-      <c r="S36" s="232">
+      <c r="S36" s="236">
         <f t="shared" si="6"/>
         <v>1.1217303124174904E-2</v>
       </c>
-      <c r="T36" s="229">
+      <c r="T36" s="233">
         <f t="shared" si="6"/>
         <v>4.9337518631215271E-2</v>
       </c>
-      <c r="U36" s="229">
+      <c r="U36" s="233">
         <f t="shared" si="6"/>
         <v>4.063571858717574E-2</v>
       </c>
-      <c r="V36" s="229">
+      <c r="V36" s="233">
         <f t="shared" si="6"/>
         <v>4.4888637919443974E-2</v>
       </c>
-      <c r="W36" s="229">
+      <c r="W36" s="233">
         <f t="shared" si="9"/>
         <v>4.2762178253309857E-2</v>
       </c>
-      <c r="X36" s="229">
+      <c r="X36" s="233">
         <f t="shared" si="7"/>
         <v>4.3825408086376916E-2</v>
       </c>
-      <c r="Y36" s="229">
+      <c r="Y36" s="233">
         <f t="shared" si="7"/>
         <v>4.3293793169843386E-2</v>
       </c>
-      <c r="Z36" s="229">
+      <c r="Z36" s="233">
         <f t="shared" si="7"/>
         <v>4.3559600628110151E-2</v>
       </c>
-      <c r="AA36" s="229">
+      <c r="AA36" s="233">
         <f t="shared" si="7"/>
         <v>4.3426696898976769E-2</v>
       </c>
     </row>
     <row r="37" spans="1:27" ht="60" x14ac:dyDescent="0.25">
-      <c r="A37" s="223" t="s">
+      <c r="A37" s="227" t="s">
         <v>41</v>
       </c>
-      <c r="B37" s="229">
+      <c r="B37" s="233">
         <v>0</v>
       </c>
-      <c r="C37" s="229">
+      <c r="C37" s="233">
         <f t="shared" si="10"/>
         <v>5.0720100187852335E-2</v>
       </c>
-      <c r="D37" s="229">
+      <c r="D37" s="233">
         <f t="shared" si="10"/>
         <v>5.2964839094159721E-2</v>
       </c>
-      <c r="E37" s="229">
+      <c r="E37" s="233">
         <f t="shared" si="10"/>
         <v>2.9925716307039218E-2</v>
       </c>
-      <c r="F37" s="229">
+      <c r="F37" s="233">
         <f t="shared" si="10"/>
         <v>2.3286165682099291E-2</v>
       </c>
-      <c r="G37" s="229">
+      <c r="G37" s="233">
         <f t="shared" si="10"/>
         <v>2.4300194670067832E-2</v>
       </c>
-      <c r="H37" s="229">
+      <c r="H37" s="233">
         <f t="shared" si="10"/>
         <v>6.0882102365816815E-2</v>
       </c>
-      <c r="I37" s="229">
+      <c r="I37" s="233">
         <f t="shared" si="10"/>
         <v>3.0207561156412099E-2</v>
       </c>
-      <c r="J37" s="229">
+      <c r="J37" s="233">
         <f t="shared" si="10"/>
         <v>6.2421298794747226E-2</v>
       </c>
-      <c r="K37" s="229">
+      <c r="K37" s="233">
         <f t="shared" si="10"/>
         <v>2.7768371147985027E-2</v>
       </c>
-      <c r="L37" s="229">
+      <c r="L37" s="233">
         <f t="shared" si="10"/>
         <v>4.2394288852279027E-2</v>
       </c>
-      <c r="M37" s="229">
+      <c r="M37" s="233">
         <f t="shared" si="10"/>
         <v>5.5420925086924422E-2</v>
       </c>
-      <c r="N37" s="229">
+      <c r="N37" s="233">
         <f t="shared" si="10"/>
         <v>2.106419087551159E-2</v>
       </c>
-      <c r="O37" s="229">
+      <c r="O37" s="233">
         <f t="shared" si="10"/>
         <v>2.2927258506061809E-2</v>
       </c>
-      <c r="P37" s="229">
+      <c r="P37" s="233">
         <f t="shared" si="10"/>
         <v>0.13037037037037047</v>
       </c>
-      <c r="Q37" s="229">
+      <c r="Q37" s="233">
         <f t="shared" si="10"/>
         <v>-0.11787088318606531</v>
       </c>
-      <c r="R37" s="229">
+      <c r="R37" s="233">
         <f t="shared" si="10"/>
         <v>0.34426072369997618</v>
       </c>
-      <c r="S37" s="232">
+      <c r="S37" s="236">
         <f t="shared" si="6"/>
         <v>0.28108956075299485</v>
       </c>
-      <c r="T37" s="229">
+      <c r="T37" s="233">
         <f t="shared" si="6"/>
         <v>0.10377936101525109</v>
       </c>
-      <c r="U37" s="229">
+      <c r="U37" s="233">
         <f t="shared" si="6"/>
         <v>8.1919265777464112E-2</v>
       </c>
-      <c r="V37" s="229">
+      <c r="V37" s="233">
         <f t="shared" si="6"/>
         <v>9.8935850823077542E-2</v>
       </c>
-      <c r="W37" s="229">
+      <c r="W37" s="233">
         <f t="shared" si="9"/>
         <v>9.0427558300270827E-2</v>
       </c>
-      <c r="X37" s="229">
+      <c r="X37" s="233">
         <f t="shared" si="7"/>
         <v>9.4681704561674185E-2</v>
       </c>
-      <c r="Y37" s="229">
+      <c r="Y37" s="233">
         <f t="shared" si="7"/>
         <v>9.2554631430972506E-2</v>
       </c>
-      <c r="Z37" s="229">
+      <c r="Z37" s="233">
         <f t="shared" si="7"/>
         <v>9.3618167996323345E-2</v>
       </c>
-      <c r="AA37" s="229">
+      <c r="AA37" s="233">
         <f t="shared" si="7"/>
         <v>9.3086399713647933E-2</v>
       </c>
     </row>
     <row r="38" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="225" t="s">
+      <c r="A38" s="229" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="230">
+      <c r="B38" s="234">
         <v>0</v>
       </c>
-      <c r="C38" s="230">
+      <c r="C38" s="234">
         <f t="shared" si="10"/>
         <v>0.11997648442092879</v>
       </c>
-      <c r="D38" s="230">
+      <c r="D38" s="234">
         <f t="shared" si="10"/>
         <v>0.10888781573477235</v>
       </c>
-      <c r="E38" s="230">
+      <c r="E38" s="234">
         <f t="shared" si="10"/>
         <v>5.0896559559199694E-2</v>
       </c>
-      <c r="F38" s="230">
+      <c r="F38" s="234">
         <f t="shared" si="10"/>
         <v>-1.5963676330156162E-2</v>
       </c>
-      <c r="G38" s="230">
+      <c r="G38" s="234">
         <f t="shared" si="10"/>
         <v>6.208916964203981E-2</v>
       </c>
-      <c r="H38" s="230">
+      <c r="H38" s="234">
         <f t="shared" si="10"/>
         <v>0.1033513774437127</v>
       </c>
-      <c r="I38" s="230">
+      <c r="I38" s="234">
         <f>(I18/H18)-1</f>
         <v>4.4874298839080451E-2</v>
       </c>
-      <c r="J38" s="230">
+      <c r="J38" s="234">
         <f t="shared" ref="J38:V38" si="11">(J18/I18)-1</f>
         <v>3.3227161933815141E-2</v>
       </c>
-      <c r="K38" s="230">
+      <c r="K38" s="234">
         <f t="shared" si="11"/>
         <v>5.5054634922932166E-2</v>
       </c>
-      <c r="L38" s="230">
+      <c r="L38" s="234">
         <f t="shared" si="11"/>
         <v>1.7147011618815045E-2</v>
       </c>
-      <c r="M38" s="230">
+      <c r="M38" s="234">
         <f t="shared" si="11"/>
         <v>1.0870004989952609E-2</v>
       </c>
-      <c r="N38" s="230">
+      <c r="N38" s="234">
         <f t="shared" si="11"/>
         <v>1.0913214595423826E-2</v>
       </c>
-      <c r="O38" s="230">
+      <c r="O38" s="234">
         <f t="shared" si="11"/>
         <v>3.0551779657661982E-2</v>
       </c>
-      <c r="P38" s="230">
+      <c r="P38" s="234">
         <f t="shared" si="11"/>
         <v>4.3553426902981141E-2</v>
       </c>
-      <c r="Q38" s="230">
+      <c r="Q38" s="234">
         <f t="shared" si="11"/>
         <v>-6.1345703101032045E-2</v>
       </c>
-      <c r="R38" s="230">
+      <c r="R38" s="234">
         <f t="shared" si="11"/>
         <v>0.15884429337168249</v>
       </c>
-      <c r="S38" s="233">
+      <c r="S38" s="237">
         <f t="shared" si="11"/>
         <v>0.16042418772563183</v>
       </c>
-      <c r="T38" s="230">
+      <c r="T38" s="234">
         <f t="shared" si="11"/>
         <v>-2.5140968306435973E-2</v>
       </c>
-      <c r="U38" s="230">
+      <c r="U38" s="234">
         <f t="shared" si="11"/>
         <v>4.9963101102978857E-3</v>
       </c>
-      <c r="V38" s="230">
+      <c r="V38" s="234">
         <f t="shared" si="11"/>
         <v>2.4730156825394145E-2</v>
       </c>
-      <c r="W38" s="230">
+      <c r="W38" s="234">
         <f t="shared" si="9"/>
         <v>1.4863233467846015E-2</v>
       </c>
-      <c r="X38" s="230">
+      <c r="X38" s="234">
         <f t="shared" si="7"/>
         <v>1.979669514662008E-2</v>
       </c>
-      <c r="Y38" s="230">
+      <c r="Y38" s="234">
         <f t="shared" si="7"/>
         <v>1.7329964307233048E-2</v>
       </c>
-      <c r="Z38" s="230">
+      <c r="Z38" s="234">
         <f t="shared" si="7"/>
         <v>1.8563329726926564E-2</v>
       </c>
-      <c r="AA38" s="230">
+      <c r="AA38" s="234">
         <f t="shared" si="7"/>
         <v>1.7946647017079806E-2</v>
       </c>
@@ -19617,141 +19791,141 @@
       </c>
     </row>
     <row r="12" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="251" t="s">
+      <c r="A12" s="256" t="s">
         <v>80</v>
       </c>
-      <c r="B12" s="252">
+      <c r="B12" s="257">
         <v>0</v>
       </c>
-      <c r="C12" s="253">
+      <c r="C12" s="258">
         <f>(C11/B11)-1</f>
         <v>6.7999604077996656E-2</v>
       </c>
-      <c r="D12" s="253">
+      <c r="D12" s="258">
         <f t="shared" ref="D12:V12" si="3">(D11/C11)-1</f>
         <v>6.7013756382998002E-2</v>
       </c>
-      <c r="E12" s="253">
+      <c r="E12" s="258">
         <f t="shared" si="3"/>
         <v>3.3143892623393345E-2</v>
       </c>
-      <c r="F12" s="253">
+      <c r="F12" s="258">
         <f t="shared" si="3"/>
         <v>1.2597506214681919E-2</v>
       </c>
-      <c r="G12" s="253">
+      <c r="G12" s="258">
         <f t="shared" si="3"/>
         <v>4.4555325833916637E-2</v>
       </c>
-      <c r="H12" s="253">
+      <c r="H12" s="258">
         <f t="shared" si="3"/>
         <v>6.6122851011238382E-2</v>
       </c>
-      <c r="I12" s="253">
+      <c r="I12" s="258">
         <f t="shared" si="3"/>
         <v>3.9102952054333784E-2</v>
       </c>
-      <c r="J12" s="253">
+      <c r="J12" s="258">
         <f t="shared" si="3"/>
         <v>5.0852894212981115E-2</v>
       </c>
-      <c r="K12" s="253">
+      <c r="K12" s="258">
         <f t="shared" si="3"/>
         <v>4.533563956399389E-2</v>
       </c>
-      <c r="L12" s="253">
+      <c r="L12" s="258">
         <f t="shared" si="3"/>
         <v>3.0565068273853635E-2</v>
       </c>
-      <c r="M12" s="253">
+      <c r="M12" s="258">
         <f t="shared" si="3"/>
         <v>2.0873825016279435E-2</v>
       </c>
-      <c r="N12" s="253">
+      <c r="N12" s="258">
         <f t="shared" si="3"/>
         <v>1.3614302808680145E-2</v>
       </c>
-      <c r="O12" s="253">
+      <c r="O12" s="258">
         <f t="shared" si="3"/>
         <v>2.5225989073742072E-2</v>
       </c>
-      <c r="P12" s="253">
+      <c r="P12" s="258">
         <f t="shared" si="3"/>
         <v>3.1428711996795089E-2</v>
       </c>
-      <c r="Q12" s="253">
+      <c r="Q12" s="258">
         <f t="shared" si="3"/>
         <v>-6.9453088444398015E-2</v>
       </c>
-      <c r="R12" s="253">
+      <c r="R12" s="258">
         <f t="shared" si="3"/>
         <v>0.1090981431713276</v>
       </c>
-      <c r="S12" s="253">
+      <c r="S12" s="258">
         <f t="shared" si="3"/>
         <v>7.347283723468867E-2</v>
       </c>
-      <c r="T12" s="253">
+      <c r="T12" s="258">
         <f t="shared" si="3"/>
         <v>4.0245532602367629E-3</v>
       </c>
-      <c r="U12" s="253">
+      <c r="U12" s="258">
         <f t="shared" si="3"/>
         <v>1.5325115014937163E-2</v>
       </c>
-      <c r="V12" s="253">
+      <c r="V12" s="258">
         <f t="shared" si="3"/>
         <v>2.5699636975810458E-2</v>
       </c>
-      <c r="W12" s="253">
+      <c r="W12" s="258">
         <f t="shared" ref="W12" si="4">(W11/V11)-1</f>
         <v>2.0354094775510756E-2</v>
       </c>
-      <c r="X12" s="253">
+      <c r="X12" s="258">
         <f t="shared" ref="X12" si="5">(X11/W11)-1</f>
         <v>2.2708532684219351E-2</v>
       </c>
-      <c r="Y12" s="253">
+      <c r="Y12" s="258">
         <f t="shared" ref="Y12" si="6">(Y11/X11)-1</f>
         <v>2.1301365712466103E-2</v>
       </c>
-      <c r="Z12" s="253">
+      <c r="Z12" s="258">
         <f t="shared" ref="Z12" si="7">(Z11/Y11)-1</f>
         <v>2.1712975854383698E-2</v>
       </c>
-      <c r="AA12" s="253">
+      <c r="AA12" s="258">
         <f t="shared" ref="AA12" si="8">(AA11/Z11)-1</f>
         <v>2.1226846163389324E-2</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="248"/>
-      <c r="B13" s="249"/>
-      <c r="C13" s="250"/>
-      <c r="D13" s="250"/>
-      <c r="E13" s="250"/>
-      <c r="F13" s="250"/>
-      <c r="G13" s="250"/>
-      <c r="H13" s="250"/>
-      <c r="I13" s="250"/>
-      <c r="J13" s="250"/>
-      <c r="K13" s="250"/>
-      <c r="L13" s="250"/>
-      <c r="M13" s="250"/>
-      <c r="N13" s="250"/>
-      <c r="O13" s="250"/>
-      <c r="P13" s="250"/>
-      <c r="Q13" s="250"/>
-      <c r="R13" s="250"/>
-      <c r="S13" s="250"/>
-      <c r="T13" s="250"/>
-      <c r="U13" s="250"/>
-      <c r="V13" s="250"/>
-      <c r="W13" s="250"/>
-      <c r="X13" s="250"/>
-      <c r="Y13" s="250"/>
-      <c r="Z13" s="250"/>
-      <c r="AA13" s="250"/>
+      <c r="A13" s="252"/>
+      <c r="B13" s="253"/>
+      <c r="C13" s="254"/>
+      <c r="D13" s="254"/>
+      <c r="E13" s="254"/>
+      <c r="F13" s="254"/>
+      <c r="G13" s="254"/>
+      <c r="H13" s="254"/>
+      <c r="I13" s="254"/>
+      <c r="J13" s="254"/>
+      <c r="K13" s="254"/>
+      <c r="L13" s="254"/>
+      <c r="M13" s="254"/>
+      <c r="N13" s="254"/>
+      <c r="O13" s="254"/>
+      <c r="P13" s="254"/>
+      <c r="Q13" s="254"/>
+      <c r="R13" s="254"/>
+      <c r="S13" s="254"/>
+      <c r="T13" s="254"/>
+      <c r="U13" s="254"/>
+      <c r="V13" s="254"/>
+      <c r="W13" s="254"/>
+      <c r="X13" s="254"/>
+      <c r="Y13" s="254"/>
+      <c r="Z13" s="254"/>
+      <c r="AA13" s="254"/>
     </row>
     <row r="14" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="190"/>
@@ -19785,7 +19959,7 @@
       <c r="AA14" s="221"/>
     </row>
     <row r="15" spans="1:28" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="234" t="s">
+      <c r="A15" s="238" t="s">
         <v>84</v>
       </c>
       <c r="B15" s="157">
@@ -19871,106 +20045,106 @@
       <c r="A16" s="205" t="s">
         <v>79</v>
       </c>
-      <c r="B16" s="235">
+      <c r="B16" s="239">
         <v>0</v>
       </c>
-      <c r="C16" s="236">
+      <c r="C16" s="240">
         <f>(C6/B6)-1</f>
         <v>6.3691966244290077E-2</v>
       </c>
-      <c r="D16" s="236">
+      <c r="D16" s="240">
         <f>(D6/C6)-1</f>
         <v>6.5528517089766147E-2</v>
       </c>
-      <c r="E16" s="236">
+      <c r="E16" s="240">
         <f>(E6/D6)-1</f>
         <v>4.1150024920242556E-2</v>
       </c>
-      <c r="F16" s="236">
+      <c r="F16" s="240">
         <f>(F6/E6)-1</f>
         <v>1.7082760263021024E-2</v>
       </c>
-      <c r="G16" s="236">
+      <c r="G16" s="240">
         <f>(G6/F6)-1</f>
         <v>5.0526094477202577E-2</v>
       </c>
-      <c r="H16" s="242">
+      <c r="H16" s="246">
         <f>(H6/G6)-1</f>
         <v>5.5007459563706451E-2</v>
       </c>
-      <c r="I16" s="242">
+      <c r="I16" s="246">
         <f>(I6/H6)-1</f>
         <v>5.6338665764155582E-2</v>
       </c>
-      <c r="J16" s="242">
+      <c r="J16" s="246">
         <f>(J6/I6)-1</f>
         <v>4.626897348303971E-2</v>
       </c>
-      <c r="K16" s="242">
+      <c r="K16" s="246">
         <f>(K6/J6)-1</f>
         <v>4.2490818199372393E-2</v>
       </c>
-      <c r="L16" s="242">
+      <c r="L16" s="246">
         <f>(L6/K6)-1</f>
         <v>3.0925153980287501E-2</v>
       </c>
-      <c r="M16" s="242">
+      <c r="M16" s="246">
         <f>(M6/L6)-1</f>
         <v>1.5836286984154624E-2</v>
       </c>
-      <c r="N16" s="242">
+      <c r="N16" s="246">
         <f>(N6/M6)-1</f>
         <v>2.0538143670531861E-2</v>
       </c>
-      <c r="O16" s="242">
+      <c r="O16" s="246">
         <f>(O6/N6)-1</f>
         <v>3.2364963631430266E-2</v>
       </c>
-      <c r="P16" s="242">
+      <c r="P16" s="246">
         <f>(P6/O6)-1</f>
         <v>4.0705551589474975E-2</v>
       </c>
-      <c r="Q16" s="242">
+      <c r="Q16" s="246">
         <f>(Q6/P6)-1</f>
         <v>-5.0072670629334182E-2</v>
       </c>
-      <c r="R16" s="242">
+      <c r="R16" s="246">
         <f>(R6/Q6)-1</f>
         <v>0.14724089489311276</v>
       </c>
-      <c r="S16" s="242">
+      <c r="S16" s="246">
         <f>(S6/R6)-1</f>
         <v>0.10789757758978991</v>
       </c>
-      <c r="T16" s="242">
+      <c r="T16" s="246">
         <f>(T6/S6)-1</f>
         <v>5.1322260068773495E-3</v>
       </c>
-      <c r="U16" s="242">
+      <c r="U16" s="246">
         <f>(U6/T6)-1</f>
         <v>1.6401564432128035E-2</v>
       </c>
-      <c r="V16" s="242">
+      <c r="V16" s="246">
         <f>(V6/U6)-1</f>
         <v>3.6317462255631039E-2</v>
       </c>
-      <c r="W16" s="245">
+      <c r="W16" s="249">
         <f>AVERAGE(U16:V16)</f>
         <v>2.6359513343879537E-2</v>
       </c>
-      <c r="X16" s="245">
+      <c r="X16" s="249">
         <f t="shared" ref="X16:AA20" si="9">AVERAGE(V16:W16)</f>
         <v>3.1338487799755288E-2</v>
       </c>
-      <c r="Y16" s="245">
+      <c r="Y16" s="249">
         <f t="shared" si="9"/>
         <v>2.8849000571817413E-2</v>
       </c>
-      <c r="Z16" s="245">
+      <c r="Z16" s="249">
         <f t="shared" si="9"/>
         <v>3.009374418578635E-2</v>
       </c>
-      <c r="AA16" s="245">
+      <c r="AA16" s="249">
         <f t="shared" si="9"/>
         <v>2.9471372378801881E-2</v>
       </c>
@@ -19979,106 +20153,106 @@
       <c r="A17" s="206" t="s">
         <v>63</v>
       </c>
-      <c r="B17" s="237">
+      <c r="B17" s="241">
         <v>0</v>
       </c>
-      <c r="C17" s="238">
+      <c r="C17" s="242">
         <f>(C7/B7)-1</f>
         <v>5.2134991119005436E-2</v>
       </c>
-      <c r="D17" s="238">
+      <c r="D17" s="242">
         <f>(D7/C7)-1</f>
         <v>4.5689049754200406E-2</v>
       </c>
-      <c r="E17" s="238">
+      <c r="E17" s="242">
         <f>(E7/D7)-1</f>
         <v>4.6973278055458589E-2</v>
       </c>
-      <c r="F17" s="238">
+      <c r="F17" s="242">
         <f>(F7/E7)-1</f>
         <v>4.7629033849797775E-2</v>
       </c>
-      <c r="G17" s="238">
+      <c r="G17" s="242">
         <f>(G7/F7)-1</f>
         <v>5.2257874595231124E-2</v>
       </c>
-      <c r="H17" s="243">
+      <c r="H17" s="247">
         <f>(H7/G7)-1</f>
         <v>6.4769535490079688E-2</v>
       </c>
-      <c r="I17" s="243">
+      <c r="I17" s="247">
         <f>(I7/H7)-1</f>
         <v>4.8070960893737302E-2</v>
       </c>
-      <c r="J17" s="243">
+      <c r="J17" s="247">
         <f>(J7/I7)-1</f>
         <v>8.89546252193536E-2</v>
       </c>
-      <c r="K17" s="243">
+      <c r="K17" s="247">
         <f>(K7/J7)-1</f>
         <v>4.6760469998894605E-2</v>
       </c>
-      <c r="L17" s="243">
+      <c r="L17" s="247">
         <f>(L7/K7)-1</f>
         <v>4.850713443707444E-2</v>
       </c>
-      <c r="M17" s="243">
+      <c r="M17" s="247">
         <f>(M7/L7)-1</f>
         <v>1.8240091284357662E-2</v>
       </c>
-      <c r="N17" s="243">
+      <c r="N17" s="247">
         <f>(N7/M7)-1</f>
         <v>3.6428206522634676E-2</v>
       </c>
-      <c r="O17" s="243">
+      <c r="O17" s="247">
         <f>(O7/N7)-1</f>
         <v>7.3515498914797694E-2</v>
       </c>
-      <c r="P17" s="243">
+      <c r="P17" s="247">
         <f>(P7/O7)-1</f>
         <v>5.2743834703399273E-2</v>
       </c>
-      <c r="Q17" s="243">
+      <c r="Q17" s="247">
         <f>(Q7/P7)-1</f>
         <v>-7.6045359896448339E-3</v>
       </c>
-      <c r="R17" s="243">
+      <c r="R17" s="247">
         <f>(R7/Q7)-1</f>
         <v>9.818460207980384E-2</v>
       </c>
-      <c r="S17" s="243">
+      <c r="S17" s="247">
         <f>(S7/R7)-1</f>
         <v>9.8759375685828488E-3</v>
       </c>
-      <c r="T17" s="243">
+      <c r="T17" s="247">
         <f>(T7/S7)-1</f>
         <v>1.5506353386342209E-2</v>
       </c>
-      <c r="U17" s="243">
+      <c r="U17" s="247">
         <f>(U7/T7)-1</f>
         <v>5.8724304183082054E-3</v>
       </c>
-      <c r="V17" s="243">
+      <c r="V17" s="247">
         <f>(V7/U7)-1</f>
         <v>7.142956962230218E-2</v>
       </c>
-      <c r="W17" s="246">
+      <c r="W17" s="250">
         <f t="shared" ref="W17:W20" si="10">AVERAGE(U17:V17)</f>
         <v>3.8651000020305193E-2</v>
       </c>
-      <c r="X17" s="246">
+      <c r="X17" s="250">
         <f t="shared" si="9"/>
         <v>5.5040284821303687E-2</v>
       </c>
-      <c r="Y17" s="246">
+      <c r="Y17" s="250">
         <f t="shared" si="9"/>
         <v>4.684564242080444E-2</v>
       </c>
-      <c r="Z17" s="246">
+      <c r="Z17" s="250">
         <f t="shared" si="9"/>
         <v>5.0942963621054063E-2</v>
       </c>
-      <c r="AA17" s="246">
+      <c r="AA17" s="250">
         <f t="shared" si="9"/>
         <v>4.8894303020929251E-2</v>
       </c>
@@ -20087,106 +20261,106 @@
       <c r="A18" s="217" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="239">
+      <c r="B18" s="243">
         <v>0</v>
       </c>
-      <c r="C18" s="238">
+      <c r="C18" s="242">
         <f>(C8/B8)-1</f>
         <v>0.16933809963099611</v>
       </c>
-      <c r="D18" s="238">
+      <c r="D18" s="242">
         <f>(D8/C8)-1</f>
         <v>0.15797051427444408</v>
       </c>
-      <c r="E18" s="238">
+      <c r="E18" s="242">
         <f>(E8/D8)-1</f>
         <v>9.0833219784711705E-2</v>
       </c>
-      <c r="F18" s="238">
+      <c r="F18" s="242">
         <f>(F8/E8)-1</f>
         <v>-6.2955734249355966E-2</v>
       </c>
-      <c r="G18" s="238">
+      <c r="G18" s="242">
         <f>(G8/F8)-1</f>
         <v>9.5620948794427951E-2</v>
       </c>
-      <c r="H18" s="243">
+      <c r="H18" s="247">
         <f>(H8/G8)-1</f>
         <v>0.18515927393291398</v>
       </c>
-      <c r="I18" s="243">
+      <c r="I18" s="247">
         <f>(I8/H8)-1</f>
         <v>2.8867130354438775E-2</v>
       </c>
-      <c r="J18" s="243">
+      <c r="J18" s="247">
         <f>(J8/I8)-1</f>
         <v>7.8066242181215051E-2</v>
       </c>
-      <c r="K18" s="243">
+      <c r="K18" s="247">
         <f>(K8/J8)-1</f>
         <v>0.1195356021033267</v>
       </c>
-      <c r="L18" s="243">
+      <c r="L18" s="247">
         <f>(L8/K8)-1</f>
         <v>-1.1512248557093652E-2</v>
       </c>
-      <c r="M18" s="243">
+      <c r="M18" s="247">
         <f>(M8/L8)-1</f>
         <v>-1.6256762761035493E-3</v>
       </c>
-      <c r="N18" s="243">
+      <c r="N18" s="247">
         <f>(N8/M8)-1</f>
         <v>-3.2283736661884666E-2</v>
       </c>
-      <c r="O18" s="243">
+      <c r="O18" s="247">
         <f>(O8/N8)-1</f>
         <v>1.5041011102213897E-2</v>
       </c>
-      <c r="P18" s="243">
+      <c r="P18" s="247">
         <f>(P8/O8)-1</f>
         <v>2.9524327320796795E-2</v>
       </c>
-      <c r="Q18" s="243">
+      <c r="Q18" s="247">
         <f>(Q8/P8)-1</f>
         <v>-0.20680621495544849</v>
       </c>
-      <c r="R18" s="243">
+      <c r="R18" s="247">
         <f>(R8/Q8)-1</f>
         <v>0.11566353139298835</v>
       </c>
-      <c r="S18" s="243">
+      <c r="S18" s="247">
         <f>(S8/R8)-1</f>
         <v>0.16042896508954319</v>
       </c>
-      <c r="T18" s="243">
+      <c r="T18" s="247">
         <f>(T8/S8)-1</f>
         <v>-0.16102327269793892</v>
       </c>
-      <c r="U18" s="243">
+      <c r="U18" s="247">
         <f>(U8/T8)-1</f>
         <v>2.3929425621672218E-2</v>
       </c>
-      <c r="V18" s="243">
+      <c r="V18" s="247">
         <f>(V8/U8)-1</f>
         <v>2.0889920449185251E-2</v>
       </c>
-      <c r="W18" s="246">
+      <c r="W18" s="250">
         <f t="shared" si="10"/>
         <v>2.2409673035428734E-2</v>
       </c>
-      <c r="X18" s="246">
+      <c r="X18" s="250">
         <f t="shared" si="9"/>
         <v>2.1649796742306993E-2</v>
       </c>
-      <c r="Y18" s="246">
+      <c r="Y18" s="250">
         <f t="shared" si="9"/>
         <v>2.2029734888867863E-2</v>
       </c>
-      <c r="Z18" s="246">
+      <c r="Z18" s="250">
         <f t="shared" si="9"/>
         <v>2.1839765815587428E-2</v>
       </c>
-      <c r="AA18" s="246">
+      <c r="AA18" s="250">
         <f t="shared" si="9"/>
         <v>2.1934750352227646E-2</v>
       </c>
@@ -20195,106 +20369,106 @@
       <c r="A19" s="210" t="s">
         <v>69</v>
       </c>
-      <c r="B19" s="239">
+      <c r="B19" s="243">
         <v>0</v>
       </c>
-      <c r="C19" s="238">
+      <c r="C19" s="242">
         <f>(C9/B9)-1</f>
         <v>9.5182978723404421E-2</v>
       </c>
-      <c r="D19" s="238">
+      <c r="D19" s="242">
         <f>(D9/C9)-1</f>
         <v>6.2198874762985135E-2</v>
       </c>
-      <c r="E19" s="238">
+      <c r="E19" s="242">
         <f>(E9/D9)-1</f>
         <v>2.0367552382067E-2</v>
       </c>
-      <c r="F19" s="238">
+      <c r="F19" s="242">
         <f>(F9/E9)-1</f>
         <v>-5.2063018622614532E-2</v>
       </c>
-      <c r="G19" s="238">
+      <c r="G19" s="242">
         <f>(G9/F9)-1</f>
         <v>2.0623651142620769E-2</v>
       </c>
-      <c r="H19" s="243">
+      <c r="H19" s="247">
         <f>(H9/G9)-1</f>
         <v>0.1225754177247711</v>
       </c>
-      <c r="I19" s="243">
+      <c r="I19" s="247">
         <f>(I9/H9)-1</f>
         <v>4.4732765298218347E-2</v>
       </c>
-      <c r="J19" s="243">
+      <c r="J19" s="247">
         <f>(J9/I9)-1</f>
         <v>4.6768893756845564E-2</v>
       </c>
-      <c r="K19" s="243">
+      <c r="K19" s="247">
         <f>(K9/J9)-1</f>
         <v>-2.8895453191779552E-3</v>
       </c>
-      <c r="L19" s="243">
+      <c r="L19" s="247">
         <f>(L9/K9)-1</f>
         <v>1.6580294150885466E-2</v>
       </c>
-      <c r="M19" s="243">
+      <c r="M19" s="247">
         <f>(M9/L9)-1</f>
         <v>-2.0883623427773168E-3</v>
       </c>
-      <c r="N19" s="243">
+      <c r="N19" s="247">
         <f>(N9/M9)-1</f>
         <v>2.5693665305992486E-2</v>
       </c>
-      <c r="O19" s="243">
+      <c r="O19" s="247">
         <f>(O9/N9)-1</f>
         <v>6.423484507610322E-3</v>
       </c>
-      <c r="P19" s="243">
+      <c r="P19" s="247">
         <f>(P9/O9)-1</f>
         <v>3.0840977414630322E-2</v>
       </c>
-      <c r="Q19" s="243">
+      <c r="Q19" s="247">
         <f>(Q9/P9)-1</f>
         <v>-0.2245926524141747</v>
       </c>
-      <c r="R19" s="243">
+      <c r="R19" s="247">
         <f>(R9/Q9)-1</f>
         <v>0.14634122820552387</v>
       </c>
-      <c r="S19" s="243">
+      <c r="S19" s="247">
         <f>(S9/R9)-1</f>
         <v>0.12460566496454129</v>
       </c>
-      <c r="T19" s="243">
+      <c r="T19" s="247">
         <f>(T9/S9)-1</f>
         <v>3.1133352782328316E-2</v>
       </c>
-      <c r="U19" s="243">
+      <c r="U19" s="247">
         <f>(U9/T9)-1</f>
         <v>3.9029344553664913E-3</v>
       </c>
-      <c r="V19" s="243">
+      <c r="V19" s="247">
         <f>(V9/U9)-1</f>
         <v>1.8434401125673849E-2</v>
       </c>
-      <c r="W19" s="246">
+      <c r="W19" s="250">
         <f t="shared" si="10"/>
         <v>1.116866779052017E-2</v>
       </c>
-      <c r="X19" s="246">
+      <c r="X19" s="250">
         <f t="shared" si="9"/>
         <v>1.480153445809701E-2</v>
       </c>
-      <c r="Y19" s="246">
+      <c r="Y19" s="250">
         <f t="shared" si="9"/>
         <v>1.298510112430859E-2</v>
       </c>
-      <c r="Z19" s="246">
+      <c r="Z19" s="250">
         <f t="shared" si="9"/>
         <v>1.38933177912028E-2</v>
       </c>
-      <c r="AA19" s="246">
+      <c r="AA19" s="250">
         <f t="shared" si="9"/>
         <v>1.3439209457755695E-2</v>
       </c>
@@ -20303,106 +20477,106 @@
       <c r="A20" s="214" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="240">
+      <c r="B20" s="244">
         <v>0</v>
       </c>
-      <c r="C20" s="241">
+      <c r="C20" s="245">
         <f>(C10/B10)-1</f>
         <v>0.17681811251715196</v>
       </c>
-      <c r="D20" s="241">
+      <c r="D20" s="245">
         <f>(D10/C10)-1</f>
         <v>0.13858029689608631</v>
       </c>
-      <c r="E20" s="241">
+      <c r="E20" s="245">
         <f>(E10/D10)-1</f>
         <v>0.12511734195579427</v>
       </c>
-      <c r="F20" s="241">
+      <c r="F20" s="245">
         <f>(F10/E10)-1</f>
         <v>-8.6476874325782105E-2</v>
       </c>
-      <c r="G20" s="241">
+      <c r="G20" s="245">
         <f>(G10/F10)-1</f>
         <v>0.10829835324507586</v>
       </c>
-      <c r="H20" s="244">
+      <c r="H20" s="248">
         <f>(H10/G10)-1</f>
         <v>0.20229077530091377</v>
       </c>
-      <c r="I20" s="244">
+      <c r="I20" s="248">
         <f>(I10/H10)-1</f>
         <v>9.3750865435210384E-2</v>
       </c>
-      <c r="J20" s="244">
+      <c r="J20" s="248">
         <f>(J10/I10)-1</f>
         <v>8.5240256493033906E-2</v>
       </c>
-      <c r="K20" s="244">
+      <c r="K20" s="248">
         <f>(K10/J10)-1</f>
         <v>7.7600135321943764E-2</v>
       </c>
-      <c r="L20" s="244">
+      <c r="L20" s="248">
         <f>(L10/K10)-1</f>
         <v>-1.0809377148207955E-2</v>
       </c>
-      <c r="M20" s="244">
+      <c r="M20" s="248">
         <f>(M10/L10)-1</f>
         <v>-3.5409028727770298E-2</v>
       </c>
-      <c r="N20" s="244">
+      <c r="N20" s="248">
         <f>(N10/M10)-1</f>
         <v>1.0188394533665379E-2</v>
       </c>
-      <c r="O20" s="244">
+      <c r="O20" s="248">
         <f>(O10/N10)-1</f>
         <v>5.8054190650006943E-2</v>
       </c>
-      <c r="P20" s="244">
+      <c r="P20" s="248">
         <f>(P10/O10)-1</f>
         <v>7.3439730804137904E-2</v>
       </c>
-      <c r="Q20" s="244">
+      <c r="Q20" s="248">
         <f>(Q10/P10)-1</f>
         <v>-0.20092459826946862</v>
       </c>
-      <c r="R20" s="244">
+      <c r="R20" s="248">
         <f>(R10/Q10)-1</f>
         <v>0.26728666629540943</v>
       </c>
-      <c r="S20" s="244">
+      <c r="S20" s="248">
         <f>(S10/R10)-1</f>
         <v>0.24003222498901433</v>
       </c>
-      <c r="T20" s="244">
+      <c r="T20" s="248">
         <f>(T10/S10)-1</f>
         <v>-0.10029885301865171</v>
       </c>
-      <c r="U20" s="244">
+      <c r="U20" s="248">
         <f>(U10/T10)-1</f>
         <v>1.1636863342348702E-2</v>
       </c>
-      <c r="V20" s="244">
+      <c r="V20" s="248">
         <f>(V10/U10)-1</f>
         <v>8.4193133174436774E-2</v>
       </c>
-      <c r="W20" s="247">
+      <c r="W20" s="251">
         <f t="shared" si="10"/>
         <v>4.7914998258392738E-2</v>
       </c>
-      <c r="X20" s="247">
+      <c r="X20" s="251">
         <f t="shared" si="9"/>
         <v>6.6054065716414756E-2</v>
       </c>
-      <c r="Y20" s="247">
+      <c r="Y20" s="251">
         <f t="shared" si="9"/>
         <v>5.6984531987403747E-2</v>
       </c>
-      <c r="Z20" s="247">
+      <c r="Z20" s="251">
         <f t="shared" si="9"/>
         <v>6.1519298851909252E-2</v>
       </c>
-      <c r="AA20" s="247">
+      <c r="AA20" s="251">
         <f t="shared" si="9"/>
         <v>5.9251915419656499E-2</v>
       </c>
@@ -20421,6 +20595,684 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27D28877-D66B-43C2-B8F1-0E3A28D1C3C8}">
+  <dimension ref="A1:AA8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="25" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="27" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A1" s="222" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="259"/>
+      <c r="C1" s="259"/>
+      <c r="D1" s="259"/>
+      <c r="E1" s="223"/>
+    </row>
+    <row r="2" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="224"/>
+      <c r="B2" s="255"/>
+      <c r="C2" s="255"/>
+      <c r="D2" s="255"/>
+      <c r="E2" s="225"/>
+    </row>
+    <row r="3" spans="1:27" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="264" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="263">
+        <v>2005</v>
+      </c>
+      <c r="C3" s="157">
+        <v>2006</v>
+      </c>
+      <c r="D3" s="157">
+        <v>2007</v>
+      </c>
+      <c r="E3" s="157">
+        <v>2008</v>
+      </c>
+      <c r="F3" s="157">
+        <v>2009</v>
+      </c>
+      <c r="G3" s="157">
+        <v>2010</v>
+      </c>
+      <c r="H3" s="157">
+        <v>2011</v>
+      </c>
+      <c r="I3" s="157">
+        <v>2012</v>
+      </c>
+      <c r="J3" s="157">
+        <v>2013</v>
+      </c>
+      <c r="K3" s="263">
+        <v>2014</v>
+      </c>
+      <c r="L3" s="157">
+        <v>2015</v>
+      </c>
+      <c r="M3" s="157">
+        <v>2016</v>
+      </c>
+      <c r="N3" s="157">
+        <v>2017</v>
+      </c>
+      <c r="O3" s="157">
+        <v>2018</v>
+      </c>
+      <c r="P3" s="157">
+        <v>2019</v>
+      </c>
+      <c r="Q3" s="157">
+        <v>2020</v>
+      </c>
+      <c r="R3" s="157">
+        <v>2021</v>
+      </c>
+      <c r="S3" s="157">
+        <v>2022</v>
+      </c>
+      <c r="T3" s="157">
+        <v>2023</v>
+      </c>
+      <c r="U3" s="157">
+        <v>2024</v>
+      </c>
+      <c r="V3" s="157">
+        <v>2025</v>
+      </c>
+      <c r="W3" s="157">
+        <v>2026</v>
+      </c>
+      <c r="X3" s="157">
+        <v>2027</v>
+      </c>
+      <c r="Y3" s="157">
+        <v>2028</v>
+      </c>
+      <c r="Z3" s="157">
+        <v>2029</v>
+      </c>
+      <c r="AA3" s="157">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4" s="269" t="s">
+        <v>92</v>
+      </c>
+      <c r="B4" s="265">
+        <f>'PIB oferta anual'!B19</f>
+        <v>517438</v>
+      </c>
+      <c r="C4" s="265">
+        <f>'PIB oferta anual'!C19</f>
+        <v>552139</v>
+      </c>
+      <c r="D4" s="265">
+        <f>'PIB oferta anual'!D19</f>
+        <v>588990</v>
+      </c>
+      <c r="E4" s="265">
+        <f>'PIB oferta anual'!E19</f>
+        <v>608384</v>
+      </c>
+      <c r="F4" s="265">
+        <f>'PIB oferta anual'!F19</f>
+        <v>614390</v>
+      </c>
+      <c r="G4" s="265">
+        <f>'PIB oferta anual'!G19</f>
+        <v>640461</v>
+      </c>
+      <c r="H4" s="265">
+        <f>'PIB oferta anual'!H19</f>
+        <v>683340</v>
+      </c>
+      <c r="I4" s="265">
+        <f>'PIB oferta anual'!I19</f>
+        <v>709685</v>
+      </c>
+      <c r="J4" s="265">
+        <f>'PIB oferta anual'!J19</f>
+        <v>745880</v>
+      </c>
+      <c r="K4" s="265">
+        <f>'PIB oferta anual'!K19</f>
+        <v>781017</v>
+      </c>
+      <c r="L4" s="265">
+        <f>'PIB oferta anual'!L19</f>
+        <v>804692</v>
+      </c>
+      <c r="M4" s="265">
+        <f>'PIB oferta anual'!M19</f>
+        <v>821489</v>
+      </c>
+      <c r="N4" s="265">
+        <f>'PIB oferta anual'!N19</f>
+        <v>831956</v>
+      </c>
+      <c r="O4" s="265">
+        <f>'PIB oferta anual'!O19</f>
+        <v>853167</v>
+      </c>
+      <c r="P4" s="265">
+        <f>'PIB oferta anual'!P19</f>
+        <v>880280</v>
+      </c>
+      <c r="Q4" s="265">
+        <f>'PIB oferta anual'!Q19</f>
+        <v>817375</v>
+      </c>
+      <c r="R4" s="265">
+        <f>'PIB oferta anual'!R19</f>
+        <v>905132</v>
+      </c>
+      <c r="S4" s="265">
+        <f>'PIB oferta anual'!S19</f>
+        <v>973165</v>
+      </c>
+      <c r="T4" s="265">
+        <f>'PIB oferta anual'!T19</f>
+        <v>982221</v>
+      </c>
+      <c r="U4" s="265">
+        <f>'PIB oferta anual'!U19</f>
+        <v>996471</v>
+      </c>
+      <c r="V4" s="265">
+        <f>'PIB oferta anual'!V19</f>
+        <v>1023465.1349187322</v>
+      </c>
+      <c r="W4" s="265">
+        <f>'PIB oferta anual'!W19</f>
+        <v>1045802.5597860662</v>
+      </c>
+      <c r="X4" s="265">
+        <f>'PIB oferta anual'!X19</f>
+        <v>1072462.9902129185</v>
+      </c>
+      <c r="Y4" s="265">
+        <f>'PIB oferta anual'!Y19</f>
+        <v>1098886.0177344962</v>
+      </c>
+      <c r="Z4" s="265">
+        <f>'PIB oferta anual'!Z19</f>
+        <v>1127514.6315809824</v>
+      </c>
+      <c r="AA4" s="265">
+        <f>'PIB oferta anual'!AA19</f>
+        <v>1157192.6819513717</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5" s="269" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="266">
+        <f>'PIB demanda anual'!B11</f>
+        <v>515253</v>
+      </c>
+      <c r="C5" s="266">
+        <f>'PIB demanda anual'!C11</f>
+        <v>550290</v>
+      </c>
+      <c r="D5" s="266">
+        <f>'PIB demanda anual'!D11</f>
+        <v>587167</v>
+      </c>
+      <c r="E5" s="266">
+        <f>'PIB demanda anual'!E11</f>
+        <v>606628</v>
+      </c>
+      <c r="F5" s="266">
+        <f>'PIB demanda anual'!F11</f>
+        <v>614270</v>
+      </c>
+      <c r="G5" s="266">
+        <f>'PIB demanda anual'!G11</f>
+        <v>641639</v>
+      </c>
+      <c r="H5" s="266">
+        <f>'PIB demanda anual'!H11</f>
+        <v>684066</v>
+      </c>
+      <c r="I5" s="266">
+        <f>'PIB demanda anual'!I11</f>
+        <v>710814.99999999988</v>
+      </c>
+      <c r="J5" s="266">
+        <f>'PIB demanda anual'!J11</f>
+        <v>746962</v>
+      </c>
+      <c r="K5" s="266">
+        <f>'PIB demanda anual'!K11</f>
+        <v>780826</v>
+      </c>
+      <c r="L5" s="266">
+        <f>'PIB demanda anual'!L11</f>
+        <v>804692</v>
+      </c>
+      <c r="M5" s="266">
+        <f>'PIB demanda anual'!M11</f>
+        <v>821489</v>
+      </c>
+      <c r="N5" s="266">
+        <f>'PIB demanda anual'!N11</f>
+        <v>832672.99999999988</v>
+      </c>
+      <c r="O5" s="266">
+        <f>'PIB demanda anual'!O11</f>
+        <v>853678</v>
+      </c>
+      <c r="P5" s="266">
+        <f>'PIB demanda anual'!P11</f>
+        <v>880508</v>
+      </c>
+      <c r="Q5" s="266">
+        <f>'PIB demanda anual'!Q11</f>
+        <v>819354</v>
+      </c>
+      <c r="R5" s="266">
+        <f>'PIB demanda anual'!R11</f>
+        <v>908744</v>
+      </c>
+      <c r="S5" s="266">
+        <f>'PIB demanda anual'!S11</f>
+        <v>975512</v>
+      </c>
+      <c r="T5" s="266">
+        <f>'PIB demanda anual'!T11</f>
+        <v>979438</v>
+      </c>
+      <c r="U5" s="266">
+        <f>'PIB demanda anual'!U11</f>
+        <v>994448</v>
+      </c>
+      <c r="V5" s="266">
+        <f>'PIB demanda anual'!V11</f>
+        <v>1020004.9525913208</v>
+      </c>
+      <c r="W5" s="266">
+        <f>'PIB demanda anual'!W11</f>
+        <v>1040766.230067855</v>
+      </c>
+      <c r="X5" s="266">
+        <f>'PIB demanda anual'!X11</f>
+        <v>1064400.5040199826</v>
+      </c>
+      <c r="Y5" s="266">
+        <f>'PIB demanda anual'!Y11</f>
+        <v>1087073.6884206454</v>
+      </c>
+      <c r="Z5" s="266">
+        <f>'PIB demanda anual'!Z11</f>
+        <v>1110677.2931692586</v>
+      </c>
+      <c r="AA5" s="266">
+        <f>'PIB demanda anual'!AA11</f>
+        <v>1134253.4692085322</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" s="269" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="267">
+        <f>ABS(B4-B5)</f>
+        <v>2185</v>
+      </c>
+      <c r="C6" s="267">
+        <f t="shared" ref="C6:AA6" si="0">ABS(C4-C5)</f>
+        <v>1849</v>
+      </c>
+      <c r="D6" s="267">
+        <f t="shared" si="0"/>
+        <v>1823</v>
+      </c>
+      <c r="E6" s="267">
+        <f t="shared" si="0"/>
+        <v>1756</v>
+      </c>
+      <c r="F6" s="267">
+        <f t="shared" si="0"/>
+        <v>120</v>
+      </c>
+      <c r="G6" s="267">
+        <f t="shared" si="0"/>
+        <v>1178</v>
+      </c>
+      <c r="H6" s="267">
+        <f t="shared" si="0"/>
+        <v>726</v>
+      </c>
+      <c r="I6" s="267">
+        <f t="shared" si="0"/>
+        <v>1129.9999999998836</v>
+      </c>
+      <c r="J6" s="267">
+        <f t="shared" si="0"/>
+        <v>1082</v>
+      </c>
+      <c r="K6" s="267">
+        <f t="shared" si="0"/>
+        <v>191</v>
+      </c>
+      <c r="L6" s="267">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="M6" s="267">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="N6" s="267">
+        <f t="shared" si="0"/>
+        <v>716.99999999988358</v>
+      </c>
+      <c r="O6" s="267">
+        <f t="shared" si="0"/>
+        <v>511</v>
+      </c>
+      <c r="P6" s="267">
+        <f t="shared" si="0"/>
+        <v>228</v>
+      </c>
+      <c r="Q6" s="267">
+        <f t="shared" si="0"/>
+        <v>1979</v>
+      </c>
+      <c r="R6" s="267">
+        <f t="shared" si="0"/>
+        <v>3612</v>
+      </c>
+      <c r="S6" s="267">
+        <f t="shared" si="0"/>
+        <v>2347</v>
+      </c>
+      <c r="T6" s="267">
+        <f t="shared" si="0"/>
+        <v>2783</v>
+      </c>
+      <c r="U6" s="267">
+        <f t="shared" si="0"/>
+        <v>2023</v>
+      </c>
+      <c r="V6" s="267">
+        <f t="shared" si="0"/>
+        <v>3460.1823274113704</v>
+      </c>
+      <c r="W6" s="267">
+        <f t="shared" si="0"/>
+        <v>5036.3297182112001</v>
+      </c>
+      <c r="X6" s="267">
+        <f t="shared" si="0"/>
+        <v>8062.4861929358449</v>
+      </c>
+      <c r="Y6" s="267">
+        <f t="shared" si="0"/>
+        <v>11812.329313850729</v>
+      </c>
+      <c r="Z6" s="267">
+        <f t="shared" si="0"/>
+        <v>16837.338411723729</v>
+      </c>
+      <c r="AA6" s="267">
+        <f t="shared" si="0"/>
+        <v>22939.212742839474</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7" s="269" t="s">
+        <v>90</v>
+      </c>
+      <c r="B7" s="268">
+        <f>B6/B4</f>
+        <v>4.2227281336121433E-3</v>
+      </c>
+      <c r="C7" s="268">
+        <f t="shared" ref="C7:AA7" si="1">C6/C4</f>
+        <v>3.3487944158988952E-3</v>
+      </c>
+      <c r="D7" s="268">
+        <f t="shared" si="1"/>
+        <v>3.0951289495577176E-3</v>
+      </c>
+      <c r="E7" s="268">
+        <f t="shared" si="1"/>
+        <v>2.8863349463496739E-3</v>
+      </c>
+      <c r="F7" s="268">
+        <f t="shared" si="1"/>
+        <v>1.95315678966129E-4</v>
+      </c>
+      <c r="G7" s="268">
+        <f t="shared" si="1"/>
+        <v>1.8393001291257391E-3</v>
+      </c>
+      <c r="H7" s="268">
+        <f t="shared" si="1"/>
+        <v>1.0624286592325928E-3</v>
+      </c>
+      <c r="I7" s="268">
+        <f t="shared" si="1"/>
+        <v>1.592255719086473E-3</v>
+      </c>
+      <c r="J7" s="268">
+        <f t="shared" si="1"/>
+        <v>1.450635490963694E-3</v>
+      </c>
+      <c r="K7" s="268">
+        <f t="shared" si="1"/>
+        <v>2.4455293546747381E-4</v>
+      </c>
+      <c r="L7" s="268">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M7" s="268">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="N7" s="268">
+        <f t="shared" si="1"/>
+        <v>8.6182442340686715E-4</v>
+      </c>
+      <c r="O7" s="268">
+        <f t="shared" si="1"/>
+        <v>5.9894487245756107E-4</v>
+      </c>
+      <c r="P7" s="268">
+        <f t="shared" si="1"/>
+        <v>2.5900849729631483E-4</v>
+      </c>
+      <c r="Q7" s="268">
+        <f t="shared" si="1"/>
+        <v>2.4211653157975225E-3</v>
+      </c>
+      <c r="R7" s="268">
+        <f t="shared" si="1"/>
+        <v>3.9905781698139058E-3</v>
+      </c>
+      <c r="S7" s="268">
+        <f t="shared" si="1"/>
+        <v>2.4117184650085033E-3</v>
+      </c>
+      <c r="T7" s="268">
+        <f t="shared" si="1"/>
+        <v>2.8333745664163158E-3</v>
+      </c>
+      <c r="U7" s="268">
+        <f t="shared" si="1"/>
+        <v>2.0301644503452686E-3</v>
+      </c>
+      <c r="V7" s="268">
+        <f t="shared" si="1"/>
+        <v>3.3808502208393493E-3</v>
+      </c>
+      <c r="W7" s="268">
+        <f t="shared" si="1"/>
+        <v>4.8157557763498426E-3</v>
+      </c>
+      <c r="X7" s="268">
+        <f t="shared" si="1"/>
+        <v>7.5177290652567704E-3</v>
+      </c>
+      <c r="Y7" s="268">
+        <f t="shared" si="1"/>
+        <v>1.0749367198431973E-2</v>
+      </c>
+      <c r="Z7" s="268">
+        <f t="shared" si="1"/>
+        <v>1.4933144049860082E-2</v>
+      </c>
+      <c r="AA7" s="268">
+        <f t="shared" si="1"/>
+        <v>1.9823157457370993E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" s="270" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="268">
+        <f>B6/B5</f>
+        <v>4.2406351831042223E-3</v>
+      </c>
+      <c r="C8" s="268">
+        <f t="shared" ref="C8:AA8" si="2">C6/C5</f>
+        <v>3.3600465209253304E-3</v>
+      </c>
+      <c r="D8" s="268">
+        <f t="shared" si="2"/>
+        <v>3.104738515618214E-3</v>
+      </c>
+      <c r="E8" s="268">
+        <f t="shared" si="2"/>
+        <v>2.8946899912302101E-3</v>
+      </c>
+      <c r="F8" s="268">
+        <f t="shared" si="2"/>
+        <v>1.9535383463297899E-4</v>
+      </c>
+      <c r="G8" s="268">
+        <f t="shared" si="2"/>
+        <v>1.835923315135146E-3</v>
+      </c>
+      <c r="H8" s="268">
+        <f t="shared" si="2"/>
+        <v>1.0613011025251949E-3</v>
+      </c>
+      <c r="I8" s="268">
+        <f t="shared" si="2"/>
+        <v>1.5897244712054243E-3</v>
+      </c>
+      <c r="J8" s="268">
+        <f t="shared" si="2"/>
+        <v>1.4485341958493203E-3</v>
+      </c>
+      <c r="K8" s="268">
+        <f t="shared" si="2"/>
+        <v>2.4461275623506389E-4</v>
+      </c>
+      <c r="L8" s="268">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="268">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="N8" s="268">
+        <f t="shared" si="2"/>
+        <v>8.6108232163152121E-4</v>
+      </c>
+      <c r="O8" s="268">
+        <f t="shared" si="2"/>
+        <v>5.9858635223116916E-4</v>
+      </c>
+      <c r="P8" s="268">
+        <f t="shared" si="2"/>
+        <v>2.5894142926583289E-4</v>
+      </c>
+      <c r="Q8" s="268">
+        <f t="shared" si="2"/>
+        <v>2.4153174330020966E-3</v>
+      </c>
+      <c r="R8" s="268">
+        <f t="shared" si="2"/>
+        <v>3.9747167519125302E-3</v>
+      </c>
+      <c r="S8" s="268">
+        <f t="shared" si="2"/>
+        <v>2.4059160727904938E-3</v>
+      </c>
+      <c r="T8" s="268">
+        <f t="shared" si="2"/>
+        <v>2.8414253888454401E-3</v>
+      </c>
+      <c r="U8" s="268">
+        <f t="shared" si="2"/>
+        <v>2.0342944025228066E-3</v>
+      </c>
+      <c r="V8" s="268">
+        <f t="shared" si="2"/>
+        <v>3.3923191437657072E-3</v>
+      </c>
+      <c r="W8" s="268">
+        <f t="shared" si="2"/>
+        <v>4.8390595051136945E-3</v>
+      </c>
+      <c r="X8" s="268">
+        <f t="shared" si="2"/>
+        <v>7.5746734076936164E-3</v>
+      </c>
+      <c r="Y8" s="268">
+        <f t="shared" si="2"/>
+        <v>1.0866171667729596E-2</v>
+      </c>
+      <c r="Z8" s="268">
+        <f t="shared" si="2"/>
+        <v>1.5159523396466744E-2</v>
+      </c>
+      <c r="AA8" s="268">
+        <f t="shared" si="2"/>
+        <v>2.0224062227331047E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:E2"/>
+  </mergeCells>
+  <conditionalFormatting sqref="B7:AA7">
+    <cfRule type="cellIs" dxfId="6" priority="4" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="lessThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B8:AA8">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>0.01</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>0.01</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF14CFF-BE42-42BE-B456-10ED5AA13F52}">
   <dimension ref="A1:CH128"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12" x14ac:dyDescent="0.2"/>

--- a/Cuadros_Prod_Gasto.xlsx
+++ b/Cuadros_Prod_Gasto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\WTF IS PROGRAMMING 2.0\UR CLASES\7_SEMESTRE\ICE\Proyecciones\ICE_Proyecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A12E7B3-DAC6-4B2D-B13C-885C88838249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20147EC0-8086-4C95-BFB1-545C24488B27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="5" xr2:uid="{A3B4AD7B-0ED6-4521-BD6B-44541A0DC533}"/>
   </bookViews>

--- a/Cuadros_Prod_Gasto.xlsx
+++ b/Cuadros_Prod_Gasto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USUARIO\Documents\WTF IS PROGRAMMING 2.0\UR CLASES\7_SEMESTRE\ICE\Proyecciones\ICE_Proyecciones\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2E541A9-36DD-4299-8C76-FE8E4E032C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D1ACEC2-F5F3-4327-B1CC-554B25A2F144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="1" activeTab="5" xr2:uid="{A3B4AD7B-0ED6-4521-BD6B-44541A0DC533}"/>
   </bookViews>
